--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="1108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="1087">
   <si>
     <t>Nombre</t>
   </si>
@@ -307,27 +307,6 @@
   </si>
   <si>
     <t>https://www.mercadolibre.com.mx/conjunto-de-46-conjuntos-de-chaves-de-manga-com-caixa-de/p/MLM2024383743#polycard_client=search-nordic&amp;search_layout=grid&amp;position=6&amp;type=product&amp;tracking_id=e0855736-86c9-4805-a462-f6db9f53d27f&amp;wid=MLM3832108740&amp;sid=search&amp;gid=1&amp;pid=1</t>
-  </si>
-  <si>
-    <t>Juego De Matracas De Herramientas Llaves  1/2, 1/4, 3/8</t>
-  </si>
-  <si>
-    <t>3 Piezas</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_847524-MLA81583384450_012025-F.webp</t>
-  </si>
-  <si>
-    <t>https://www.mercadolibre.com.mx/goxawee-juego-de-trinquetes-matracas-de-herramientas-llaves-color-plateado-juego-de-llaves-de-carraca-herramientas-manuales-tamano-12-14-38-fijacion-adaptadores/p/MLM45003714#&amp;gid=1&amp;pid=1</t>
-  </si>
-  <si>
-    <t>Juego De Trinquetes Matracas De 1/2, 3/8 Y 1/4 Llaves - Aceros Inoxidables</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_904437-MLM78839133753_082024-F.webp</t>
-  </si>
-  <si>
-    <t>https://www.mercadolibre.com.mx/juego-de-trinquetes-matracas-de-12-38-y-14-llaves/up/MLMU717012567</t>
   </si>
   <si>
     <t>Llave De Impacto Pistola Impacto Trinquete Inalámbrica</t>
@@ -890,15 +869,6 @@
     <t>https://articulo.mercadolibre.com.mx/MLM-1969622895-panaleras-modernas-multifuncional-mochila-mochilas-escolares-_JM?attributes=COLOR_SECONDARY_COLOR%3AQXp1bA%3D%3D#origin%3Dshare%26sid%3Dshare</t>
   </si>
   <si>
-    <t>Pechera Mochila Táctica Militar Bandolera Hombre</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_832026-MLM50687167058_072022-F-pechera-mochila-tactica-militar-bandolera-hombre.webp</t>
-  </si>
-  <si>
-    <t>https://articulo.mercadolibre.com.mx/MLM-1426933546-pechera-mochila-tactica-militar-bandolera-hombre-_JM?quantity=1&amp;variation_id=174553218415</t>
-  </si>
-  <si>
     <t>Bolso Multifuncional Impermeable  Para Mujer</t>
   </si>
   <si>
@@ -2403,15 +2373,6 @@
     <t>Apoyo Digestivo con Psyllium, Sen y Cáscara Sagrada – 30 Cápsulas</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/view/product/1731368129784219125?_svg=1&amp;chain_key=%7B%22t%22%3A1%2C%22k%22%3A%22000000000000000007602486489440503573%22%2C%22sc%22%3A%22whatsapp%22%7D&amp;checksum=c33a50b28ad1392955d9a4c14d24f527ffac09b49ab8a8799ad72bddb0f7ba01&amp;encode_params=MIIBVAQMTNngvMHKp9L-4q5qBIIBMAqIc-bNhnDIEGQB62_AICN3wBWbPMa4mDw-s1RqUAHBHwKYqtMTO8DKoXHu_pnefAuzJ0Vig3Zpo-vtpcGrkkHmfjg18CUHfRK-VvXiNBgJc2dKtUd8Uq8XvqpNyI43YTzg0UdOWebGrycaS4eBumL_RBHN_f_mzDusWI_t9azTIB5NGJnjGjO3W8cF4zLJ_y3a68RARCaohuukrUJCgr1aGkCFdDBt7t1bpuTNPqjh9tcvHAgcE-TCVW29uMrotL0TGov6P63R6cXZKvSRdKmABZXH9InBDhCQHSmUueYs8-2dRpuiAaeETvsxvZkVbQcnk45CwCg8Wojiuliwl0G5cWaQPTxRCePAr5gd6xIN7Q67qCUzut7JskRqEEIUUODRmUlG1hX8oUcA13Ee-8kEEAyAQDGNMQbEf_VSzpAo0pE%3D&amp;og_info=%7B%22title%22%3A%22Ofertas+Especiales+de+Fin+de+A%C3%B1o+%7C+LeafStory+Limpieza+de+Candida+para+Mujeres+y+Hombres%2C+Limpieza+Intestinal+con+Or%C3%A9gano+y+%C3%81cido+Capr%C3%ADlico%2C+Suplemento+Herbario+para+la+Salud+Digestiva+e+Intestinal%2C+Equilibrio+de+la+Flora+Intestinal%2C+60+C%C3%A1psulas-bd%22%2C%22image%22%3A%22https%3A%5C%2F%5C%2Fp16-oec-sg.ibyteimg.com%5C%2Ftos-alisg-i-aphluv4xwc-sg%5C%2F8eedbf457116417194b89e49976eddd0~tplv-aphluv4xwc-resize-webp%3A260%3A260.webp%3Fdr%3D15582%26t%3D555f072d%26ps%3D933b5bde%26shp%3D7745054a%26shcp%3D9b759fb9%26idc%3Dmy2%26from%3D2001012042%22%7D&amp;sec_user_id=MS4wLjABAAAASh2XXiFeSXjTUYaYz4MxFDXXVmOq30p_JQbVKHsf_hX8Kja4AE7JYjvumb9XvZe8&amp;share_app_id=1233&amp;share_iid=7602393301812037397&amp;share_link_id=a49e1153-6c63-4a06-93af-c3ed928607a1&amp;share_region=MX&amp;social_share_type=15&amp;timestamp=1770091838&amp;trackParams=%7B%22traffic_source_list%22%3A%5B2%5D%2C%22enable_shop_tab_popup%22%3A1%2C%22device_id%22%3A%227544950396772566544%22%7D&amp;u_code=e4mdabb91ak1c0&amp;ug_btm=b5836%2Cb2878&amp;ugbiz_name=UNKNOWN&amp;unique_id=crece.con.iris&amp;user_id=7165686835900843014&amp;utm_campaign=client_share&amp;utm_medium=android&amp;utm_source=whatsapp</t>
-  </si>
-  <si>
-    <t>https://p16-oec-sg.ibyteimg.com/tos-alisg-i-aphluv4xwc-sg/fda7c2a693c14968acbcace2136aa6b0~tplv-aphluv4xwc-resize-webp:800:800.webp?dr=15584&amp;t=555f072d&amp;ps=933b5bde&amp;shp=6ce186a1&amp;shcp=e1be8f53&amp;idc=my2&amp;from=1826719393</t>
-  </si>
-  <si>
-    <t>Candida Limpieza</t>
-  </si>
-  <si>
     <t>Mejora la salud del cabello, uñas, piel y funcional intestinal</t>
   </si>
   <si>
@@ -2430,18 +2391,6 @@
     <t>Activa la vitalidad celular, para el envejecimiento de la piel, la energía y la concentración</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/view/product/1731558371427321030?_svg=1&amp;chain_key=%7B%22t%22%3A1%2C%22k%22%3A%22000000000000000007602488035075852052%22%2C%22sc%22%3A%22whatsapp%22%7D&amp;checksum=f736e04c0856538db12af045c013df0fe0c16021fa5f23b1e05934143586cc3e&amp;encode_params=MIIBVAQMTHMZtGo8OCBrDkVDBIIBMLyZ-i-mL2jBerSh_WFmZFHGBqkv2JF2zsawMIBB_R4scs9VfxK6fl32wBN7lrwZGTj-1ggr-xhT7AMOy1CQlEYzyuQzPz64wOa0Tk5VVAxf8l_g9-rgZpP7WCZGNFeBlTvW8Ma67FnhoO7CFy8mS7E6oWhP4RC_AygBU-Mc4NifXlPZSPj9VCLC0irqzSFd4H3d2ghar6bv5JInesh_Uiqkku7AhAX1lGvaBpNjqk8wfpsOllj8Ku36ejfES6HQy6PpLPuMGdBo5PO4rvPjU9_2JIfLQUFfMhFUG9b1152ekswJkC70bhKCDRCb3o2IZl_FpSnKDlgxRZETK3dKypPImH_rm0-w8ba9IU_pdM7iigivokdgJvhhSpCd7e0kptXc8sFnTU_7RboEaGmH3-QEENV9RGPzqVloPik8UMSiInk%3D&amp;og_info=%7B%22title%22%3A%22Suplemento+con+lute%C3%ADna%2C+zeaxantina+y+vitaminas+clave+%E2%80%94+Perfecto+para+quienes+pasan+muchas+horas+frente+a+pantallas+y+quieren+cuidar+su+salud+visual+%E2%80%94+90+c%C3%A1psulas%22%2C%22image%22%3A%22https%3A%5C%2F%5C%2Fp16-oec-sg.ibyteimg.com%5C%2Ftos-alisg-i-aphluv4xwc-sg%5C%2F5db86029c27a449b9aecc05a79511b57~tplv-aphluv4xwc-resize-webp%3A260%3A260.webp%3Fdr%3D15582%26t%3D555f072d%26ps%3D933b5bde%26shp%3D7745054a%26shcp%3D9b759fb9%26idc%3Dmy2%26from%3D2001012042%22%7D&amp;sec_user_id=MS4wLjABAAAASh2XXiFeSXjTUYaYz4MxFDXXVmOq30p_JQbVKHsf_hX8Kja4AE7JYjvumb9XvZe8&amp;share_app_id=1233&amp;share_iid=7602393301812037397&amp;share_link_id=200986d7-debe-4e6e-9237-95925e346f8c&amp;share_region=MX&amp;social_share_type=15&amp;timestamp=1770092189&amp;trackParams=%7B%22traffic_source_list%22%3A%5B2%5D%2C%22enable_shop_tab_popup%22%3A1%2C%22device_id%22%3A%227544950396772566544%22%7D&amp;u_code=e4mdabb91ak1c0&amp;ug_btm=b5836%2Cb2878&amp;ugbiz_name=UNKNOWN&amp;unique_id=crece.con.iris&amp;user_id=7165686835900843014&amp;utm_campaign=client_share&amp;utm_medium=android&amp;utm_source=whatsapp</t>
-  </si>
-  <si>
-    <t>https://p16-oec-sg.ibyteimg.com/tos-alisg-i-aphluv4xwc-sg/1efc39bc5f344cf5902b6951e626a33f~tplv-aphluv4xwc-resize-webp:800:800.webp?dr=15584&amp;t=555f072d&amp;ps=933b5bde&amp;shp=6ce186a1&amp;shcp=e1be8f53&amp;idc=my&amp;from=1826719393</t>
-  </si>
-  <si>
-    <t>Salud ocular</t>
-  </si>
-  <si>
-    <t>Vision+ Luteína Natural</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/view/product/1732465801434858623?_svg=1&amp;chain_key=%7B%22t%22%3A1%2C%22k%22%3A%22000000000000000007602488449971521300%22%2C%22sc%22%3A%22whatsapp%22%7D&amp;checksum=c6213184df6eee64d2c503fb93de6975db6271ffe29ea36f641f0b7de3836c62&amp;encode_params=MIIBVAQMVC1LNohOfsMS9ShbBIIBMFG_J_gRJ4nQ6kjSp1y7xNx_IdHURGFL9lejkIG2MOZLrJmonruROFYNdoMgj69mpjBBeuxBmpKXCVkcvzspsYdqZukoyJFtPRUHvsyaSw6QzxmXc5drsWe9sALucPIgq0XNGctYzer6YFgsPvWgzpei6M8xnswTfz9B0uJNIPZ4AvnQtxksY5sqy5UG6eFkediF8iODaL_a_2b1F3zr6RnELqOGnFMNOdTlAPz-ut4L_seRcW5oKFLXbmtHE4WWI3F1e8Ops2TEaUhIze8EWYo7kaIHrq9NP_bAsG1N_UULlFCIo-HRs5s2Wf8fGyBxtnIVsom1aD5fkloH5h_CLmDXKI_Lt1SEWQcq4uIWtvq4bmIy-dwLuE_Ydx24rfuHetwSguBxzIqSBgQRRDT7OYsEECYAuiTpvpaf7z7eOq03eIc%3D&amp;og_info=%7B%22title%22%3A%22Windboss+Biotina+%7C+Contribuye+al+Mantenimiento+del+Cabello%2C+Piel+y+U%C3%B1as+%7C+Apoyo+al+Metabolismo+Energ%C3%A9tico+%7C+60+C%C3%A1psulas+Buen+Fin+x+Black+Friday%22%2C%22image%22%3A%22https%3A%5C%2F%5C%2Fp16-oec-sg.ibyteimg.com%5C%2Ftos-alisg-i-aphluv4xwc-sg%5C%2Ff5219232832e4cb18e5d9b2de616d21c~tplv-aphluv4xwc-resize-webp%3A260%3A260.webp%3Fdr%3D15582%26t%3D555f072d%26ps%3D933b5bde%26shp%3D7745054a%26shcp%3D9b759fb9%26idc%3Dmy2%26from%3D2001012042%22%7D&amp;sec_user_id=MS4wLjABAAAASh2XXiFeSXjTUYaYz4MxFDXXVmOq30p_JQbVKHsf_hX8Kja4AE7JYjvumb9XvZe8&amp;share_app_id=1233&amp;share_iid=7602393301812037397&amp;share_link_id=4ca6a11e-8fd3-4a29-b2a2-15f1c5010b0c&amp;share_region=MX&amp;social_share_type=15&amp;timestamp=1770092290&amp;trackParams=%7B%22traffic_source_list%22%3A%5B2%5D%2C%22enable_shop_tab_popup%22%3A1%2C%22device_id%22%3A%227544950396772566544%22%7D&amp;u_code=e4mdabb91ak1c0&amp;ug_btm=b5836%2Cb2878&amp;ugbiz_name=UNKNOWN&amp;unique_id=crece.con.iris&amp;user_id=7165686835900843014&amp;utm_campaign=client_share&amp;utm_medium=android&amp;utm_source=whatsapp</t>
   </si>
   <si>
@@ -2512,18 +2461,6 @@
   </si>
   <si>
     <t>USB o Baterias AA</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/view/product/1732005909938801277?_svg=1&amp;chain_key=%7B%22t%22%3A1%2C%22k%22%3A%22000000000000000007602491991348299540%22%2C%22sc%22%3A%22whatsapp%22%7D&amp;checksum=9741594419c90271722fb6db2f10eea1e77359714fbc7bee10eeccadb713a979&amp;encode_params=MIIBVAQMZnsJNgto5jWYFl0_BIIBMLxDTOeI2UkQAN2gJuZFUY_R7m6oi_WKs6-UhTciarVF2xvtmZ3VIm_HeiYe6EZDPR-LnVdNNWncqEtHZHgSEevFzH_dl4j1Ha4ihmOX1nYwbQrD1LJFAMn6KcUTajoXYBv8y6It5XmZZlhu2MzR9xJKSupEBNJTzdSQ_AmScnHUQmYWev9CZ0gwtiUqZnXuPc8mjdXFn6pRDGeA-xvV2IHEZIZdTekoY9V4eX6bzugNymXJ-aHlNMNavFE_SXzudRMPbQcUf3nSHiWakgWW967A76OSBoQtVZDNQ69q50zQ4ja9ixIjQTR9b3Nvi6stQUaWrzT1RoVMg5JiV3MaI74NvAuwb85U79BWl3Dmq-A1IXs9RRZMzoTVMF-88Dtgmsbj0T37DdVlq2DJaYCGMS8EEBcR7UAoP9tlJ1ml7wSqh4U%3D&amp;og_info=%7B%22title%22%3A%22Consola+de+Juegos+Retro+con+20000%2B+Juegos+Integrados+26+Emuladores+HDMI+4K+y+Controladores+Duales+Premium+para+Juegos+Inmersivos%22%2C%22image%22%3A%22https%3A%5C%2F%5C%2Fp16-oec-sg.ibyteimg.com%5C%2Ftos-alisg-i-aphluv4xwc-sg%5C%2F02a61bc45023450a9ed974a8d934476e~tplv-aphluv4xwc-resize-webp%3A260%3A260.webp%3Fdr%3D15582%26t%3D555f072d%26ps%3D933b5bde%26shp%3D7745054a%26shcp%3D9b759fb9%26idc%3Dmy2%26from%3D2001012042%22%7D&amp;sec_user_id=MS4wLjABAAAASh2XXiFeSXjTUYaYz4MxFDXXVmOq30p_JQbVKHsf_hX8Kja4AE7JYjvumb9XvZe8&amp;share_app_id=1233&amp;share_iid=7602393301812037397&amp;share_link_id=6aa98c08-d46b-4a50-b305-6f22fd3b069b&amp;share_region=MX&amp;social_share_type=15&amp;timestamp=1770093113&amp;trackParams=%7B%22traffic_source_list%22%3A%5B2%5D%2C%22enable_shop_tab_popup%22%3A1%2C%22device_id%22%3A%227544950396772566544%22%7D&amp;u_code=e4mdabb91ak1c0&amp;ug_btm=b8727%2Cb2878&amp;ugbiz_name=UNKNOWN&amp;unique_id=crece.con.iris&amp;user_id=7165686835900843014&amp;utm_campaign=client_share&amp;utm_medium=android&amp;utm_source=whatsapp</t>
-  </si>
-  <si>
-    <t>https://p16-oec-sg.ibyteimg.com/tos-alisg-i-aphluv4xwc-sg/02a61bc45023450a9ed974a8d934476e~tplv-aphluv4xwc-resize-webp:800:800.webp?dr=15584&amp;t=555f072d&amp;ps=933b5bde&amp;shp=6ce186a1&amp;shcp=e1be8f53&amp;idc=my2&amp;from=1826719393</t>
-  </si>
-  <si>
-    <t>Consola de Juegos Retro HDMI 4K y Controladores Duales Premium para Juegos Inmersivos</t>
-  </si>
-  <si>
-    <t>con 20000+ Juegos Integrados 26 Emuladores</t>
   </si>
   <si>
     <t>https://www.tiktok.com/view/product/1732856549931123773?_svg=1&amp;chain_key=%7B%22t%22%3A1%2C%22k%22%3A%22000000000000000007602492425596454676%22%2C%22sc%22%3A%22whatsapp%22%7D&amp;checksum=fbba70ad198b20dffd4788c9af4056bb28cb82e1b50f6758dbacaae706d1a7e7&amp;encode_params=MIIBVAQM4Ov0MOJQ2gSIDcmJBIIBMAybWaZOswRXBPk8RqCfjSw43b-ogx2un6vMWPCldlaeWIME_maDMkHfPpk3fP2d8kDXk1QfaU8gnJZ-TJZ56hZtA10yK4eb_3RuWrUB0L3Fk_zWLV0NCYwDOvcCNHDlclxc7Cts5X0CkEHNOP71mR7_LfeOFiA5nENOVVEYBy98JNzkNA8ajqvuu62kMJZblnUlIk891rfXM9NHbNWtO57wP9t7LMOG3AYtAYmWX0b74wMYyeNnjA8uvmh4gL2Gr6L9NUuKWusO87pYASRi48PApJdwLX8eXC-t08xg2o1EJH8sZK3NNce5mZBw9MuyKM8n2-ukSQVJf8TVlE-wktykDscu4xruHEU_QGgTS0TlT1R4Ed6-NxSJe5qGLtQHdnJZwY_R2ZsLyF9EkRMMIlkEEPjRapBpbZnzH2gPLSXAoVU%3D&amp;og_info=%7B%22title%22%3A%22Kit+para+el+crecimiento+de+la+barba%3A+set+de+suero+y+rodillo+para+una+barba+m%C3%A1s+gruesa+y+abundante%2C+cuidado+diario+para+hombres%2C+liviano+y+f%C3%A1cil+de+usar%2C+regalo+perfecto.%22%2C%22image%22%3A%22https%3A%5C%2F%5C%2Fp16-oec-va.ibyteimg.com%5C%2Ftos-maliva-i-o3syd03w52-us%5C%2Fa82cf4b5a197496487e0b8ee2562af8c~tplv-o3syd03w52-resize-webp%3A260%3A260.webp%3Fdr%3D15582%26t%3D555f072d%26ps%3D933b5bde%26shp%3D7745054a%26shcp%3D9b759fb9%26idc%3Dmy2%26from%3D2001012042%22%7D&amp;sec_user_id=MS4wLjABAAAASh2XXiFeSXjTUYaYz4MxFDXXVmOq30p_JQbVKHsf_hX8Kja4AE7JYjvumb9XvZe8&amp;share_app_id=1233&amp;share_iid=7602393301812037397&amp;share_link_id=3f922587-5c87-41fb-bd1c-7c8894e84a7c&amp;share_region=MX&amp;social_share_type=15&amp;timestamp=1770093236&amp;trackParams=%7B%22enable_shop_tab_popup%22%3A1%2C%22device_id%22%3A%227544950396772566544%22%7D&amp;u_code=e4mdabb91ak1c0&amp;ug_btm=b0813%2Cb6661&amp;ugbiz_name=UNKNOWN&amp;unique_id=crece.con.iris&amp;user_id=7165686835900843014&amp;utm_campaign=client_share&amp;utm_medium=android&amp;utm_source=whatsapp</t>
@@ -3408,8 +3345,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H308" totalsRowShown="0">
-  <autoFilter ref="A1:H308"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H302" totalsRowShown="0">
+  <autoFilter ref="A1:H302"/>
   <sortState ref="A2:H230">
     <sortCondition ref="H1:H230"/>
   </sortState>
@@ -3712,7 +3649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H308"/>
+  <dimension ref="A1:H302"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -3773,7 +3710,7 @@
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -3799,7 +3736,7 @@
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3825,7 +3762,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -3851,12 +3788,12 @@
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
@@ -3868,21 +3805,21 @@
         <v>500</v>
       </c>
       <c r="E6" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="F6" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G6" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="H6" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -3894,21 +3831,21 @@
         <v>150</v>
       </c>
       <c r="E7" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="F7" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="G7" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H7" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
@@ -3920,21 +3857,21 @@
         <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="F8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="G8" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H8" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
@@ -3946,21 +3883,21 @@
         <v>450</v>
       </c>
       <c r="E9" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="F9" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G9">
         <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
@@ -3972,24 +3909,24 @@
         <v>150</v>
       </c>
       <c r="E10" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="F10" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="G10">
         <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="B11" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C11">
         <v>1050</v>
@@ -3998,18 +3935,18 @@
         <v>600</v>
       </c>
       <c r="E11" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="G11" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="H11" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
@@ -4018,21 +3955,21 @@
         <v>250</v>
       </c>
       <c r="E12" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="F12" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="G12" t="s">
-        <v>1014</v>
+        <v>993</v>
       </c>
       <c r="H12" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="B13" t="s">
         <v>40</v>
@@ -4044,13 +3981,13 @@
         <v>150</v>
       </c>
       <c r="E13" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="F13" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="G13" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="H13" t="s">
         <v>86</v>
@@ -4058,7 +3995,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="B14" t="s">
         <v>40</v>
@@ -4070,21 +4007,21 @@
         <v>190</v>
       </c>
       <c r="E14" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="F14" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="G14" t="s">
         <v>40</v>
       </c>
       <c r="H14" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="B15" t="s">
         <v>40</v>
@@ -4096,21 +4033,21 @@
         <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="F15" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="G15" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="H15" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s">
         <v>18</v>
@@ -4119,24 +4056,24 @@
         <v>150</v>
       </c>
       <c r="E16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F16" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C17">
         <v>450</v>
@@ -4145,24 +4082,24 @@
         <v>350</v>
       </c>
       <c r="E17" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F17" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C18">
         <v>298</v>
@@ -4171,24 +4108,24 @@
         <v>170</v>
       </c>
       <c r="E18" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F18" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
       <c r="H18" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C19">
         <v>298</v>
@@ -4197,21 +4134,21 @@
         <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F19" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G19">
         <v>5</v>
       </c>
       <c r="H19" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s">
         <v>18</v>
@@ -4220,21 +4157,21 @@
         <v>200</v>
       </c>
       <c r="E20" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F20" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
       <c r="H20" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
@@ -4246,21 +4183,21 @@
         <v>180</v>
       </c>
       <c r="E21" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="F21" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
       <c r="H21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s">
         <v>18</v>
@@ -4272,21 +4209,21 @@
         <v>200</v>
       </c>
       <c r="E22" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F22" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B23" t="s">
         <v>18</v>
@@ -4295,24 +4232,24 @@
         <v>230</v>
       </c>
       <c r="E23" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F23" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C24">
         <v>6758</v>
@@ -4321,24 +4258,24 @@
         <v>5500</v>
       </c>
       <c r="E24" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F24" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C25">
         <v>5999</v>
@@ -4347,24 +4284,24 @@
         <v>5200</v>
       </c>
       <c r="E25" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F25" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G25">
         <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B26" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C26">
         <v>350</v>
@@ -4373,21 +4310,21 @@
         <v>180</v>
       </c>
       <c r="E26" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F26" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G26">
         <v>5</v>
       </c>
       <c r="H26" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B27" t="s">
         <v>18</v>
@@ -4399,21 +4336,21 @@
         <v>500</v>
       </c>
       <c r="E27" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F27" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="H27" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B28" t="s">
         <v>18</v>
@@ -4425,21 +4362,21 @@
         <v>650</v>
       </c>
       <c r="E28" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F28" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="H28" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B29" t="s">
         <v>18</v>
@@ -4451,24 +4388,24 @@
         <v>500</v>
       </c>
       <c r="E29" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F29" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="G29">
         <v>5</v>
       </c>
       <c r="H29" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B30" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C30">
         <v>445</v>
@@ -4477,21 +4414,21 @@
         <v>200</v>
       </c>
       <c r="E30" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="G30">
         <v>5</v>
       </c>
       <c r="H30" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B31" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C31">
         <v>325</v>
@@ -4500,24 +4437,24 @@
         <v>180</v>
       </c>
       <c r="E31" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F31" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="G31">
         <v>5</v>
       </c>
       <c r="H31" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B32" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C32">
         <v>250</v>
@@ -4526,24 +4463,24 @@
         <v>150</v>
       </c>
       <c r="E32" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F32" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G32">
         <v>5</v>
       </c>
       <c r="H32" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B33" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C33">
         <v>270</v>
@@ -4552,24 +4489,24 @@
         <v>150</v>
       </c>
       <c r="E33" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F33" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G33">
         <v>5</v>
       </c>
       <c r="H33" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B34" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C34">
         <v>300</v>
@@ -4578,10 +4515,10 @@
         <v>200</v>
       </c>
       <c r="E34" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F34" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="G34">
         <v>7</v>
@@ -4592,7 +4529,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s">
         <v>18</v>
@@ -4604,21 +4541,21 @@
         <v>250</v>
       </c>
       <c r="E35" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="F35" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="G35">
         <v>8</v>
       </c>
       <c r="H35" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s">
         <v>18</v>
@@ -4630,24 +4567,24 @@
         <v>250</v>
       </c>
       <c r="E36" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F36" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="G36" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="H36" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="B37" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C37">
         <v>699</v>
@@ -4656,21 +4593,21 @@
         <v>300</v>
       </c>
       <c r="E37" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="F37" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="G37" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="H37" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="B38" t="s">
         <v>18</v>
@@ -4682,21 +4619,21 @@
         <v>900</v>
       </c>
       <c r="E38" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="F38" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="G38" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="H38" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="B39" t="s">
         <v>18</v>
@@ -4705,21 +4642,21 @@
         <v>350</v>
       </c>
       <c r="E39" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F39" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="G39" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="H39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="B40" t="s">
         <v>18</v>
@@ -4728,21 +4665,21 @@
         <v>200</v>
       </c>
       <c r="E40" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="F40" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="G40" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="H40" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="B41" t="s">
         <v>29</v>
@@ -4751,13 +4688,13 @@
         <v>70</v>
       </c>
       <c r="E41" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="F41" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="G41" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H41" t="s">
         <v>86</v>
@@ -4765,33 +4702,33 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="B42" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="C42">
         <v>200</v>
       </c>
       <c r="E42" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="F42" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="G42" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H42" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="B43" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="C43">
         <v>5150</v>
@@ -4800,24 +4737,24 @@
         <v>3500</v>
       </c>
       <c r="E43" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="F43" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="G43" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H43" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="B44" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C44">
         <v>1700</v>
@@ -4826,44 +4763,44 @@
         <v>1000</v>
       </c>
       <c r="E44" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F44" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="G44" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H44" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="B45" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="C45">
         <v>200</v>
       </c>
       <c r="E45" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="F45" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="G45" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H45" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="B46" t="s">
         <v>18</v>
@@ -4872,16 +4809,16 @@
         <v>500</v>
       </c>
       <c r="E46" t="s">
+        <v>712</v>
+      </c>
+      <c r="F46" t="s">
+        <v>713</v>
+      </c>
+      <c r="G46" t="s">
+        <v>600</v>
+      </c>
+      <c r="H46" t="s">
         <v>722</v>
-      </c>
-      <c r="F46" t="s">
-        <v>723</v>
-      </c>
-      <c r="G46" t="s">
-        <v>610</v>
-      </c>
-      <c r="H46" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -4907,7 +4844,7 @@
         <v>3</v>
       </c>
       <c r="H47" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -4930,7 +4867,7 @@
         <v>3</v>
       </c>
       <c r="H48" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -4953,7 +4890,7 @@
         <v>3</v>
       </c>
       <c r="H49" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -4979,7 +4916,7 @@
         <v>3</v>
       </c>
       <c r="H50" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -5005,7 +4942,7 @@
         <v>3</v>
       </c>
       <c r="H51" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -5031,7 +4968,7 @@
         <v>3</v>
       </c>
       <c r="H52" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -5054,7 +4991,7 @@
         <v>3</v>
       </c>
       <c r="H53" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -5077,7 +5014,7 @@
         <v>3</v>
       </c>
       <c r="H54" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -5100,7 +5037,7 @@
         <v>3</v>
       </c>
       <c r="H55" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -5126,7 +5063,7 @@
         <v>3</v>
       </c>
       <c r="H56" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -5149,7 +5086,7 @@
         <v>3</v>
       </c>
       <c r="H57" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -5175,7 +5112,7 @@
         <v>3</v>
       </c>
       <c r="H58" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -5198,12 +5135,12 @@
         <v>3.1</v>
       </c>
       <c r="H59" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B60" t="s">
         <v>83</v>
@@ -5215,21 +5152,21 @@
         <v>500</v>
       </c>
       <c r="E60" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F60" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G60">
         <v>3.1</v>
       </c>
       <c r="H60" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B61" t="s">
         <v>18</v>
@@ -5238,24 +5175,24 @@
         <v>250</v>
       </c>
       <c r="E61" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F61" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="G61">
         <v>4</v>
       </c>
       <c r="H61" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B62" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C62">
         <v>144</v>
@@ -5264,21 +5201,21 @@
         <v>100</v>
       </c>
       <c r="E62" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F62" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="G62">
         <v>5</v>
       </c>
       <c r="H62" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B63" t="s">
         <v>18</v>
@@ -5290,21 +5227,21 @@
         <v>150</v>
       </c>
       <c r="E63" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F63" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="G63">
         <v>6</v>
       </c>
       <c r="H63" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B64" t="s">
         <v>18</v>
@@ -5316,21 +5253,21 @@
         <v>150</v>
       </c>
       <c r="E64" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F64" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="G64">
         <v>6</v>
       </c>
       <c r="H64" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B65" t="s">
         <v>18</v>
@@ -5342,24 +5279,24 @@
         <v>150</v>
       </c>
       <c r="E65" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F65" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G65">
         <v>6</v>
       </c>
       <c r="H65" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B66" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C66">
         <v>650</v>
@@ -5368,10 +5305,10 @@
         <v>350</v>
       </c>
       <c r="E66" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="F66" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="G66">
         <v>7</v>
@@ -5382,10 +5319,10 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="B67" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C67">
         <v>1100</v>
@@ -5394,13 +5331,13 @@
         <v>900</v>
       </c>
       <c r="E67" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="F67" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G67" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="H67" t="s">
         <v>86</v>
@@ -5408,10 +5345,10 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B68" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C68">
         <v>731.5</v>
@@ -5420,21 +5357,21 @@
         <v>490</v>
       </c>
       <c r="E68" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="F68" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="G68" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="H68" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="B69" s="2">
         <v>9005</v>
@@ -5443,24 +5380,24 @@
         <v>350</v>
       </c>
       <c r="E69" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="F69" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="G69" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="H69" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="B70" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C70">
         <v>220</v>
@@ -5469,59 +5406,59 @@
         <v>100</v>
       </c>
       <c r="E70" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="F70" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="G70" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="H70" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="B71" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="C71">
         <v>670</v>
       </c>
       <c r="E71" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="F71" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="G71" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H71" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="B72" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="C72">
         <v>350</v>
       </c>
       <c r="E72" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="F72" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="G72" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H72" t="s">
         <v>86</v>
@@ -5529,91 +5466,91 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="B73" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="C73">
         <v>400</v>
       </c>
       <c r="E73" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="F73" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="G73" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H73" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="B74" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="C74">
         <v>600</v>
       </c>
       <c r="E74" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="F74" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="G74" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H74" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="B75" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="C75">
         <v>200</v>
       </c>
       <c r="E75" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="F75" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="G75" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H75" t="s">
-        <v>926</v>
+        <v>905</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="B76" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="C76">
         <v>500</v>
       </c>
       <c r="E76" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="F76" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="G76" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H76" t="s">
         <v>86</v>
@@ -5642,7 +5579,7 @@
         <v>3.1</v>
       </c>
       <c r="H77" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -5668,7 +5605,7 @@
         <v>3.1</v>
       </c>
       <c r="H78" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -5676,126 +5613,120 @@
         <v>95</v>
       </c>
       <c r="B79" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79">
+        <v>750</v>
+      </c>
+      <c r="D79">
+        <v>650</v>
+      </c>
+      <c r="E79" t="s">
         <v>96</v>
       </c>
-      <c r="C79">
-        <v>699</v>
-      </c>
-      <c r="D79">
-        <v>500</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>97</v>
-      </c>
-      <c r="F79" t="s">
-        <v>98</v>
       </c>
       <c r="G79">
         <v>3.1</v>
       </c>
       <c r="H79" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="B80" t="s">
-        <v>96</v>
+        <v>225</v>
       </c>
       <c r="C80">
-        <v>388</v>
+        <v>480</v>
       </c>
       <c r="D80">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E80" t="s">
-        <v>100</v>
+        <v>226</v>
       </c>
       <c r="F80" t="s">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="G80">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="H80" t="s">
-        <v>732</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>102</v>
+        <v>228</v>
       </c>
       <c r="B81" t="s">
-        <v>83</v>
+        <v>229</v>
       </c>
       <c r="C81">
-        <v>750</v>
+        <v>368</v>
       </c>
       <c r="D81">
-        <v>650</v>
+        <v>170</v>
       </c>
       <c r="E81" t="s">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="F81" t="s">
-        <v>104</v>
+        <v>231</v>
       </c>
       <c r="G81">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="H81" t="s">
-        <v>732</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="B82" t="s">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="C82">
-        <v>480</v>
+        <v>200</v>
       </c>
       <c r="D82">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="E82" t="s">
-        <v>233</v>
-      </c>
-      <c r="F82" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G82">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H82" t="s">
-        <v>86</v>
+        <v>722</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="B83" t="s">
-        <v>236</v>
+        <v>40</v>
       </c>
       <c r="C83">
-        <v>368</v>
+        <v>150</v>
       </c>
       <c r="D83">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="E83" t="s">
-        <v>237</v>
-      </c>
-      <c r="F83" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="G83">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H83" t="s">
         <v>86</v>
@@ -5803,45 +5734,51 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>271</v>
+        <v>346</v>
       </c>
       <c r="B84" t="s">
-        <v>40</v>
+        <v>333</v>
       </c>
       <c r="C84">
-        <v>200</v>
+        <v>399</v>
       </c>
       <c r="D84">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E84" t="s">
-        <v>272</v>
-      </c>
-      <c r="G84">
-        <v>8</v>
+        <v>347</v>
+      </c>
+      <c r="F84" t="s">
+        <v>348</v>
+      </c>
+      <c r="G84" t="s">
+        <v>336</v>
       </c>
       <c r="H84" t="s">
-        <v>732</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>273</v>
+        <v>363</v>
       </c>
       <c r="B85" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C85">
-        <v>150</v>
+        <v>298</v>
       </c>
       <c r="D85">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E85" t="s">
-        <v>274</v>
-      </c>
-      <c r="G85">
-        <v>8</v>
+        <v>364</v>
+      </c>
+      <c r="F85" t="s">
+        <v>365</v>
+      </c>
+      <c r="G85" t="s">
+        <v>359</v>
       </c>
       <c r="H85" t="s">
         <v>86</v>
@@ -5849,25 +5786,25 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="B86" t="s">
-        <v>343</v>
+        <v>383</v>
       </c>
       <c r="C86">
-        <v>399</v>
+        <v>450</v>
       </c>
       <c r="D86">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="E86" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="F86" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="G86" t="s">
-        <v>346</v>
+        <v>386</v>
       </c>
       <c r="H86" t="s">
         <v>86</v>
@@ -5875,25 +5812,25 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>373</v>
+        <v>427</v>
       </c>
       <c r="B87" t="s">
         <v>18</v>
       </c>
       <c r="C87">
-        <v>298</v>
+        <v>1600</v>
       </c>
       <c r="D87">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="E87" t="s">
-        <v>374</v>
+        <v>428</v>
       </c>
       <c r="F87" t="s">
-        <v>375</v>
+        <v>429</v>
       </c>
       <c r="G87" t="s">
-        <v>369</v>
+        <v>430</v>
       </c>
       <c r="H87" t="s">
         <v>86</v>
@@ -5901,25 +5838,25 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>392</v>
+        <v>439</v>
       </c>
       <c r="B88" t="s">
-        <v>393</v>
+        <v>440</v>
       </c>
       <c r="C88">
-        <v>450</v>
+        <v>693</v>
       </c>
       <c r="D88">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="E88" t="s">
-        <v>394</v>
+        <v>441</v>
       </c>
       <c r="F88" t="s">
-        <v>395</v>
+        <v>442</v>
       </c>
       <c r="G88" t="s">
-        <v>396</v>
+        <v>430</v>
       </c>
       <c r="H88" t="s">
         <v>86</v>
@@ -5927,25 +5864,22 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>437</v>
+        <v>479</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>480</v>
       </c>
       <c r="C89">
-        <v>1600</v>
-      </c>
-      <c r="D89">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="E89" t="s">
-        <v>438</v>
+        <v>481</v>
       </c>
       <c r="F89" t="s">
-        <v>439</v>
+        <v>482</v>
       </c>
       <c r="G89" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H89" t="s">
         <v>86</v>
@@ -5953,25 +5887,22 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>449</v>
+        <v>483</v>
       </c>
       <c r="B90" t="s">
-        <v>450</v>
+        <v>484</v>
       </c>
       <c r="C90">
-        <v>693</v>
-      </c>
-      <c r="D90">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="E90" t="s">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="F90" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="G90" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H90" t="s">
         <v>86</v>
@@ -5979,22 +5910,25 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>489</v>
+        <v>556</v>
       </c>
       <c r="B91" t="s">
-        <v>490</v>
+        <v>40</v>
       </c>
       <c r="C91">
-        <v>300</v>
+        <v>195</v>
+      </c>
+      <c r="D91">
+        <v>120</v>
       </c>
       <c r="E91" t="s">
-        <v>491</v>
+        <v>557</v>
       </c>
       <c r="F91" t="s">
-        <v>492</v>
+        <v>558</v>
       </c>
       <c r="G91" t="s">
-        <v>456</v>
+        <v>515</v>
       </c>
       <c r="H91" t="s">
         <v>86</v>
@@ -6002,22 +5936,25 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>493</v>
+        <v>581</v>
       </c>
       <c r="B92" t="s">
-        <v>494</v>
+        <v>582</v>
       </c>
       <c r="C92">
-        <v>300</v>
+        <v>169</v>
+      </c>
+      <c r="D92">
+        <v>100</v>
       </c>
       <c r="E92" t="s">
-        <v>495</v>
+        <v>583</v>
       </c>
       <c r="F92" t="s">
-        <v>496</v>
+        <v>584</v>
       </c>
       <c r="G92" t="s">
-        <v>456</v>
+        <v>515</v>
       </c>
       <c r="H92" t="s">
         <v>86</v>
@@ -6025,51 +5962,48 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>566</v>
+        <v>679</v>
       </c>
       <c r="B93" t="s">
-        <v>40</v>
+        <v>680</v>
       </c>
       <c r="C93">
-        <v>195</v>
-      </c>
-      <c r="D93">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E93" t="s">
-        <v>567</v>
+        <v>681</v>
       </c>
       <c r="F93" t="s">
-        <v>568</v>
+        <v>682</v>
       </c>
       <c r="G93" t="s">
-        <v>525</v>
+        <v>600</v>
       </c>
       <c r="H93" t="s">
-        <v>86</v>
+        <v>721</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>591</v>
+        <v>332</v>
       </c>
       <c r="B94" t="s">
-        <v>592</v>
+        <v>333</v>
       </c>
       <c r="C94">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="D94">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E94" t="s">
-        <v>593</v>
+        <v>334</v>
       </c>
       <c r="F94" t="s">
-        <v>594</v>
+        <v>335</v>
       </c>
       <c r="G94" t="s">
-        <v>525</v>
+        <v>336</v>
       </c>
       <c r="H94" t="s">
         <v>86</v>
@@ -6077,292 +6011,289 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>689</v>
+        <v>545</v>
       </c>
       <c r="B95" t="s">
-        <v>690</v>
+        <v>40</v>
       </c>
       <c r="C95">
-        <v>100</v>
+        <v>150</v>
+      </c>
+      <c r="D95">
+        <v>50</v>
       </c>
       <c r="E95" t="s">
-        <v>691</v>
+        <v>546</v>
       </c>
       <c r="F95" t="s">
-        <v>692</v>
+        <v>547</v>
       </c>
       <c r="G95" t="s">
-        <v>610</v>
+        <v>515</v>
       </c>
       <c r="H95" t="s">
-        <v>731</v>
+        <v>86</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>342</v>
+        <v>66</v>
       </c>
       <c r="B96" t="s">
-        <v>343</v>
+        <v>40</v>
       </c>
       <c r="C96">
-        <v>230</v>
+        <v>268</v>
       </c>
       <c r="D96">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E96" t="s">
-        <v>344</v>
+        <v>67</v>
       </c>
       <c r="F96" t="s">
-        <v>345</v>
-      </c>
-      <c r="G96" t="s">
-        <v>346</v>
+        <v>68</v>
+      </c>
+      <c r="G96">
+        <v>3</v>
       </c>
       <c r="H96" t="s">
-        <v>86</v>
+        <v>722</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>555</v>
+        <v>398</v>
       </c>
       <c r="B97" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C97">
-        <v>150</v>
+        <v>429</v>
       </c>
       <c r="D97">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="E97" t="s">
-        <v>556</v>
+        <v>399</v>
       </c>
       <c r="F97" t="s">
-        <v>557</v>
+        <v>400</v>
       </c>
       <c r="G97" t="s">
-        <v>525</v>
+        <v>394</v>
       </c>
       <c r="H97" t="s">
-        <v>86</v>
+        <v>721</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C98">
-        <v>268</v>
-      </c>
-      <c r="D98">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E98" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="F98" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="G98">
-        <v>3</v>
+        <v>8.1</v>
       </c>
       <c r="H98" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>408</v>
+        <v>104</v>
       </c>
       <c r="B99" t="s">
         <v>18</v>
       </c>
       <c r="C99">
-        <v>429</v>
-      </c>
-      <c r="D99">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="E99" t="s">
-        <v>409</v>
-      </c>
-      <c r="F99" t="s">
-        <v>410</v>
-      </c>
-      <c r="G99" t="s">
-        <v>404</v>
+        <v>105</v>
+      </c>
+      <c r="G99">
+        <v>4</v>
       </c>
       <c r="H99" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>17</v>
+        <v>121</v>
       </c>
       <c r="B100" t="s">
         <v>18</v>
       </c>
       <c r="C100">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E100" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="F100" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="G100">
-        <v>8.1</v>
+        <v>4</v>
       </c>
       <c r="H100" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B101" t="s">
         <v>18</v>
       </c>
       <c r="C101">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E101" t="s">
-        <v>112</v>
+        <v>125</v>
+      </c>
+      <c r="F101" t="s">
+        <v>126</v>
       </c>
       <c r="G101">
         <v>4</v>
       </c>
       <c r="H101" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>128</v>
+        <v>683</v>
       </c>
       <c r="B102" t="s">
-        <v>18</v>
+        <v>684</v>
       </c>
       <c r="C102">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E102" t="s">
-        <v>129</v>
+        <v>685</v>
       </c>
       <c r="F102" t="s">
-        <v>130</v>
-      </c>
-      <c r="G102">
-        <v>4</v>
+        <v>686</v>
+      </c>
+      <c r="G102" t="s">
+        <v>600</v>
       </c>
       <c r="H102" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>131</v>
+        <v>687</v>
       </c>
       <c r="B103" t="s">
-        <v>18</v>
+        <v>688</v>
       </c>
       <c r="C103">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="E103" t="s">
-        <v>132</v>
+        <v>689</v>
       </c>
       <c r="F103" t="s">
-        <v>133</v>
-      </c>
-      <c r="G103">
-        <v>4</v>
+        <v>690</v>
+      </c>
+      <c r="G103" t="s">
+        <v>600</v>
       </c>
       <c r="H103" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B104" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C104">
         <v>300</v>
       </c>
       <c r="E104" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F104" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G104" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H104" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>697</v>
+        <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>698</v>
+        <v>18</v>
       </c>
       <c r="C105">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E105" t="s">
-        <v>699</v>
+        <v>102</v>
       </c>
       <c r="F105" t="s">
-        <v>700</v>
-      </c>
-      <c r="G105" t="s">
-        <v>610</v>
+        <v>103</v>
+      </c>
+      <c r="G105">
+        <v>4</v>
       </c>
       <c r="H105" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>705</v>
+        <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>706</v>
+        <v>18</v>
       </c>
       <c r="C106">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E106" t="s">
-        <v>707</v>
+        <v>107</v>
       </c>
       <c r="F106" t="s">
-        <v>708</v>
-      </c>
-      <c r="G106" t="s">
-        <v>610</v>
+        <v>108</v>
+      </c>
+      <c r="G106">
+        <v>4</v>
       </c>
       <c r="H106" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B107" t="s">
         <v>18</v>
@@ -6370,22 +6301,25 @@
       <c r="C107">
         <v>250</v>
       </c>
+      <c r="D107">
+        <v>150</v>
+      </c>
       <c r="E107" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F107" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G107">
         <v>4</v>
       </c>
       <c r="H107" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B108" t="s">
         <v>18</v>
@@ -6394,21 +6328,21 @@
         <v>250</v>
       </c>
       <c r="E108" t="s">
+        <v>113</v>
+      </c>
+      <c r="F108" t="s">
         <v>114</v>
-      </c>
-      <c r="F108" t="s">
-        <v>115</v>
       </c>
       <c r="G108">
         <v>4</v>
       </c>
       <c r="H108" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B109" t="s">
         <v>18</v>
@@ -6416,215 +6350,215 @@
       <c r="C109">
         <v>250</v>
       </c>
-      <c r="D109">
-        <v>150</v>
-      </c>
       <c r="E109" t="s">
+        <v>116</v>
+      </c>
+      <c r="F109" t="s">
         <v>117</v>
-      </c>
-      <c r="F109" t="s">
-        <v>118</v>
       </c>
       <c r="G109">
         <v>4</v>
       </c>
       <c r="H109" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B110" t="s">
         <v>18</v>
       </c>
       <c r="C110">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E110" t="s">
+        <v>119</v>
+      </c>
+      <c r="F110" t="s">
         <v>120</v>
-      </c>
-      <c r="F110" t="s">
-        <v>121</v>
       </c>
       <c r="G110">
         <v>4</v>
       </c>
       <c r="H110" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="B111" t="s">
         <v>18</v>
       </c>
       <c r="C111">
-        <v>250</v>
+        <v>365</v>
       </c>
       <c r="E111" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="F111" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="G111">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H111" t="s">
-        <v>731</v>
+        <v>133</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="B112" t="s">
         <v>18</v>
       </c>
       <c r="C112">
-        <v>150</v>
+        <v>169</v>
+      </c>
+      <c r="D112">
+        <v>100</v>
       </c>
       <c r="E112" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="F112" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="G112">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H112" t="s">
-        <v>731</v>
+        <v>133</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B113" t="s">
         <v>18</v>
       </c>
       <c r="C113">
-        <v>365</v>
+        <v>250</v>
       </c>
       <c r="E113" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F113" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G113">
         <v>5</v>
       </c>
       <c r="H113" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B114" t="s">
         <v>18</v>
       </c>
       <c r="C114">
-        <v>169</v>
+        <v>420</v>
       </c>
       <c r="D114">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="E114" t="s">
-        <v>169</v>
-      </c>
-      <c r="F114" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G114">
         <v>5</v>
       </c>
       <c r="H114" t="s">
-        <v>140</v>
+        <v>721</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B115" t="s">
         <v>18</v>
       </c>
       <c r="C115">
-        <v>250</v>
+        <v>365</v>
       </c>
       <c r="E115" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="F115" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="G115">
         <v>5</v>
       </c>
       <c r="H115" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B116" t="s">
         <v>18</v>
       </c>
       <c r="C116">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="D116">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E116" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G116">
         <v>5</v>
       </c>
       <c r="H116" t="s">
-        <v>731</v>
+        <v>133</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="B117" t="s">
-        <v>18</v>
+        <v>221</v>
       </c>
       <c r="C117">
-        <v>365</v>
+        <v>189</v>
+      </c>
+      <c r="D117">
+        <v>150</v>
       </c>
       <c r="E117" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="F117" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="G117">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H117" t="s">
-        <v>140</v>
+        <v>721</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="B118" t="s">
-        <v>18</v>
+        <v>1075</v>
       </c>
       <c r="C118">
         <v>350</v>
@@ -6633,85 +6567,88 @@
         <v>250</v>
       </c>
       <c r="E118" t="s">
-        <v>200</v>
-      </c>
-      <c r="G118">
-        <v>5</v>
+        <v>233</v>
+      </c>
+      <c r="F118" t="s">
+        <v>234</v>
+      </c>
+      <c r="G118" t="s">
+        <v>1025</v>
       </c>
       <c r="H118" t="s">
-        <v>140</v>
+        <v>905</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="B119" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C119">
-        <v>189</v>
+        <v>420</v>
       </c>
       <c r="D119">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="E119" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="F119" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="G119">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H119" t="s">
-        <v>731</v>
+        <v>86</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B120" t="s">
-        <v>1096</v>
+        <v>249</v>
       </c>
       <c r="C120">
+        <v>439</v>
+      </c>
+      <c r="D120">
         <v>350</v>
       </c>
-      <c r="D120">
-        <v>250</v>
-      </c>
       <c r="E120" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="F120" t="s">
-        <v>241</v>
-      </c>
-      <c r="G120" t="s">
-        <v>1046</v>
+        <v>254</v>
+      </c>
+      <c r="G120">
+        <v>7</v>
       </c>
       <c r="H120" t="s">
-        <v>926</v>
+        <v>86</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B121" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C121">
-        <v>420</v>
+        <v>200</v>
       </c>
       <c r="D121">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E121" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F121" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G121">
         <v>7</v>
@@ -6722,22 +6659,22 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>258</v>
+      </c>
+      <c r="B122" t="s">
+        <v>29</v>
+      </c>
+      <c r="C122">
+        <v>575</v>
+      </c>
+      <c r="D122">
+        <v>300</v>
+      </c>
+      <c r="E122" t="s">
         <v>259</v>
       </c>
-      <c r="B122" t="s">
-        <v>256</v>
-      </c>
-      <c r="C122">
-        <v>439</v>
-      </c>
-      <c r="D122">
-        <v>350</v>
-      </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>260</v>
-      </c>
-      <c r="F122" t="s">
-        <v>261</v>
       </c>
       <c r="G122">
         <v>7</v>
@@ -6748,106 +6685,106 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B123" t="s">
-        <v>256</v>
+        <v>18</v>
       </c>
       <c r="C123">
+        <v>347</v>
+      </c>
+      <c r="D123">
         <v>200</v>
       </c>
-      <c r="D123">
-        <v>150</v>
-      </c>
       <c r="E123" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F123" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G123">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H123" t="s">
-        <v>86</v>
+        <v>724</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B124" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C124">
-        <v>575</v>
+        <v>498</v>
       </c>
       <c r="D124">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E124" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="F124" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="G124">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H124" t="s">
-        <v>86</v>
+        <v>724</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B125" t="s">
-        <v>18</v>
+        <v>278</v>
       </c>
       <c r="C125">
-        <v>347</v>
+        <v>280</v>
       </c>
       <c r="D125">
         <v>200</v>
       </c>
       <c r="E125" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F125" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G125">
         <v>8</v>
       </c>
       <c r="H125" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B126" t="s">
         <v>18</v>
       </c>
       <c r="C126">
-        <v>498</v>
+        <v>250</v>
       </c>
       <c r="D126">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E126" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F126" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G126">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="H126" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -6855,253 +6792,250 @@
         <v>284</v>
       </c>
       <c r="B127" t="s">
+        <v>40</v>
+      </c>
+      <c r="C127">
+        <v>138</v>
+      </c>
+      <c r="D127">
+        <v>100</v>
+      </c>
+      <c r="E127" t="s">
         <v>285</v>
       </c>
-      <c r="C127">
-        <v>280</v>
-      </c>
-      <c r="D127">
-        <v>200</v>
-      </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>286</v>
       </c>
-      <c r="F127" t="s">
-        <v>287</v>
-      </c>
       <c r="G127">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="H127" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>287</v>
+      </c>
+      <c r="B128" t="s">
+        <v>18</v>
+      </c>
+      <c r="C128">
+        <v>389</v>
+      </c>
+      <c r="D128">
+        <v>300</v>
+      </c>
+      <c r="E128" t="s">
+        <v>723</v>
+      </c>
+      <c r="F128" t="s">
         <v>288</v>
       </c>
-      <c r="B128" t="s">
-        <v>40</v>
-      </c>
-      <c r="C128">
-        <v>179</v>
-      </c>
-      <c r="D128">
-        <v>100</v>
-      </c>
-      <c r="E128" t="s">
-        <v>289</v>
-      </c>
-      <c r="F128" t="s">
-        <v>290</v>
-      </c>
       <c r="G128">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="H128" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>291</v>
+        <v>991</v>
       </c>
       <c r="B129" t="s">
-        <v>18</v>
+        <v>990</v>
       </c>
       <c r="C129">
-        <v>250</v>
+        <v>219.5</v>
       </c>
       <c r="D129">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E129" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F129" t="s">
-        <v>293</v>
-      </c>
-      <c r="G129">
-        <v>8.1</v>
+        <v>290</v>
+      </c>
+      <c r="G129" t="s">
+        <v>901</v>
       </c>
       <c r="H129" t="s">
-        <v>734</v>
+        <v>294</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B130" t="s">
-        <v>40</v>
+        <v>312</v>
       </c>
       <c r="C130">
-        <v>138</v>
+        <v>685</v>
       </c>
       <c r="D130">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E130" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="F130" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="G130">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="H130" t="s">
-        <v>734</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="B131" t="s">
         <v>18</v>
       </c>
       <c r="C131">
-        <v>389</v>
+        <v>150</v>
       </c>
       <c r="D131">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E131" t="s">
-        <v>733</v>
+        <v>325</v>
       </c>
       <c r="F131" t="s">
-        <v>298</v>
-      </c>
-      <c r="G131">
-        <v>8.1</v>
+        <v>326</v>
+      </c>
+      <c r="G131" t="s">
+        <v>327</v>
       </c>
       <c r="H131" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>1012</v>
+        <v>328</v>
       </c>
       <c r="B132" t="s">
-        <v>1011</v>
+        <v>18</v>
       </c>
       <c r="C132">
-        <v>219.5</v>
+        <v>1899</v>
       </c>
       <c r="D132">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="E132" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="F132" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="G132" t="s">
-        <v>922</v>
+        <v>331</v>
       </c>
       <c r="H132" t="s">
-        <v>304</v>
+        <v>722</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="B133" t="s">
-        <v>322</v>
+        <v>18</v>
       </c>
       <c r="C133">
-        <v>685</v>
-      </c>
-      <c r="D133">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E133" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="F133" t="s">
-        <v>324</v>
-      </c>
-      <c r="G133">
-        <v>10</v>
+        <v>342</v>
+      </c>
+      <c r="G133" t="s">
+        <v>336</v>
       </c>
       <c r="H133" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B134" t="s">
-        <v>18</v>
+        <v>333</v>
       </c>
       <c r="C134">
-        <v>150</v>
+        <v>399</v>
       </c>
       <c r="D134">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E134" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="F134" t="s">
+        <v>345</v>
+      </c>
+      <c r="G134" t="s">
         <v>336</v>
       </c>
-      <c r="G134" t="s">
-        <v>337</v>
-      </c>
       <c r="H134" t="s">
-        <v>732</v>
+        <v>86</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="B135" t="s">
         <v>18</v>
       </c>
       <c r="C135">
-        <v>1899</v>
-      </c>
-      <c r="D135">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="E135" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="F135" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="G135" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="H135" t="s">
-        <v>732</v>
+        <v>86</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B136" t="s">
         <v>18</v>
       </c>
       <c r="C136">
-        <v>200</v>
+        <v>299</v>
+      </c>
+      <c r="D136">
+        <v>250</v>
       </c>
       <c r="E136" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="F136" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="G136" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="H136" t="s">
         <v>86</v>
@@ -7109,25 +7043,22 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B137" t="s">
-        <v>343</v>
+        <v>18</v>
       </c>
       <c r="C137">
-        <v>399</v>
-      </c>
-      <c r="D137">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="E137" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="F137" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="G137" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="H137" t="s">
         <v>86</v>
@@ -7135,22 +7066,25 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B138" t="s">
-        <v>18</v>
+        <v>367</v>
       </c>
       <c r="C138">
-        <v>500</v>
+        <v>599</v>
+      </c>
+      <c r="D138">
+        <v>350</v>
       </c>
       <c r="E138" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F138" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="G138" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="H138" t="s">
         <v>86</v>
@@ -7158,25 +7092,25 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B139" t="s">
         <v>18</v>
       </c>
       <c r="C139">
-        <v>299</v>
+        <v>599</v>
       </c>
       <c r="D139">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E139" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F139" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G139" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="H139" t="s">
         <v>86</v>
@@ -7184,74 +7118,77 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B140" t="s">
         <v>18</v>
       </c>
       <c r="C140">
-        <v>370</v>
+        <v>350</v>
+      </c>
+      <c r="D140">
+        <v>200</v>
       </c>
       <c r="E140" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F140" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="G140" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="H140" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B141" t="s">
-        <v>377</v>
+        <v>18</v>
       </c>
       <c r="C141">
-        <v>599</v>
+        <v>519</v>
       </c>
       <c r="D141">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="E141" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F141" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G141" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="H141" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B142" t="s">
         <v>18</v>
       </c>
       <c r="C142">
-        <v>599</v>
+        <v>250</v>
       </c>
       <c r="D142">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E142" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F142" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G142" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="H142" t="s">
         <v>86</v>
@@ -7259,77 +7196,77 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B143" t="s">
         <v>18</v>
       </c>
       <c r="C143">
-        <v>350</v>
+        <v>899</v>
       </c>
       <c r="D143">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E143" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F143" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G143" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="H143" t="s">
-        <v>140</v>
+        <v>721</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B144" t="s">
         <v>18</v>
       </c>
       <c r="C144">
-        <v>519</v>
+        <v>553</v>
       </c>
       <c r="D144">
-        <v>330</v>
+        <v>450</v>
       </c>
       <c r="E144" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F144" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="G144" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="H144" t="s">
-        <v>140</v>
+        <v>721</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="B145" t="s">
         <v>18</v>
       </c>
       <c r="C145">
-        <v>250</v>
+        <v>785</v>
       </c>
       <c r="D145">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="E145" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="F145" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="G145" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H145" t="s">
         <v>86</v>
@@ -7337,77 +7274,77 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="B146" t="s">
-        <v>18</v>
+        <v>416</v>
       </c>
       <c r="C146">
-        <v>899</v>
+        <v>411.67</v>
       </c>
       <c r="D146">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="E146" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="F146" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G146" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="H146" t="s">
-        <v>731</v>
+        <v>133</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="B147" t="s">
         <v>18</v>
       </c>
       <c r="C147">
-        <v>553</v>
+        <v>850</v>
       </c>
       <c r="D147">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="E147" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="F147" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="G147" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="H147" t="s">
-        <v>731</v>
+        <v>86</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="B148" t="s">
-        <v>18</v>
+        <v>432</v>
       </c>
       <c r="C148">
-        <v>785</v>
+        <v>1439</v>
       </c>
       <c r="D148">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E148" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="F148" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="G148" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="H148" t="s">
         <v>86</v>
@@ -7415,149 +7352,140 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="B149" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="C149">
-        <v>411.67</v>
+        <v>1499</v>
       </c>
       <c r="D149">
-        <v>350</v>
+        <v>850</v>
       </c>
       <c r="E149" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F149" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="G149" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H149" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="B150" t="s">
         <v>18</v>
       </c>
       <c r="C150">
-        <v>850</v>
-      </c>
-      <c r="D150">
-        <v>550</v>
+        <v>170</v>
       </c>
       <c r="E150" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="F150" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="G150" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="H150" t="s">
-        <v>86</v>
+        <v>724</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="B151" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="C151">
-        <v>1439</v>
-      </c>
-      <c r="D151">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E151" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="F151" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="G151" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H151" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="B152" t="s">
-        <v>446</v>
+        <v>992</v>
       </c>
       <c r="C152">
-        <v>1499</v>
-      </c>
-      <c r="D152">
-        <v>850</v>
+        <v>40</v>
       </c>
       <c r="E152" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F152" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="G152" t="s">
-        <v>440</v>
+        <v>901</v>
       </c>
       <c r="H152" t="s">
-        <v>86</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B153" t="s">
         <v>18</v>
       </c>
       <c r="C153">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="E153" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="F153" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="G153" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="H153" t="s">
-        <v>734</v>
+        <v>86</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="B154" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="C154">
         <v>200</v>
       </c>
       <c r="E154" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="F154" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="G154" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="H154" t="s">
         <v>12</v>
@@ -7565,143 +7493,149 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="B155" t="s">
-        <v>1013</v>
+        <v>495</v>
       </c>
       <c r="C155">
-        <v>40</v>
+        <v>239</v>
+      </c>
+      <c r="D155">
+        <v>150</v>
       </c>
       <c r="E155" t="s">
-        <v>465</v>
+        <v>496</v>
       </c>
       <c r="F155" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="G155" t="s">
-        <v>922</v>
+        <v>498</v>
       </c>
       <c r="H155" t="s">
-        <v>304</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>477</v>
+        <v>516</v>
       </c>
       <c r="B156" t="s">
-        <v>18</v>
+        <v>517</v>
       </c>
       <c r="C156">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="E156" t="s">
-        <v>478</v>
+        <v>518</v>
       </c>
       <c r="F156" t="s">
-        <v>479</v>
+        <v>519</v>
       </c>
       <c r="G156" t="s">
-        <v>456</v>
+        <v>498</v>
       </c>
       <c r="H156" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>483</v>
+        <v>973</v>
       </c>
       <c r="B157" t="s">
-        <v>461</v>
+        <v>972</v>
       </c>
       <c r="C157">
-        <v>200</v>
+        <v>170</v>
+      </c>
+      <c r="D157">
+        <v>100</v>
       </c>
       <c r="E157" t="s">
-        <v>484</v>
+        <v>535</v>
       </c>
       <c r="F157" t="s">
-        <v>485</v>
+        <v>536</v>
       </c>
       <c r="G157" t="s">
-        <v>456</v>
+        <v>515</v>
       </c>
       <c r="H157" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>504</v>
+        <v>537</v>
       </c>
       <c r="B158" t="s">
-        <v>505</v>
+        <v>40</v>
       </c>
       <c r="C158">
-        <v>239</v>
+        <v>150</v>
       </c>
       <c r="D158">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E158" t="s">
-        <v>506</v>
-      </c>
-      <c r="F158" t="s">
-        <v>507</v>
+        <v>538</v>
       </c>
       <c r="G158" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="H158" t="s">
-        <v>12</v>
+        <v>721</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="B159" t="s">
-        <v>527</v>
+        <v>40</v>
       </c>
       <c r="C159">
         <v>300</v>
       </c>
+      <c r="D159">
+        <v>200</v>
+      </c>
       <c r="E159" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="F159" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G159" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="H159" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>994</v>
+        <v>542</v>
       </c>
       <c r="B160" t="s">
-        <v>993</v>
+        <v>40</v>
       </c>
       <c r="C160">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D160">
         <v>100</v>
       </c>
       <c r="E160" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F160" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G160" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="H160" t="s">
         <v>86</v>
@@ -7709,10 +7643,10 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B161" t="s">
-        <v>40</v>
+        <v>549</v>
       </c>
       <c r="C161">
         <v>150</v>
@@ -7721,36 +7655,39 @@
         <v>100</v>
       </c>
       <c r="E161" t="s">
-        <v>548</v>
+        <v>550</v>
+      </c>
+      <c r="F161" t="s">
+        <v>551</v>
       </c>
       <c r="G161" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="H161" t="s">
-        <v>731</v>
+        <v>562</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B162" t="s">
-        <v>40</v>
+        <v>553</v>
       </c>
       <c r="C162">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D162">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E162" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F162" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="G162" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="H162" t="s">
         <v>86</v>
@@ -7758,80 +7695,77 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="B163" t="s">
         <v>40</v>
       </c>
       <c r="C163">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D163">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E163" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="F163" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="G163" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="H163" t="s">
-        <v>86</v>
+        <v>722</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="B164" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="C164">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D164">
         <v>100</v>
       </c>
       <c r="E164" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="F164" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="G164" t="s">
-        <v>525</v>
+        <v>40</v>
       </c>
       <c r="H164" t="s">
-        <v>572</v>
+        <v>294</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="B165" t="s">
-        <v>563</v>
+        <v>40</v>
       </c>
       <c r="C165">
-        <v>200</v>
-      </c>
-      <c r="D165">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="E165" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="F165" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="G165" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="H165" t="s">
-        <v>86</v>
+        <v>721</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -7839,567 +7773,561 @@
         <v>573</v>
       </c>
       <c r="B166" t="s">
-        <v>40</v>
+        <v>574</v>
       </c>
       <c r="C166">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="D166">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E166" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F166" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G166" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="H166" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B167" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="C167">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="D167">
-        <v>100</v>
+        <v>550</v>
       </c>
       <c r="E167" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="F167" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="G167" t="s">
-        <v>40</v>
+        <v>580</v>
       </c>
       <c r="H167" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="B168" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C168">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="E168" t="s">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="F168" t="s">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="G168" t="s">
-        <v>525</v>
+        <v>592</v>
       </c>
       <c r="H168" t="s">
-        <v>731</v>
+        <v>133</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="B169" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="C169">
-        <v>180</v>
+        <v>2299</v>
       </c>
       <c r="D169">
-        <v>100</v>
+        <v>1450</v>
       </c>
       <c r="E169" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="F169" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="G169" t="s">
-        <v>525</v>
+        <v>600</v>
       </c>
       <c r="H169" t="s">
-        <v>731</v>
+        <v>294</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="B170" t="s">
-        <v>599</v>
+        <v>623</v>
       </c>
       <c r="C170">
-        <v>1200</v>
-      </c>
-      <c r="D170">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="E170" t="s">
+        <v>624</v>
+      </c>
+      <c r="F170" t="s">
+        <v>625</v>
+      </c>
+      <c r="G170" t="s">
         <v>600</v>
       </c>
-      <c r="F170" t="s">
-        <v>601</v>
-      </c>
-      <c r="G170" t="s">
-        <v>590</v>
-      </c>
       <c r="H170" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>603</v>
+        <v>626</v>
       </c>
       <c r="B171" t="s">
-        <v>29</v>
+        <v>627</v>
       </c>
       <c r="C171">
-        <v>150</v>
+        <v>399</v>
+      </c>
+      <c r="D171">
+        <v>350</v>
       </c>
       <c r="E171" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="F171" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="G171" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H171" t="s">
-        <v>140</v>
+        <v>724</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>606</v>
+        <v>633</v>
       </c>
       <c r="B172" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="C172">
-        <v>2299</v>
+        <v>159</v>
       </c>
       <c r="D172">
-        <v>1450</v>
+        <v>120</v>
       </c>
       <c r="E172" t="s">
-        <v>608</v>
+        <v>634</v>
       </c>
       <c r="F172" t="s">
-        <v>609</v>
+        <v>635</v>
       </c>
       <c r="G172" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H172" t="s">
-        <v>304</v>
+        <v>133</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>632</v>
+        <v>903</v>
       </c>
       <c r="B173" t="s">
-        <v>633</v>
+        <v>655</v>
       </c>
       <c r="C173">
-        <v>700</v>
+        <v>500</v>
+      </c>
+      <c r="D173">
+        <v>450</v>
       </c>
       <c r="E173" t="s">
-        <v>634</v>
+        <v>906</v>
       </c>
       <c r="F173" t="s">
-        <v>635</v>
+        <v>904</v>
       </c>
       <c r="G173" t="s">
-        <v>610</v>
+        <v>1025</v>
       </c>
       <c r="H173" t="s">
-        <v>304</v>
+        <v>905</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>636</v>
+        <v>902</v>
       </c>
       <c r="B174" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="C174">
-        <v>399</v>
+        <v>500</v>
       </c>
       <c r="D174">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="E174" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
       <c r="F174" t="s">
-        <v>639</v>
+        <v>657</v>
       </c>
       <c r="G174" t="s">
-        <v>610</v>
+        <v>1025</v>
       </c>
       <c r="H174" t="s">
-        <v>734</v>
+        <v>905</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>643</v>
+        <v>670</v>
       </c>
       <c r="B175" t="s">
-        <v>633</v>
+        <v>29</v>
       </c>
       <c r="C175">
-        <v>159</v>
+        <v>1830</v>
       </c>
       <c r="D175">
-        <v>120</v>
+        <v>1050</v>
       </c>
       <c r="E175" t="s">
-        <v>644</v>
+        <v>671</v>
       </c>
       <c r="F175" t="s">
-        <v>645</v>
+        <v>672</v>
       </c>
       <c r="G175" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H175" t="s">
-        <v>140</v>
+        <v>722</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>924</v>
+        <v>877</v>
       </c>
       <c r="B176" t="s">
-        <v>665</v>
+        <v>876</v>
       </c>
       <c r="C176">
-        <v>500</v>
-      </c>
-      <c r="D176">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="E176" t="s">
-        <v>927</v>
+        <v>677</v>
       </c>
       <c r="F176" t="s">
-        <v>925</v>
+        <v>678</v>
       </c>
       <c r="G176" t="s">
-        <v>1046</v>
+        <v>901</v>
       </c>
       <c r="H176" t="s">
-        <v>926</v>
+        <v>294</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>923</v>
+        <v>691</v>
       </c>
       <c r="B177" t="s">
-        <v>665</v>
+        <v>692</v>
       </c>
       <c r="C177">
-        <v>500</v>
-      </c>
-      <c r="D177">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="E177" t="s">
-        <v>666</v>
+        <v>693</v>
       </c>
       <c r="F177" t="s">
-        <v>667</v>
+        <v>694</v>
       </c>
       <c r="G177" t="s">
-        <v>1046</v>
+        <v>600</v>
       </c>
       <c r="H177" t="s">
-        <v>926</v>
+        <v>133</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>680</v>
+        <v>714</v>
       </c>
       <c r="B178" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C178">
-        <v>1830</v>
-      </c>
-      <c r="D178">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="E178" t="s">
-        <v>681</v>
+        <v>715</v>
       </c>
       <c r="F178" t="s">
-        <v>682</v>
+        <v>716</v>
       </c>
       <c r="G178" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H178" t="s">
-        <v>732</v>
+        <v>86</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>898</v>
+        <v>499</v>
       </c>
       <c r="B179" t="s">
-        <v>897</v>
+        <v>18</v>
       </c>
       <c r="C179">
-        <v>300</v>
+        <v>106</v>
+      </c>
+      <c r="D179">
+        <v>80</v>
       </c>
       <c r="E179" t="s">
-        <v>687</v>
-      </c>
-      <c r="F179" t="s">
-        <v>688</v>
+        <v>500</v>
       </c>
       <c r="G179" t="s">
-        <v>922</v>
+        <v>498</v>
       </c>
       <c r="H179" t="s">
-        <v>304</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>701</v>
+        <v>181</v>
       </c>
       <c r="B180" t="s">
-        <v>702</v>
+        <v>18</v>
       </c>
       <c r="C180">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="E180" t="s">
-        <v>703</v>
+        <v>182</v>
       </c>
       <c r="F180" t="s">
-        <v>704</v>
-      </c>
-      <c r="G180" t="s">
-        <v>610</v>
+        <v>183</v>
+      </c>
+      <c r="G180">
+        <v>5</v>
       </c>
       <c r="H180" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>724</v>
+        <v>703</v>
       </c>
       <c r="B181" t="s">
-        <v>18</v>
+        <v>704</v>
       </c>
       <c r="C181">
-        <v>200</v>
+        <v>859</v>
+      </c>
+      <c r="D181">
+        <v>650</v>
       </c>
       <c r="E181" t="s">
-        <v>725</v>
+        <v>705</v>
       </c>
       <c r="F181" t="s">
-        <v>726</v>
+        <v>706</v>
       </c>
       <c r="G181" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="H181" t="s">
-        <v>86</v>
+        <v>721</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>509</v>
+        <v>717</v>
       </c>
       <c r="B182" t="s">
-        <v>18</v>
+        <v>718</v>
       </c>
       <c r="C182">
-        <v>106</v>
-      </c>
-      <c r="D182">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="E182" t="s">
-        <v>510</v>
+        <v>719</v>
+      </c>
+      <c r="F182" t="s">
+        <v>720</v>
       </c>
       <c r="G182" t="s">
-        <v>508</v>
+        <v>600</v>
       </c>
       <c r="H182" t="s">
-        <v>12</v>
+        <v>721</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C183">
-        <v>160</v>
+        <v>180</v>
+      </c>
+      <c r="D183">
+        <v>150</v>
       </c>
       <c r="E183" t="s">
-        <v>189</v>
+        <v>10</v>
       </c>
       <c r="F183" t="s">
-        <v>190</v>
+        <v>11</v>
       </c>
       <c r="G183">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H183" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>713</v>
+        <v>13</v>
       </c>
       <c r="B184" t="s">
-        <v>714</v>
+        <v>14</v>
       </c>
       <c r="C184">
-        <v>859</v>
+        <v>298</v>
       </c>
       <c r="D184">
-        <v>650</v>
+        <v>200</v>
       </c>
       <c r="E184" t="s">
-        <v>715</v>
+        <v>15</v>
       </c>
       <c r="F184" t="s">
-        <v>716</v>
-      </c>
-      <c r="G184" t="s">
-        <v>610</v>
+        <v>16</v>
+      </c>
+      <c r="G184">
+        <v>2</v>
       </c>
       <c r="H184" t="s">
-        <v>731</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>727</v>
+        <v>21</v>
       </c>
       <c r="B185" t="s">
-        <v>728</v>
+        <v>22</v>
       </c>
       <c r="C185">
-        <v>250</v>
+        <v>439</v>
+      </c>
+      <c r="D185">
+        <v>200</v>
       </c>
       <c r="E185" t="s">
-        <v>729</v>
+        <v>23</v>
       </c>
       <c r="F185" t="s">
-        <v>730</v>
-      </c>
-      <c r="G185" t="s">
-        <v>610</v>
+        <v>24</v>
+      </c>
+      <c r="G185">
+        <v>2</v>
       </c>
       <c r="H185" t="s">
-        <v>731</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>8</v>
+        <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C186">
-        <v>180</v>
-      </c>
-      <c r="D186">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E186" t="s">
-        <v>10</v>
+        <v>185</v>
       </c>
       <c r="F186" t="s">
-        <v>11</v>
+        <v>186</v>
       </c>
       <c r="G186">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H186" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="B187" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C187">
-        <v>298</v>
-      </c>
-      <c r="D187">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E187" t="s">
-        <v>15</v>
-      </c>
-      <c r="F187" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="G187">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H187" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="B188" t="s">
-        <v>22</v>
+        <v>305</v>
       </c>
       <c r="C188">
-        <v>439</v>
+        <v>419.19</v>
       </c>
       <c r="D188">
         <v>200</v>
       </c>
       <c r="E188" t="s">
-        <v>23</v>
+        <v>306</v>
       </c>
       <c r="F188" t="s">
-        <v>24</v>
+        <v>307</v>
       </c>
       <c r="G188">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H188" t="s">
         <v>12</v>
@@ -8407,94 +8335,100 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>191</v>
+        <v>308</v>
       </c>
       <c r="B189" t="s">
-        <v>18</v>
+        <v>305</v>
       </c>
       <c r="C189">
-        <v>100</v>
+        <v>170</v>
+      </c>
+      <c r="D189">
+        <v>150</v>
       </c>
       <c r="E189" t="s">
-        <v>192</v>
+        <v>309</v>
       </c>
       <c r="F189" t="s">
-        <v>193</v>
+        <v>310</v>
       </c>
       <c r="G189">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H189" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>194</v>
+        <v>315</v>
       </c>
       <c r="B190" t="s">
-        <v>18</v>
+        <v>316</v>
       </c>
       <c r="C190">
-        <v>150</v>
+        <v>600</v>
+      </c>
+      <c r="D190">
+        <v>350</v>
       </c>
       <c r="E190" t="s">
-        <v>195</v>
+        <v>317</v>
+      </c>
+      <c r="F190" t="s">
+        <v>318</v>
       </c>
       <c r="G190">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H190" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B191" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C191">
-        <v>419.19</v>
+        <v>2154</v>
       </c>
       <c r="D191">
-        <v>200</v>
+        <v>1550</v>
       </c>
       <c r="E191" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F191" t="s">
-        <v>317</v>
-      </c>
-      <c r="G191">
-        <v>10</v>
+        <v>322</v>
+      </c>
+      <c r="G191" t="s">
+        <v>323</v>
       </c>
       <c r="H191" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>318</v>
+        <v>460</v>
       </c>
       <c r="B192" t="s">
-        <v>315</v>
+        <v>461</v>
       </c>
       <c r="C192">
-        <v>170</v>
-      </c>
-      <c r="D192">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E192" t="s">
-        <v>319</v>
+        <v>462</v>
       </c>
       <c r="F192" t="s">
-        <v>320</v>
-      </c>
-      <c r="G192">
-        <v>10</v>
+        <v>463</v>
+      </c>
+      <c r="G192" t="s">
+        <v>446</v>
       </c>
       <c r="H192" t="s">
         <v>12</v>
@@ -8502,25 +8436,22 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>325</v>
+        <v>470</v>
       </c>
       <c r="B193" t="s">
-        <v>326</v>
+        <v>18</v>
       </c>
       <c r="C193">
-        <v>600</v>
-      </c>
-      <c r="D193">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="E193" t="s">
-        <v>327</v>
+        <v>471</v>
       </c>
       <c r="F193" t="s">
-        <v>328</v>
-      </c>
-      <c r="G193">
-        <v>10</v>
+        <v>472</v>
+      </c>
+      <c r="G193" t="s">
+        <v>446</v>
       </c>
       <c r="H193" t="s">
         <v>12</v>
@@ -8528,48 +8459,42 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>329</v>
+        <v>476</v>
       </c>
       <c r="B194" t="s">
-        <v>330</v>
+        <v>461</v>
       </c>
       <c r="C194">
-        <v>2154</v>
-      </c>
-      <c r="D194">
-        <v>1550</v>
+        <v>350</v>
       </c>
       <c r="E194" t="s">
-        <v>331</v>
+        <v>477</v>
       </c>
       <c r="F194" t="s">
-        <v>332</v>
+        <v>478</v>
       </c>
       <c r="G194" t="s">
-        <v>333</v>
+        <v>446</v>
       </c>
       <c r="H194" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="B195" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="C195">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E195" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="F195" t="s">
-        <v>473</v>
-      </c>
-      <c r="G195" t="s">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="H195" t="s">
         <v>12</v>
@@ -8577,22 +8502,25 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="B196" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C196">
-        <v>280</v>
+        <v>178.03</v>
+      </c>
+      <c r="D196">
+        <v>80</v>
       </c>
       <c r="E196" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="F196" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="G196" t="s">
-        <v>456</v>
+        <v>498</v>
       </c>
       <c r="H196" t="s">
         <v>12</v>
@@ -8600,22 +8528,25 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="B197" t="s">
-        <v>471</v>
+        <v>505</v>
       </c>
       <c r="C197">
-        <v>350</v>
+        <v>150</v>
+      </c>
+      <c r="D197">
+        <v>100</v>
       </c>
       <c r="E197" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="F197" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="G197" t="s">
-        <v>456</v>
+        <v>498</v>
       </c>
       <c r="H197" t="s">
         <v>12</v>
@@ -8623,19 +8554,25 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="B198" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C198">
-        <v>400</v>
+        <v>150</v>
+      </c>
+      <c r="D198">
+        <v>100</v>
       </c>
       <c r="E198" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F198" t="s">
-        <v>503</v>
+        <v>510</v>
+      </c>
+      <c r="G198" t="s">
+        <v>498</v>
       </c>
       <c r="H198" t="s">
         <v>12</v>
@@ -8643,25 +8580,22 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="B199" t="s">
-        <v>9</v>
+        <v>521</v>
       </c>
       <c r="C199">
-        <v>178.03</v>
-      </c>
-      <c r="D199">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E199" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="F199" t="s">
-        <v>513</v>
-      </c>
-      <c r="G199" t="s">
-        <v>508</v>
+        <v>523</v>
+      </c>
+      <c r="G199">
+        <v>10</v>
       </c>
       <c r="H199" t="s">
         <v>12</v>
@@ -8669,25 +8603,25 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="B200" t="s">
-        <v>515</v>
+        <v>9</v>
       </c>
       <c r="C200">
+        <v>248.02</v>
+      </c>
+      <c r="D200">
         <v>150</v>
       </c>
-      <c r="D200">
-        <v>100</v>
-      </c>
       <c r="E200" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="F200" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="G200" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="H200" t="s">
         <v>12</v>
@@ -8695,25 +8629,25 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="B201" t="s">
-        <v>515</v>
+        <v>9</v>
       </c>
       <c r="C201">
-        <v>150</v>
+        <v>290</v>
       </c>
       <c r="D201">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E201" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="F201" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="G201" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="H201" t="s">
         <v>12</v>
@@ -8724,19 +8658,22 @@
         <v>530</v>
       </c>
       <c r="B202" t="s">
+        <v>9</v>
+      </c>
+      <c r="C202">
+        <v>149</v>
+      </c>
+      <c r="D202">
+        <v>100</v>
+      </c>
+      <c r="E202" t="s">
         <v>531</v>
       </c>
-      <c r="C202">
-        <v>100</v>
-      </c>
-      <c r="E202" t="s">
+      <c r="F202" t="s">
         <v>532</v>
       </c>
-      <c r="F202" t="s">
-        <v>533</v>
-      </c>
-      <c r="G202">
-        <v>10</v>
+      <c r="G202" t="s">
+        <v>498</v>
       </c>
       <c r="H202" t="s">
         <v>12</v>
@@ -8744,25 +8681,22 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B203" t="s">
         <v>9</v>
       </c>
       <c r="C203">
-        <v>248.02</v>
+        <v>149</v>
       </c>
       <c r="D203">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E203" t="s">
-        <v>535</v>
-      </c>
-      <c r="F203" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G203" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="H203" t="s">
         <v>12</v>
@@ -8770,25 +8704,25 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>537</v>
+        <v>601</v>
       </c>
       <c r="B204" t="s">
-        <v>9</v>
+        <v>602</v>
       </c>
       <c r="C204">
-        <v>290</v>
+        <v>820</v>
       </c>
       <c r="D204">
-        <v>200</v>
+        <v>655</v>
       </c>
       <c r="E204" t="s">
-        <v>538</v>
+        <v>603</v>
       </c>
       <c r="F204" t="s">
-        <v>539</v>
+        <v>604</v>
       </c>
       <c r="G204" t="s">
-        <v>508</v>
+        <v>605</v>
       </c>
       <c r="H204" t="s">
         <v>12</v>
@@ -8796,25 +8730,25 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>540</v>
+        <v>606</v>
       </c>
       <c r="B205" t="s">
-        <v>9</v>
+        <v>607</v>
       </c>
       <c r="C205">
-        <v>149</v>
+        <v>885</v>
       </c>
       <c r="D205">
-        <v>100</v>
+        <v>710</v>
       </c>
       <c r="E205" t="s">
-        <v>541</v>
+        <v>608</v>
       </c>
       <c r="F205" t="s">
-        <v>542</v>
+        <v>609</v>
       </c>
       <c r="G205" t="s">
-        <v>508</v>
+        <v>605</v>
       </c>
       <c r="H205" t="s">
         <v>12</v>
@@ -8822,22 +8756,25 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>543</v>
+        <v>610</v>
       </c>
       <c r="B206" t="s">
-        <v>9</v>
+        <v>611</v>
       </c>
       <c r="C206">
-        <v>149</v>
+        <v>350</v>
       </c>
       <c r="D206">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E206" t="s">
-        <v>544</v>
+        <v>612</v>
+      </c>
+      <c r="F206" t="s">
+        <v>613</v>
       </c>
       <c r="G206" t="s">
-        <v>508</v>
+        <v>605</v>
       </c>
       <c r="H206" t="s">
         <v>12</v>
@@ -8845,25 +8782,25 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B207" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C207">
-        <v>820</v>
+        <v>350</v>
       </c>
       <c r="D207">
-        <v>655</v>
+        <v>300</v>
       </c>
       <c r="E207" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="F207" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="G207" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="H207" t="s">
         <v>12</v>
@@ -8871,25 +8808,25 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B208" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C208">
-        <v>885</v>
+        <v>800</v>
       </c>
       <c r="D208">
-        <v>710</v>
+        <v>500</v>
       </c>
       <c r="E208" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F208" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="G208" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="H208" t="s">
         <v>12</v>
@@ -8897,25 +8834,25 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>620</v>
+        <v>699</v>
       </c>
       <c r="B209" t="s">
-        <v>621</v>
+        <v>700</v>
       </c>
       <c r="C209">
-        <v>350</v>
+        <v>298</v>
       </c>
       <c r="D209">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E209" t="s">
-        <v>622</v>
+        <v>701</v>
       </c>
       <c r="F209" t="s">
-        <v>623</v>
+        <v>702</v>
       </c>
       <c r="G209" t="s">
-        <v>615</v>
+        <v>600</v>
       </c>
       <c r="H209" t="s">
         <v>12</v>
@@ -8923,287 +8860,278 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>624</v>
+        <v>725</v>
       </c>
       <c r="B210" t="s">
-        <v>625</v>
+        <v>726</v>
       </c>
       <c r="C210">
-        <v>350</v>
-      </c>
-      <c r="D210">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="E210" t="s">
-        <v>626</v>
+        <v>738</v>
       </c>
       <c r="F210" t="s">
-        <v>627</v>
+        <v>729</v>
       </c>
       <c r="G210" t="s">
-        <v>615</v>
+        <v>728</v>
       </c>
       <c r="H210" t="s">
-        <v>12</v>
+        <v>727</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>628</v>
+        <v>769</v>
       </c>
       <c r="B211" t="s">
-        <v>629</v>
+        <v>731</v>
       </c>
       <c r="C211">
-        <v>800</v>
-      </c>
-      <c r="D211">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="E211" t="s">
-        <v>630</v>
+        <v>739</v>
       </c>
       <c r="F211" t="s">
-        <v>631</v>
+        <v>730</v>
       </c>
       <c r="G211" t="s">
-        <v>615</v>
+        <v>728</v>
       </c>
       <c r="H211" t="s">
-        <v>12</v>
+        <v>727</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>709</v>
+        <v>734</v>
       </c>
       <c r="B212" t="s">
-        <v>710</v>
+        <v>733</v>
       </c>
       <c r="C212">
-        <v>298</v>
-      </c>
-      <c r="D212">
         <v>200</v>
       </c>
       <c r="E212" t="s">
-        <v>711</v>
+        <v>740</v>
       </c>
       <c r="F212" t="s">
-        <v>712</v>
+        <v>732</v>
       </c>
       <c r="G212" t="s">
-        <v>610</v>
+        <v>728</v>
       </c>
       <c r="H212" t="s">
-        <v>12</v>
+        <v>727</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="B213" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="C213">
         <v>210</v>
       </c>
       <c r="E213" t="s">
-        <v>748</v>
+        <v>783</v>
       </c>
       <c r="F213" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="G213" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H213" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>779</v>
+        <v>725</v>
       </c>
       <c r="B214" t="s">
+        <v>726</v>
+      </c>
+      <c r="C214">
+        <v>210</v>
+      </c>
+      <c r="E214" t="s">
         <v>741</v>
       </c>
-      <c r="C214">
-        <v>230</v>
-      </c>
-      <c r="E214" t="s">
-        <v>749</v>
-      </c>
       <c r="F214" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="G214" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H214" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>744</v>
+        <v>769</v>
       </c>
       <c r="B215" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="C215">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="E215" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="F215" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G215" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H215" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>735</v>
+        <v>746</v>
       </c>
       <c r="B216" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="C216">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="E216" t="s">
-        <v>796</v>
+        <v>744</v>
       </c>
       <c r="F216" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G216" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H216" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
       <c r="B217" t="s">
-        <v>736</v>
+        <v>750</v>
       </c>
       <c r="C217">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="E217" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="F217" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G217" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H217" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>779</v>
+        <v>754</v>
       </c>
       <c r="B218" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="C218">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="E218" t="s">
         <v>752</v>
       </c>
       <c r="F218" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="G218" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H218" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>757</v>
+      </c>
+      <c r="B219" t="s">
+        <v>758</v>
+      </c>
+      <c r="C219">
+        <v>400</v>
+      </c>
+      <c r="E219" t="s">
         <v>756</v>
       </c>
-      <c r="B219" t="s">
+      <c r="F219" t="s">
         <v>755</v>
       </c>
-      <c r="C219">
-        <v>180</v>
-      </c>
-      <c r="E219" t="s">
-        <v>754</v>
-      </c>
-      <c r="F219" t="s">
-        <v>753</v>
-      </c>
       <c r="G219" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H219" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>761</v>
+      </c>
+      <c r="B220" t="s">
+        <v>762</v>
+      </c>
+      <c r="C220">
+        <v>200</v>
+      </c>
+      <c r="E220" t="s">
+        <v>760</v>
+      </c>
+      <c r="F220" t="s">
         <v>759</v>
       </c>
-      <c r="B220" t="s">
-        <v>760</v>
-      </c>
-      <c r="C220">
-        <v>180</v>
-      </c>
-      <c r="E220" t="s">
-        <v>758</v>
-      </c>
-      <c r="F220" t="s">
-        <v>757</v>
-      </c>
       <c r="G220" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H220" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>764</v>
+        <v>749</v>
       </c>
       <c r="B221" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="C221">
         <v>180</v>
       </c>
       <c r="E221" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="F221" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="G221" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H221" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
@@ -9214,7 +9142,7 @@
         <v>768</v>
       </c>
       <c r="C222">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E222" t="s">
         <v>766</v>
@@ -9223,194 +9151,194 @@
         <v>765</v>
       </c>
       <c r="G222" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H222" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B223" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C223">
         <v>200</v>
       </c>
       <c r="E223" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="F223" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="G223" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H223" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>759</v>
+        <v>777</v>
       </c>
       <c r="B224" t="s">
-        <v>760</v>
+        <v>776</v>
       </c>
       <c r="C224">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E224" t="s">
+        <v>775</v>
+      </c>
+      <c r="F224" t="s">
         <v>774</v>
       </c>
-      <c r="F224" t="s">
-        <v>773</v>
-      </c>
       <c r="G224" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H224" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B225" t="s">
+        <v>781</v>
+      </c>
+      <c r="C225">
+        <v>200</v>
+      </c>
+      <c r="E225" t="s">
+        <v>779</v>
+      </c>
+      <c r="F225" t="s">
         <v>778</v>
       </c>
-      <c r="C225">
-        <v>300</v>
-      </c>
-      <c r="E225" t="s">
-        <v>776</v>
-      </c>
-      <c r="F225" t="s">
-        <v>775</v>
-      </c>
       <c r="G225" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H225" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="B226" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C226">
         <v>200</v>
       </c>
       <c r="E226" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="F226" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="G226" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H226" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="B227" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C227">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E227" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="F227" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="G227" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="H227" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="B228" t="s">
+        <v>29</v>
+      </c>
+      <c r="C228">
+        <v>550</v>
+      </c>
+      <c r="E228" t="s">
+        <v>792</v>
+      </c>
+      <c r="F228" t="s">
         <v>791</v>
       </c>
-      <c r="C228">
-        <v>200</v>
-      </c>
-      <c r="E228" t="s">
-        <v>789</v>
-      </c>
-      <c r="F228" t="s">
-        <v>788</v>
-      </c>
       <c r="G228" t="s">
-        <v>738</v>
+        <v>600</v>
       </c>
       <c r="H228" t="s">
-        <v>737</v>
+        <v>721</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>797</v>
+      </c>
+      <c r="B229" t="s">
+        <v>796</v>
+      </c>
+      <c r="C229">
+        <v>500</v>
+      </c>
+      <c r="E229" t="s">
+        <v>795</v>
+      </c>
+      <c r="F229" t="s">
         <v>794</v>
       </c>
-      <c r="B229" t="s">
-        <v>795</v>
-      </c>
-      <c r="C229">
-        <v>250</v>
-      </c>
-      <c r="E229" t="s">
-        <v>793</v>
-      </c>
-      <c r="F229" t="s">
-        <v>792</v>
-      </c>
       <c r="G229" t="s">
-        <v>738</v>
+        <v>600</v>
       </c>
       <c r="H229" t="s">
-        <v>737</v>
+        <v>133</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>800</v>
+      </c>
+      <c r="B230" t="s">
+        <v>801</v>
+      </c>
+      <c r="C230">
+        <v>180</v>
+      </c>
+      <c r="E230" t="s">
         <v>799</v>
       </c>
-      <c r="B230" t="s">
-        <v>800</v>
-      </c>
-      <c r="C230">
-        <v>200</v>
-      </c>
-      <c r="E230" t="s">
+      <c r="F230" t="s">
         <v>798</v>
       </c>
-      <c r="F230" t="s">
-        <v>797</v>
-      </c>
       <c r="G230" t="s">
-        <v>738</v>
+        <v>600</v>
       </c>
       <c r="H230" t="s">
-        <v>737</v>
+        <v>86</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
@@ -9418,45 +9346,45 @@
         <v>804</v>
       </c>
       <c r="B231" t="s">
+        <v>229</v>
+      </c>
+      <c r="C231">
+        <v>100</v>
+      </c>
+      <c r="E231" t="s">
         <v>803</v>
       </c>
-      <c r="C231">
-        <v>200</v>
-      </c>
-      <c r="E231" t="s">
+      <c r="F231" t="s">
         <v>802</v>
       </c>
-      <c r="F231" t="s">
-        <v>801</v>
-      </c>
       <c r="G231" t="s">
-        <v>738</v>
+        <v>901</v>
       </c>
       <c r="H231" t="s">
-        <v>737</v>
+        <v>294</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>805</v>
+      </c>
+      <c r="B232" t="s">
+        <v>806</v>
+      </c>
+      <c r="C232">
+        <v>400</v>
+      </c>
+      <c r="E232" t="s">
+        <v>971</v>
+      </c>
+      <c r="F232" t="s">
         <v>807</v>
       </c>
-      <c r="B232" t="s">
-        <v>795</v>
-      </c>
-      <c r="C232">
-        <v>250</v>
-      </c>
-      <c r="E232" t="s">
-        <v>806</v>
-      </c>
-      <c r="F232" t="s">
-        <v>805</v>
-      </c>
       <c r="G232" t="s">
-        <v>738</v>
+        <v>901</v>
       </c>
       <c r="H232" t="s">
-        <v>737</v>
+        <v>294</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
@@ -9464,10 +9392,10 @@
         <v>810</v>
       </c>
       <c r="B233" t="s">
-        <v>29</v>
+        <v>811</v>
       </c>
       <c r="C233">
-        <v>550</v>
+        <v>150</v>
       </c>
       <c r="E233" t="s">
         <v>809</v>
@@ -9476,10 +9404,10 @@
         <v>808</v>
       </c>
       <c r="G233" t="s">
-        <v>610</v>
+        <v>901</v>
       </c>
       <c r="H233" t="s">
-        <v>731</v>
+        <v>294</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
@@ -9487,45 +9415,48 @@
         <v>814</v>
       </c>
       <c r="B234" t="s">
+        <v>815</v>
+      </c>
+      <c r="C234">
+        <v>130</v>
+      </c>
+      <c r="E234" t="s">
         <v>813</v>
       </c>
-      <c r="C234">
-        <v>500</v>
-      </c>
-      <c r="E234" t="s">
+      <c r="F234" t="s">
         <v>812</v>
       </c>
-      <c r="F234" t="s">
-        <v>811</v>
-      </c>
       <c r="G234" t="s">
-        <v>610</v>
+        <v>901</v>
       </c>
       <c r="H234" t="s">
-        <v>140</v>
+        <v>294</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
+        <v>816</v>
+      </c>
+      <c r="B235" t="s">
         <v>817</v>
       </c>
-      <c r="B235" t="s">
+      <c r="C235">
+        <v>250</v>
+      </c>
+      <c r="D235">
+        <v>200</v>
+      </c>
+      <c r="E235" t="s">
+        <v>819</v>
+      </c>
+      <c r="F235" t="s">
         <v>818</v>
       </c>
-      <c r="C235">
-        <v>180</v>
-      </c>
-      <c r="E235" t="s">
-        <v>816</v>
-      </c>
-      <c r="F235" t="s">
-        <v>815</v>
-      </c>
       <c r="G235" t="s">
-        <v>610</v>
+        <v>900</v>
       </c>
       <c r="H235" t="s">
-        <v>86</v>
+        <v>724</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
@@ -9533,304 +9464,316 @@
         <v>821</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>822</v>
       </c>
       <c r="C236">
-        <v>100</v>
+        <v>250</v>
+      </c>
+      <c r="D236">
+        <v>200</v>
       </c>
       <c r="E236" t="s">
+        <v>823</v>
+      </c>
+      <c r="F236" t="s">
         <v>820</v>
       </c>
-      <c r="F236" t="s">
-        <v>819</v>
-      </c>
       <c r="G236" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H236" t="s">
-        <v>304</v>
+        <v>724</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B237" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C237">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="E237" t="s">
-        <v>992</v>
+        <v>827</v>
       </c>
       <c r="F237" t="s">
         <v>824</v>
       </c>
       <c r="G237" t="s">
-        <v>922</v>
+        <v>1025</v>
       </c>
       <c r="H237" t="s">
-        <v>304</v>
+        <v>724</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B238" t="s">
+        <v>831</v>
+      </c>
+      <c r="C238">
+        <v>70</v>
+      </c>
+      <c r="E238" t="s">
+        <v>830</v>
+      </c>
+      <c r="F238" t="s">
         <v>828</v>
       </c>
-      <c r="C238">
-        <v>150</v>
-      </c>
-      <c r="E238" t="s">
-        <v>826</v>
-      </c>
-      <c r="F238" t="s">
-        <v>825</v>
-      </c>
       <c r="G238" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H238" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>831</v>
-      </c>
-      <c r="B239" t="s">
+        <v>834</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="C239">
+        <v>500</v>
+      </c>
+      <c r="D239">
+        <v>390</v>
+      </c>
+      <c r="E239" t="s">
+        <v>835</v>
+      </c>
+      <c r="F239" t="s">
         <v>832</v>
       </c>
-      <c r="C239">
-        <v>600</v>
-      </c>
-      <c r="E239" t="s">
-        <v>830</v>
-      </c>
-      <c r="F239" t="s">
-        <v>829</v>
-      </c>
       <c r="G239" t="s">
-        <v>610</v>
+        <v>901</v>
       </c>
       <c r="H239" t="s">
-        <v>731</v>
+        <v>294</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B240" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C240">
-        <v>130</v>
+        <v>200</v>
+      </c>
+      <c r="D240">
+        <v>150</v>
       </c>
       <c r="E240" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="F240" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="G240" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H240" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="B241" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="C241">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="D241">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E241" t="s">
+        <v>841</v>
+      </c>
+      <c r="F241" t="s">
         <v>840</v>
       </c>
-      <c r="F241" t="s">
-        <v>839</v>
-      </c>
       <c r="G241" t="s">
-        <v>921</v>
+        <v>901</v>
       </c>
       <c r="H241" t="s">
-        <v>734</v>
+        <v>294</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B242" t="s">
         <v>843</v>
       </c>
       <c r="C242">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="D242">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E242" t="s">
+        <v>845</v>
+      </c>
+      <c r="F242" t="s">
         <v>844</v>
       </c>
-      <c r="F242" t="s">
-        <v>841</v>
-      </c>
       <c r="G242" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H242" t="s">
-        <v>734</v>
+        <v>294</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B243" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C243">
-        <v>50</v>
+        <v>200</v>
+      </c>
+      <c r="D243">
+        <v>120</v>
       </c>
       <c r="E243" t="s">
         <v>848</v>
       </c>
       <c r="F243" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="G243" t="s">
-        <v>1046</v>
+        <v>901</v>
       </c>
       <c r="H243" t="s">
-        <v>734</v>
+        <v>294</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B244" t="s">
         <v>852</v>
       </c>
       <c r="C244">
-        <v>70</v>
+        <v>688</v>
+      </c>
+      <c r="D244">
+        <v>400</v>
       </c>
       <c r="E244" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="F244" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="G244" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H244" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>855</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>854</v>
+        <v>857</v>
+      </c>
+      <c r="B245" t="s">
+        <v>858</v>
       </c>
       <c r="C245">
-        <v>500</v>
-      </c>
-      <c r="D245">
-        <v>390</v>
+        <v>240</v>
       </c>
       <c r="E245" t="s">
         <v>856</v>
       </c>
       <c r="F245" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="G245" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H245" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>857</v>
+        <v>875</v>
       </c>
       <c r="B246" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="C246">
-        <v>200</v>
+        <v>698</v>
       </c>
       <c r="D246">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E246" t="s">
+        <v>860</v>
+      </c>
+      <c r="F246" t="s">
         <v>859</v>
       </c>
-      <c r="F246" t="s">
-        <v>860</v>
-      </c>
       <c r="G246" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H246" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>861</v>
+      </c>
+      <c r="B247" t="s">
+        <v>862</v>
+      </c>
+      <c r="C247">
+        <v>120</v>
+      </c>
+      <c r="D247">
+        <v>80</v>
+      </c>
+      <c r="E247" t="s">
+        <v>864</v>
+      </c>
+      <c r="F247" t="s">
         <v>863</v>
       </c>
-      <c r="B247" t="s">
-        <v>864</v>
-      </c>
-      <c r="C247">
-        <v>170</v>
-      </c>
-      <c r="D247">
-        <v>120</v>
-      </c>
-      <c r="E247" t="s">
-        <v>862</v>
-      </c>
-      <c r="F247" t="s">
-        <v>861</v>
-      </c>
       <c r="G247" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H247" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>868</v>
+      </c>
+      <c r="B248" t="s">
         <v>867</v>
       </c>
-      <c r="B248" t="s">
-        <v>864</v>
-      </c>
       <c r="C248">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="D248">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E248" t="s">
         <v>866</v>
@@ -9839,10 +9782,10 @@
         <v>865</v>
       </c>
       <c r="G248" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H248" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
@@ -9850,126 +9793,126 @@
         <v>871</v>
       </c>
       <c r="B249" t="s">
+        <v>872</v>
+      </c>
+      <c r="C249">
+        <v>250</v>
+      </c>
+      <c r="D249">
+        <v>200</v>
+      </c>
+      <c r="E249" t="s">
         <v>870</v>
       </c>
-      <c r="C249">
-        <v>200</v>
-      </c>
-      <c r="D249">
-        <v>120</v>
-      </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
         <v>869</v>
       </c>
-      <c r="F249" t="s">
-        <v>868</v>
-      </c>
       <c r="G249" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H249" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B250" t="s">
+        <v>876</v>
+      </c>
+      <c r="C250">
+        <v>300</v>
+      </c>
+      <c r="E250" t="s">
+        <v>874</v>
+      </c>
+      <c r="F250" t="s">
         <v>873</v>
       </c>
-      <c r="C250">
-        <v>688</v>
-      </c>
-      <c r="D250">
-        <v>400</v>
-      </c>
-      <c r="E250" t="s">
-        <v>875</v>
-      </c>
-      <c r="F250" t="s">
-        <v>874</v>
-      </c>
       <c r="G250" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H250" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B251" t="s">
+        <v>881</v>
+      </c>
+      <c r="C251">
+        <v>150</v>
+      </c>
+      <c r="D251">
+        <v>100</v>
+      </c>
+      <c r="E251" t="s">
+        <v>882</v>
+      </c>
+      <c r="F251" t="s">
         <v>879</v>
       </c>
-      <c r="C251">
-        <v>240</v>
-      </c>
-      <c r="E251" t="s">
-        <v>877</v>
-      </c>
-      <c r="F251" t="s">
-        <v>876</v>
-      </c>
       <c r="G251" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H251" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>896</v>
+        <v>885</v>
       </c>
       <c r="B252" t="s">
-        <v>899</v>
+        <v>1079</v>
       </c>
       <c r="C252">
-        <v>698</v>
+        <v>300</v>
       </c>
       <c r="D252">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="E252" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="F252" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="G252" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H252" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="B253" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="C253">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="D253">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E253" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F253" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="G253" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H253" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
@@ -9977,134 +9920,137 @@
         <v>889</v>
       </c>
       <c r="B254" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C254">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D254">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E254" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="F254" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="G254" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H254" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B255" t="s">
+        <v>895</v>
+      </c>
+      <c r="C255">
+        <v>150</v>
+      </c>
+      <c r="D255">
+        <v>100</v>
+      </c>
+      <c r="E255" t="s">
+        <v>894</v>
+      </c>
+      <c r="F255" t="s">
         <v>893</v>
       </c>
-      <c r="C255">
-        <v>250</v>
-      </c>
-      <c r="D255">
-        <v>200</v>
-      </c>
-      <c r="E255" t="s">
-        <v>891</v>
-      </c>
-      <c r="F255" t="s">
-        <v>890</v>
-      </c>
       <c r="G255" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H255" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
+        <v>899</v>
+      </c>
+      <c r="B256" t="s">
+        <v>898</v>
+      </c>
+      <c r="C256">
+        <v>200</v>
+      </c>
+      <c r="D256">
+        <v>150</v>
+      </c>
+      <c r="E256" t="s">
+        <v>897</v>
+      </c>
+      <c r="F256" t="s">
         <v>896</v>
       </c>
-      <c r="B256" t="s">
-        <v>897</v>
-      </c>
-      <c r="C256">
-        <v>300</v>
-      </c>
-      <c r="E256" t="s">
-        <v>895</v>
-      </c>
-      <c r="F256" t="s">
-        <v>894</v>
-      </c>
       <c r="G256" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H256" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
+        <v>907</v>
+      </c>
+      <c r="B257" t="s">
+        <v>908</v>
+      </c>
+      <c r="C257">
+        <v>445</v>
+      </c>
+      <c r="D257">
+        <v>300</v>
+      </c>
+      <c r="E257" t="s">
+        <v>910</v>
+      </c>
+      <c r="F257" t="s">
+        <v>909</v>
+      </c>
+      <c r="G257" t="s">
         <v>901</v>
       </c>
-      <c r="B257" t="s">
-        <v>902</v>
-      </c>
-      <c r="C257">
-        <v>150</v>
-      </c>
-      <c r="D257">
-        <v>100</v>
-      </c>
-      <c r="E257" t="s">
-        <v>903</v>
-      </c>
-      <c r="F257" t="s">
-        <v>900</v>
-      </c>
-      <c r="G257" t="s">
-        <v>922</v>
-      </c>
       <c r="H257" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="B258" t="s">
-        <v>1100</v>
+        <v>914</v>
       </c>
       <c r="C258">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="D258">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E258" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="F258" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="G258" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H258" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="B259" t="s">
-        <v>909</v>
+        <v>918</v>
       </c>
       <c r="C259">
         <v>150</v>
@@ -10113,94 +10059,91 @@
         <v>100</v>
       </c>
       <c r="E259" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="F259" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="G259" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H259" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="B260" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="C260">
+        <v>210</v>
+      </c>
+      <c r="D260">
         <v>150</v>
       </c>
-      <c r="D260">
-        <v>100</v>
-      </c>
       <c r="E260" t="s">
-        <v>911</v>
+        <v>922</v>
       </c>
       <c r="F260" t="s">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="G260" t="s">
-        <v>922</v>
+        <v>600</v>
       </c>
       <c r="H260" t="s">
-        <v>304</v>
+        <v>86</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>910</v>
+        <v>925</v>
       </c>
       <c r="B261" t="s">
-        <v>916</v>
+        <v>926</v>
       </c>
       <c r="C261">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="D261">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="E261" t="s">
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="F261" t="s">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="G261" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H261" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="B262" t="s">
-        <v>919</v>
+        <v>18</v>
       </c>
       <c r="C262">
-        <v>200</v>
-      </c>
-      <c r="D262">
         <v>150</v>
       </c>
       <c r="E262" t="s">
-        <v>918</v>
+        <v>933</v>
       </c>
       <c r="F262" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
       <c r="G262" t="s">
-        <v>922</v>
+        <v>600</v>
       </c>
       <c r="H262" t="s">
-        <v>304</v>
+        <v>721</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
@@ -10211,10 +10154,10 @@
         <v>929</v>
       </c>
       <c r="C263">
-        <v>445</v>
+        <v>350</v>
       </c>
       <c r="D263">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E263" t="s">
         <v>931</v>
@@ -10223,62 +10166,59 @@
         <v>930</v>
       </c>
       <c r="G263" t="s">
-        <v>922</v>
+        <v>600</v>
       </c>
       <c r="H263" t="s">
-        <v>304</v>
+        <v>12</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>935</v>
+      </c>
+      <c r="B264" t="s">
+        <v>18</v>
+      </c>
+      <c r="C264">
+        <v>200</v>
+      </c>
+      <c r="D264">
+        <v>150</v>
+      </c>
+      <c r="E264" t="s">
+        <v>936</v>
+      </c>
+      <c r="F264" t="s">
         <v>934</v>
       </c>
-      <c r="B264" t="s">
-        <v>935</v>
-      </c>
-      <c r="C264">
-        <v>150</v>
-      </c>
-      <c r="D264">
-        <v>100</v>
-      </c>
-      <c r="E264" t="s">
-        <v>933</v>
-      </c>
-      <c r="F264" t="s">
-        <v>932</v>
-      </c>
       <c r="G264" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H264" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B265" t="s">
-        <v>939</v>
+        <v>29</v>
       </c>
       <c r="C265">
         <v>150</v>
       </c>
-      <c r="D265">
-        <v>100</v>
-      </c>
       <c r="E265" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="F265" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="G265" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H265" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
@@ -10286,137 +10226,128 @@
         <v>940</v>
       </c>
       <c r="B266" t="s">
+        <v>29</v>
+      </c>
+      <c r="C266">
+        <v>200</v>
+      </c>
+      <c r="E266" t="s">
+        <v>942</v>
+      </c>
+      <c r="F266" t="s">
         <v>941</v>
       </c>
-      <c r="C266">
-        <v>210</v>
-      </c>
-      <c r="D266">
-        <v>150</v>
-      </c>
-      <c r="E266" t="s">
-        <v>943</v>
-      </c>
-      <c r="F266" t="s">
-        <v>942</v>
-      </c>
       <c r="G266" t="s">
-        <v>610</v>
+        <v>901</v>
       </c>
       <c r="H266" t="s">
-        <v>86</v>
+        <v>294</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>945</v>
+      </c>
+      <c r="B267" t="s">
         <v>946</v>
       </c>
-      <c r="B267" t="s">
-        <v>947</v>
-      </c>
       <c r="C267">
-        <v>250</v>
-      </c>
-      <c r="D267">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="E267" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="F267" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G267" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H267" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>949</v>
+      </c>
+      <c r="B268" t="s">
+        <v>950</v>
+      </c>
+      <c r="C268">
+        <v>50</v>
+      </c>
+      <c r="E268" t="s">
         <v>948</v>
       </c>
-      <c r="B268" t="s">
-        <v>18</v>
-      </c>
-      <c r="C268">
-        <v>150</v>
-      </c>
-      <c r="E268" t="s">
-        <v>954</v>
-      </c>
       <c r="F268" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="G268" t="s">
-        <v>610</v>
+        <v>901</v>
       </c>
       <c r="H268" t="s">
-        <v>731</v>
+        <v>294</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B269" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="C269">
-        <v>350</v>
-      </c>
-      <c r="D269">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E269" t="s">
+        <v>951</v>
+      </c>
+      <c r="F269" t="s">
         <v>952</v>
       </c>
-      <c r="F269" t="s">
-        <v>951</v>
-      </c>
       <c r="G269" t="s">
-        <v>610</v>
+        <v>901</v>
       </c>
       <c r="H269" t="s">
-        <v>12</v>
+        <v>294</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
+        <v>955</v>
+      </c>
+      <c r="B270" t="s">
         <v>956</v>
       </c>
-      <c r="B270" t="s">
-        <v>18</v>
-      </c>
       <c r="C270">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D270">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E270" t="s">
         <v>957</v>
       </c>
       <c r="F270" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="G270" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H270" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="B271" t="s">
-        <v>29</v>
+        <v>961</v>
       </c>
       <c r="C271">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="E271" t="s">
         <v>960</v>
@@ -10425,324 +10356,324 @@
         <v>959</v>
       </c>
       <c r="G271" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H271" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="B272" t="s">
-        <v>29</v>
+        <v>963</v>
       </c>
       <c r="C272">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E272" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="F272" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="G272" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H272" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="B273" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C273">
         <v>150</v>
       </c>
+      <c r="D273">
+        <v>100</v>
+      </c>
       <c r="E273" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="F273" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="G273" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H273" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="B274" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="C274">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E274" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="F274" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="G274" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H274" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="B275" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="C275">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E275" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="F275" t="s">
-        <v>973</v>
+        <v>978</v>
       </c>
       <c r="G275" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H275" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="B276" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="C276">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D276">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E276" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="F276" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="G276" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H276" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="B277" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="C277">
-        <v>50</v>
+        <v>180</v>
+      </c>
+      <c r="D277">
+        <v>120</v>
       </c>
       <c r="E277" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="F277" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="G277" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H277" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
       <c r="B278" t="s">
-        <v>984</v>
+        <v>996</v>
       </c>
       <c r="C278">
-        <v>50</v>
+        <v>300</v>
+      </c>
+      <c r="D278">
+        <v>200</v>
       </c>
       <c r="E278" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="F278" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="G278" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H278" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>990</v>
+        <v>1001</v>
       </c>
       <c r="B279" t="s">
-        <v>989</v>
+        <v>1000</v>
       </c>
       <c r="C279">
         <v>150</v>
       </c>
-      <c r="D279">
-        <v>100</v>
-      </c>
       <c r="E279" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="F279" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="G279" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H279" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="B280" t="s">
-        <v>998</v>
+        <v>1003</v>
       </c>
       <c r="C280">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E280" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="F280" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="G280" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H280" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="B281" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="C281">
-        <v>200</v>
+        <v>100</v>
+      </c>
+      <c r="D281">
+        <v>80</v>
       </c>
       <c r="E281" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="F281" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="G281" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H281" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>1003</v>
+        <v>1016</v>
       </c>
       <c r="B282" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="C282">
-        <v>198</v>
-      </c>
-      <c r="D282">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E282" t="s">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="F282" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
       <c r="G282" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H282" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="B283" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="C283">
-        <v>180</v>
-      </c>
-      <c r="D283">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="E283" t="s">
-        <v>1008</v>
+        <v>1013</v>
       </c>
       <c r="F283" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="G283" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H283" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B284" t="s">
         <v>1018</v>
       </c>
-      <c r="B284" t="s">
-        <v>1017</v>
-      </c>
       <c r="C284">
-        <v>300</v>
-      </c>
-      <c r="D284">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E284" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="F284" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="G284" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="H284" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
@@ -10753,19 +10684,22 @@
         <v>1021</v>
       </c>
       <c r="C285">
+        <v>200</v>
+      </c>
+      <c r="D285">
         <v>150</v>
       </c>
       <c r="E285" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="F285" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="G285" t="s">
-        <v>922</v>
+        <v>600</v>
       </c>
       <c r="H285" t="s">
-        <v>304</v>
+        <v>721</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
@@ -10773,22 +10707,25 @@
         <v>1026</v>
       </c>
       <c r="B286" t="s">
-        <v>1024</v>
+        <v>1003</v>
       </c>
       <c r="C286">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="D286">
+        <v>80</v>
       </c>
       <c r="E286" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F286" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G286" t="s">
         <v>1025</v>
       </c>
-      <c r="F286" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G286" t="s">
-        <v>922</v>
-      </c>
       <c r="H286" t="s">
-        <v>304</v>
+        <v>721</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
@@ -10799,79 +10736,82 @@
         <v>1030</v>
       </c>
       <c r="C287">
-        <v>100</v>
-      </c>
-      <c r="D287">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="E287" t="s">
-        <v>1027</v>
+        <v>1032</v>
       </c>
       <c r="F287" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="G287" t="s">
-        <v>922</v>
+        <v>1025</v>
       </c>
       <c r="H287" t="s">
-        <v>304</v>
+        <v>905</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B288" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C288">
+        <v>200</v>
+      </c>
+      <c r="E288" t="s">
         <v>1033</v>
       </c>
-      <c r="C288">
-        <v>150</v>
-      </c>
-      <c r="E288" t="s">
-        <v>1032</v>
-      </c>
       <c r="F288" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="G288" t="s">
-        <v>922</v>
+        <v>1025</v>
       </c>
       <c r="H288" t="s">
-        <v>304</v>
+        <v>905</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B289" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C289">
+        <v>399</v>
+      </c>
+      <c r="D289">
+        <v>250</v>
+      </c>
+      <c r="E289" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F289" t="s">
         <v>1037</v>
       </c>
-      <c r="B289" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C289">
-        <v>300</v>
-      </c>
-      <c r="E289" t="s">
-        <v>1034</v>
-      </c>
-      <c r="F289" t="s">
-        <v>1035</v>
-      </c>
       <c r="G289" t="s">
-        <v>922</v>
+        <v>1025</v>
       </c>
       <c r="H289" t="s">
-        <v>304</v>
+        <v>905</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1038</v>
+        <v>1043</v>
       </c>
       <c r="B290" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C290">
-        <v>50</v>
+        <v>300</v>
+      </c>
+      <c r="D290">
+        <v>200</v>
       </c>
       <c r="E290" t="s">
         <v>1041</v>
@@ -10880,25 +10820,22 @@
         <v>1040</v>
       </c>
       <c r="G290" t="s">
-        <v>922</v>
+        <v>1025</v>
       </c>
       <c r="H290" t="s">
-        <v>304</v>
+        <v>905</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="B291" t="s">
-        <v>1042</v>
+        <v>18</v>
       </c>
       <c r="C291">
         <v>200</v>
       </c>
-      <c r="D291">
-        <v>150</v>
-      </c>
       <c r="E291" t="s">
         <v>1045</v>
       </c>
@@ -10906,36 +10843,33 @@
         <v>1044</v>
       </c>
       <c r="G291" t="s">
-        <v>610</v>
+        <v>1025</v>
       </c>
       <c r="H291" t="s">
-        <v>731</v>
+        <v>905</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B292" t="s">
+        <v>18</v>
+      </c>
+      <c r="C292">
+        <v>200</v>
+      </c>
+      <c r="E292" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F292" t="s">
         <v>1047</v>
       </c>
-      <c r="B292" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C292">
-        <v>100</v>
-      </c>
-      <c r="D292">
-        <v>80</v>
-      </c>
-      <c r="E292" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F292" t="s">
-        <v>1048</v>
-      </c>
       <c r="G292" t="s">
-        <v>1046</v>
+        <v>1025</v>
       </c>
       <c r="H292" t="s">
-        <v>731</v>
+        <v>905</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
@@ -10946,7 +10880,7 @@
         <v>1051</v>
       </c>
       <c r="C293">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E293" t="s">
         <v>1053</v>
@@ -10955,113 +10889,107 @@
         <v>1052</v>
       </c>
       <c r="G293" t="s">
-        <v>1046</v>
+        <v>1025</v>
       </c>
       <c r="H293" t="s">
-        <v>926</v>
+        <v>721</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B294" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C294">
+        <v>100</v>
+      </c>
+      <c r="E294" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F294" t="s">
         <v>1056</v>
       </c>
-      <c r="B294" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C294">
-        <v>200</v>
-      </c>
-      <c r="E294" t="s">
-        <v>1054</v>
-      </c>
-      <c r="F294" t="s">
-        <v>1055</v>
-      </c>
       <c r="G294" t="s">
-        <v>1046</v>
+        <v>1025</v>
       </c>
       <c r="H294" t="s">
-        <v>926</v>
+        <v>905</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="B295" t="s">
-        <v>1060</v>
+        <v>18</v>
       </c>
       <c r="C295">
-        <v>399</v>
-      </c>
-      <c r="D295">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E295" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F295" t="s">
         <v>1059</v>
       </c>
-      <c r="F295" t="s">
-        <v>1058</v>
-      </c>
       <c r="G295" t="s">
-        <v>1046</v>
+        <v>1025</v>
       </c>
       <c r="H295" t="s">
-        <v>926</v>
+        <v>905</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B296" t="s">
+        <v>18</v>
+      </c>
+      <c r="C296">
+        <v>250</v>
+      </c>
+      <c r="E296" t="s">
         <v>1063</v>
       </c>
-      <c r="C296">
-        <v>300</v>
-      </c>
-      <c r="D296">
-        <v>200</v>
-      </c>
-      <c r="E296" t="s">
+      <c r="F296" t="s">
         <v>1062</v>
       </c>
-      <c r="F296" t="s">
-        <v>1061</v>
-      </c>
       <c r="G296" t="s">
-        <v>1046</v>
+        <v>1025</v>
       </c>
       <c r="H296" t="s">
-        <v>926</v>
+        <v>905</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B297" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C297">
+        <v>120</v>
+      </c>
+      <c r="E297" t="s">
         <v>1067</v>
       </c>
-      <c r="B297" t="s">
-        <v>18</v>
-      </c>
-      <c r="C297">
-        <v>200</v>
-      </c>
-      <c r="E297" t="s">
+      <c r="F297" t="s">
         <v>1066</v>
       </c>
-      <c r="F297" t="s">
-        <v>1065</v>
-      </c>
       <c r="G297" t="s">
-        <v>1046</v>
+        <v>1025</v>
       </c>
       <c r="H297" t="s">
-        <v>926</v>
+        <v>905</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B298" t="s">
         <v>18</v>
@@ -11073,64 +11001,67 @@
         <v>1069</v>
       </c>
       <c r="F298" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G298" t="s">
-        <v>1046</v>
+        <v>1025</v>
       </c>
       <c r="H298" t="s">
-        <v>926</v>
+        <v>905</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B299" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C299">
+        <v>100</v>
+      </c>
+      <c r="D299">
+        <v>60</v>
+      </c>
+      <c r="E299" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F299" t="s">
         <v>1071</v>
       </c>
-      <c r="B299" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C299">
-        <v>50</v>
-      </c>
-      <c r="E299" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F299" t="s">
-        <v>1073</v>
-      </c>
       <c r="G299" t="s">
-        <v>1046</v>
+        <v>1025</v>
       </c>
       <c r="H299" t="s">
-        <v>731</v>
+        <v>905</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="B300" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="C300">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E300" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="F300" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="G300" t="s">
-        <v>1046</v>
+        <v>1025</v>
       </c>
       <c r="H300" t="s">
-        <v>926</v>
+        <v>133</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="B301" t="s">
         <v>18</v>
@@ -11139,180 +11070,39 @@
         <v>150</v>
       </c>
       <c r="E301" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F301" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G301" t="s">
-        <v>1046</v>
+        <v>1025</v>
       </c>
       <c r="H301" t="s">
-        <v>926</v>
+        <v>905</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="B302" t="s">
         <v>18</v>
       </c>
       <c r="C302">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="E302" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F302" t="s">
         <v>1084</v>
       </c>
-      <c r="F302" t="s">
-        <v>1083</v>
-      </c>
       <c r="G302" t="s">
-        <v>1046</v>
+        <v>1025</v>
       </c>
       <c r="H302" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B303" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C303">
-        <v>120</v>
-      </c>
-      <c r="E303" t="s">
-        <v>1088</v>
-      </c>
-      <c r="F303" t="s">
-        <v>1087</v>
-      </c>
-      <c r="G303" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H303" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B304" t="s">
-        <v>18</v>
-      </c>
-      <c r="C304">
-        <v>200</v>
-      </c>
-      <c r="E304" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F304" t="s">
-        <v>1091</v>
-      </c>
-      <c r="G304" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H304" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B305" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C305">
-        <v>100</v>
-      </c>
-      <c r="D305">
-        <v>60</v>
-      </c>
-      <c r="E305" t="s">
-        <v>1093</v>
-      </c>
-      <c r="F305" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G305" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H305" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>1101</v>
-      </c>
-      <c r="B306" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C306">
-        <v>50</v>
-      </c>
-      <c r="E306" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F306" t="s">
-        <v>1102</v>
-      </c>
-      <c r="G306" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H306" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>1097</v>
-      </c>
-      <c r="B307" t="s">
-        <v>18</v>
-      </c>
-      <c r="C307">
-        <v>150</v>
-      </c>
-      <c r="E307" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F307" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G307" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H307" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>1107</v>
-      </c>
-      <c r="B308" t="s">
-        <v>18</v>
-      </c>
-      <c r="C308">
-        <v>100</v>
-      </c>
-      <c r="E308" t="s">
-        <v>1106</v>
-      </c>
-      <c r="F308" t="s">
-        <v>1105</v>
-      </c>
-      <c r="G308" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H308" t="s">
-        <v>926</v>
+        <v>905</v>
       </c>
     </row>
   </sheetData>

--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="1145">
   <si>
     <t>Nombre</t>
   </si>
@@ -3286,6 +3286,180 @@
   </si>
   <si>
     <t>Conjunto de Collar con Colgante de Lágrima de Cristal y Aretes</t>
+  </si>
+  <si>
+    <t>Zapatos Casuales Versátiles De Moda Con Patrón De Cocodrilo</t>
+  </si>
+  <si>
+    <t>Color: Beige, Talla: 29.5</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-1585296499-zapatos-casuales-versatiles-de-moda-con-patron-de-cocodrilo-_JM?quantity=1&amp;variation_id=179412877537</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_730419-CBT103500748521_012026-F-zapatos-casuales-versatiles-de-moda-con-patron-de-cocodrilo.webp;https://http2.mlstatic.com/D_NQ_NP_2X_996108-CBT103497713925_012026-F-zapatos-casuales-versatiles-de-moda-con-patron-de-cocodrilo.webp;https://http2.mlstatic.com/D_NQ_NP_2X_683363-CBT102983612396_012026-F-zapatos-casuales-versatiles-de-moda-con-patron-de-cocodrilo.webp</t>
+  </si>
+  <si>
+    <t>Zapato Hombre Tenis Casal Plataforma Moda Transpirable Sport</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-1863972705-zapato-hombre-tenis-casal-plataforma-moda-transpirable-sport-_JM?quantity=1&amp;variation_id=177138143622</t>
+  </si>
+  <si>
+    <t>Color: Gris, Talla: 23.5</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_936628-CBT106943681987_022026-F-zapato-hombre-tenis-casal-plataforma-moda-transpirable-sport.webp;https://http2.mlstatic.com/D_NQ_NP_2X_688210-CBT104197322259_012026-F-zapato-hombre-tenis-casal-plataforma-moda-transpirable-sport.webp;https://http2.mlstatic.com/D_NQ_NP_2X_820243-CBT74914869169_032024-F-zapato-hombre-tenis-casal-plataforma-moda-transpirable-sport.webp</t>
+  </si>
+  <si>
+    <t>Color: Caqui, Talla: 26</t>
+  </si>
+  <si>
+    <t>Botas Tacticas Hombre Zapatos De Trabajo Casual Outdoor 588</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-1907810375-botas-tacticas-hombre-zapatos-de-trabajo-casual-outdoor-588-_JM?quantity=1&amp;variation_id=178019331588</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_722244-CBT105692274218_012026-F-botas-tacticas-hombre-zapatos-de-trabajo-casual-outdoor-588.webp;https://http2.mlstatic.com/D_NQ_NP_2X_817878-CBT81532198186_012025-F-botas-tacticas-hombre-zapatos-de-trabajo-casual-outdoor-588.webp;https://http2.mlstatic.com/D_NQ_NP_2X_963367-CBT105692452258_012026-F-botas-tacticas-hombre-zapatos-de-trabajo-casual-outdoor-588.webp</t>
+  </si>
+  <si>
+    <t>Negro Talla: 25</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-1391870088-botas-de-seguridad-industrial-trabajo-casquillo-aislamiento-_JM?quantity=1&amp;variation_id=174304565690</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_952510-CBT76527863055_052024-F-botas-de-seguridad-industrial-trabajo-casquillo-aislamiento.webp;https://http2.mlstatic.com/D_NQ_NP_2X_735652-CBT93046766673_092025-F-botas-de-seguridad-industrial-trabajo-casquillo-aislamiento.webp;https://http2.mlstatic.com/D_NQ_NP_2X_931407-CBT49361572113_032022-F-botas-de-seguridad-industrial-trabajo-casquillo-aislamiento.webp</t>
+  </si>
+  <si>
+    <t>Botas De Seguridad Industrial Trabajo Casquillo Aislamiento</t>
+  </si>
+  <si>
+    <t>Botas Casquillo Hombre, Botas De Seguridad Laboral Cómodas</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-1399770488-botas-casquillo-hombre-botas-de-seguridad-laboral-comodas-_JM?quantity=1&amp;variation_id=180999225836</t>
+  </si>
+  <si>
+    <t>Color: Verde oscuro Talla: 29.5</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_650135-CBT77371017482_072024-F-botas-casquillo-hombre-botas-de-seguridad-laboral-comodas.webp;https://http2.mlstatic.com/D_NQ_NP_2X_719875-CBT77371017326_072024-F-botas-casquillo-hombre-botas-de-seguridad-laboral-comodas.webp;https://http2.mlstatic.com/D_NQ_NP_2X_824985-CBT77586643241_072024-F-botas-casquillo-hombre-botas-de-seguridad-laboral-comodas.webp</t>
+  </si>
+  <si>
+    <t>Color: Negro Talla: 31</t>
+  </si>
+  <si>
+    <t>Botas Tácticas Militares Para Exteriores Para Hombre</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-1736189418-botas-tacticas-militares-para-exteriores-para-hombre-_JM?quantity=1&amp;variation_id=176248942451</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_708527-CBT54910132787_042023-F-botas-tacticas-militares-para-exteriores-para-hombre.webp;https://http2.mlstatic.com/D_NQ_NP_2X_977035-CBT54910134985_042023-F-botas-tacticas-militares-para-exteriores-para-hombre.webp;https://http2.mlstatic.com/D_NQ_NP_2X_978862-CBT54910125531_042023-F-botas-tacticas-militares-para-exteriores-para-hombre.webp</t>
+  </si>
+  <si>
+    <t>Color: Negro Talla: 26</t>
+  </si>
+  <si>
+    <t>Bota De Seguridad Industrial Casquillo Trabajo Moda Anbaili</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-2345998809-bota-de-seguridad-industrial-casquillo-trabajo-moda-anbaili-_JM?quantity=1&amp;variation_id=183949487610</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_810360-CBT99999995999_112025-F-bota-de-seguridad-industrial-casquillo-trabajo-moda-anbaili.webp;https://http2.mlstatic.com/D_NQ_NP_2X_960862-CBT99516025326_112025-F-bota-de-seguridad-industrial-casquillo-trabajo-moda-anbaili.webp</t>
+  </si>
+  <si>
+    <t>Tenis De Seguridad Industrial Zapatos Mujer Hombre Pugood</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-3325324470-tenis-de-seguridad-industrial-zapatos-mujer-hombre-pugood-_JM?quantity=1&amp;variation_id=181446523738</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_828567-CBT93494609292_102025-F-tenis-de-seguridad-industrial-zapatos-mujer-hombre-pugood.webp;https://http2.mlstatic.com/D_NQ_NP_2X_678720-CBT78985742993_092024-F-tenis-de-seguridad-industrial-zapatos-mujer-hombre-pugood.webp;https://http2.mlstatic.com/D_NQ_NP_2X_909663-CBT78985909479_092024-F-tenis-de-seguridad-industrial-zapatos-mujer-hombre-pugood.webp</t>
+  </si>
+  <si>
+    <t>Color: Negro Talla: 25</t>
+  </si>
+  <si>
+    <t>Tenis De Seguridad Industrial Zapatos Cómodo Transpirable</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-3480729512-tenis-de-seguridad-industrial-zapatos-comodo-transpirable-_JM?quantity=1&amp;variation_id=186205261537</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_703874-CBT80747477078_112024-F-tenis-de-seguridad-industrial-zapatos-comodo-transpirable.webp;https://http2.mlstatic.com/D_NQ_NP_2X_672386-CBT80747477076_112024-F-tenis-de-seguridad-industrial-zapatos-comodo-transpirable.webp;https://http2.mlstatic.com/D_NQ_NP_2X_820311-CBT80747477074_112024-F-tenis-de-seguridad-industrial-zapatos-comodo-transpirable.webp</t>
+  </si>
+  <si>
+    <t>Regalos De Cumpleaños Para Mujeres, Cesta De Regalo Relajant Rojo</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/regalos-de-cumpleanos-para-mujeres-cesta-de-regalo-relajant/up/MLMU3473451389?pdp_filters=item_id:MLM2490113661#&amp;gid=1&amp;pid=1</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_842536-MLM106725939723_022026-F.webp</t>
+  </si>
+  <si>
+    <t>Ventiladores De Techo</t>
+  </si>
+  <si>
+    <t>Descripción: Cantidad De Aspas 6 Estructura Blanco Aspas Blanco Diámetro 52 Cm Frecuencia 60hz Material De Las Aspas Plástico</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/cozylady-lampara-de-ventilador-led-48w-e26-205-ventiladores-de-techo-cantidad-de-aspas-6-estructura-blanco-aspas-blanco-diametro-52-cm-frecuencia-60hz-material-de-las-aspas-plastico/p/MLM54407252?pdp_filters=item_id:MLM2430884049</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_711430-MLA100058619227_122025-F.webp</t>
+  </si>
+  <si>
+    <t>Audífonos Bluetooth Mini Corazón Audífonos</t>
+  </si>
+  <si>
+    <t>Descripción: Bluetooth Audífonos Cancelación Ruido</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/trymiss-k520-audifonos-bluetooth-mini-corazon-audifonos-con-microfono-audifonos-para-el-gym-manos-libres-audifonos-gamer-bluetooth-audifonos-cancelacion-ruido-14-de-febrero-regalos-para-mujer/p/MLM45453811?pdp_filters=item_id:MLM3532166646</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_827140-MLA105524534674_012026-F.webp</t>
+  </si>
+  <si>
+    <t>Pulsera De Tenis Ajustable Con Cristal Para Hombre Mujer</t>
+  </si>
+  <si>
+    <t>Largo: 19 cm, Material principal: Aleación.</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/sumlin-pulsera-de-tenis-ajustable-con-cristal-para-hombre-mujer-pulsera-de-pareja-plata-19-cm-regalos-de-san-valentin-incluye-una-hermosa-caja-de-regalo/p/MLM65215922?pdp_filters=item_id:MLM2728909083</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_840204-MLA106485769181_022026-F.webp</t>
+  </si>
+  <si>
+    <t>Marca:  Cowin</t>
+  </si>
+  <si>
+    <t>Auriculares híbridos With Ruido Activa Cancelación</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/auriculares-hibridos-cowin-e11a-with-ruido-activa-cancelacion/p/MLM65118526?pdp_filters=item_id:MLM4731897778</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_951489-MLA106257537077_012026-F.webp</t>
+  </si>
+  <si>
+    <t>Color: TK902-DY, Diseño: Sólido, Tamaño del casco: L</t>
+  </si>
+  <si>
+    <t>Casco De Moto Con Visera Abatible Y Plegable Certificado Dot</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-3853286468-casco-de-moto-con-visera-abatible-y-plegable-certificado-dot-_JM?quantity=1&amp;variation_id=189147248851</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_719669-MLM98288984742_112025-F-casco-de-moto-con-visera-abatible-y-plegable-certificado-dot.webp</t>
   </si>
 </sst>
 </file>
@@ -3321,11 +3495,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3345,8 +3522,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H302" totalsRowShown="0">
-  <autoFilter ref="A1:H302"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H317" totalsRowShown="0">
+  <autoFilter ref="A1:H317"/>
   <sortState ref="A2:H230">
     <sortCondition ref="H1:H230"/>
   </sortState>
@@ -3649,7 +3826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:H317"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -11105,6 +11282,393 @@
         <v>905</v>
       </c>
     </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B303" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C303">
+        <v>691</v>
+      </c>
+      <c r="D303">
+        <v>350</v>
+      </c>
+      <c r="E303" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F303" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G303" t="s">
+        <v>600</v>
+      </c>
+      <c r="H303" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A304" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B304" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C304">
+        <v>555</v>
+      </c>
+      <c r="D304">
+        <v>300</v>
+      </c>
+      <c r="E304" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F304" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G304" t="s">
+        <v>600</v>
+      </c>
+      <c r="H304" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B305" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C305">
+        <v>897</v>
+      </c>
+      <c r="D305">
+        <v>570</v>
+      </c>
+      <c r="E305" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F305" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G305" t="s">
+        <v>600</v>
+      </c>
+      <c r="H305" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B306" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C306">
+        <v>726</v>
+      </c>
+      <c r="D306">
+        <v>500</v>
+      </c>
+      <c r="E306" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F306" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G306" t="s">
+        <v>600</v>
+      </c>
+      <c r="H306" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B307" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C307">
+        <v>713</v>
+      </c>
+      <c r="D307">
+        <v>530</v>
+      </c>
+      <c r="E307" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F307" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G307" t="s">
+        <v>600</v>
+      </c>
+      <c r="H307" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B308" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C308">
+        <v>1095</v>
+      </c>
+      <c r="D308">
+        <v>800</v>
+      </c>
+      <c r="E308" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F308" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G308" t="s">
+        <v>600</v>
+      </c>
+      <c r="H308" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B309" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C309">
+        <v>890</v>
+      </c>
+      <c r="D309">
+        <v>500</v>
+      </c>
+      <c r="E309" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F309" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G309" t="s">
+        <v>600</v>
+      </c>
+      <c r="H309" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B310" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C310">
+        <v>635</v>
+      </c>
+      <c r="D310">
+        <v>400</v>
+      </c>
+      <c r="E310" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F310" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G310" t="s">
+        <v>600</v>
+      </c>
+      <c r="H310" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B311" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C311">
+        <v>715</v>
+      </c>
+      <c r="D311">
+        <v>550</v>
+      </c>
+      <c r="E311" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F311" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G311" t="s">
+        <v>600</v>
+      </c>
+      <c r="H311" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B312" t="s">
+        <v>18</v>
+      </c>
+      <c r="C312">
+        <v>280</v>
+      </c>
+      <c r="E312" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F312" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G312" t="s">
+        <v>600</v>
+      </c>
+      <c r="H312" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B313" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C313">
+        <v>450</v>
+      </c>
+      <c r="D313">
+        <v>350</v>
+      </c>
+      <c r="E313" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F313" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G313" t="s">
+        <v>600</v>
+      </c>
+      <c r="H313" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B314" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C314">
+        <v>365</v>
+      </c>
+      <c r="D314">
+        <v>200</v>
+      </c>
+      <c r="E314" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F314" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G314" t="s">
+        <v>600</v>
+      </c>
+      <c r="H314" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B315" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C315">
+        <v>250</v>
+      </c>
+      <c r="D315">
+        <v>200</v>
+      </c>
+      <c r="E315" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F315" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G315" t="s">
+        <v>600</v>
+      </c>
+      <c r="H315" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B316" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C316">
+        <v>515</v>
+      </c>
+      <c r="D316">
+        <v>400</v>
+      </c>
+      <c r="E316" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F316" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G316" t="s">
+        <v>600</v>
+      </c>
+      <c r="H316" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B317" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C317">
+        <v>820</v>
+      </c>
+      <c r="D317">
+        <v>680</v>
+      </c>
+      <c r="E317" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F317" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G317" t="s">
+        <v>600</v>
+      </c>
+      <c r="H317" t="s">
+        <v>722</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2200" uniqueCount="1213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="1211">
   <si>
     <t>Nombre</t>
   </si>
@@ -3146,12 +3146,6 @@
   </si>
   <si>
     <t>No recargable, Tamaño del producto: 34.5x12x12cm</t>
-  </si>
-  <si>
-    <t>Lámpara De Ventilador Led 48W E26 20.5 Con Mando A Distancia</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tamaño del producto: 52x20.5x20.5</t>
   </si>
   <si>
     <t>OK</t>
@@ -3765,8 +3759,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H334" totalsRowShown="0">
-  <autoFilter ref="A1:H334"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H333" totalsRowShown="0">
+  <autoFilter ref="A1:H333"/>
   <sortState ref="A2:H340">
     <sortCondition ref="G1:G340"/>
   </sortState>
@@ -4069,7 +4063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I334"/>
+  <dimension ref="A1:I333"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -4127,13 +4121,13 @@
         <v>392</v>
       </c>
       <c r="G2" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -4156,13 +4150,13 @@
         <v>398</v>
       </c>
       <c r="G3" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="H3" t="s">
         <v>12</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4182,21 +4176,21 @@
         <v>411</v>
       </c>
       <c r="G4" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="H4" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C5">
         <v>589</v>
@@ -4205,24 +4199,24 @@
         <v>500</v>
       </c>
       <c r="E5" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="F5" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="G5" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H5" t="s">
         <v>602</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>173</v>
@@ -4234,24 +4228,24 @@
         <v>350</v>
       </c>
       <c r="E6" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="F6" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G6" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H6" t="s">
         <v>602</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>18</v>
@@ -4260,19 +4254,19 @@
         <v>250</v>
       </c>
       <c r="E7" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="F7" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="G7" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H7" t="s">
         <v>602</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -4280,7 +4274,7 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C8">
         <v>250</v>
@@ -4292,13 +4286,13 @@
         <v>82</v>
       </c>
       <c r="G8" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H8" t="s">
         <v>602</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -4306,7 +4300,7 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C9">
         <v>150</v>
@@ -4315,13 +4309,13 @@
         <v>84</v>
       </c>
       <c r="G9" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H9" t="s">
         <v>602</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -4329,7 +4323,7 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C10">
         <v>250</v>
@@ -4341,13 +4335,13 @@
         <v>87</v>
       </c>
       <c r="G10" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H10" t="s">
         <v>602</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -4367,13 +4361,13 @@
         <v>570</v>
       </c>
       <c r="G11" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H11" t="s">
         <v>602</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -4396,13 +4390,13 @@
         <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H12" t="s">
         <v>602</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -4422,13 +4416,13 @@
         <v>93</v>
       </c>
       <c r="G13" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H13" t="s">
         <v>602</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -4436,7 +4430,7 @@
         <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C14">
         <v>250</v>
@@ -4448,7 +4442,7 @@
         <v>96</v>
       </c>
       <c r="G14" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H14" t="s">
         <v>602</v>
@@ -4459,7 +4453,7 @@
         <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C15">
         <v>150</v>
@@ -4471,13 +4465,13 @@
         <v>99</v>
       </c>
       <c r="G15" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H15" t="s">
         <v>602</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -4485,7 +4479,7 @@
         <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C16">
         <v>250</v>
@@ -4497,13 +4491,13 @@
         <v>102</v>
       </c>
       <c r="G16" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H16" t="s">
         <v>602</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -4523,7 +4517,7 @@
         <v>105</v>
       </c>
       <c r="G17" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H17" t="s">
         <v>602</v>
@@ -4546,7 +4540,7 @@
         <v>108</v>
       </c>
       <c r="G18" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H18" t="s">
         <v>602</v>
@@ -4569,7 +4563,7 @@
         <v>560</v>
       </c>
       <c r="G19" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H19" t="s">
         <v>602</v>
@@ -4577,10 +4571,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B20" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="C20">
         <v>376.51</v>
@@ -4595,21 +4589,21 @@
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H20" t="s">
         <v>603</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B21" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C21">
         <v>1599</v>
@@ -4618,13 +4612,13 @@
         <v>1150</v>
       </c>
       <c r="E21" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="F21" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="G21" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H21" t="s">
         <v>603</v>
@@ -4651,7 +4645,7 @@
         <v>969</v>
       </c>
       <c r="G22" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H22" t="s">
         <v>603</v>
@@ -4675,13 +4669,13 @@
         <v>29</v>
       </c>
       <c r="G23" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H23" t="s">
         <v>603</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -4701,13 +4695,13 @@
         <v>32</v>
       </c>
       <c r="G24" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H24" t="s">
         <v>603</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -4730,13 +4724,13 @@
         <v>35</v>
       </c>
       <c r="G25" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H25" t="s">
         <v>603</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -4759,13 +4753,13 @@
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H26" t="s">
         <v>603</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -4788,13 +4782,13 @@
         <v>42</v>
       </c>
       <c r="G27" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H27" t="s">
         <v>603</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -4814,13 +4808,13 @@
         <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H28" t="s">
         <v>603</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -4840,13 +4834,13 @@
         <v>49</v>
       </c>
       <c r="G29" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H29" t="s">
         <v>603</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -4869,13 +4863,13 @@
         <v>53</v>
       </c>
       <c r="G30" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H30" t="s">
         <v>603</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -4898,13 +4892,13 @@
         <v>56</v>
       </c>
       <c r="G31" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H31" t="s">
         <v>603</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -4927,13 +4921,13 @@
         <v>59</v>
       </c>
       <c r="G32" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H32" t="s">
         <v>603</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -4956,13 +4950,13 @@
         <v>62</v>
       </c>
       <c r="G33" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H33" t="s">
         <v>603</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -4985,13 +4979,13 @@
         <v>65</v>
       </c>
       <c r="G34" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H34" t="s">
         <v>603</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -5011,13 +5005,13 @@
         <v>386</v>
       </c>
       <c r="G35" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="H35" t="s">
         <v>603</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -5040,13 +5034,13 @@
         <v>239</v>
       </c>
       <c r="G36" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H36" t="s">
         <v>233</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -5069,13 +5063,13 @@
         <v>242</v>
       </c>
       <c r="G37" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H37" t="s">
         <v>233</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -5098,13 +5092,13 @@
         <v>785</v>
       </c>
       <c r="G38" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H38" t="s">
         <v>233</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -5127,7 +5121,7 @@
         <v>860</v>
       </c>
       <c r="G39" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H39" t="s">
         <v>233</v>
@@ -5154,13 +5148,13 @@
         <v>727</v>
       </c>
       <c r="G40" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H40" t="s">
         <v>233</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -5180,13 +5174,13 @@
         <v>851</v>
       </c>
       <c r="G41" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H41" t="s">
         <v>233</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -5206,13 +5200,13 @@
         <v>688</v>
       </c>
       <c r="G42" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H42" t="s">
         <v>233</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -5235,7 +5229,7 @@
         <v>771</v>
       </c>
       <c r="G43" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H43" t="s">
         <v>233</v>
@@ -5259,7 +5253,7 @@
         <v>379</v>
       </c>
       <c r="G44" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H44" t="s">
         <v>233</v>
@@ -5286,13 +5280,13 @@
         <v>743</v>
       </c>
       <c r="G45" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H45" t="s">
         <v>233</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -5315,13 +5309,13 @@
         <v>773</v>
       </c>
       <c r="G46" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H46" t="s">
         <v>233</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5341,13 +5335,13 @@
         <v>836</v>
       </c>
       <c r="G47" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H47" t="s">
         <v>233</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -5370,13 +5364,13 @@
         <v>701</v>
       </c>
       <c r="G48" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H48" t="s">
         <v>233</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -5396,13 +5390,13 @@
         <v>562</v>
       </c>
       <c r="G49" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H49" t="s">
         <v>233</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -5425,13 +5419,13 @@
         <v>723</v>
       </c>
       <c r="G50" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H50" t="s">
         <v>233</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -5451,13 +5445,13 @@
         <v>737</v>
       </c>
       <c r="G51" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H51" t="s">
         <v>233</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -5480,13 +5474,13 @@
         <v>232</v>
       </c>
       <c r="G52" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H52" t="s">
         <v>233</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -5509,13 +5503,13 @@
         <v>236</v>
       </c>
       <c r="G53" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H53" t="s">
         <v>233</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -5538,13 +5532,13 @@
         <v>796</v>
       </c>
       <c r="G54" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H54" t="s">
         <v>233</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -5567,13 +5561,13 @@
         <v>840</v>
       </c>
       <c r="G55" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H55" t="s">
         <v>233</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -5596,13 +5590,13 @@
         <v>777</v>
       </c>
       <c r="G56" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H56" t="s">
         <v>233</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -5622,13 +5616,13 @@
         <v>809</v>
       </c>
       <c r="G57" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H57" t="s">
         <v>233</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -5651,13 +5645,13 @@
         <v>707</v>
       </c>
       <c r="G58" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H58" t="s">
         <v>233</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -5680,13 +5674,13 @@
         <v>733</v>
       </c>
       <c r="G59" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H59" t="s">
         <v>233</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -5706,13 +5700,13 @@
         <v>689</v>
       </c>
       <c r="G60" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H60" t="s">
         <v>233</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -5735,13 +5729,13 @@
         <v>820</v>
       </c>
       <c r="G61" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H61" t="s">
         <v>233</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -5761,13 +5755,13 @@
         <v>814</v>
       </c>
       <c r="G62" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H62" t="s">
         <v>233</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -5787,13 +5781,13 @@
         <v>805</v>
       </c>
       <c r="G63" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H63" t="s">
         <v>233</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -5813,13 +5807,13 @@
         <v>855</v>
       </c>
       <c r="G64" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H64" t="s">
         <v>233</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -5842,13 +5836,13 @@
         <v>729</v>
       </c>
       <c r="G65" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H65" t="s">
         <v>233</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -5868,13 +5862,13 @@
         <v>821</v>
       </c>
       <c r="G66" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H66" t="s">
         <v>233</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -5897,7 +5891,7 @@
         <v>847</v>
       </c>
       <c r="G67" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H67" t="s">
         <v>233</v>
@@ -5921,7 +5915,7 @@
         <v>833</v>
       </c>
       <c r="G68" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H68" t="s">
         <v>233</v>
@@ -5948,7 +5942,7 @@
         <v>708</v>
       </c>
       <c r="G69" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H69" t="s">
         <v>233</v>
@@ -5975,7 +5969,7 @@
         <v>229</v>
       </c>
       <c r="G70" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H70" t="s">
         <v>233</v>
@@ -6002,7 +5996,7 @@
         <v>712</v>
       </c>
       <c r="G71" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H71" t="s">
         <v>233</v>
@@ -6026,7 +6020,7 @@
         <v>683</v>
       </c>
       <c r="G72" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H72" t="s">
         <v>233</v>
@@ -6050,13 +6044,13 @@
         <v>697</v>
       </c>
       <c r="G73" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H73" t="s">
         <v>233</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -6079,7 +6073,7 @@
         <v>750</v>
       </c>
       <c r="G74" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H74" t="s">
         <v>233</v>
@@ -6106,7 +6100,7 @@
         <v>755</v>
       </c>
       <c r="G75" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H75" t="s">
         <v>233</v>
@@ -6133,7 +6127,7 @@
         <v>757</v>
       </c>
       <c r="G76" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H76" t="s">
         <v>233</v>
@@ -6160,13 +6154,13 @@
         <v>760</v>
       </c>
       <c r="G77" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H77" t="s">
         <v>233</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -6186,13 +6180,13 @@
         <v>800</v>
       </c>
       <c r="G78" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H78" t="s">
         <v>233</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -6212,13 +6206,13 @@
         <v>803</v>
       </c>
       <c r="G79" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H79" t="s">
         <v>233</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -6241,7 +6235,7 @@
         <v>747</v>
       </c>
       <c r="G80" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H80" t="s">
         <v>233</v>
@@ -6268,13 +6262,13 @@
         <v>825</v>
       </c>
       <c r="G81" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H81" t="s">
         <v>233</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -6294,13 +6288,13 @@
         <v>865</v>
       </c>
       <c r="G82" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H82" t="s">
         <v>233</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -6320,7 +6314,7 @@
         <v>719</v>
       </c>
       <c r="G83" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H83" t="s">
         <v>233</v>
@@ -6347,7 +6341,7 @@
         <v>717</v>
       </c>
       <c r="G84" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="H84" t="s">
         <v>233</v>
@@ -6401,7 +6395,7 @@
         <v>263</v>
       </c>
       <c r="G86" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="H86" t="s">
         <v>603</v>
@@ -6428,7 +6422,7 @@
         <v>225</v>
       </c>
       <c r="G87" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H87" t="s">
         <v>605</v>
@@ -6437,7 +6431,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B88" t="s">
         <v>18</v>
@@ -6446,13 +6440,13 @@
         <v>250</v>
       </c>
       <c r="E88" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="F88" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="G88" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H88" t="s">
         <v>605</v>
@@ -6461,7 +6455,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B89" t="s">
         <v>18</v>
@@ -6470,13 +6464,13 @@
         <v>250</v>
       </c>
       <c r="E89" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="F89" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="G89" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H89" t="s">
         <v>605</v>
@@ -6485,7 +6479,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B90" t="s">
         <v>18</v>
@@ -6494,13 +6488,13 @@
         <v>250</v>
       </c>
       <c r="E90" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="F90" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="G90" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H90" t="s">
         <v>605</v>
@@ -6509,7 +6503,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B91" t="s">
         <v>18</v>
@@ -6521,13 +6515,13 @@
         <v>200</v>
       </c>
       <c r="E91" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="F91" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="G91" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H91" t="s">
         <v>605</v>
@@ -6536,7 +6530,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B92" t="s">
         <v>18</v>
@@ -6545,13 +6539,13 @@
         <v>250</v>
       </c>
       <c r="E92" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="F92" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G92" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H92" t="s">
         <v>605</v>
@@ -6578,7 +6572,7 @@
         <v>372</v>
       </c>
       <c r="G93" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H93" t="s">
         <v>605</v>
@@ -6605,7 +6599,7 @@
         <v>227</v>
       </c>
       <c r="G94" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H94" t="s">
         <v>605</v>
@@ -6629,7 +6623,7 @@
         <v>582</v>
       </c>
       <c r="G95" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H95" t="s">
         <v>602</v>
@@ -6638,7 +6632,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="B96" t="s">
         <v>18</v>
@@ -6650,24 +6644,24 @@
         <v>120</v>
       </c>
       <c r="E96" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="F96" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="G96" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H96" t="s">
         <v>605</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="B97" t="s">
         <v>18</v>
@@ -6679,13 +6673,13 @@
         <v>120</v>
       </c>
       <c r="E97" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="F97" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="G97" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H97" t="s">
         <v>605</v>
@@ -6694,7 +6688,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B98" t="s">
         <v>18</v>
@@ -6706,13 +6700,13 @@
         <v>200</v>
       </c>
       <c r="E98" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="F98" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G98" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H98" t="s">
         <v>602</v>
@@ -6739,7 +6733,7 @@
         <v>20</v>
       </c>
       <c r="G99" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="H99" t="s">
         <v>602</v>
@@ -7168,7 +7162,7 @@
         <v>602</v>
       </c>
       <c r="I115" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -7197,7 +7191,7 @@
         <v>602</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -7307,7 +7301,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="B121" t="s">
         <v>66</v>
@@ -7325,7 +7319,7 @@
         <v>68</v>
       </c>
       <c r="G121" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="H121" t="s">
         <v>603</v>
@@ -7348,13 +7342,13 @@
         <v>73</v>
       </c>
       <c r="G122" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="H122" t="s">
         <v>603</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -7377,13 +7371,13 @@
         <v>351</v>
       </c>
       <c r="G123" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="H123" t="s">
         <v>603</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -7406,13 +7400,13 @@
         <v>76</v>
       </c>
       <c r="G124" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="H124" t="s">
         <v>603</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -7435,13 +7429,13 @@
         <v>79</v>
       </c>
       <c r="G125" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="H125" t="s">
         <v>603</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -7470,24 +7464,24 @@
         <v>602</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B127" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C127">
         <v>150</v>
       </c>
       <c r="E127" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="F127" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="G127" t="s">
         <v>482</v>
@@ -7498,10 +7492,10 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="B128" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C128">
         <v>150</v>
@@ -7510,10 +7504,10 @@
         <v>100</v>
       </c>
       <c r="E128" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="F128" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="G128" t="s">
         <v>482</v>
@@ -7524,10 +7518,10 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B129" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C129">
         <v>150</v>
@@ -7536,10 +7530,10 @@
         <v>100</v>
       </c>
       <c r="E129" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="F129" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G129" t="s">
         <v>482</v>
@@ -7550,10 +7544,10 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B130" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C130">
         <v>120</v>
@@ -7562,10 +7556,10 @@
         <v>100</v>
       </c>
       <c r="E130" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="F130" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G130" t="s">
         <v>482</v>
@@ -7663,7 +7657,7 @@
         <v>370</v>
       </c>
       <c r="E134" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="F134" t="s">
         <v>316</v>
@@ -7700,7 +7694,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B136" t="s">
         <v>1010</v>
@@ -7712,10 +7706,10 @@
         <v>220</v>
       </c>
       <c r="E136" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F136" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G136" t="s">
         <v>482</v>
@@ -7729,7 +7723,7 @@
         <v>479</v>
       </c>
       <c r="B137" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C137">
         <v>200</v>
@@ -7764,7 +7758,7 @@
         <v>250</v>
       </c>
       <c r="E138" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="F138" t="s">
         <v>401</v>
@@ -7790,7 +7784,7 @@
         <v>250</v>
       </c>
       <c r="E139" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="F139" t="s">
         <v>404</v>
@@ -7924,7 +7918,7 @@
         <v>207</v>
       </c>
       <c r="G144" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="H144" t="s">
         <v>603</v>
@@ -7950,7 +7944,7 @@
         <v>521</v>
       </c>
       <c r="G145" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="H145" t="s">
         <v>605</v>
@@ -7973,13 +7967,13 @@
         <v>209</v>
       </c>
       <c r="G146" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="H146" t="s">
         <v>605</v>
       </c>
       <c r="I146" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
@@ -8002,13 +7996,13 @@
         <v>212</v>
       </c>
       <c r="G147" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="H147" t="s">
         <v>605</v>
       </c>
       <c r="I147" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
@@ -8031,13 +8025,13 @@
         <v>215</v>
       </c>
       <c r="G148" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="H148" t="s">
         <v>605</v>
       </c>
       <c r="I148" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
@@ -8060,13 +8054,13 @@
         <v>218</v>
       </c>
       <c r="G149" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="H149" t="s">
         <v>605</v>
       </c>
       <c r="I149" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
@@ -8089,13 +8083,13 @@
         <v>222</v>
       </c>
       <c r="G150" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="H150" t="s">
         <v>605</v>
       </c>
       <c r="I150" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
@@ -8115,13 +8109,13 @@
         <v>389</v>
       </c>
       <c r="G151" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H151" t="s">
         <v>69</v>
       </c>
       <c r="I151" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
@@ -8144,13 +8138,13 @@
         <v>182</v>
       </c>
       <c r="G152" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H152" t="s">
         <v>602</v>
       </c>
       <c r="I152" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -8173,13 +8167,13 @@
         <v>185</v>
       </c>
       <c r="G153" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H153" t="s">
         <v>602</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
@@ -8202,13 +8196,13 @@
         <v>188</v>
       </c>
       <c r="G154" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H154" t="s">
         <v>602</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -8228,13 +8222,13 @@
         <v>407</v>
       </c>
       <c r="G155" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H155" t="s">
         <v>109</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
@@ -8254,7 +8248,7 @@
         <v>672</v>
       </c>
       <c r="G156" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H156" t="s">
         <v>602</v>
@@ -8280,13 +8274,13 @@
         <v>783</v>
       </c>
       <c r="G157" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H157" t="s">
         <v>69</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
@@ -8306,13 +8300,13 @@
         <v>524</v>
       </c>
       <c r="G158" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H158" t="s">
         <v>69</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
@@ -8332,13 +8326,13 @@
         <v>679</v>
       </c>
       <c r="G159" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H159" t="s">
         <v>69</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -8358,13 +8352,13 @@
         <v>517</v>
       </c>
       <c r="G160" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H160" t="s">
         <v>233</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
@@ -8384,13 +8378,13 @@
         <v>574</v>
       </c>
       <c r="G161" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H161" t="s">
         <v>602</v>
       </c>
       <c r="I161" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
@@ -8410,7 +8404,7 @@
         <v>794</v>
       </c>
       <c r="G162" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H162" t="s">
         <v>602</v>
@@ -8433,7 +8427,7 @@
         <v>594</v>
       </c>
       <c r="G163" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H163" t="s">
         <v>69</v>
@@ -8456,7 +8450,7 @@
         <v>530</v>
       </c>
       <c r="G164" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H164" t="s">
         <v>233</v>
@@ -8480,13 +8474,13 @@
         <v>543</v>
       </c>
       <c r="G165" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H165" t="s">
         <v>233</v>
       </c>
       <c r="I165" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
@@ -8506,13 +8500,13 @@
         <v>540</v>
       </c>
       <c r="G166" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H166" t="s">
         <v>233</v>
       </c>
       <c r="I166" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
@@ -8532,13 +8526,13 @@
         <v>601</v>
       </c>
       <c r="G167" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H167" t="s">
         <v>602</v>
       </c>
       <c r="I167" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
@@ -8558,13 +8552,13 @@
         <v>566</v>
       </c>
       <c r="G168" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H168" t="s">
         <v>602</v>
       </c>
       <c r="I168" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
@@ -8587,13 +8581,13 @@
         <v>590</v>
       </c>
       <c r="G169" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H169" t="s">
         <v>602</v>
       </c>
       <c r="I169" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
@@ -8616,13 +8610,13 @@
         <v>965</v>
       </c>
       <c r="G170" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H170" t="s">
         <v>767</v>
       </c>
       <c r="I170" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
@@ -8642,7 +8636,7 @@
         <v>954</v>
       </c>
       <c r="G171" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H171" t="s">
         <v>233</v>
@@ -8669,7 +8663,7 @@
         <v>500</v>
       </c>
       <c r="G172" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H172" t="s">
         <v>233</v>
@@ -8696,7 +8690,7 @@
         <v>869</v>
       </c>
       <c r="G173" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H173" t="s">
         <v>602</v>
@@ -8723,13 +8717,13 @@
         <v>958</v>
       </c>
       <c r="G174" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H174" t="s">
         <v>69</v>
       </c>
       <c r="I174" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
@@ -8752,13 +8746,13 @@
         <v>348</v>
       </c>
       <c r="G175" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H175" t="s">
         <v>603</v>
       </c>
       <c r="I175" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
@@ -8781,13 +8775,13 @@
         <v>556</v>
       </c>
       <c r="G176" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="H176" t="s">
         <v>603</v>
       </c>
       <c r="I176" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
@@ -8840,7 +8834,7 @@
         <v>69</v>
       </c>
       <c r="I178" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
@@ -8896,7 +8890,7 @@
         <v>69</v>
       </c>
       <c r="I180" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
@@ -8952,7 +8946,7 @@
         <v>69</v>
       </c>
       <c r="I182" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
@@ -8981,7 +8975,7 @@
         <v>69</v>
       </c>
       <c r="I183" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
@@ -9010,7 +9004,7 @@
         <v>468</v>
       </c>
       <c r="I184" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -9066,7 +9060,7 @@
         <v>603</v>
       </c>
       <c r="I186" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
@@ -9092,7 +9086,7 @@
         <v>602</v>
       </c>
       <c r="I187" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
@@ -9148,7 +9142,7 @@
         <v>602</v>
       </c>
       <c r="I189" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
@@ -9204,7 +9198,7 @@
         <v>233</v>
       </c>
       <c r="I191" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
@@ -9224,13 +9218,13 @@
         <v>376</v>
       </c>
       <c r="G192" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H192" t="s">
         <v>12</v>
       </c>
       <c r="I192" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
@@ -9253,13 +9247,13 @@
         <v>11</v>
       </c>
       <c r="G193" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H193" t="s">
         <v>12</v>
       </c>
       <c r="I193" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
@@ -9282,13 +9276,13 @@
         <v>24</v>
       </c>
       <c r="G194" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H194" t="s">
         <v>12</v>
       </c>
       <c r="I194" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
@@ -9311,13 +9305,13 @@
         <v>16</v>
       </c>
       <c r="G195" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H195" t="s">
         <v>12</v>
       </c>
       <c r="I195" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
@@ -9325,7 +9319,7 @@
         <v>380</v>
       </c>
       <c r="B196" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C196">
         <v>250</v>
@@ -9340,13 +9334,13 @@
         <v>383</v>
       </c>
       <c r="G196" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H196" t="s">
         <v>12</v>
       </c>
       <c r="I196" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
@@ -9366,18 +9360,18 @@
         <v>395</v>
       </c>
       <c r="G197" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H197" t="s">
         <v>12</v>
       </c>
       <c r="I197" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="B198" t="s">
         <v>791</v>
@@ -9389,19 +9383,19 @@
         <v>200</v>
       </c>
       <c r="E198" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="F198" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="G198" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H198" t="s">
         <v>12</v>
       </c>
       <c r="I198" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
@@ -9424,13 +9418,13 @@
         <v>792</v>
       </c>
       <c r="G199" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H199" t="s">
         <v>12</v>
       </c>
       <c r="I199" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
@@ -9453,13 +9447,13 @@
         <v>586</v>
       </c>
       <c r="G200" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H200" t="s">
         <v>12</v>
       </c>
       <c r="I200" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
@@ -9479,13 +9473,13 @@
         <v>413</v>
       </c>
       <c r="G201" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H201" t="s">
         <v>12</v>
       </c>
       <c r="I201" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
@@ -9493,7 +9487,7 @@
         <v>414</v>
       </c>
       <c r="B202" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C202">
         <v>141</v>
@@ -9508,13 +9502,13 @@
         <v>416</v>
       </c>
       <c r="G202" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H202" t="s">
         <v>12</v>
       </c>
       <c r="I202" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
@@ -9537,13 +9531,13 @@
         <v>420</v>
       </c>
       <c r="G203" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H203" t="s">
         <v>12</v>
       </c>
       <c r="I203" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
@@ -9566,13 +9560,13 @@
         <v>423</v>
       </c>
       <c r="G204" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H204" t="s">
         <v>12</v>
       </c>
       <c r="I204" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
@@ -9592,7 +9586,7 @@
         <v>431</v>
       </c>
       <c r="G205" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H205" t="s">
         <v>12</v>
@@ -9619,7 +9613,7 @@
         <v>438</v>
       </c>
       <c r="G206" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H206" t="s">
         <v>12</v>
@@ -9628,10 +9622,10 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="B207" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C207">
         <v>250</v>
@@ -9640,13 +9634,13 @@
         <v>200</v>
       </c>
       <c r="E207" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="F207" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="G207" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H207" t="s">
         <v>12</v>
@@ -9655,10 +9649,10 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B208" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C208">
         <v>333</v>
@@ -9673,7 +9667,7 @@
         <v>440</v>
       </c>
       <c r="G208" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H208" t="s">
         <v>12</v>
@@ -9682,22 +9676,22 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="B209" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C209">
         <v>300</v>
       </c>
       <c r="E209" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="F209" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G209" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H209" t="s">
         <v>12</v>
@@ -9706,22 +9700,22 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B210" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C210">
         <v>200</v>
       </c>
       <c r="E210" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="F210" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G210" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H210" t="s">
         <v>12</v>
@@ -9730,7 +9724,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B211" t="s">
         <v>9</v>
@@ -9739,13 +9733,13 @@
         <v>300</v>
       </c>
       <c r="E211" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="F211" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="G211" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H211" t="s">
         <v>12</v>
@@ -9754,7 +9748,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="B212" t="s">
         <v>22</v>
@@ -9763,13 +9757,13 @@
         <v>350</v>
       </c>
       <c r="E212" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="F212" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="G212" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="H212" t="s">
         <v>12</v>
@@ -9778,19 +9772,19 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="B213" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C213">
         <v>200</v>
       </c>
       <c r="E213" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="F213" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="G213" t="s">
         <v>609</v>
@@ -9799,24 +9793,24 @@
         <v>608</v>
       </c>
       <c r="I213" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="B214" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C214">
         <v>200</v>
       </c>
       <c r="E214" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="F214" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="G214" t="s">
         <v>609</v>
@@ -9828,19 +9822,19 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="B215" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C215">
         <v>150</v>
       </c>
       <c r="E215" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="F215" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="G215" t="s">
         <v>609</v>
@@ -9852,19 +9846,19 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B216" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C216">
         <v>550</v>
       </c>
       <c r="E216" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="F216" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="G216" t="s">
         <v>609</v>
@@ -9873,24 +9867,24 @@
         <v>608</v>
       </c>
       <c r="I216" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B217" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="C217">
         <v>200</v>
       </c>
       <c r="E217" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="F217" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="G217" t="s">
         <v>609</v>
@@ -9899,24 +9893,24 @@
         <v>608</v>
       </c>
       <c r="I217" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B218" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="C218">
         <v>200</v>
       </c>
       <c r="E218" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="F218" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="G218" t="s">
         <v>609</v>
@@ -9925,24 +9919,24 @@
         <v>608</v>
       </c>
       <c r="I218" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B219" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="C219">
         <v>200</v>
       </c>
       <c r="E219" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="F219" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="G219" t="s">
         <v>609</v>
@@ -9951,24 +9945,24 @@
         <v>608</v>
       </c>
       <c r="I219" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B220" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C220">
         <v>250</v>
       </c>
       <c r="E220" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="F220" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="G220" t="s">
         <v>609</v>
@@ -9977,24 +9971,24 @@
         <v>608</v>
       </c>
       <c r="I220" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B221" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="C221">
         <v>300</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="F221" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="G221" t="s">
         <v>609</v>
@@ -10003,24 +9997,24 @@
         <v>608</v>
       </c>
       <c r="I221" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="B222" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="C222">
         <v>200</v>
       </c>
       <c r="E222" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="F222" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G222" t="s">
         <v>609</v>
@@ -10029,7 +10023,7 @@
         <v>608</v>
       </c>
       <c r="I222" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
@@ -10055,7 +10049,7 @@
         <v>608</v>
       </c>
       <c r="I223" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
@@ -10081,7 +10075,7 @@
         <v>608</v>
       </c>
       <c r="I224" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
@@ -10107,7 +10101,7 @@
         <v>608</v>
       </c>
       <c r="I225" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
@@ -10133,7 +10127,7 @@
         <v>608</v>
       </c>
       <c r="I226" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
@@ -10159,7 +10153,7 @@
         <v>608</v>
       </c>
       <c r="I227" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
@@ -10185,7 +10179,7 @@
         <v>608</v>
       </c>
       <c r="I228" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
@@ -10211,7 +10205,7 @@
         <v>608</v>
       </c>
       <c r="I229" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
@@ -10237,7 +10231,7 @@
         <v>608</v>
       </c>
       <c r="I230" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
@@ -10263,7 +10257,7 @@
         <v>608</v>
       </c>
       <c r="I231" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
@@ -10289,7 +10283,7 @@
         <v>608</v>
       </c>
       <c r="I232" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
@@ -10315,7 +10309,7 @@
         <v>608</v>
       </c>
       <c r="I233" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="234" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10341,7 +10335,7 @@
         <v>608</v>
       </c>
       <c r="I234" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
@@ -10367,7 +10361,7 @@
         <v>608</v>
       </c>
       <c r="I235" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
@@ -10505,7 +10499,7 @@
         <v>256</v>
       </c>
       <c r="G241" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H241" t="s">
         <v>109</v>
@@ -10513,7 +10507,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B242" t="s">
         <v>515</v>
@@ -10531,7 +10525,7 @@
         <v>526</v>
       </c>
       <c r="G242" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H242" t="s">
         <v>109</v>
@@ -10557,7 +10551,7 @@
         <v>340</v>
       </c>
       <c r="G243" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H243" t="s">
         <v>109</v>
@@ -10583,7 +10577,7 @@
         <v>550</v>
       </c>
       <c r="G244" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H244" t="s">
         <v>109</v>
@@ -10609,7 +10603,7 @@
         <v>1024</v>
       </c>
       <c r="G245" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H245" t="s">
         <v>109</v>
@@ -10635,7 +10629,7 @@
         <v>1020</v>
       </c>
       <c r="G246" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H246" t="s">
         <v>109</v>
@@ -10661,7 +10655,7 @@
         <v>1015</v>
       </c>
       <c r="G247" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H247" t="s">
         <v>109</v>
@@ -10687,7 +10681,7 @@
         <v>1011</v>
       </c>
       <c r="G248" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H248" t="s">
         <v>109</v>
@@ -10713,13 +10707,13 @@
         <v>526</v>
       </c>
       <c r="G249" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H249" t="s">
         <v>109</v>
       </c>
       <c r="I249" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
@@ -10742,13 +10736,13 @@
         <v>112</v>
       </c>
       <c r="G250" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H250" t="s">
         <v>109</v>
       </c>
       <c r="I250" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
@@ -10771,7 +10765,7 @@
         <v>116</v>
       </c>
       <c r="G251" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H251" t="s">
         <v>109</v>
@@ -10797,7 +10791,7 @@
         <v>532</v>
       </c>
       <c r="G252" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H252" t="s">
         <v>109</v>
@@ -10821,7 +10815,7 @@
         <v>119</v>
       </c>
       <c r="G253" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H253" t="s">
         <v>109</v>
@@ -10848,7 +10842,7 @@
         <v>994</v>
       </c>
       <c r="G254" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H254" t="s">
         <v>109</v>
@@ -10875,7 +10869,7 @@
         <v>990</v>
       </c>
       <c r="G255" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H255" t="s">
         <v>109</v>
@@ -10902,13 +10896,13 @@
         <v>988</v>
       </c>
       <c r="G256" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H256" t="s">
         <v>109</v>
       </c>
       <c r="I256" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
@@ -10916,7 +10910,7 @@
         <v>120</v>
       </c>
       <c r="B257" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C257">
         <v>515</v>
@@ -10931,13 +10925,13 @@
         <v>122</v>
       </c>
       <c r="G257" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H257" t="s">
         <v>109</v>
       </c>
       <c r="I257" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
@@ -10957,13 +10951,13 @@
         <v>125</v>
       </c>
       <c r="G258" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H258" t="s">
         <v>109</v>
       </c>
       <c r="I258" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
@@ -10986,13 +10980,13 @@
         <v>961</v>
       </c>
       <c r="G259" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H259" t="s">
         <v>109</v>
       </c>
       <c r="I259" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
@@ -11015,13 +11009,13 @@
         <v>553</v>
       </c>
       <c r="G260" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H260" t="s">
         <v>109</v>
       </c>
       <c r="I260" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
@@ -11044,13 +11038,13 @@
         <v>127</v>
       </c>
       <c r="G261" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H261" t="s">
         <v>109</v>
       </c>
       <c r="I261" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
@@ -11070,13 +11064,13 @@
         <v>128</v>
       </c>
       <c r="G262" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H262" t="s">
         <v>109</v>
       </c>
       <c r="I262" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
@@ -11099,13 +11093,13 @@
         <v>369</v>
       </c>
       <c r="G263" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H263" t="s">
         <v>109</v>
       </c>
       <c r="I263" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
@@ -11128,13 +11122,13 @@
         <v>1031</v>
       </c>
       <c r="G264" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H264" t="s">
         <v>109</v>
       </c>
       <c r="I264" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
@@ -11157,13 +11151,13 @@
         <v>1028</v>
       </c>
       <c r="G265" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H265" t="s">
         <v>109</v>
       </c>
       <c r="I265" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
@@ -11186,21 +11180,21 @@
         <v>1026</v>
       </c>
       <c r="G266" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H266" t="s">
         <v>109</v>
       </c>
       <c r="I266" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="B267" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C267">
         <v>3500</v>
@@ -11209,24 +11203,24 @@
         <v>2500</v>
       </c>
       <c r="E267" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="F267" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="G267" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H267" t="s">
         <v>109</v>
       </c>
       <c r="I267" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="B268" t="s">
         <v>129</v>
@@ -11244,18 +11238,18 @@
         <v>131</v>
       </c>
       <c r="G268" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H268" t="s">
         <v>109</v>
       </c>
       <c r="I268" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="B269" t="s">
         <v>129</v>
@@ -11267,19 +11261,19 @@
         <v>6800</v>
       </c>
       <c r="E269" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="F269" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="G269" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H269" t="s">
         <v>109</v>
       </c>
       <c r="I269" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
@@ -11302,13 +11296,13 @@
         <v>135</v>
       </c>
       <c r="G270" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H270" t="s">
         <v>109</v>
       </c>
       <c r="I270" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
@@ -11331,13 +11325,13 @@
         <v>344</v>
       </c>
       <c r="G271" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H271" t="s">
         <v>109</v>
       </c>
       <c r="I271" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
@@ -11357,13 +11351,13 @@
         <v>578</v>
       </c>
       <c r="G272" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H272" t="s">
         <v>109</v>
       </c>
       <c r="I272" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
@@ -11383,18 +11377,18 @@
         <v>1000</v>
       </c>
       <c r="G273" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H273" t="s">
         <v>109</v>
       </c>
       <c r="I273" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="B274" t="s">
         <v>18</v>
@@ -11412,13 +11406,13 @@
         <v>1002</v>
       </c>
       <c r="G274" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H274" t="s">
         <v>109</v>
       </c>
       <c r="I274" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
@@ -11441,13 +11435,13 @@
         <v>997</v>
       </c>
       <c r="G275" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H275" t="s">
         <v>109</v>
       </c>
       <c r="I275" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
@@ -11467,13 +11461,13 @@
         <v>137</v>
       </c>
       <c r="G276" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H276" t="s">
         <v>602</v>
       </c>
       <c r="I276" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
@@ -11496,13 +11490,13 @@
         <v>979</v>
       </c>
       <c r="G277" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H277" t="s">
         <v>109</v>
       </c>
       <c r="I277" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
@@ -11522,13 +11516,13 @@
         <v>143</v>
       </c>
       <c r="G278" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H278" t="s">
         <v>109</v>
       </c>
       <c r="I278" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
@@ -11551,7 +11545,7 @@
         <v>144</v>
       </c>
       <c r="G279" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H279" t="s">
         <v>109</v>
@@ -11560,7 +11554,7 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B280" t="s">
         <v>18</v>
@@ -11575,13 +11569,13 @@
         <v>146</v>
       </c>
       <c r="G280" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H280" t="s">
         <v>109</v>
       </c>
       <c r="I280" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
@@ -11592,10 +11586,10 @@
         <v>677</v>
       </c>
       <c r="C281">
+        <v>600</v>
+      </c>
+      <c r="D281">
         <v>550</v>
-      </c>
-      <c r="D281">
-        <v>200</v>
       </c>
       <c r="E281" t="s">
         <v>676</v>
@@ -11604,13 +11598,13 @@
         <v>675</v>
       </c>
       <c r="G281" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H281" t="s">
         <v>109</v>
       </c>
       <c r="I281" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
@@ -11630,13 +11624,13 @@
         <v>147</v>
       </c>
       <c r="G282" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H282" t="s">
         <v>109</v>
       </c>
       <c r="I282" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
@@ -11659,13 +11653,13 @@
         <v>150</v>
       </c>
       <c r="G283" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H283" t="s">
         <v>109</v>
       </c>
       <c r="I283" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
@@ -11688,13 +11682,13 @@
         <v>153</v>
       </c>
       <c r="G284" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H284" t="s">
         <v>109</v>
       </c>
       <c r="I284" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
@@ -11717,18 +11711,18 @@
         <v>156</v>
       </c>
       <c r="G285" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H285" t="s">
         <v>109</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="B286" t="s">
         <v>158</v>
@@ -11746,18 +11740,18 @@
         <v>160</v>
       </c>
       <c r="G286" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H286" t="s">
         <v>109</v>
       </c>
       <c r="I286" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="B287" t="s">
         <v>161</v>
@@ -11775,18 +11769,18 @@
         <v>163</v>
       </c>
       <c r="G287" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H287" t="s">
         <v>109</v>
       </c>
       <c r="I287" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="B288" t="s">
         <v>138</v>
@@ -11804,13 +11798,13 @@
         <v>140</v>
       </c>
       <c r="G288" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H288" t="s">
         <v>109</v>
       </c>
       <c r="I288" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
@@ -11833,18 +11827,18 @@
         <v>165</v>
       </c>
       <c r="G289" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H289" t="s">
         <v>109</v>
       </c>
       <c r="I289" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="5" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="B290" t="s">
         <v>117</v>
@@ -11859,13 +11853,13 @@
         <v>157</v>
       </c>
       <c r="G290" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H290" t="s">
         <v>109</v>
       </c>
       <c r="I290" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
@@ -11888,13 +11882,13 @@
         <v>167</v>
       </c>
       <c r="G291" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H291" t="s">
         <v>603</v>
       </c>
       <c r="I291" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
@@ -11914,13 +11908,13 @@
         <v>496</v>
       </c>
       <c r="G292" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H292" t="s">
         <v>109</v>
       </c>
       <c r="I292" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
@@ -11946,7 +11940,7 @@
         <v>767</v>
       </c>
       <c r="I293" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
@@ -11972,7 +11966,7 @@
         <v>767</v>
       </c>
       <c r="I294" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
@@ -11998,7 +11992,7 @@
         <v>767</v>
       </c>
       <c r="I295" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
@@ -12027,7 +12021,7 @@
         <v>767</v>
       </c>
       <c r="I296" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
@@ -12053,7 +12047,7 @@
         <v>767</v>
       </c>
       <c r="I297" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
@@ -12079,7 +12073,7 @@
         <v>767</v>
       </c>
       <c r="I298" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
@@ -12105,7 +12099,7 @@
         <v>767</v>
       </c>
       <c r="I299" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
@@ -12131,7 +12125,7 @@
         <v>767</v>
       </c>
       <c r="I300" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
@@ -12157,7 +12151,7 @@
         <v>767</v>
       </c>
       <c r="I301" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
@@ -12354,7 +12348,7 @@
         <v>767</v>
       </c>
       <c r="I309" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
@@ -12383,7 +12377,7 @@
         <v>767</v>
       </c>
       <c r="I310" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
@@ -12412,7 +12406,7 @@
         <v>69</v>
       </c>
       <c r="I311" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
@@ -12441,27 +12435,27 @@
         <v>69</v>
       </c>
       <c r="I312" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>1041</v>
+        <v>195</v>
       </c>
       <c r="B313" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="C313">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D313">
         <v>350</v>
       </c>
       <c r="E313" t="s">
-        <v>959</v>
+        <v>196</v>
       </c>
       <c r="F313" t="s">
-        <v>958</v>
+        <v>197</v>
       </c>
       <c r="G313" t="s">
         <v>1035</v>
@@ -12470,27 +12464,27 @@
         <v>69</v>
       </c>
       <c r="I313" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>195</v>
+        <v>1210</v>
       </c>
       <c r="B314" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C314">
-        <v>439</v>
+        <v>200</v>
       </c>
       <c r="D314">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="E314" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F314" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G314" t="s">
         <v>1035</v>
@@ -12499,27 +12493,27 @@
         <v>69</v>
       </c>
       <c r="I314" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>1212</v>
+        <v>200</v>
       </c>
       <c r="B315" t="s">
-        <v>1039</v>
+        <v>27</v>
       </c>
       <c r="C315">
-        <v>200</v>
+        <v>575</v>
       </c>
       <c r="D315">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E315" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F315" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G315" t="s">
         <v>1035</v>
@@ -12528,27 +12522,27 @@
         <v>69</v>
       </c>
       <c r="I315" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B316" t="s">
-        <v>27</v>
+        <v>1040</v>
       </c>
       <c r="C316">
-        <v>575</v>
+        <v>650</v>
       </c>
       <c r="D316">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E316" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F316" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G316" t="s">
         <v>1035</v>
@@ -12557,56 +12551,56 @@
         <v>69</v>
       </c>
       <c r="I316" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>203</v>
+        <v>934</v>
       </c>
       <c r="B317" t="s">
-        <v>1040</v>
+        <v>936</v>
       </c>
       <c r="C317">
-        <v>650</v>
+        <v>735</v>
       </c>
       <c r="D317">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="E317" t="s">
-        <v>204</v>
+        <v>937</v>
       </c>
       <c r="F317" t="s">
-        <v>205</v>
+        <v>935</v>
       </c>
       <c r="G317" t="s">
-        <v>1035</v>
+        <v>501</v>
       </c>
       <c r="H317" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="I317" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>934</v>
+        <v>943</v>
       </c>
       <c r="B318" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="C318">
-        <v>735</v>
+        <v>890</v>
       </c>
       <c r="D318">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E318" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="F318" t="s">
-        <v>935</v>
+        <v>944</v>
       </c>
       <c r="G318" t="s">
         <v>501</v>
@@ -12615,27 +12609,27 @@
         <v>12</v>
       </c>
       <c r="I318" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>943</v>
+        <v>933</v>
       </c>
       <c r="B319" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="C319">
-        <v>890</v>
+        <v>749</v>
       </c>
       <c r="D319">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E319" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
       <c r="F319" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="G319" t="s">
         <v>501</v>
@@ -12644,27 +12638,27 @@
         <v>12</v>
       </c>
       <c r="I319" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="B320" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="C320">
-        <v>749</v>
+        <v>879</v>
       </c>
       <c r="D320">
-        <v>400</v>
+        <v>650</v>
       </c>
       <c r="E320" t="s">
-        <v>932</v>
+        <v>941</v>
       </c>
       <c r="F320" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="G320" t="s">
         <v>501</v>
@@ -12673,27 +12667,27 @@
         <v>12</v>
       </c>
       <c r="I320" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>939</v>
+        <v>950</v>
       </c>
       <c r="B321" t="s">
-        <v>938</v>
+        <v>949</v>
       </c>
       <c r="C321">
-        <v>879</v>
+        <v>715</v>
       </c>
       <c r="D321">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="E321" t="s">
-        <v>941</v>
+        <v>952</v>
       </c>
       <c r="F321" t="s">
-        <v>940</v>
+        <v>951</v>
       </c>
       <c r="G321" t="s">
         <v>501</v>
@@ -12702,27 +12696,27 @@
         <v>12</v>
       </c>
       <c r="I321" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B322" t="s">
-        <v>949</v>
+        <v>942</v>
       </c>
       <c r="C322">
-        <v>715</v>
+        <v>635</v>
       </c>
       <c r="D322">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="E322" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="F322" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="G322" t="s">
         <v>501</v>
@@ -12731,27 +12725,27 @@
         <v>12</v>
       </c>
       <c r="I322" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A323" t="s">
-        <v>946</v>
+      <c r="A323" s="3" t="s">
+        <v>926</v>
       </c>
       <c r="B323" t="s">
-        <v>942</v>
+        <v>928</v>
       </c>
       <c r="C323">
-        <v>635</v>
+        <v>570</v>
       </c>
       <c r="D323">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E323" t="s">
-        <v>948</v>
+        <v>929</v>
       </c>
       <c r="F323" t="s">
-        <v>947</v>
+        <v>927</v>
       </c>
       <c r="G323" t="s">
         <v>501</v>
@@ -12760,27 +12754,27 @@
         <v>12</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A324" s="3" t="s">
-        <v>926</v>
+      <c r="A324" t="s">
+        <v>922</v>
       </c>
       <c r="B324" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="C324">
-        <v>570</v>
+        <v>497</v>
       </c>
       <c r="D324">
         <v>300</v>
       </c>
       <c r="E324" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="F324" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="G324" t="s">
         <v>501</v>
@@ -12789,27 +12783,27 @@
         <v>12</v>
       </c>
       <c r="I324" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>922</v>
+        <v>247</v>
       </c>
       <c r="B325" t="s">
-        <v>923</v>
+        <v>1179</v>
       </c>
       <c r="C325">
-        <v>497</v>
+        <v>678</v>
       </c>
       <c r="D325">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="E325" t="s">
-        <v>925</v>
+        <v>248</v>
       </c>
       <c r="F325" t="s">
-        <v>924</v>
+        <v>249</v>
       </c>
       <c r="G325" t="s">
         <v>501</v>
@@ -12818,27 +12812,24 @@
         <v>12</v>
       </c>
       <c r="I325" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>247</v>
+        <v>432</v>
       </c>
       <c r="B326" t="s">
-        <v>1181</v>
+        <v>433</v>
       </c>
       <c r="C326">
-        <v>678</v>
-      </c>
-      <c r="D326">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="E326" t="s">
-        <v>248</v>
+        <v>434</v>
       </c>
       <c r="F326" t="s">
-        <v>249</v>
+        <v>435</v>
       </c>
       <c r="G326" t="s">
         <v>501</v>
@@ -12847,24 +12838,27 @@
         <v>12</v>
       </c>
       <c r="I326" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>432</v>
+        <v>243</v>
       </c>
       <c r="B327" t="s">
-        <v>433</v>
+        <v>244</v>
       </c>
       <c r="C327">
-        <v>100</v>
+        <v>419.19</v>
+      </c>
+      <c r="D327">
+        <v>300</v>
       </c>
       <c r="E327" t="s">
-        <v>434</v>
+        <v>245</v>
       </c>
       <c r="F327" t="s">
-        <v>435</v>
+        <v>246</v>
       </c>
       <c r="G327" t="s">
         <v>501</v>
@@ -12873,27 +12867,27 @@
         <v>12</v>
       </c>
       <c r="I327" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B328" t="s">
-        <v>244</v>
+        <v>1180</v>
       </c>
       <c r="C328">
-        <v>419.19</v>
+        <v>600</v>
       </c>
       <c r="D328">
         <v>300</v>
       </c>
       <c r="E328" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F328" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="G328" t="s">
         <v>501</v>
@@ -12902,27 +12896,27 @@
         <v>12</v>
       </c>
       <c r="I328" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>250</v>
+        <v>502</v>
       </c>
       <c r="B329" t="s">
-        <v>1182</v>
+        <v>503</v>
       </c>
       <c r="C329">
-        <v>600</v>
+        <v>911</v>
       </c>
       <c r="D329">
-        <v>300</v>
+        <v>540</v>
       </c>
       <c r="E329" t="s">
-        <v>251</v>
+        <v>504</v>
       </c>
       <c r="F329" t="s">
-        <v>252</v>
+        <v>505</v>
       </c>
       <c r="G329" t="s">
         <v>501</v>
@@ -12931,27 +12925,27 @@
         <v>12</v>
       </c>
       <c r="I329" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="B330" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C330">
-        <v>911</v>
+        <v>800</v>
       </c>
       <c r="D330">
-        <v>540</v>
+        <v>400</v>
       </c>
       <c r="E330" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="F330" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="G330" t="s">
         <v>501</v>
@@ -12960,27 +12954,27 @@
         <v>12</v>
       </c>
       <c r="I330" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B331" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C331">
-        <v>800</v>
+        <v>365</v>
       </c>
       <c r="D331">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E331" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="F331" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="G331" t="s">
         <v>501</v>
@@ -12989,27 +12983,24 @@
         <v>12</v>
       </c>
       <c r="I331" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>506</v>
+        <v>1170</v>
       </c>
       <c r="B332" t="s">
-        <v>507</v>
+        <v>1171</v>
       </c>
       <c r="C332">
-        <v>365</v>
-      </c>
-      <c r="D332">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E332" t="s">
-        <v>508</v>
+        <v>1173</v>
       </c>
       <c r="F332" t="s">
-        <v>509</v>
+        <v>1172</v>
       </c>
       <c r="G332" t="s">
         <v>501</v>
@@ -13018,24 +13009,27 @@
         <v>12</v>
       </c>
       <c r="I332" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B333" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="C333">
-        <v>350</v>
+        <v>200</v>
+      </c>
+      <c r="D333">
+        <v>170</v>
       </c>
       <c r="E333" t="s">
         <v>1175</v>
       </c>
       <c r="F333" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="G333" t="s">
         <v>501</v>
@@ -13044,36 +13038,7 @@
         <v>12</v>
       </c>
       <c r="I333" s="6" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B334" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C334">
-        <v>200</v>
-      </c>
-      <c r="D334">
-        <v>170</v>
-      </c>
-      <c r="E334" t="s">
-        <v>1177</v>
-      </c>
-      <c r="F334" t="s">
-        <v>1178</v>
-      </c>
-      <c r="G334" t="s">
-        <v>501</v>
-      </c>
-      <c r="H334" t="s">
-        <v>12</v>
-      </c>
-      <c r="I334" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
   </sheetData>

--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -465,7 +465,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>

--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -465,7 +465,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>

--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Proyecto\Catalogo\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Respaldo\Catalogo\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2420" uniqueCount="1354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="1395">
   <si>
     <t>Nombre</t>
   </si>
@@ -4091,6 +4091,133 @@
   </si>
   <si>
     <t>https://panchochacharas.netlify.app/imagenes/4aaa7507c541c0dc0aac5e2393fb2c31.jpeg</t>
+  </si>
+  <si>
+    <t>Aluminio Negro con Mango de Madera, Set de 3 Unidades (24 y 28 cm)</t>
+  </si>
+  <si>
+    <t>Pack de Sartenes Antiadherentes</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_718669-MLA109014019546_032026-F.webp</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pack-de-sartenes-antiadherentes-xinest-de-aluminio-negro-con-mango-de-madera-set-de-3-unidades-24-y-28-cm/p/MLM67441876?pdp_filters=item_id%3AMLM5595517674#&amp;gid=1&amp;pid=1</t>
+  </si>
+  <si>
+    <t>Pistola Para Pintar Eléctrica</t>
+  </si>
+  <si>
+    <t>1500 W con Tanque de 1 L y 4 Boquillas</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pistola-para-pintar-electrica-kozfule-1500-w-con-tanque-de-1-l-y-4-boquillas/p/MLM74444635?pdp_filters=item_id:MLM5570051942#&amp;gid=1&amp;pid=1</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_766896-MLA112984703506_072026-F.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pistola Pintar Inalámbrica </t>
+  </si>
+  <si>
+    <t>24v 3 Baterías Profesional Hvlp</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-5179674838-pistola-pintar-inalambrica-24v-3-baterias-profesional-hvlp-_JM?quantity=1#&amp;gid=1&amp;pid=1</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_693699-CBT113902483621_062026-F-pistola-pintar-inalambrica-24v-3-baterias-profesional-hvlp.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set De Bloques Bonsái Flor Cerezo </t>
+  </si>
+  <si>
+    <t>775 Piezas</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-5457979378-set-de-bloques-bonsai-flor-cerezo-775-piezas-_JM?quantity=1#&amp;gid=1&amp;pid=1</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_980602-CBT111696934142_062026-F-set-de-bloques-bonsai-flor-cerezo-775-piezas.webp</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-2999989219-set-de-bloques-de-construccion-de-bote-482-piezas-ninos-_JM?quantity=1</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_676962-CBT111935393828_062026-F-set-de-bloques-de-construccion-de-bote-482-piezas-ninos.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set De Bloques De Construcción De Bote </t>
+  </si>
+  <si>
+    <t>482 Piezas</t>
+  </si>
+  <si>
+    <t>Epicentro Restaurador De Bajos Audishako MAX-MX Ecualizador Para Sistema De Audio Auto, Pickup Y Suv, Para Subwoofer, Incluye Control Remoto Y Accesorios De Instalación</t>
+  </si>
+  <si>
+    <t>Sistema de audio</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/epicentro-restaurador-de-bajos-audishako-max-mx-ecualizador-para-sistema-de-audio-auto-pickup-y-suv-para-subwoofer-incluye-control-remoto-y-accesorios-de-instalacion/p/MLM51149598?pdp_filters=item_id:MLM2546220371</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_831886-MLA99444153134_112025-F.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epicentro Audishako Max-02 Restaurador De Bajos Para Auto, Subwoofer Para Carro, Pickups Y Suv, Accesorios Para Auto Audio Diseño En Relieve 3d, Incluye Dash Remoto Control De Bajos
+</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/epicentro-audishako-max-02-restaurador-de-bajos-para-auto-subwoofer-para-carro-pickups-y-suv-accesorios-para-auto-audio-diseno-en-relieve-3d-incluye-dash-remoto-control-de-bajos/p/MLM64640099?pdp_filters=item_id:MLM4697020282</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_801469-MLA105455425099_012026-F.webp</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-5166780854-espejo-luz-led-touch-pared-bano-decorativo-tocador-3-luces-_JM?quantity=1&amp;variation_id=192915215412</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_647415-CBT111501198724_062026-F-espejo-luz-led-touch-pared-bano-decorativo-tocador-3-luces.webp</t>
+  </si>
+  <si>
+    <t>Espejo Luz Led Touch Pared Baño Decorativo Tocador 3 Luces</t>
+  </si>
+  <si>
+    <t>Altura: 52.5 cm, Ancho: 37.5 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversor Hzero 600W de Onda Senoidal Modificada para Auto con 2 Salidas AC y 2 USB
+</t>
+  </si>
+  <si>
+    <t>Inversor</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/inversor-hzero-600w-de-onda-senoidal-modificada-para-auto-con-2-salidas-ac-y-2-usb/p/MLM52856540?pdp_filters=item_id:MLM2587727551</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_996228-MLA110110565683_042026-F.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hzero Inversor De Corriente 1000W 12v A 110v, Transformador Portatil Para Coche Con 2 Ac Y 2 Usb, Ideal Para Respaldo Eléctrico Hogar, Protección Eléctrica Múltiple
+</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/hzero-inversor-de-corriente-1000w-12v-a-110v-transformador-portatil-para-coche-con-2-ac-y-2-usb-ideal-para-respaldo-electrico-hogar-proteccion-electrica-multiple/p/MLM57806893?pdp_filters=item_id:MLM2587781837</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_911255-MLA109065062914_032026-F.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hzero Convertidor Inversor De Corriente 4000W 12v-110v Para Herramientas Eléctricas Feria Exterior, Transformador Portatil 2 AC+ 2 USB, Protección Eléctrica Múltiple
+</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/hzero-convertidor-inversor-de-corriente-4000w-12v-110v-para-herramientas-electricas-feria-exterior-transformador-portatil-2-ac-2-usb-proteccion-electrica-multiple/p/MLM68452917?pdp_filters=item_id:MLM5235134128</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_987469-MLA110791222267_042026-F.webp</t>
   </si>
 </sst>
 </file>
@@ -4264,8 +4391,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H367" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H367"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H378" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H378"/>
   <sortState ref="A2:H342">
     <sortCondition ref="A1:A342"/>
   </sortState>
@@ -4568,7 +4695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I367"/>
+  <dimension ref="A1:I378"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" style="1" customWidth="1"/>
@@ -14501,13 +14628,299 @@
         <v>1346</v>
       </c>
       <c r="G367" s="7" t="s">
-        <v>1338</v>
+        <v>441</v>
       </c>
       <c r="H367" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I367" s="14" t="s">
         <v>903</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A368" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C368" s="7">
+        <v>1383</v>
+      </c>
+      <c r="D368" s="7">
+        <v>630</v>
+      </c>
+      <c r="E368" s="15" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F368" s="15" t="s">
+        <v>1357</v>
+      </c>
+      <c r="G368" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="H368" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A369" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C369" s="7">
+        <v>899</v>
+      </c>
+      <c r="D369" s="7">
+        <v>485</v>
+      </c>
+      <c r="E369" s="15" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F369" s="15" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G369" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="H369" s="7" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A370" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C370" s="7">
+        <v>1050</v>
+      </c>
+      <c r="D370" s="7">
+        <v>600</v>
+      </c>
+      <c r="E370" s="15" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F370" s="15" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G370" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="H370" s="7" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A371" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C371" s="7">
+        <v>1084</v>
+      </c>
+      <c r="D371" s="7">
+        <v>650</v>
+      </c>
+      <c r="E371" s="15" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F371" s="15" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G371" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="H371" s="7" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A372" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C372" s="7">
+        <v>1265</v>
+      </c>
+      <c r="D372" s="7">
+        <v>650</v>
+      </c>
+      <c r="E372" s="15" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F372" s="15" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G372" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="H372" s="7" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A373" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C373" s="7">
+        <v>1225</v>
+      </c>
+      <c r="D373" s="7">
+        <v>700</v>
+      </c>
+      <c r="E373" s="15" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F373" s="15" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G373" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="H373" s="7" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A374" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C374" s="7">
+        <v>1225</v>
+      </c>
+      <c r="D374" s="7">
+        <v>700</v>
+      </c>
+      <c r="E374" s="15" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F374" s="15" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G374" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="H374" s="7" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A375" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C375" s="7">
+        <v>535</v>
+      </c>
+      <c r="D375" s="7">
+        <v>400</v>
+      </c>
+      <c r="E375" s="15" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F375" s="15" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G375" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="H375" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A376" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C376" s="7">
+        <v>1033</v>
+      </c>
+      <c r="D376" s="7">
+        <v>675</v>
+      </c>
+      <c r="E376" s="15" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F376" s="15" t="s">
+        <v>1387</v>
+      </c>
+      <c r="G376" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="H376" s="7" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A377" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C377" s="7">
+        <v>614</v>
+      </c>
+      <c r="D377" s="7">
+        <v>375</v>
+      </c>
+      <c r="E377" s="15" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F377" s="15" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G377" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="H377" s="7" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A378" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C378" s="7">
+        <v>946</v>
+      </c>
+      <c r="D378" s="7">
+        <v>575</v>
+      </c>
+      <c r="E378" s="15" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F378" s="15" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G378" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="H378" s="7" t="s">
+        <v>535</v>
       </c>
     </row>
   </sheetData>
@@ -14521,11 +14934,33 @@
     <hyperlink ref="E263" r:id="rId7"/>
     <hyperlink ref="E343" r:id="rId8"/>
     <hyperlink ref="E157" r:id="rId9"/>
+    <hyperlink ref="E368" r:id="rId10"/>
+    <hyperlink ref="F368" r:id="rId11" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="F369" r:id="rId12" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="E369" r:id="rId13"/>
+    <hyperlink ref="F370" r:id="rId14" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="E370" r:id="rId15"/>
+    <hyperlink ref="F371" r:id="rId16" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="E371" r:id="rId17"/>
+    <hyperlink ref="F372" r:id="rId18"/>
+    <hyperlink ref="E372" r:id="rId19"/>
+    <hyperlink ref="F373" r:id="rId20"/>
+    <hyperlink ref="E373" r:id="rId21"/>
+    <hyperlink ref="F374"/>
+    <hyperlink ref="E374" r:id="rId22"/>
+    <hyperlink ref="F375" r:id="rId23"/>
+    <hyperlink ref="E375" r:id="rId24"/>
+    <hyperlink ref="F376" r:id="rId25"/>
+    <hyperlink ref="E376" r:id="rId26"/>
+    <hyperlink ref="F377" r:id="rId27"/>
+    <hyperlink ref="E377" r:id="rId28"/>
+    <hyperlink ref="F378" r:id="rId29"/>
+    <hyperlink ref="E378" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId31"/>
   <tableParts count="1">
-    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId32"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="1430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2539" uniqueCount="1434">
   <si>
     <t>Nombre</t>
   </si>
@@ -4325,6 +4325,19 @@
   </si>
   <si>
     <t>Dimensiones: 21.5 cm x 24.5 cm x 27.5 cm</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/triciclo-electrico-para-ninos-ykioea-de-drift-con-control-remoto-bluetooth-y-3-velocidades/p/MLM63671276</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_715614-MLA103111958883_122025-F.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velocidad máxima: 20 km/h, Peso máximo soportado. 85 kg
+</t>
+  </si>
+  <si>
+    <t>Triciclo Eléctrico para Niños, Adolescentes y Adultos de Drift con Control Remoto, Bluetooth y 3 Velocidades</t>
   </si>
 </sst>
 </file>
@@ -4498,8 +4511,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H386" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H386"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H387" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H387"/>
   <sortState ref="A2:H342">
     <sortCondition ref="A1:A342"/>
   </sortState>
@@ -4802,7 +4815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I386"/>
+  <dimension ref="A1:I387"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" style="1" customWidth="1"/>
@@ -15235,6 +15248,32 @@
       </c>
       <c r="H386" s="7" t="s">
         <v>211</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A387" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C387" s="7">
+        <v>4699</v>
+      </c>
+      <c r="D387" s="7">
+        <v>2832</v>
+      </c>
+      <c r="E387" s="15" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F387" s="15" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G387" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="H387" s="7" t="s">
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -15292,11 +15331,13 @@
     <hyperlink ref="E385" r:id="rId50" display="https://http2.mlstatic.com/D_NQ_NP_2X_984373-MLA112451559563_052026-F.webp"/>
     <hyperlink ref="F386" r:id="rId51"/>
     <hyperlink ref="E386" r:id="rId52"/>
+    <hyperlink ref="F387" r:id="rId53"/>
+    <hyperlink ref="E387" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId53"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId55"/>
   <tableParts count="1">
-    <tablePart r:id="rId54"/>
+    <tablePart r:id="rId56"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2539" uniqueCount="1434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2547" uniqueCount="1438">
   <si>
     <t>Nombre</t>
   </si>
@@ -4338,6 +4338,18 @@
   </si>
   <si>
     <t>Triciclo Eléctrico para Niños, Adolescentes y Adultos de Drift con Control Remoto, Bluetooth y 3 Velocidades</t>
+  </si>
+  <si>
+    <t>Batidora De Inmersión Trituradora Electrodomesticos</t>
+  </si>
+  <si>
+    <t>De 1000w</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-5261364026-batidora-de-inmersion-trituradora-de-1000w-electrodomesticos-_JM?quantity=1&amp;sid=purchases</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_816888-CBT110109284844_042026-F-batidora-de-inmersion-trituradora-de-1000w-electrodomesticos.webp</t>
   </si>
 </sst>
 </file>
@@ -4382,7 +4394,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4404,6 +4416,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4432,7 +4450,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4461,6 +4479,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -4511,8 +4530,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H387" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H387"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H388" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H388"/>
   <sortState ref="A2:H342">
     <sortCondition ref="A1:A342"/>
   </sortState>
@@ -4815,7 +4834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I387"/>
+  <dimension ref="A1:I388"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" style="1" customWidth="1"/>
@@ -4866,7 +4885,7 @@
         <v>350</v>
       </c>
       <c r="D2" s="7">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>1055</v>
@@ -6120,7 +6139,7 @@
         <v>399</v>
       </c>
       <c r="D48" s="7">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>471</v>
@@ -6805,10 +6824,10 @@
         <v>865</v>
       </c>
       <c r="C73" s="7">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D73" s="7">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>898</v>
@@ -8608,7 +8627,7 @@
         <v>1069</v>
       </c>
       <c r="C140" s="7">
-        <v>398</v>
+        <v>599</v>
       </c>
       <c r="D140" s="7">
         <v>300</v>
@@ -9103,6 +9122,9 @@
       <c r="C158" s="7">
         <v>350</v>
       </c>
+      <c r="D158" s="7">
+        <v>300</v>
+      </c>
       <c r="E158" s="7" t="s">
         <v>481</v>
       </c>
@@ -9110,12 +9132,14 @@
         <v>482</v>
       </c>
       <c r="G158" s="7" t="s">
-        <v>438</v>
+        <v>1326</v>
       </c>
       <c r="H158" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I158" s="9"/>
+      <c r="I158" s="16" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
@@ -9958,7 +9982,7 @@
         <v>347</v>
       </c>
       <c r="D190" s="7">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E190" s="7" t="s">
         <v>191</v>
@@ -9987,7 +10011,7 @@
         <v>498</v>
       </c>
       <c r="D191" s="7">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E191" s="7" t="s">
         <v>194</v>
@@ -10302,7 +10326,7 @@
         <v>398</v>
       </c>
       <c r="D203" s="7">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E203" s="7" t="s">
         <v>201</v>
@@ -12506,10 +12530,10 @@
         <v>367</v>
       </c>
       <c r="C282" s="7">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D282" s="7">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="E282" s="7" t="s">
         <v>893</v>
@@ -13170,7 +13194,7 @@
         <v>350</v>
       </c>
       <c r="D306" s="7">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="E306" s="7" t="s">
         <v>1096</v>
@@ -13196,10 +13220,10 @@
         <v>1193</v>
       </c>
       <c r="C307" s="7">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="D307" s="7">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="E307" s="7" t="s">
         <v>1098</v>
@@ -14111,7 +14135,7 @@
         <v>850</v>
       </c>
       <c r="D343" s="7">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="E343" s="7" t="s">
         <v>1236</v>
@@ -14434,7 +14458,7 @@
         <v>399</v>
       </c>
       <c r="D356" s="7">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E356" s="7" t="s">
         <v>1284</v>
@@ -15198,7 +15222,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="385" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
         <v>1423</v>
       </c>
@@ -15224,7 +15248,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="386" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A386" s="1" t="s">
         <v>1428</v>
       </c>
@@ -15250,7 +15274,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="387" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A387" s="1" t="s">
         <v>1433</v>
       </c>
@@ -15274,6 +15298,35 @@
       </c>
       <c r="H387" s="7" t="s">
         <v>531</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A388" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C388" s="7">
+        <v>349</v>
+      </c>
+      <c r="D388" s="7">
+        <v>295</v>
+      </c>
+      <c r="E388" s="15" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F388" s="15" t="s">
+        <v>1436</v>
+      </c>
+      <c r="G388" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="H388" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I388" s="14" t="s">
+        <v>892</v>
       </c>
     </row>
   </sheetData>
@@ -15333,11 +15386,13 @@
     <hyperlink ref="E386" r:id="rId52"/>
     <hyperlink ref="F387" r:id="rId53"/>
     <hyperlink ref="E387" r:id="rId54"/>
+    <hyperlink ref="F388" r:id="rId55"/>
+    <hyperlink ref="E388" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId55"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId57"/>
   <tableParts count="1">
-    <tablePart r:id="rId56"/>
+    <tablePart r:id="rId58"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2547" uniqueCount="1438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="1453">
   <si>
     <t>Nombre</t>
   </si>
@@ -4350,6 +4350,51 @@
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_816888-CBT110109284844_042026-F-batidora-de-inmersion-trituradora-de-1000w-electrodomesticos.webp</t>
+  </si>
+  <si>
+    <t>Fotos</t>
+  </si>
+  <si>
+    <t>Videos</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_977864-MLA82522530268_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728802-MLA82808708997_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_714871-MLA82808836891_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_701331-MLA82522530264_032025-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_975974-MLA110282318125_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_901430-MLA109417756350_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_716338-MLA109417409976_042026-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019ee6404503792cb5a83c5452d9eb90/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_881622-MLA100107482214_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_853470-MLA83211986807_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_889429-MLA82708797484_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_812049-MLA83211986809_032025-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_691159-MLA74393127536_022024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_797614-MLA74213272750_012024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_768655-MLA74336317695_012024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_993093-MLA74278567380_022024-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_665383-MLA110622349795_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_998155-MLA109812957268_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_967066-MLA109813016698_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_993911-MLA110707086745_042026-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019f53b0c5ba7e4aa020656ff7567db8/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_754117-MLA87918629604_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_955266-MLA88256438081_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_924778-MLA88256272783_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_848672-MLA88256224285_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_727336-MLA88256418511_072025-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_651538-MLA109474609027_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_786870-MLA109384870397_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_877937-MLA109385877631_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_883221-MLA109385877633_032026-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_659872-MLA110558100656_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_654212-MLA110558217136_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728798-MLA110558100602_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_731400-MLA110558217100_052026-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019f04af571c7ee5add44bdb2a1e4d1f/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_693716-MLA109741709300_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_840288-MLA110631194955_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_855707-MLA110246770132_052026-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_704682-MLA112632086794_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648062-MLA114215908179_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_721338-MLA112631444306_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_666014-MLA110019279904_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_747141-MLA110928994963_042026-F.webp</t>
   </si>
 </sst>
 </file>
@@ -4394,36 +4439,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -4450,7 +4471,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4471,21 +4492,23 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="12">
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -4530,20 +4553,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:H388" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H388"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J388" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J388">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Amplificador De Audio Para Auto"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState ref="A2:H342">
     <sortCondition ref="A1:A342"/>
   </sortState>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Nombre" dataDxfId="7"/>
-    <tableColumn id="2" name="Descripción" dataDxfId="6"/>
-    <tableColumn id="3" name="Precio" dataDxfId="5"/>
-    <tableColumn id="4" name="PrecioRebaja" dataDxfId="4"/>
-    <tableColumn id="5" name="ImagenURL" dataDxfId="3"/>
-    <tableColumn id="6" name="LinkCompra" dataDxfId="2"/>
-    <tableColumn id="7" name="Caja" dataDxfId="1"/>
-    <tableColumn id="8" name="Categoria" dataDxfId="0"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Nombre" dataDxfId="9"/>
+    <tableColumn id="2" name="Descripción" dataDxfId="8"/>
+    <tableColumn id="3" name="Precio" dataDxfId="7"/>
+    <tableColumn id="4" name="PrecioRebaja" dataDxfId="6"/>
+    <tableColumn id="5" name="ImagenURL" dataDxfId="5"/>
+    <tableColumn id="6" name="LinkCompra" dataDxfId="4"/>
+    <tableColumn id="7" name="Caja" dataDxfId="3"/>
+    <tableColumn id="8" name="Categoria" dataDxfId="2"/>
+    <tableColumn id="9" name="Fotos" dataDxfId="1"/>
+    <tableColumn id="10" name="Videos" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4834,7 +4865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I388"/>
+  <dimension ref="A1:J388"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" style="1" customWidth="1"/>
@@ -4848,7 +4879,7 @@
     <col min="9" max="16384" width="9.1796875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4873,8 +4904,14 @@
       <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I1" s="7" t="s">
+        <v>1438</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1083</v>
       </c>
@@ -4899,11 +4936,10 @@
       <c r="H2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+    </row>
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1085</v>
       </c>
@@ -4928,11 +4964,8 @@
       <c r="H3" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>589</v>
       </c>
@@ -4954,11 +4987,8 @@
       <c r="H4" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>155</v>
       </c>
@@ -4983,11 +5013,8 @@
       <c r="H5" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>406</v>
       </c>
@@ -5009,11 +5036,8 @@
       <c r="H6" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>863</v>
       </c>
@@ -5038,11 +5062,8 @@
       <c r="H7" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>104</v>
       </c>
@@ -5067,11 +5088,8 @@
       <c r="H8" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>694</v>
       </c>
@@ -5096,11 +5114,8 @@
       <c r="H9" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>862</v>
       </c>
@@ -5125,11 +5140,8 @@
       <c r="H10" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>238</v>
       </c>
@@ -5154,11 +5166,8 @@
       <c r="H11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>751</v>
       </c>
@@ -5183,11 +5192,8 @@
       <c r="H12" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>972</v>
       </c>
@@ -5209,11 +5215,8 @@
       <c r="H13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>633</v>
       </c>
@@ -5238,11 +5241,8 @@
       <c r="H14" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>993</v>
       </c>
@@ -5264,11 +5264,8 @@
       <c r="H15" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>109</v>
       </c>
@@ -5291,7 +5288,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>857</v>
       </c>
@@ -5314,7 +5311,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>764</v>
       </c>
@@ -5339,11 +5336,8 @@
       <c r="H18" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>579</v>
       </c>
@@ -5365,9 +5359,8 @@
       <c r="H19" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I19" s="9"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>790</v>
       </c>
@@ -5389,11 +5382,8 @@
       <c r="H20" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I20" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>766</v>
       </c>
@@ -5418,11 +5408,8 @@
       <c r="H21" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I21" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>534</v>
       </c>
@@ -5444,11 +5431,8 @@
       <c r="H22" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I22" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>534</v>
       </c>
@@ -5470,11 +5454,8 @@
       <c r="H23" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I23" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>534</v>
       </c>
@@ -5496,11 +5477,8 @@
       <c r="H24" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I24" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>496</v>
       </c>
@@ -5525,11 +5503,8 @@
       <c r="H25" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I25" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>111</v>
       </c>
@@ -5554,11 +5529,8 @@
       <c r="H26" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I26" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>851</v>
       </c>
@@ -5583,11 +5555,8 @@
       <c r="H27" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I27" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>840</v>
       </c>
@@ -5612,11 +5581,8 @@
       <c r="H28" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I28" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>114</v>
       </c>
@@ -5638,11 +5604,8 @@
       <c r="H29" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I29" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>841</v>
       </c>
@@ -5667,11 +5630,8 @@
       <c r="H30" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I30" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>850</v>
       </c>
@@ -5696,11 +5656,8 @@
       <c r="H31" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I31" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>842</v>
       </c>
@@ -5725,11 +5682,8 @@
       <c r="H32" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I32" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>845</v>
       </c>
@@ -5754,11 +5708,8 @@
       <c r="H33" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I33" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>843</v>
       </c>
@@ -5783,11 +5734,8 @@
       <c r="H34" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I34" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>844</v>
       </c>
@@ -5809,11 +5757,8 @@
       <c r="H35" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I35" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>1062</v>
       </c>
@@ -5838,9 +5783,8 @@
       <c r="H36" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>1330</v>
       </c>
@@ -5865,11 +5809,8 @@
       <c r="H37" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I37" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>1001</v>
       </c>
@@ -5891,9 +5832,8 @@
       <c r="H38" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I38" s="9"/>
-    </row>
-    <row r="39" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>599</v>
       </c>
@@ -5915,9 +5855,8 @@
       <c r="H39" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>923</v>
       </c>
@@ -5942,11 +5881,8 @@
       <c r="H40" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I40" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>77</v>
       </c>
@@ -5965,11 +5901,8 @@
       <c r="H41" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I41" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>186</v>
       </c>
@@ -5991,11 +5924,8 @@
       <c r="H42" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I42" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>159</v>
       </c>
@@ -6020,11 +5950,8 @@
       <c r="H43" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I43" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>930</v>
       </c>
@@ -6046,11 +5973,8 @@
       <c r="H44" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I44" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>935</v>
       </c>
@@ -6072,11 +5996,8 @@
       <c r="H45" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I45" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>931</v>
       </c>
@@ -6098,11 +6019,8 @@
       <c r="H46" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I46" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>931</v>
       </c>
@@ -6124,11 +6042,8 @@
       <c r="H47" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I47" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>469</v>
       </c>
@@ -6153,11 +6068,8 @@
       <c r="H48" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I48" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>203</v>
       </c>
@@ -6182,11 +6094,8 @@
       <c r="H49" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I49" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>337</v>
       </c>
@@ -6211,11 +6120,8 @@
       <c r="H50" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I50" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>188</v>
       </c>
@@ -6237,11 +6143,8 @@
       <c r="H51" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I51" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>809</v>
       </c>
@@ -6266,11 +6169,8 @@
       <c r="H52" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I52" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>808</v>
       </c>
@@ -6295,11 +6195,8 @@
       <c r="H53" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I53" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>458</v>
       </c>
@@ -6324,11 +6221,8 @@
       <c r="H54" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I54" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>221</v>
       </c>
@@ -6353,11 +6247,8 @@
       <c r="H55" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I55" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>814</v>
       </c>
@@ -6382,11 +6273,8 @@
       <c r="H56" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I56" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>900</v>
       </c>
@@ -6411,11 +6299,8 @@
       <c r="H57" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I57" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>1329</v>
       </c>
@@ -6440,11 +6325,8 @@
       <c r="H58" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I58" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>979</v>
       </c>
@@ -6466,11 +6348,8 @@
       <c r="H59" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I59" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>797</v>
       </c>
@@ -6492,9 +6371,8 @@
       <c r="H60" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I60" s="9"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>1064</v>
       </c>
@@ -6507,10 +6385,10 @@
       <c r="D61" s="7">
         <v>1000</v>
       </c>
-      <c r="E61" s="15" t="s">
+      <c r="E61" s="12" t="s">
         <v>1336</v>
       </c>
-      <c r="F61" s="15" t="s">
+      <c r="F61" s="12" t="s">
         <v>1065</v>
       </c>
       <c r="G61" s="7" t="s">
@@ -6519,11 +6397,8 @@
       <c r="H61" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I61" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>340</v>
       </c>
@@ -6545,11 +6420,8 @@
       <c r="H62" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I62" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>975</v>
       </c>
@@ -6571,11 +6443,8 @@
       <c r="H63" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I63" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>854</v>
       </c>
@@ -6600,11 +6469,8 @@
       <c r="H64" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I64" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>943</v>
       </c>
@@ -6629,9 +6495,8 @@
       <c r="H65" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I65" s="9"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>945</v>
       </c>
@@ -6656,9 +6521,8 @@
       <c r="H66" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I66" s="9"/>
-    </row>
-    <row r="67" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>1078</v>
       </c>
@@ -6678,16 +6542,19 @@
         <v>1080</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>1026</v>
+        <v>948</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I67" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="I67" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>120</v>
       </c>
@@ -6712,9 +6579,11 @@
       <c r="H68" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I68" s="9"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I68" s="12" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>747</v>
       </c>
@@ -6736,9 +6605,8 @@
       <c r="H69" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I69" s="9"/>
-    </row>
-    <row r="70" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>677</v>
       </c>
@@ -6763,9 +6631,8 @@
       <c r="H70" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I70" s="9"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>344</v>
       </c>
@@ -6787,9 +6654,8 @@
       <c r="H71" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I71" s="9"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>410</v>
       </c>
@@ -6814,9 +6680,8 @@
       <c r="H72" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I72" s="9"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>896</v>
       </c>
@@ -6841,11 +6706,11 @@
       <c r="H73" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I73" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I73" s="12" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>379</v>
       </c>
@@ -6867,11 +6732,8 @@
       <c r="H74" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I74" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>375</v>
       </c>
@@ -6893,11 +6755,8 @@
       <c r="H75" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I75" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>413</v>
       </c>
@@ -6922,9 +6781,8 @@
       <c r="H76" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="I76" s="9"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>787</v>
       </c>
@@ -6949,9 +6807,8 @@
       <c r="H77" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I77" s="9"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>775</v>
       </c>
@@ -6973,11 +6830,8 @@
       <c r="H78" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I78" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>786</v>
       </c>
@@ -6999,9 +6853,8 @@
       <c r="H79" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I79" s="9"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>1035</v>
       </c>
@@ -7026,9 +6879,8 @@
       <c r="H80" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I80" s="9"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>772</v>
       </c>
@@ -7053,9 +6905,8 @@
       <c r="H81" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I81" s="9"/>
-    </row>
-    <row r="82" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>576</v>
       </c>
@@ -7077,9 +6928,8 @@
       <c r="H82" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I82" s="9"/>
-    </row>
-    <row r="83" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>570</v>
       </c>
@@ -7101,9 +6951,8 @@
       <c r="H83" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I83" s="9"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>1041</v>
       </c>
@@ -7128,19 +6977,18 @@
       <c r="H84" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I84" s="9"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>1049</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>1040</v>
       </c>
-      <c r="C85" s="11">
+      <c r="C85" s="9">
         <v>120</v>
       </c>
-      <c r="D85" s="11">
+      <c r="D85" s="9">
         <v>80</v>
       </c>
       <c r="E85" s="7" t="s">
@@ -7155,9 +7003,8 @@
       <c r="H85" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I85" s="9"/>
-    </row>
-    <row r="86" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>314</v>
       </c>
@@ -7182,9 +7029,8 @@
       <c r="H86" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I86" s="9"/>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>602</v>
       </c>
@@ -7206,9 +7052,8 @@
       <c r="H87" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I87" s="9"/>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>381</v>
       </c>
@@ -7233,11 +7078,8 @@
       <c r="H88" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I88" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>1319</v>
       </c>
@@ -7262,11 +7104,8 @@
       <c r="H89" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I89" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>907</v>
       </c>
@@ -7291,11 +7130,8 @@
       <c r="H90" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I90" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>652</v>
       </c>
@@ -7320,9 +7156,8 @@
       <c r="H91" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I91" s="9"/>
-    </row>
-    <row r="92" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>683</v>
       </c>
@@ -7347,11 +7182,8 @@
       <c r="H92" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I92" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>732</v>
       </c>
@@ -7373,11 +7205,8 @@
       <c r="H93" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I93" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>231</v>
       </c>
@@ -7402,9 +7231,8 @@
       <c r="H94" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I94" s="9"/>
-    </row>
-    <row r="95" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>612</v>
       </c>
@@ -7429,9 +7257,8 @@
       <c r="H95" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I95" s="9"/>
-    </row>
-    <row r="96" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>649</v>
       </c>
@@ -7453,9 +7280,8 @@
       <c r="H96" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I96" s="9"/>
-    </row>
-    <row r="97" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>647</v>
       </c>
@@ -7480,9 +7306,8 @@
       <c r="H97" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I97" s="9"/>
-    </row>
-    <row r="98" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>647</v>
       </c>
@@ -7505,7 +7330,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>308</v>
       </c>
@@ -7530,11 +7355,8 @@
       <c r="H99" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I99" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>208</v>
       </c>
@@ -7559,11 +7381,8 @@
       <c r="H100" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I100" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>243</v>
       </c>
@@ -7588,11 +7407,8 @@
       <c r="H101" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="I101" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="102" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>173</v>
       </c>
@@ -7617,11 +7433,8 @@
       <c r="H102" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I102" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="103" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>176</v>
       </c>
@@ -7643,11 +7456,8 @@
       <c r="H103" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I103" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>329</v>
       </c>
@@ -7673,7 +7483,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>465</v>
       </c>
@@ -7696,7 +7506,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>919</v>
       </c>
@@ -7721,11 +7531,8 @@
       <c r="H106" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I106" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>212</v>
       </c>
@@ -7751,7 +7558,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>1004</v>
       </c>
@@ -7776,11 +7583,8 @@
       <c r="H108" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I108" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>347</v>
       </c>
@@ -7806,7 +7610,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>1005</v>
       </c>
@@ -7832,7 +7636,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>1074</v>
       </c>
@@ -7858,7 +7662,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>28</v>
       </c>
@@ -7881,7 +7685,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>30</v>
       </c>
@@ -7904,7 +7708,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>509</v>
       </c>
@@ -7926,11 +7730,8 @@
       <c r="H114" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I114" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>525</v>
       </c>
@@ -7952,11 +7753,8 @@
       <c r="H115" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I115" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>417</v>
       </c>
@@ -7982,7 +7780,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>876</v>
       </c>
@@ -8008,7 +7806,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>868</v>
       </c>
@@ -8033,11 +7831,8 @@
       <c r="H118" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I118" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>421</v>
       </c>
@@ -8062,11 +7857,8 @@
       <c r="H119" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I119" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>79</v>
       </c>
@@ -8091,11 +7883,8 @@
       <c r="H120" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I120" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>701</v>
       </c>
@@ -8120,11 +7909,8 @@
       <c r="H121" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I121" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    </row>
+    <row r="122" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>735</v>
       </c>
@@ -8149,11 +7935,8 @@
       <c r="H122" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I122" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="123" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>687</v>
       </c>
@@ -8178,11 +7961,8 @@
       <c r="H123" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I123" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="124" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>709</v>
       </c>
@@ -8204,11 +7984,8 @@
       <c r="H124" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I124" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>8</v>
       </c>
@@ -8233,11 +8010,8 @@
       <c r="H125" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I125" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>513</v>
       </c>
@@ -8259,11 +8033,8 @@
       <c r="H126" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I126" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>696</v>
       </c>
@@ -8285,11 +8056,8 @@
       <c r="H127" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I127" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="128" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>566</v>
       </c>
@@ -8312,7 +8080,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>246</v>
       </c>
@@ -8334,11 +8102,8 @@
       <c r="H129" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I129" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>249</v>
       </c>
@@ -8363,11 +8128,8 @@
       <c r="H130" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I130" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>252</v>
       </c>
@@ -8392,11 +8154,8 @@
       <c r="H131" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I131" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>384</v>
       </c>
@@ -8421,11 +8180,8 @@
       <c r="H132" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I132" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>388</v>
       </c>
@@ -8450,11 +8206,8 @@
       <c r="H133" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I133" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>82</v>
       </c>
@@ -8476,11 +8229,11 @@
       <c r="H134" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I134" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I134" s="12" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>1025</v>
       </c>
@@ -8505,11 +8258,8 @@
       <c r="H135" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I135" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    </row>
+    <row r="136" spans="1:9" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>990</v>
       </c>
@@ -8531,11 +8281,8 @@
       <c r="H136" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I136" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>446</v>
       </c>
@@ -8560,11 +8307,8 @@
       <c r="H137" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I137" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>85</v>
       </c>
@@ -8586,11 +8330,8 @@
       <c r="H138" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I138" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>288</v>
       </c>
@@ -8615,11 +8356,8 @@
       <c r="H139" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I139" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="140" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>1320</v>
       </c>
@@ -8644,11 +8382,8 @@
       <c r="H140" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I140" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>88</v>
       </c>
@@ -8670,11 +8405,8 @@
       <c r="H141" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I141" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>91</v>
       </c>
@@ -8696,11 +8428,8 @@
       <c r="H142" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I142" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>94</v>
       </c>
@@ -8722,11 +8451,8 @@
       <c r="H143" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I143" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>473</v>
       </c>
@@ -8748,11 +8474,8 @@
       <c r="H144" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I144" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>487</v>
       </c>
@@ -8774,11 +8497,8 @@
       <c r="H145" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I145" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>483</v>
       </c>
@@ -8800,9 +8520,8 @@
       <c r="H146" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I146" s="9"/>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>255</v>
       </c>
@@ -8827,11 +8546,8 @@
       <c r="H147" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I147" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>97</v>
       </c>
@@ -8853,11 +8569,8 @@
       <c r="H148" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I148" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>33</v>
       </c>
@@ -8882,11 +8595,8 @@
       <c r="H149" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I149" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>36</v>
       </c>
@@ -8911,9 +8621,8 @@
       <c r="H150" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I150" s="9"/>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>40</v>
       </c>
@@ -8938,11 +8647,8 @@
       <c r="H151" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I151" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>164</v>
       </c>
@@ -8967,11 +8673,8 @@
       <c r="H152" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I152" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>167</v>
       </c>
@@ -8996,9 +8699,8 @@
       <c r="H153" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I153" s="9"/>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>170</v>
       </c>
@@ -9023,11 +8725,8 @@
       <c r="H154" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I154" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>614</v>
       </c>
@@ -9040,7 +8739,7 @@
       <c r="D155" s="7">
         <v>150</v>
       </c>
-      <c r="E155" s="15" t="s">
+      <c r="E155" s="12" t="s">
         <v>1341</v>
       </c>
       <c r="F155" s="7" t="s">
@@ -9052,11 +8751,8 @@
       <c r="H155" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I155" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>391</v>
       </c>
@@ -9081,9 +8777,8 @@
       <c r="H156" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I156" s="9"/>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>643</v>
       </c>
@@ -9108,11 +8803,8 @@
       <c r="H157" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I157" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>479</v>
       </c>
@@ -9137,11 +8829,8 @@
       <c r="H158" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I158" s="16" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>351</v>
       </c>
@@ -9163,11 +8852,8 @@
       <c r="H159" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I159" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>872</v>
       </c>
@@ -9192,11 +8878,8 @@
       <c r="H160" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I160" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="161" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>608</v>
       </c>
@@ -9218,11 +8901,8 @@
       <c r="H161" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I161" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>43</v>
       </c>
@@ -9244,11 +8924,8 @@
       <c r="H162" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I162" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>715</v>
       </c>
@@ -9273,11 +8950,8 @@
       <c r="H163" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I163" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    </row>
+    <row r="164" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>713</v>
       </c>
@@ -9299,11 +8973,8 @@
       <c r="H164" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I164" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="165" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>705</v>
       </c>
@@ -9325,11 +8996,8 @@
       <c r="H165" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I165" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>291</v>
       </c>
@@ -9354,11 +9022,8 @@
       <c r="H166" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I166" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>499</v>
       </c>
@@ -9380,11 +9045,8 @@
       <c r="H167" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I167" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>304</v>
       </c>
@@ -9409,11 +9071,8 @@
       <c r="H168" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I168" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>124</v>
       </c>
@@ -9435,11 +9094,8 @@
       <c r="H169" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I169" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>1081</v>
       </c>
@@ -9461,9 +9117,8 @@
       <c r="H170" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I170" s="9"/>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>67</v>
       </c>
@@ -9485,9 +9140,8 @@
       <c r="H171" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I171" s="9"/>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>318</v>
       </c>
@@ -9512,9 +9166,8 @@
       <c r="H172" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I172" s="9"/>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>71</v>
       </c>
@@ -9539,9 +9192,8 @@
       <c r="H173" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I173" s="9"/>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>761</v>
       </c>
@@ -9566,9 +9218,8 @@
       <c r="H174" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I174" s="9"/>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>776</v>
       </c>
@@ -9590,9 +9241,8 @@
       <c r="H175" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I175" s="9"/>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>505</v>
       </c>
@@ -9614,9 +9264,8 @@
       <c r="H176" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I176" s="9"/>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>47</v>
       </c>
@@ -9638,11 +9287,8 @@
       <c r="H177" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I177" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>50</v>
       </c>
@@ -9667,9 +9313,8 @@
       <c r="H178" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I178" s="9"/>
-    </row>
-    <row r="179" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="179" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>640</v>
       </c>
@@ -9694,9 +9339,8 @@
       <c r="H179" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I179" s="9"/>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>54</v>
       </c>
@@ -9721,11 +9365,8 @@
       <c r="H180" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I180" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>558</v>
       </c>
@@ -9747,11 +9388,8 @@
       <c r="H181" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I181" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>558</v>
       </c>
@@ -9773,11 +9411,8 @@
       <c r="H182" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I182" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="183" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>996</v>
       </c>
@@ -9799,11 +9434,8 @@
       <c r="H183" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I183" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="184" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>1066</v>
       </c>
@@ -9828,11 +9460,8 @@
       <c r="H184" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I184" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="185" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>956</v>
       </c>
@@ -9854,11 +9483,8 @@
       <c r="H185" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I185" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+    </row>
+    <row r="186" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>743</v>
       </c>
@@ -9883,11 +9509,8 @@
       <c r="H186" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I186" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="187" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>555</v>
       </c>
@@ -9909,11 +9532,8 @@
       <c r="H187" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I187" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="188" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>425</v>
       </c>
@@ -9938,11 +9558,8 @@
       <c r="H188" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I188" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>837</v>
       </c>
@@ -9967,11 +9584,8 @@
       <c r="H189" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I189" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>190</v>
       </c>
@@ -9996,11 +9610,8 @@
       <c r="H190" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I190" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>193</v>
       </c>
@@ -10025,11 +9636,8 @@
       <c r="H191" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I191" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>196</v>
       </c>
@@ -10054,11 +9662,8 @@
       <c r="H192" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I192" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>354</v>
       </c>
@@ -10080,11 +9685,8 @@
       <c r="H193" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I193" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>940</v>
       </c>
@@ -10109,11 +9711,8 @@
       <c r="H194" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I194" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="195" spans="1:9" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>227</v>
       </c>
@@ -10138,11 +9737,11 @@
       <c r="H195" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I195" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="I195" s="12" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>578</v>
       </c>
@@ -10164,11 +9763,8 @@
       <c r="H196" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I196" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="197" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>578</v>
       </c>
@@ -10191,7 +9787,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>960</v>
       </c>
@@ -10201,7 +9797,7 @@
       <c r="C198" s="7">
         <v>300</v>
       </c>
-      <c r="E198" s="10" t="s">
+      <c r="E198" s="8" t="s">
         <v>959</v>
       </c>
       <c r="F198" s="7" t="s">
@@ -10214,7 +9810,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>962</v>
       </c>
@@ -10237,7 +9833,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>595</v>
       </c>
@@ -10260,7 +9856,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>269</v>
       </c>
@@ -10286,7 +9882,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>1010</v>
       </c>
@@ -10311,11 +9907,8 @@
       <c r="H202" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I202" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="203" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>199</v>
       </c>
@@ -10340,11 +9933,8 @@
       <c r="H203" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I203" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>725</v>
       </c>
@@ -10367,7 +9957,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>17</v>
       </c>
@@ -10393,20 +9983,20 @@
         <v>531</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>1048</v>
       </c>
       <c r="B206" s="4" t="s">
         <v>1040</v>
       </c>
-      <c r="C206" s="11">
+      <c r="C206" s="9">
         <v>100</v>
       </c>
-      <c r="D206" s="11">
+      <c r="D206" s="9">
         <v>50</v>
       </c>
-      <c r="E206" s="12" t="s">
+      <c r="E206" s="10" t="s">
         <v>1047</v>
       </c>
       <c r="F206" s="7" t="s">
@@ -10419,7 +10009,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>618</v>
       </c>
@@ -10445,7 +10035,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>738</v>
       </c>
@@ -10471,7 +10061,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>622</v>
       </c>
@@ -10496,11 +10086,8 @@
       <c r="H209" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I209" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>781</v>
       </c>
@@ -10522,11 +10109,8 @@
       <c r="H210" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I210" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>21</v>
       </c>
@@ -10551,11 +10135,8 @@
       <c r="H211" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I211" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>357</v>
       </c>
@@ -10580,9 +10161,8 @@
       <c r="H212" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I212" s="9"/>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>605</v>
       </c>
@@ -10604,9 +10184,8 @@
       <c r="H213" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I213" s="9"/>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>295</v>
       </c>
@@ -10631,11 +10210,8 @@
       <c r="H214" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I214" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>428</v>
       </c>
@@ -10657,9 +10233,8 @@
       <c r="H215" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I215" s="9"/>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>951</v>
       </c>
@@ -10684,11 +10259,8 @@
       <c r="H216" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I216" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>517</v>
       </c>
@@ -10713,11 +10285,8 @@
       <c r="H217" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I217" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>13</v>
       </c>
@@ -10742,11 +10311,8 @@
       <c r="H218" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I218" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>129</v>
       </c>
@@ -10768,11 +10334,8 @@
       <c r="H219" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I219" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>833</v>
       </c>
@@ -10797,11 +10360,8 @@
       <c r="H220" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I220" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>521</v>
       </c>
@@ -10826,11 +10386,8 @@
       <c r="H221" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I221" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="222" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>661</v>
       </c>
@@ -10855,11 +10412,8 @@
       <c r="H222" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I222" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="223" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>661</v>
       </c>
@@ -10884,11 +10438,8 @@
       <c r="H223" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I223" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>661</v>
       </c>
@@ -10913,11 +10464,8 @@
       <c r="H224" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I224" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="225" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>671</v>
       </c>
@@ -10942,11 +10490,8 @@
       <c r="H225" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I225" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>724</v>
       </c>
@@ -10971,11 +10516,8 @@
       <c r="H226" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I226" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="227" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>1028</v>
       </c>
@@ -11000,11 +10542,8 @@
       <c r="H227" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I227" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>885</v>
       </c>
@@ -11029,11 +10568,8 @@
       <c r="H228" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I228" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>864</v>
       </c>
@@ -11046,7 +10582,7 @@
       <c r="D229" s="7">
         <v>100</v>
       </c>
-      <c r="E229" s="10" t="s">
+      <c r="E229" s="8" t="s">
         <v>867</v>
       </c>
       <c r="F229" s="7" t="s">
@@ -11058,11 +10594,8 @@
       <c r="H229" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I229" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>57</v>
       </c>
@@ -11087,11 +10620,8 @@
       <c r="H230" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I230" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>395</v>
       </c>
@@ -11113,11 +10643,8 @@
       <c r="H231" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I231" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>298</v>
       </c>
@@ -11142,11 +10669,8 @@
       <c r="H232" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I232" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>311</v>
       </c>
@@ -11171,11 +10695,8 @@
       <c r="H233" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I233" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>74</v>
       </c>
@@ -11200,11 +10721,8 @@
       <c r="H234" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I234" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>672</v>
       </c>
@@ -11229,11 +10747,8 @@
       <c r="H235" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I235" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>794</v>
       </c>
@@ -11258,11 +10773,8 @@
       <c r="H236" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I236" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="237" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>1317</v>
       </c>
@@ -11287,11 +10799,8 @@
       <c r="H237" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I237" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>1029</v>
       </c>
@@ -11316,11 +10825,8 @@
       <c r="H238" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I238" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>1032</v>
       </c>
@@ -11345,11 +10851,8 @@
       <c r="H239" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I239" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>673</v>
       </c>
@@ -11374,11 +10877,8 @@
       <c r="H240" s="7" t="s">
         <v>675</v>
       </c>
-      <c r="I240" s="9" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>321</v>
       </c>
@@ -11403,11 +10903,8 @@
       <c r="H241" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I241" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>360</v>
       </c>
@@ -11429,11 +10926,8 @@
       <c r="H242" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I242" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>235</v>
       </c>
@@ -11458,11 +10952,8 @@
       <c r="H243" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I243" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>821</v>
       </c>
@@ -11484,11 +10975,8 @@
       <c r="H244" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I244" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>272</v>
       </c>
@@ -11513,11 +11001,8 @@
       <c r="H245" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I245" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>1019</v>
       </c>
@@ -11539,11 +11024,8 @@
       <c r="H246" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I246" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>450</v>
       </c>
@@ -11565,11 +11047,8 @@
       <c r="H247" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I247" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="248" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="248" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>543</v>
       </c>
@@ -11591,11 +11070,8 @@
       <c r="H248" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I248" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="249" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="249" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>657</v>
       </c>
@@ -11620,11 +11096,8 @@
       <c r="H249" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I249" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>259</v>
       </c>
@@ -11646,11 +11119,8 @@
       <c r="H250" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I250" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>135</v>
       </c>
@@ -11675,11 +11145,8 @@
       <c r="H251" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I251" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>138</v>
       </c>
@@ -11704,11 +11171,8 @@
       <c r="H252" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I252" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>141</v>
       </c>
@@ -11733,11 +11197,8 @@
       <c r="H253" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I253" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>721</v>
       </c>
@@ -11762,11 +11223,8 @@
       <c r="H254" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I254" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>399</v>
       </c>
@@ -11791,11 +11249,8 @@
       <c r="H255" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I255" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>914</v>
       </c>
@@ -11817,11 +11272,8 @@
       <c r="H256" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I256" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>1050</v>
       </c>
@@ -11846,11 +11298,8 @@
       <c r="H257" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I257" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>453</v>
       </c>
@@ -11875,11 +11324,8 @@
       <c r="H258" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I258" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>276</v>
       </c>
@@ -11905,7 +11351,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>753</v>
       </c>
@@ -11928,7 +11374,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>301</v>
       </c>
@@ -11941,7 +11387,7 @@
       <c r="D261" s="7">
         <v>600</v>
       </c>
-      <c r="E261" s="15" t="s">
+      <c r="E261" s="12" t="s">
         <v>1339</v>
       </c>
       <c r="G261" s="7" t="s">
@@ -11950,11 +11396,8 @@
       <c r="H261" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I261" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="262" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="262" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>629</v>
       </c>
@@ -11976,11 +11419,8 @@
       <c r="H262" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I262" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="263" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="263" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>757</v>
       </c>
@@ -12005,11 +11445,8 @@
       <c r="H263" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I263" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>431</v>
       </c>
@@ -12034,11 +11471,8 @@
       <c r="H264" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I264" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="265" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="265" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>1020</v>
       </c>
@@ -12063,11 +11497,8 @@
       <c r="H265" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I265" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>880</v>
       </c>
@@ -12092,11 +11523,8 @@
       <c r="H266" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I266" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>279</v>
       </c>
@@ -12121,11 +11549,8 @@
       <c r="H267" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I267" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>262</v>
       </c>
@@ -12150,11 +11575,8 @@
       <c r="H268" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I268" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>363</v>
       </c>
@@ -12179,11 +11601,8 @@
       <c r="H269" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I269" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="270" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="270" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>1291</v>
       </c>
@@ -12205,11 +11624,8 @@
       <c r="H270" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I270" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="271" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="271" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>968</v>
       </c>
@@ -12231,11 +11647,8 @@
       <c r="H271" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="I271" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>266</v>
       </c>
@@ -12257,11 +11670,8 @@
       <c r="H272" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I272" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>1015</v>
       </c>
@@ -12286,11 +11696,11 @@
       <c r="H273" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I273" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I273" s="12" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>435</v>
       </c>
@@ -12315,11 +11725,8 @@
       <c r="H274" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I274" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>282</v>
       </c>
@@ -12344,11 +11751,8 @@
       <c r="H275" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I275" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>285</v>
       </c>
@@ -12373,11 +11777,8 @@
       <c r="H276" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I276" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>818</v>
       </c>
@@ -12402,11 +11803,8 @@
       <c r="H277" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I277" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>462</v>
       </c>
@@ -12431,11 +11829,8 @@
       <c r="H278" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I278" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>218</v>
       </c>
@@ -12448,7 +11843,7 @@
       <c r="D279" s="7">
         <v>300</v>
       </c>
-      <c r="E279" s="15" t="s">
+      <c r="E279" s="12" t="s">
         <v>219</v>
       </c>
       <c r="F279" s="7" t="s">
@@ -12460,11 +11855,8 @@
       <c r="H279" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I279" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>224</v>
       </c>
@@ -12489,11 +11881,8 @@
       <c r="H280" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I280" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>1071</v>
       </c>
@@ -12518,11 +11907,8 @@
       <c r="H281" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I281" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>366</v>
       </c>
@@ -12547,11 +11933,8 @@
       <c r="H282" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I282" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>369</v>
       </c>
@@ -12576,11 +11959,8 @@
       <c r="H283" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I283" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>439</v>
       </c>
@@ -12605,11 +11985,8 @@
       <c r="H284" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I284" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>1024</v>
       </c>
@@ -12634,11 +12011,8 @@
       <c r="H285" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I285" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>1023</v>
       </c>
@@ -12663,11 +12037,8 @@
       <c r="H286" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I286" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>1022</v>
       </c>
@@ -12692,11 +12063,8 @@
       <c r="H287" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I287" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>834</v>
       </c>
@@ -12721,11 +12089,8 @@
       <c r="H288" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I288" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="289" spans="1:9" ht="16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="289" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>1021</v>
       </c>
@@ -12747,11 +12112,8 @@
       <c r="H289" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I289" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>835</v>
       </c>
@@ -12776,11 +12138,8 @@
       <c r="H290" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I290" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>60</v>
       </c>
@@ -12805,21 +12164,18 @@
       <c r="H291" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I291" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>372</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C292" s="13">
+      <c r="C292" s="11">
         <v>200</v>
       </c>
-      <c r="D292" s="13"/>
+      <c r="D292" s="11"/>
       <c r="E292" s="7" t="s">
         <v>373</v>
       </c>
@@ -12832,11 +12188,8 @@
       <c r="H292" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I292" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
         <v>215</v>
       </c>
@@ -12861,11 +12214,8 @@
       <c r="H293" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I293" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
         <v>180</v>
       </c>
@@ -12890,11 +12240,8 @@
       <c r="H294" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I294" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="295" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>325</v>
       </c>
@@ -12919,11 +12266,8 @@
       <c r="H295" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I295" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="296" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="1" t="s">
         <v>183</v>
       </c>
@@ -12948,11 +12292,8 @@
       <c r="H296" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I296" s="8" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
         <v>443</v>
       </c>
@@ -12978,7 +12319,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>623</v>
       </c>
@@ -13004,7 +12345,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>985</v>
       </c>
@@ -13027,7 +12368,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>563</v>
       </c>
@@ -13050,7 +12391,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
         <v>586</v>
       </c>
@@ -13073,7 +12414,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>801</v>
       </c>
@@ -13098,11 +12439,8 @@
       <c r="H302" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I302" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="303" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>1292</v>
       </c>
@@ -13127,11 +12465,8 @@
       <c r="H303" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I303" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="304" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="304" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>1086</v>
       </c>
@@ -13157,7 +12492,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>1090</v>
       </c>
@@ -13183,7 +12518,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>1094</v>
       </c>
@@ -13208,11 +12543,8 @@
       <c r="H306" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I306" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
         <v>1194</v>
       </c>
@@ -13237,11 +12569,8 @@
       <c r="H307" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I307" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>1099</v>
       </c>
@@ -13266,8 +12595,14 @@
       <c r="H308" s="7" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I308" s="12" t="s">
+        <v>1441</v>
+      </c>
+      <c r="J308" s="12" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
         <v>1103</v>
       </c>
@@ -13293,7 +12628,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>1107</v>
       </c>
@@ -13318,11 +12653,8 @@
       <c r="H310" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I310" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
         <v>1109</v>
       </c>
@@ -13347,11 +12679,8 @@
       <c r="H311" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I311" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>1115</v>
       </c>
@@ -13376,11 +12705,8 @@
       <c r="H312" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I312" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
         <v>1119</v>
       </c>
@@ -13406,7 +12732,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
         <v>1127</v>
       </c>
@@ -13426,7 +12752,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
         <v>1129</v>
       </c>
@@ -13446,7 +12772,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
         <v>1133</v>
       </c>
@@ -13469,7 +12795,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
         <v>1137</v>
       </c>
@@ -13489,7 +12815,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
         <v>1141</v>
       </c>
@@ -13511,11 +12837,8 @@
       <c r="H318" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I318" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="319" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="319" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
         <v>1145</v>
       </c>
@@ -13538,7 +12861,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
         <v>1149</v>
       </c>
@@ -13558,7 +12881,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
         <v>1289</v>
       </c>
@@ -13583,11 +12906,8 @@
       <c r="H321" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I321" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
         <v>1156</v>
       </c>
@@ -13612,11 +12932,8 @@
       <c r="H322" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I322" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="323" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="323" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
         <v>1160</v>
       </c>
@@ -13636,7 +12953,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>1164</v>
       </c>
@@ -13659,7 +12976,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
         <v>1168</v>
       </c>
@@ -13684,11 +13001,8 @@
       <c r="H325" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I325" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>1172</v>
       </c>
@@ -13713,11 +13027,8 @@
       <c r="H326" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I326" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="327" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="327" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>1176</v>
       </c>
@@ -13740,7 +13051,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
         <v>1180</v>
       </c>
@@ -13765,11 +13076,8 @@
       <c r="H328" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I328" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
         <v>1183</v>
       </c>
@@ -13789,7 +13097,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
         <v>1318</v>
       </c>
@@ -13811,11 +13119,8 @@
       <c r="H330" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I330" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
         <v>1189</v>
       </c>
@@ -13837,11 +13142,8 @@
       <c r="H331" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I331" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
         <v>1285</v>
       </c>
@@ -13866,11 +13168,8 @@
       <c r="H332" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I332" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
         <v>1198</v>
       </c>
@@ -13895,11 +13194,8 @@
       <c r="H333" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I333" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
         <v>1202</v>
       </c>
@@ -13924,11 +13220,8 @@
       <c r="H334" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I334" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="335" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="335" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
         <v>1205</v>
       </c>
@@ -13954,7 +13247,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
         <v>1209</v>
       </c>
@@ -13977,7 +13270,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>1212</v>
       </c>
@@ -14002,11 +13295,8 @@
       <c r="H337" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I337" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>1216</v>
       </c>
@@ -14031,11 +13321,8 @@
       <c r="H338" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I338" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
         <v>1221</v>
       </c>
@@ -14058,7 +13345,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
         <v>1223</v>
       </c>
@@ -14071,7 +13358,7 @@
       <c r="D340" s="7">
         <v>1700</v>
       </c>
-      <c r="E340" s="15" t="s">
+      <c r="E340" s="12" t="s">
         <v>1340</v>
       </c>
       <c r="F340" s="7" t="s">
@@ -14080,8 +13367,11 @@
       <c r="H340" s="7" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I340" s="12" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
         <v>1224</v>
       </c>
@@ -14123,8 +13413,11 @@
       <c r="H342" s="7" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I342" s="12" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
         <v>1233</v>
       </c>
@@ -14149,11 +13442,8 @@
       <c r="H343" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I343" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="344" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="344" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
         <v>1238</v>
       </c>
@@ -14178,11 +13468,8 @@
       <c r="H344" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I344" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="345" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="345" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>1241</v>
       </c>
@@ -14205,7 +13492,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
         <v>1242</v>
       </c>
@@ -14228,7 +13515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>1247</v>
       </c>
@@ -14251,7 +13538,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>1253</v>
       </c>
@@ -14274,7 +13561,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
         <v>1255</v>
       </c>
@@ -14297,7 +13584,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
         <v>1259</v>
       </c>
@@ -14322,11 +13609,8 @@
       <c r="H350" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I350" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
         <v>1265</v>
       </c>
@@ -14349,7 +13633,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
         <v>1267</v>
       </c>
@@ -14372,7 +13656,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>1271</v>
       </c>
@@ -14395,7 +13679,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>1277</v>
       </c>
@@ -14418,7 +13702,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>1327</v>
       </c>
@@ -14443,11 +13727,8 @@
       <c r="H355" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I355" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>1328</v>
       </c>
@@ -14472,11 +13753,8 @@
       <c r="H356" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I356" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>1293</v>
       </c>
@@ -14501,11 +13779,8 @@
       <c r="H357" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I357" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>1296</v>
       </c>
@@ -14530,11 +13805,8 @@
       <c r="H358" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I358" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>1301</v>
       </c>
@@ -14559,11 +13831,8 @@
       <c r="H359" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I359" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>1304</v>
       </c>
@@ -14588,11 +13857,8 @@
       <c r="H360" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I360" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>1309</v>
       </c>
@@ -14617,11 +13883,8 @@
       <c r="H361" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I361" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="362" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="362" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>1314</v>
       </c>
@@ -14631,7 +13894,7 @@
       <c r="C362" s="7">
         <v>350</v>
       </c>
-      <c r="E362" s="15" t="s">
+      <c r="E362" s="12" t="s">
         <v>1337</v>
       </c>
       <c r="F362" s="7" t="s">
@@ -14640,11 +13903,8 @@
       <c r="H362" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I362" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>1322</v>
       </c>
@@ -14669,11 +13929,8 @@
       <c r="H363" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I363" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>1332</v>
       </c>
@@ -14698,11 +13955,8 @@
       <c r="H364" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I364" s="14" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="365" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="365" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>1343</v>
       </c>
@@ -14715,10 +13969,10 @@
       <c r="D365" s="7">
         <v>630</v>
       </c>
-      <c r="E365" s="15" t="s">
+      <c r="E365" s="12" t="s">
         <v>1344</v>
       </c>
-      <c r="F365" s="15" t="s">
+      <c r="F365" s="12" t="s">
         <v>1345</v>
       </c>
       <c r="G365" s="7" t="s">
@@ -14728,7 +13982,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>1346</v>
       </c>
@@ -14741,10 +13995,10 @@
       <c r="D366" s="7">
         <v>485</v>
       </c>
-      <c r="E366" s="15" t="s">
+      <c r="E366" s="12" t="s">
         <v>1349</v>
       </c>
-      <c r="F366" s="15" t="s">
+      <c r="F366" s="12" t="s">
         <v>1348</v>
       </c>
       <c r="G366" s="7" t="s">
@@ -14754,7 +14008,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>1350</v>
       </c>
@@ -14767,10 +14021,10 @@
       <c r="D367" s="7">
         <v>600</v>
       </c>
-      <c r="E367" s="15" t="s">
+      <c r="E367" s="12" t="s">
         <v>1353</v>
       </c>
-      <c r="F367" s="15" t="s">
+      <c r="F367" s="12" t="s">
         <v>1352</v>
       </c>
       <c r="G367" s="7" t="s">
@@ -14780,7 +14034,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>1354</v>
       </c>
@@ -14793,10 +14047,10 @@
       <c r="D368" s="7">
         <v>650</v>
       </c>
-      <c r="E368" s="15" t="s">
+      <c r="E368" s="12" t="s">
         <v>1357</v>
       </c>
-      <c r="F368" s="15" t="s">
+      <c r="F368" s="12" t="s">
         <v>1356</v>
       </c>
       <c r="G368" s="7" t="s">
@@ -14806,7 +14060,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>1360</v>
       </c>
@@ -14819,10 +14073,10 @@
       <c r="D369" s="7">
         <v>650</v>
       </c>
-      <c r="E369" s="15" t="s">
+      <c r="E369" s="12" t="s">
         <v>1359</v>
       </c>
-      <c r="F369" s="15" t="s">
+      <c r="F369" s="12" t="s">
         <v>1358</v>
       </c>
       <c r="G369" s="7" t="s">
@@ -14832,7 +14086,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="370" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>1379</v>
       </c>
@@ -14845,10 +14099,10 @@
       <c r="D370" s="7">
         <v>700</v>
       </c>
-      <c r="E370" s="15" t="s">
+      <c r="E370" s="12" t="s">
         <v>1363</v>
       </c>
-      <c r="F370" s="15" t="s">
+      <c r="F370" s="12" t="s">
         <v>1362</v>
       </c>
       <c r="G370" s="7" t="s">
@@ -14858,7 +14112,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="371" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:8" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>1378</v>
       </c>
@@ -14871,10 +14125,10 @@
       <c r="D371" s="7">
         <v>700</v>
       </c>
-      <c r="E371" s="15" t="s">
+      <c r="E371" s="12" t="s">
         <v>1365</v>
       </c>
-      <c r="F371" s="15" t="s">
+      <c r="F371" s="12" t="s">
         <v>1364</v>
       </c>
       <c r="G371" s="7" t="s">
@@ -14884,7 +14138,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
         <v>1368</v>
       </c>
@@ -14897,10 +14151,10 @@
       <c r="D372" s="7">
         <v>400</v>
       </c>
-      <c r="E372" s="15" t="s">
+      <c r="E372" s="12" t="s">
         <v>1367</v>
       </c>
-      <c r="F372" s="15" t="s">
+      <c r="F372" s="12" t="s">
         <v>1366</v>
       </c>
       <c r="G372" s="7" t="s">
@@ -14910,7 +14164,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="373" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>1384</v>
       </c>
@@ -14923,10 +14177,10 @@
       <c r="D373" s="7">
         <v>675</v>
       </c>
-      <c r="E373" s="15" t="s">
+      <c r="E373" s="12" t="s">
         <v>1371</v>
       </c>
-      <c r="F373" s="15" t="s">
+      <c r="F373" s="12" t="s">
         <v>1370</v>
       </c>
       <c r="G373" s="7" t="s">
@@ -14936,7 +14190,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="374" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>1386</v>
       </c>
@@ -14949,10 +14203,10 @@
       <c r="D374" s="7">
         <v>375</v>
       </c>
-      <c r="E374" s="15" t="s">
+      <c r="E374" s="12" t="s">
         <v>1373</v>
       </c>
-      <c r="F374" s="15" t="s">
+      <c r="F374" s="12" t="s">
         <v>1372</v>
       </c>
       <c r="G374" s="7" t="s">
@@ -14962,7 +14216,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="375" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
         <v>1388</v>
       </c>
@@ -14975,10 +14229,10 @@
       <c r="D375" s="7">
         <v>575</v>
       </c>
-      <c r="E375" s="15" t="s">
+      <c r="E375" s="12" t="s">
         <v>1375</v>
       </c>
-      <c r="F375" s="15" t="s">
+      <c r="F375" s="12" t="s">
         <v>1374</v>
       </c>
       <c r="G375" s="7" t="s">
@@ -14988,7 +14242,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="376" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>1380</v>
       </c>
@@ -15001,10 +14255,10 @@
       <c r="D376" s="7">
         <v>700</v>
       </c>
-      <c r="E376" s="15" t="s">
+      <c r="E376" s="12" t="s">
         <v>1383</v>
       </c>
-      <c r="F376" s="15" t="s">
+      <c r="F376" s="12" t="s">
         <v>1382</v>
       </c>
       <c r="G376" s="7" t="s">
@@ -15014,7 +14268,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="377" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>1390</v>
       </c>
@@ -15027,10 +14281,10 @@
       <c r="D377" s="7">
         <v>920</v>
       </c>
-      <c r="E377" s="15" t="s">
+      <c r="E377" s="12" t="s">
         <v>1393</v>
       </c>
-      <c r="F377" s="15" t="s">
+      <c r="F377" s="12" t="s">
         <v>1392</v>
       </c>
       <c r="G377" s="7" t="s">
@@ -15040,7 +14294,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="378" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
         <v>1394</v>
       </c>
@@ -15053,10 +14307,10 @@
       <c r="D378" s="7">
         <v>400</v>
       </c>
-      <c r="E378" s="15" t="s">
+      <c r="E378" s="12" t="s">
         <v>1397</v>
       </c>
-      <c r="F378" s="15" t="s">
+      <c r="F378" s="12" t="s">
         <v>1396</v>
       </c>
       <c r="G378" s="7" t="s">
@@ -15066,7 +14320,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
         <v>1398</v>
       </c>
@@ -15079,10 +14333,10 @@
       <c r="D379" s="7">
         <v>200</v>
       </c>
-      <c r="E379" s="15" t="s">
+      <c r="E379" s="12" t="s">
         <v>1400</v>
       </c>
-      <c r="F379" s="15" t="s">
+      <c r="F379" s="12" t="s">
         <v>1399</v>
       </c>
       <c r="G379" s="7" t="s">
@@ -15092,7 +14346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="380" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
         <v>1402</v>
       </c>
@@ -15105,10 +14359,10 @@
       <c r="D380" s="7">
         <v>250</v>
       </c>
-      <c r="E380" s="15" t="s">
+      <c r="E380" s="12" t="s">
         <v>1404</v>
       </c>
-      <c r="F380" s="15" t="s">
+      <c r="F380" s="12" t="s">
         <v>1403</v>
       </c>
       <c r="G380" s="7" t="s">
@@ -15118,7 +14372,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="1" t="s">
         <v>1406</v>
       </c>
@@ -15131,10 +14385,10 @@
       <c r="D381" s="7">
         <v>120</v>
       </c>
-      <c r="E381" s="15" t="s">
+      <c r="E381" s="12" t="s">
         <v>1409</v>
       </c>
-      <c r="F381" s="15" t="s">
+      <c r="F381" s="12" t="s">
         <v>1408</v>
       </c>
       <c r="G381" s="7" t="s">
@@ -15144,7 +14398,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="382" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="1" t="s">
         <v>1410</v>
       </c>
@@ -15157,10 +14411,10 @@
       <c r="D382" s="7">
         <v>300</v>
       </c>
-      <c r="E382" s="15" t="s">
+      <c r="E382" s="12" t="s">
         <v>1413</v>
       </c>
-      <c r="F382" s="15" t="s">
+      <c r="F382" s="12" t="s">
         <v>1412</v>
       </c>
       <c r="G382" s="7" t="s">
@@ -15170,7 +14424,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="1" t="s">
         <v>1414</v>
       </c>
@@ -15183,10 +14437,10 @@
       <c r="D383" s="7">
         <v>300</v>
       </c>
-      <c r="E383" s="15" t="s">
+      <c r="E383" s="12" t="s">
         <v>1417</v>
       </c>
-      <c r="F383" s="15" t="s">
+      <c r="F383" s="12" t="s">
         <v>1416</v>
       </c>
       <c r="G383" s="7" t="s">
@@ -15196,7 +14450,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="384" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
         <v>1420</v>
       </c>
@@ -15209,10 +14463,10 @@
       <c r="D384" s="7">
         <v>300</v>
       </c>
-      <c r="E384" s="15" t="s">
+      <c r="E384" s="12" t="s">
         <v>1419</v>
       </c>
-      <c r="F384" s="15" t="s">
+      <c r="F384" s="12" t="s">
         <v>1418</v>
       </c>
       <c r="G384" s="7" t="s">
@@ -15222,7 +14476,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
         <v>1423</v>
       </c>
@@ -15235,10 +14489,10 @@
       <c r="D385" s="7">
         <v>1090</v>
       </c>
-      <c r="E385" s="15" t="s">
+      <c r="E385" s="12" t="s">
         <v>1425</v>
       </c>
-      <c r="F385" s="15" t="s">
+      <c r="F385" s="12" t="s">
         <v>1424</v>
       </c>
       <c r="G385" s="7" t="s">
@@ -15248,7 +14502,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="1" t="s">
         <v>1428</v>
       </c>
@@ -15261,10 +14515,10 @@
       <c r="D386" s="7">
         <v>800</v>
       </c>
-      <c r="E386" s="15" t="s">
+      <c r="E386" s="12" t="s">
         <v>1427</v>
       </c>
-      <c r="F386" s="15" t="s">
+      <c r="F386" s="12" t="s">
         <v>1426</v>
       </c>
       <c r="G386" s="7" t="s">
@@ -15274,7 +14528,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="1" t="s">
         <v>1433</v>
       </c>
@@ -15287,10 +14541,10 @@
       <c r="D387" s="7">
         <v>2832</v>
       </c>
-      <c r="E387" s="15" t="s">
+      <c r="E387" s="12" t="s">
         <v>1431</v>
       </c>
-      <c r="F387" s="15" t="s">
+      <c r="F387" s="12" t="s">
         <v>1430</v>
       </c>
       <c r="G387" s="7" t="s">
@@ -15299,8 +14553,14 @@
       <c r="H387" s="7" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I387" s="12" t="s">
+        <v>1451</v>
+      </c>
+      <c r="J387" s="12" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" s="1" t="s">
         <v>1434</v>
       </c>
@@ -15313,10 +14573,10 @@
       <c r="D388" s="7">
         <v>295</v>
       </c>
-      <c r="E388" s="15" t="s">
+      <c r="E388" s="12" t="s">
         <v>1437</v>
       </c>
-      <c r="F388" s="15" t="s">
+      <c r="F388" s="12" t="s">
         <v>1436</v>
       </c>
       <c r="G388" s="7" t="s">
@@ -15324,9 +14584,6 @@
       </c>
       <c r="H388" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="I388" s="14" t="s">
-        <v>892</v>
       </c>
     </row>
   </sheetData>
@@ -15388,11 +14645,24 @@
     <hyperlink ref="E387" r:id="rId54"/>
     <hyperlink ref="F388" r:id="rId55"/>
     <hyperlink ref="E388" r:id="rId56"/>
+    <hyperlink ref="I73"/>
+    <hyperlink ref="I308" r:id="rId57"/>
+    <hyperlink ref="J308" r:id="rId58"/>
+    <hyperlink ref="I195"/>
+    <hyperlink ref="I134"/>
+    <hyperlink ref="I67"/>
+    <hyperlink ref="J67" r:id="rId59"/>
+    <hyperlink ref="I68"/>
+    <hyperlink ref="I273"/>
+    <hyperlink ref="I340"/>
+    <hyperlink ref="J387" r:id="rId60"/>
+    <hyperlink ref="I387" r:id="rId61"/>
+    <hyperlink ref="I342"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId57"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId62"/>
   <tableParts count="1">
-    <tablePart r:id="rId58"/>
+    <tablePart r:id="rId63"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="1453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2307" uniqueCount="1457">
   <si>
     <t>Nombre</t>
   </si>
@@ -1388,9 +1388,6 @@
   </si>
   <si>
     <t>Potencia: 1300 W</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_885715-MLA103257094455_122025-F.webp; https://http2.mlstatic.com/D_NQ_NP_2X_612358-MLA102745474728_122025-F.webp</t>
   </si>
   <si>
     <t>https://www.mercadolibre.com.mx/kaxws-secadora-de-cabello-alta-velocidad-profesional-6-en-1-profesional-cepillo-secador-plancha-rizadora-alaciadora-4-temperaturas-y-3-velocidades-del-viento-y-caliente/p/MLM63711565?pdp_filters=item_id:MLM4724304668</t>
@@ -4312,9 +4309,6 @@
     <t>https://www.mercadolibre.com.mx/momovida-bebedero-para-gatos-45l-inalambrico-inteligente-con-dos-filtros-para-perros-y-gatosfuente-de-agua-dispensador-automatico-silencioso-pw-2/p/MLM70108146?pdp_filters=item_id:MLM5408292164</t>
   </si>
   <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_984373-MLA112451559563_052026-F.webp; https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp</t>
-  </si>
-  <si>
     <t>https://www.mercadolibre.com.mx/minibar-yqalley-6-l-inverter-con-espejo-led-para-maquillaje-frio-y-calor/p/MLM70649258?pdp_filters=item_id:MLM5445249182</t>
   </si>
   <si>
@@ -4395,6 +4389,24 @@
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_704682-MLA112632086794_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648062-MLA114215908179_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_721338-MLA112631444306_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_666014-MLA110019279904_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_747141-MLA110928994963_042026-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_885715-MLA103257094455_122025-F.webp;</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_679078-MLA106513626675_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_867289-MLA106513332881_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_837213-MLA106512862341_022026-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-static-clips.mms.mlstatic.com/62c82f1f923a3f082b72612d/019e9a873965741d803e421ad4a1a045/packaging/static/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_877039-MLA114231711531_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_669195-MLA111691242302_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_694108-MLA111868098195_052026-F.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://http2.mlstatic.com/D_NQ_NP_2X_984373-MLA112451559563_052026-F.webp; </t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_870766-MLA111944165952_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_835091-MLA112882459449_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_865807-MLA113706863262_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_881890-MLA115108214329_072026-F.webp</t>
   </si>
 </sst>
 </file>
@@ -4557,7 +4569,7 @@
   <autoFilter ref="A1:J388">
     <filterColumn colId="0">
       <filters>
-        <filter val="Amplificador De Audio Para Auto"/>
+        <filter val="Bebedero Para mascotas 4.5L, Fuente de Agua Dispensador Automático Silencioso"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4905,18 +4917,18 @@
         <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C2" s="7">
         <v>350</v>
@@ -4925,13 +4937,13 @@
         <v>200</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>66</v>
@@ -4941,10 +4953,10 @@
     </row>
     <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C3" s="7">
         <v>693</v>
@@ -4967,25 +4979,25 @@
     </row>
     <row r="4" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>589</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>590</v>
       </c>
       <c r="C4" s="7">
         <v>200</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
@@ -5011,7 +5023,7 @@
         <v>438</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
@@ -5034,12 +5046,12 @@
         <v>31</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>101</v>
@@ -5057,7 +5069,7 @@
         <v>103</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>100</v>
@@ -5083,7 +5095,7 @@
         <v>107</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>100</v>
@@ -5091,10 +5103,10 @@
     </row>
     <row r="9" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>694</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="C9" s="7">
         <v>250</v>
@@ -5103,13 +5115,13 @@
         <v>180</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>211</v>
@@ -5117,10 +5129,10 @@
     </row>
     <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C10" s="7">
         <v>300</v>
@@ -5129,13 +5141,13 @@
         <v>250</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>478</v>
-      </c>
       <c r="G10" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>100</v>
@@ -5169,10 +5181,10 @@
     </row>
     <row r="12" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>751</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>752</v>
       </c>
       <c r="C12" s="7">
         <v>100</v>
@@ -5181,13 +5193,13 @@
         <v>80</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>749</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>750</v>
-      </c>
       <c r="G12" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>211</v>
@@ -5195,7 +5207,7 @@
     </row>
     <row r="13" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>22</v>
@@ -5204,13 +5216,13 @@
         <v>350</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>12</v>
@@ -5218,10 +5230,10 @@
     </row>
     <row r="14" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>633</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>634</v>
       </c>
       <c r="C14" s="7">
         <v>120</v>
@@ -5230,13 +5242,13 @@
         <v>80</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>211</v>
@@ -5244,25 +5256,25 @@
     </row>
     <row r="15" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>993</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>994</v>
       </c>
       <c r="C15" s="7">
         <v>150</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
@@ -5282,7 +5294,7 @@
         <v>110</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>100</v>
@@ -5290,7 +5302,7 @@
     </row>
     <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>18</v>
@@ -5299,13 +5311,13 @@
         <v>50</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>100</v>
@@ -5313,10 +5325,10 @@
     </row>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>764</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>765</v>
       </c>
       <c r="C18" s="7">
         <v>220</v>
@@ -5325,70 +5337,70 @@
         <v>180</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C19" s="7">
         <v>200</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>790</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>791</v>
       </c>
       <c r="C20" s="7">
         <v>120</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C21" s="7">
         <v>399</v>
@@ -5397,90 +5409,90 @@
         <v>250</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>535</v>
       </c>
       <c r="C22" s="7">
         <v>210</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>535</v>
       </c>
       <c r="C23" s="7">
         <v>210</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>535</v>
       </c>
       <c r="C24" s="7">
         <v>210</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>27</v>
@@ -5492,16 +5504,16 @@
         <v>1050</v>
       </c>
       <c r="E25" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>498</v>
-      </c>
       <c r="G25" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -5509,7 +5521,7 @@
         <v>111</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C26" s="7">
         <v>515</v>
@@ -5524,7 +5536,7 @@
         <v>113</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>100</v>
@@ -5532,7 +5544,7 @@
     </row>
     <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>18</v>
@@ -5544,13 +5556,13 @@
         <v>200</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>100</v>
@@ -5558,7 +5570,7 @@
     </row>
     <row r="28" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>18</v>
@@ -5576,7 +5588,7 @@
         <v>336</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>100</v>
@@ -5599,7 +5611,7 @@
         <v>116</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>100</v>
@@ -5607,10 +5619,10 @@
     </row>
     <row r="30" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C30" s="7">
         <v>250</v>
@@ -5619,13 +5631,13 @@
         <v>180</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>100</v>
@@ -5633,7 +5645,7 @@
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>18</v>
@@ -5645,13 +5657,13 @@
         <v>180</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>100</v>
@@ -5659,10 +5671,10 @@
     </row>
     <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C32" s="7">
         <v>1354</v>
@@ -5671,21 +5683,21 @@
         <v>850</v>
       </c>
       <c r="E32" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>495</v>
-      </c>
       <c r="G32" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>18</v>
@@ -5697,21 +5709,21 @@
         <v>220</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>18</v>
@@ -5729,15 +5741,15 @@
         <v>118</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>18</v>
@@ -5752,18 +5764,18 @@
         <v>119</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C36" s="7">
         <v>1750</v>
@@ -5772,24 +5784,27 @@
         <v>1150</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I36" s="12" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>1330</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>1331</v>
       </c>
       <c r="C37" s="7">
         <v>300</v>
@@ -5804,61 +5819,61 @@
         <v>409</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>1001</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>1002</v>
       </c>
       <c r="C38" s="7">
         <v>200</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C39" s="7">
         <v>250</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>160</v>
@@ -5870,24 +5885,24 @@
         <v>350</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C41" s="7">
         <v>150</v>
@@ -5896,13 +5911,13 @@
         <v>78</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>186</v>
       </c>
@@ -5919,13 +5934,13 @@
         <v>187</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>159</v>
       </c>
@@ -5951,9 +5966,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>18</v>
@@ -5962,21 +5977,21 @@
         <v>250</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>18</v>
@@ -5985,21 +6000,21 @@
         <v>250</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>18</v>
@@ -6008,21 +6023,21 @@
         <v>250</v>
       </c>
       <c r="E46" s="7" t="s">
+        <v>931</v>
+      </c>
+      <c r="F46" s="7" t="s">
         <v>932</v>
       </c>
-      <c r="F46" s="7" t="s">
-        <v>933</v>
-      </c>
       <c r="G46" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>18</v>
@@ -6031,24 +6046,24 @@
         <v>250</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>470</v>
       </c>
       <c r="C48" s="7">
         <v>399</v>
@@ -6057,16 +6072,16 @@
         <v>300</v>
       </c>
       <c r="E48" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="F48" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>472</v>
-      </c>
       <c r="G48" s="7" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -6089,10 +6104,10 @@
         <v>205</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -6115,10 +6130,10 @@
         <v>339</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -6138,18 +6153,18 @@
         <v>189</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C52" s="7">
         <v>715</v>
@@ -6158,13 +6173,13 @@
         <v>450</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>12</v>
@@ -6172,10 +6187,10 @@
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C53" s="7">
         <v>728</v>
@@ -6184,13 +6199,13 @@
         <v>450</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>12</v>
@@ -6198,10 +6213,10 @@
     </row>
     <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="C54" s="7">
         <v>870</v>
@@ -6210,13 +6225,13 @@
         <v>500</v>
       </c>
       <c r="E54" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="F54" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="F54" s="7" t="s">
-        <v>461</v>
-      </c>
       <c r="G54" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>12</v>
@@ -6227,7 +6242,7 @@
         <v>221</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C55" s="7">
         <v>652</v>
@@ -6242,7 +6257,7 @@
         <v>223</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>12</v>
@@ -6250,10 +6265,10 @@
     </row>
     <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C56" s="7">
         <v>1098</v>
@@ -6262,13 +6277,13 @@
         <v>658</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>12</v>
@@ -6276,10 +6291,10 @@
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>900</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>901</v>
       </c>
       <c r="C57" s="7">
         <v>120</v>
@@ -6288,13 +6303,13 @@
         <v>100</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>66</v>
@@ -6302,10 +6317,10 @@
     </row>
     <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C58" s="7">
         <v>150</v>
@@ -6314,13 +6329,13 @@
         <v>100</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>66</v>
@@ -6328,22 +6343,22 @@
     </row>
     <row r="59" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C59" s="7">
         <v>200</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>12</v>
@@ -6351,7 +6366,7 @@
     </row>
     <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>18</v>
@@ -6360,24 +6375,24 @@
         <v>150</v>
       </c>
       <c r="E60" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="F60" s="7" t="s">
         <v>798</v>
       </c>
-      <c r="F60" s="7" t="s">
-        <v>799</v>
-      </c>
       <c r="G60" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C61" s="7">
         <v>1200</v>
@@ -6386,13 +6401,13 @@
         <v>1000</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>12</v>
@@ -6415,7 +6430,7 @@
         <v>343</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>12</v>
@@ -6423,7 +6438,7 @@
     </row>
     <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>9</v>
@@ -6432,13 +6447,13 @@
         <v>300</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H63" s="7" t="s">
         <v>12</v>
@@ -6446,7 +6461,7 @@
     </row>
     <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>18</v>
@@ -6458,13 +6473,13 @@
         <v>200</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>100</v>
@@ -6472,7 +6487,7 @@
     </row>
     <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>18</v>
@@ -6484,21 +6499,21 @@
         <v>120</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>18</v>
@@ -6510,24 +6525,24 @@
         <v>120</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>1078</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>1079</v>
       </c>
       <c r="C67" s="7">
         <v>5000</v>
@@ -6536,22 +6551,22 @@
         <v>3500</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>100</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -6574,33 +6589,33 @@
         <v>123</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>100</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C69" s="7">
         <v>150</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H69" s="7" t="s">
         <v>211</v>
@@ -6608,10 +6623,10 @@
     </row>
     <row r="70" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>677</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>678</v>
       </c>
       <c r="C70" s="7">
         <v>445</v>
@@ -6620,13 +6635,13 @@
         <v>300</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>211</v>
@@ -6637,7 +6652,7 @@
         <v>344</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C71" s="7">
         <v>40</v>
@@ -6649,7 +6664,7 @@
         <v>346</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>211</v>
@@ -6683,10 +6698,10 @@
     </row>
     <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C73" s="7">
         <v>350</v>
@@ -6695,10 +6710,10 @@
         <v>200</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="G73" s="7" t="s">
         <v>438</v>
@@ -6707,7 +6722,7 @@
         <v>66</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
@@ -6727,7 +6742,7 @@
         <v>380</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>12</v>
@@ -6750,7 +6765,7 @@
         <v>378</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H75" s="7" t="s">
         <v>12</v>
@@ -6784,7 +6799,7 @@
     </row>
     <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>18</v>
@@ -6796,21 +6811,21 @@
         <v>150</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>18</v>
@@ -6819,21 +6834,21 @@
         <v>200</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>18</v>
@@ -6842,24 +6857,24 @@
         <v>150</v>
       </c>
       <c r="E79" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="F79" s="7" t="s">
         <v>784</v>
       </c>
-      <c r="F79" s="7" t="s">
-        <v>785</v>
-      </c>
       <c r="G79" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C80" s="7">
         <v>450</v>
@@ -6868,21 +6883,21 @@
         <v>430</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>18</v>
@@ -6894,70 +6909,70 @@
         <v>150</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>577</v>
       </c>
       <c r="C82" s="7">
         <v>300</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>571</v>
       </c>
       <c r="C83" s="7">
         <v>200</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C84" s="7">
         <v>120</v>
@@ -6966,24 +6981,24 @@
         <v>100</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C85" s="9">
         <v>120</v>
@@ -6992,16 +7007,16 @@
         <v>80</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
@@ -7024,7 +7039,7 @@
         <v>317</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H86" s="7" t="s">
         <v>100</v>
@@ -7032,7 +7047,7 @@
     </row>
     <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>27</v>
@@ -7041,16 +7056,16 @@
         <v>550</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -7058,7 +7073,7 @@
         <v>381</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C88" s="7">
         <v>141</v>
@@ -7073,7 +7088,7 @@
         <v>383</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H88" s="7" t="s">
         <v>12</v>
@@ -7081,10 +7096,10 @@
     </row>
     <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C89" s="7">
         <v>210</v>
@@ -7093,10 +7108,10 @@
         <v>150</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G89" s="7" t="s">
         <v>438</v>
@@ -7107,10 +7122,10 @@
     </row>
     <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C90" s="7">
         <v>150</v>
@@ -7119,10 +7134,10 @@
         <v>100</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G90" s="7" t="s">
         <v>438</v>
@@ -7133,10 +7148,10 @@
     </row>
     <row r="91" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>652</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>653</v>
       </c>
       <c r="C91" s="7">
         <v>150</v>
@@ -7145,13 +7160,13 @@
         <v>100</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H91" s="7" t="s">
         <v>211</v>
@@ -7159,10 +7174,10 @@
     </row>
     <row r="92" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>683</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>684</v>
       </c>
       <c r="C92" s="7">
         <v>150</v>
@@ -7171,13 +7186,13 @@
         <v>100</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H92" s="7" t="s">
         <v>211</v>
@@ -7185,22 +7200,22 @@
     </row>
     <row r="93" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C93" s="7">
         <v>200</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>211</v>
@@ -7229,15 +7244,15 @@
         <v>234</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C95" s="7">
         <v>500</v>
@@ -7246,13 +7261,13 @@
         <v>390</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H95" s="7" t="s">
         <v>211</v>
@@ -7260,22 +7275,22 @@
     </row>
     <row r="96" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C96" s="7">
         <v>300</v>
       </c>
       <c r="E96" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="F96" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="F96" s="7" t="s">
-        <v>504</v>
-      </c>
       <c r="G96" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H96" s="7" t="s">
         <v>211</v>
@@ -7283,10 +7298,10 @@
     </row>
     <row r="97" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C97" s="7">
         <v>698</v>
@@ -7295,13 +7310,13 @@
         <v>400</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H97" s="7" t="s">
         <v>211</v>
@@ -7309,22 +7324,22 @@
     </row>
     <row r="98" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>647</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>648</v>
       </c>
       <c r="C98" s="7">
         <v>300</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H98" s="7" t="s">
         <v>211</v>
@@ -7376,7 +7391,7 @@
         <v>210</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H100" s="7" t="s">
         <v>211</v>
@@ -7413,7 +7428,7 @@
         <v>173</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C102" s="7">
         <v>420</v>
@@ -7428,7 +7443,7 @@
         <v>175</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H102" s="7" t="s">
         <v>66</v>
@@ -7439,7 +7454,7 @@
         <v>176</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C103" s="7">
         <v>300</v>
@@ -7451,7 +7466,7 @@
         <v>177</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H103" s="7" t="s">
         <v>66</v>
@@ -7485,22 +7500,22 @@
     </row>
     <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="C105" s="7">
         <v>700</v>
       </c>
       <c r="E105" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="F105" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="F105" s="7" t="s">
-        <v>468</v>
-      </c>
       <c r="G105" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H105" s="7" t="s">
         <v>211</v>
@@ -7508,10 +7523,10 @@
     </row>
     <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>919</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>920</v>
       </c>
       <c r="C106" s="7">
         <v>589</v>
@@ -7520,16 +7535,16 @@
         <v>500</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -7552,7 +7567,7 @@
         <v>214</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H107" s="7" t="s">
         <v>211</v>
@@ -7560,10 +7575,10 @@
     </row>
     <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C108" s="7">
         <v>333</v>
@@ -7578,7 +7593,7 @@
         <v>403</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H108" s="7" t="s">
         <v>12</v>
@@ -7589,7 +7604,7 @@
         <v>347</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C109" s="7">
         <v>250</v>
@@ -7604,7 +7619,7 @@
         <v>350</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H109" s="7" t="s">
         <v>12</v>
@@ -7612,10 +7627,10 @@
     </row>
     <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C110" s="7">
         <v>250</v>
@@ -7624,13 +7639,13 @@
         <v>200</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H110" s="7" t="s">
         <v>12</v>
@@ -7638,10 +7653,10 @@
     </row>
     <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C111" s="7">
         <v>300</v>
@@ -7650,16 +7665,16 @@
         <v>250</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -7679,10 +7694,10 @@
         <v>29</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -7702,38 +7717,38 @@
         <v>32</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>510</v>
       </c>
       <c r="C114" s="7">
         <v>300</v>
       </c>
       <c r="E114" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="F114" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="F114" s="7" t="s">
-        <v>512</v>
-      </c>
       <c r="G114" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H114" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>18</v>
@@ -7742,10 +7757,10 @@
         <v>200</v>
       </c>
       <c r="E115" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="F115" s="7" t="s">
         <v>526</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>527</v>
       </c>
       <c r="G115" s="7" t="s">
         <v>438</v>
@@ -7782,10 +7797,10 @@
     </row>
     <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>876</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>877</v>
       </c>
       <c r="C117" s="7">
         <v>150</v>
@@ -7794,13 +7809,13 @@
         <v>100</v>
       </c>
       <c r="E117" s="7" t="s">
+        <v>877</v>
+      </c>
+      <c r="F117" s="7" t="s">
         <v>878</v>
       </c>
-      <c r="F117" s="7" t="s">
-        <v>879</v>
-      </c>
       <c r="G117" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H117" s="7" t="s">
         <v>100</v>
@@ -7808,10 +7823,10 @@
     </row>
     <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>868</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>869</v>
       </c>
       <c r="C118" s="7">
         <v>250</v>
@@ -7820,13 +7835,13 @@
         <v>100</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H118" s="7" t="s">
         <v>100</v>
@@ -7852,7 +7867,7 @@
         <v>423</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H119" s="7" t="s">
         <v>66</v>
@@ -7878,15 +7893,15 @@
         <v>81</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H120" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>18</v>
@@ -7898,13 +7913,13 @@
         <v>150</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H121" s="7" t="s">
         <v>211</v>
@@ -7912,10 +7927,10 @@
     </row>
     <row r="122" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>735</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>736</v>
       </c>
       <c r="C122" s="7">
         <v>180</v>
@@ -7924,13 +7939,13 @@
         <v>120</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H122" s="7" t="s">
         <v>211</v>
@@ -7938,10 +7953,10 @@
     </row>
     <row r="123" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>687</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>688</v>
       </c>
       <c r="C123" s="7">
         <v>150</v>
@@ -7950,13 +7965,13 @@
         <v>100</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H123" s="7" t="s">
         <v>211</v>
@@ -7964,22 +7979,22 @@
     </row>
     <row r="124" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>709</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>710</v>
       </c>
       <c r="C124" s="7">
         <v>50</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H124" s="7" t="s">
         <v>211</v>
@@ -8005,7 +8020,7 @@
         <v>11</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H125" s="7" t="s">
         <v>12</v>
@@ -8013,30 +8028,30 @@
     </row>
     <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="C126" s="7">
         <v>100</v>
       </c>
       <c r="E126" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="F126" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="F126" s="7" t="s">
-        <v>516</v>
-      </c>
       <c r="G126" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H126" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>18</v>
@@ -8045,39 +8060,39 @@
         <v>150</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H127" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>566</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>567</v>
       </c>
       <c r="C128" s="7">
         <v>400</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G128" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H128" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
@@ -8175,7 +8190,7 @@
         <v>387</v>
       </c>
       <c r="G132" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H132" s="7" t="s">
         <v>12</v>
@@ -8201,7 +8216,7 @@
         <v>390</v>
       </c>
       <c r="G133" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H133" s="7" t="s">
         <v>12</v>
@@ -8224,18 +8239,18 @@
         <v>84</v>
       </c>
       <c r="G134" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H134" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I134" s="12" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>63</v>
@@ -8253,33 +8268,33 @@
         <v>65</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H135" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C136" s="7">
         <v>550</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H136" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
@@ -8313,7 +8328,7 @@
         <v>85</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C138" s="7">
         <v>250</v>
@@ -8325,10 +8340,10 @@
         <v>87</v>
       </c>
       <c r="G138" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H138" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
@@ -8345,7 +8360,7 @@
         <v>370</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F139" s="7" t="s">
         <v>290</v>
@@ -8359,10 +8374,10 @@
     </row>
     <row r="140" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C140" s="7">
         <v>599</v>
@@ -8371,10 +8386,10 @@
         <v>300</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G140" s="7" t="s">
         <v>438</v>
@@ -8388,7 +8403,7 @@
         <v>88</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C141" s="7">
         <v>150</v>
@@ -8400,10 +8415,10 @@
         <v>90</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H141" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
@@ -8411,7 +8426,7 @@
         <v>91</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C142" s="7">
         <v>250</v>
@@ -8423,10 +8438,10 @@
         <v>93</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H142" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
@@ -8446,30 +8461,30 @@
         <v>96</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H143" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>474</v>
       </c>
       <c r="C144" s="7">
         <v>670</v>
       </c>
       <c r="E144" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="F144" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="F144" s="7" t="s">
-        <v>476</v>
-      </c>
       <c r="G144" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H144" s="7" t="s">
         <v>211</v>
@@ -8477,22 +8492,22 @@
     </row>
     <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C145" s="7">
         <v>600</v>
       </c>
       <c r="E145" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="F145" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="F145" s="7" t="s">
-        <v>489</v>
-      </c>
       <c r="G145" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H145" s="7" t="s">
         <v>211</v>
@@ -8500,22 +8515,22 @@
     </row>
     <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="C146" s="7">
         <v>400</v>
       </c>
       <c r="E146" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="F146" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="F146" s="7" t="s">
-        <v>486</v>
-      </c>
       <c r="G146" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H146" s="7" t="s">
         <v>211</v>
@@ -8564,10 +8579,10 @@
         <v>99</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -8590,10 +8605,10 @@
         <v>35</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -8616,10 +8631,10 @@
         <v>39</v>
       </c>
       <c r="G150" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H150" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -8642,10 +8657,10 @@
         <v>42</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -8668,10 +8683,10 @@
         <v>166</v>
       </c>
       <c r="G152" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H152" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -8694,10 +8709,10 @@
         <v>169</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H153" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -8720,18 +8735,18 @@
         <v>172</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H154" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C155" s="7">
         <v>200</v>
@@ -8740,13 +8755,13 @@
         <v>150</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H155" s="7" t="s">
         <v>211</v>
@@ -8775,15 +8790,15 @@
         <v>31</v>
       </c>
       <c r="H156" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>643</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>644</v>
       </c>
       <c r="C157" s="7">
         <v>250</v>
@@ -8792,13 +8807,13 @@
         <v>200</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H157" s="7" t="s">
         <v>211</v>
@@ -8806,10 +8821,10 @@
     </row>
     <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="C158" s="7">
         <v>350</v>
@@ -8818,13 +8833,13 @@
         <v>300</v>
       </c>
       <c r="E158" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="F158" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="F158" s="7" t="s">
-        <v>482</v>
-      </c>
       <c r="G158" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H158" s="7" t="s">
         <v>66</v>
@@ -8847,18 +8862,18 @@
         <v>353</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H159" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>872</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>873</v>
       </c>
       <c r="C160" s="7">
         <v>150</v>
@@ -8867,13 +8882,13 @@
         <v>100</v>
       </c>
       <c r="E160" s="7" t="s">
+        <v>873</v>
+      </c>
+      <c r="F160" s="7" t="s">
         <v>874</v>
       </c>
-      <c r="F160" s="7" t="s">
-        <v>875</v>
-      </c>
       <c r="G160" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H160" s="7" t="s">
         <v>100</v>
@@ -8881,22 +8896,22 @@
     </row>
     <row r="161" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>609</v>
       </c>
       <c r="C161" s="7">
         <v>130</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G161" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H161" s="7" t="s">
         <v>211</v>
@@ -8919,18 +8934,18 @@
         <v>46</v>
       </c>
       <c r="G162" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H162" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>715</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>716</v>
       </c>
       <c r="C163" s="7">
         <v>199</v>
@@ -8939,13 +8954,13 @@
         <v>100</v>
       </c>
       <c r="E163" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="F163" s="7" t="s">
         <v>717</v>
       </c>
-      <c r="F163" s="7" t="s">
-        <v>718</v>
-      </c>
       <c r="G163" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H163" s="7" t="s">
         <v>211</v>
@@ -8953,22 +8968,22 @@
     </row>
     <row r="164" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>714</v>
       </c>
       <c r="C164" s="7">
         <v>50</v>
       </c>
       <c r="E164" s="7" t="s">
+        <v>710</v>
+      </c>
+      <c r="F164" s="7" t="s">
         <v>711</v>
       </c>
-      <c r="F164" s="7" t="s">
-        <v>712</v>
-      </c>
       <c r="G164" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H164" s="7" t="s">
         <v>211</v>
@@ -8976,22 +8991,22 @@
     </row>
     <row r="165" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>705</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>706</v>
       </c>
       <c r="C165" s="7">
         <v>150</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G165" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H165" s="7" t="s">
         <v>211</v>
@@ -9020,30 +9035,30 @@
         <v>294</v>
       </c>
       <c r="H166" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>500</v>
       </c>
       <c r="C167" s="7">
         <v>250</v>
       </c>
       <c r="E167" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="F167" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="F167" s="7" t="s">
-        <v>502</v>
-      </c>
       <c r="G167" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H167" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -9089,33 +9104,33 @@
         <v>125</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H169" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C170" s="7">
         <v>250</v>
       </c>
       <c r="E170" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="F170" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="F170" s="7" t="s">
+      <c r="G170" s="7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H170" s="7" t="s">
         <v>530</v>
-      </c>
-      <c r="G170" s="7" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H170" s="7" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -9135,10 +9150,10 @@
         <v>70</v>
       </c>
       <c r="G171" s="7" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H171" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -9161,10 +9176,10 @@
         <v>320</v>
       </c>
       <c r="G172" s="7" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H172" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -9187,18 +9202,18 @@
         <v>73</v>
       </c>
       <c r="G173" s="7" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C174" s="7">
         <v>100</v>
@@ -9207,62 +9222,62 @@
         <v>80</v>
       </c>
       <c r="E174" s="7" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="G174" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H174" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>776</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>777</v>
       </c>
       <c r="C175" s="7">
         <v>50</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G175" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H175" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="C176" s="7">
         <v>100</v>
       </c>
       <c r="E176" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="F176" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="F176" s="7" t="s">
-        <v>508</v>
-      </c>
       <c r="G176" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H176" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -9282,10 +9297,10 @@
         <v>49</v>
       </c>
       <c r="G177" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H177" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -9308,18 +9323,18 @@
         <v>53</v>
       </c>
       <c r="G178" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H178" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C179" s="7">
         <v>180</v>
@@ -9328,13 +9343,13 @@
         <v>150</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H179" s="7" t="s">
         <v>211</v>
@@ -9360,87 +9375,87 @@
         <v>56</v>
       </c>
       <c r="G180" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H180" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>559</v>
       </c>
       <c r="C181" s="7">
         <v>180</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H181" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>559</v>
       </c>
       <c r="C182" s="7">
         <v>180</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G182" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H182" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>996</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>997</v>
       </c>
       <c r="C183" s="7">
         <v>200</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="G183" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H183" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C184" s="7">
         <v>700</v>
@@ -9449,13 +9464,13 @@
         <v>530</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="G184" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H184" s="7" t="s">
         <v>66</v>
@@ -9463,33 +9478,33 @@
     </row>
     <row r="185" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>956</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>957</v>
       </c>
       <c r="C185" s="7">
         <v>200</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G185" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H185" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C186" s="7">
         <v>300</v>
@@ -9498,13 +9513,13 @@
         <v>200</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G186" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H186" s="7" t="s">
         <v>211</v>
@@ -9512,25 +9527,25 @@
     </row>
     <row r="187" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C187" s="7">
         <v>180</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G187" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H187" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -9556,12 +9571,12 @@
         <v>31</v>
       </c>
       <c r="H188" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>18</v>
@@ -9573,13 +9588,13 @@
         <v>350</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G189" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H189" s="7" t="s">
         <v>100</v>
@@ -9605,10 +9620,10 @@
         <v>192</v>
       </c>
       <c r="G190" s="7" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H190" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -9631,10 +9646,10 @@
         <v>195</v>
       </c>
       <c r="G191" s="7" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H191" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -9657,10 +9672,10 @@
         <v>198</v>
       </c>
       <c r="G192" s="7" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H192" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
@@ -9680,7 +9695,7 @@
         <v>356</v>
       </c>
       <c r="G193" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H193" s="7" t="s">
         <v>66</v>
@@ -9688,7 +9703,7 @@
     </row>
     <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>18</v>
@@ -9700,16 +9715,16 @@
         <v>200</v>
       </c>
       <c r="E194" s="7" t="s">
+        <v>937</v>
+      </c>
+      <c r="F194" s="7" t="s">
         <v>938</v>
       </c>
-      <c r="F194" s="7" t="s">
-        <v>939</v>
-      </c>
       <c r="G194" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H194" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
@@ -9732,128 +9747,128 @@
         <v>230</v>
       </c>
       <c r="G195" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H195" s="7" t="s">
         <v>100</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C196" s="7">
         <v>230</v>
       </c>
       <c r="E196" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G196" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H196" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C197" s="7">
         <v>230</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G197" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H197" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>960</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>961</v>
       </c>
       <c r="C198" s="7">
         <v>300</v>
       </c>
       <c r="E198" s="8" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G198" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H198" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>962</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>963</v>
       </c>
       <c r="C199" s="7">
         <v>250</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G199" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H199" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>595</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>596</v>
       </c>
       <c r="C200" s="7">
         <v>200</v>
       </c>
       <c r="E200" s="7" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G200" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H200" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
@@ -9884,10 +9899,10 @@
     </row>
     <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C202" s="7">
         <v>250</v>
@@ -9896,13 +9911,13 @@
         <v>200</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G202" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H202" s="7" t="s">
         <v>12</v>
@@ -9928,30 +9943,30 @@
         <v>202</v>
       </c>
       <c r="G203" s="7" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H203" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C204" s="7">
         <v>200</v>
       </c>
       <c r="E204" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G204" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H204" s="7" t="s">
         <v>211</v>
@@ -9977,18 +9992,18 @@
         <v>20</v>
       </c>
       <c r="G205" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H205" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C206" s="9">
         <v>100</v>
@@ -9997,24 +10012,24 @@
         <v>50</v>
       </c>
       <c r="E206" s="10" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="G206" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H206" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>619</v>
       </c>
       <c r="C207" s="7">
         <v>170</v>
@@ -10023,13 +10038,13 @@
         <v>120</v>
       </c>
       <c r="E207" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H207" s="7" t="s">
         <v>211</v>
@@ -10037,10 +10052,10 @@
     </row>
     <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C208" s="7">
         <v>219.5</v>
@@ -10055,7 +10070,7 @@
         <v>207</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H208" s="7" t="s">
         <v>211</v>
@@ -10063,10 +10078,10 @@
     </row>
     <row r="209" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C209" s="7">
         <v>228</v>
@@ -10075,13 +10090,13 @@
         <v>120</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G209" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H209" s="7" t="s">
         <v>211</v>
@@ -10089,25 +10104,25 @@
     </row>
     <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C210" s="7">
         <v>100</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="G210" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H210" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -10130,7 +10145,7 @@
         <v>24</v>
       </c>
       <c r="G211" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H211" s="7" t="s">
         <v>12</v>
@@ -10156,7 +10171,7 @@
         <v>359</v>
       </c>
       <c r="G212" s="7" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H212" s="7" t="s">
         <v>12</v>
@@ -10164,7 +10179,7 @@
     </row>
     <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>163</v>
@@ -10173,13 +10188,13 @@
         <v>100</v>
       </c>
       <c r="E213" s="7" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G213" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H213" s="7" t="s">
         <v>211</v>
@@ -10208,7 +10223,7 @@
         <v>294</v>
       </c>
       <c r="H214" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -10231,15 +10246,15 @@
         <v>31</v>
       </c>
       <c r="H215" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C216" s="7">
         <v>376.51</v>
@@ -10254,18 +10269,18 @@
         <v>26</v>
       </c>
       <c r="G216" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H216" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>518</v>
       </c>
       <c r="C217" s="7">
         <v>298</v>
@@ -10274,13 +10289,13 @@
         <v>200</v>
       </c>
       <c r="E217" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="F217" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="F217" s="7" t="s">
-        <v>520</v>
-      </c>
       <c r="G217" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H217" s="7" t="s">
         <v>12</v>
@@ -10306,7 +10321,7 @@
         <v>16</v>
       </c>
       <c r="G218" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H218" s="7" t="s">
         <v>12</v>
@@ -10329,7 +10344,7 @@
         <v>131</v>
       </c>
       <c r="G219" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H219" s="7" t="s">
         <v>100</v>
@@ -10337,10 +10352,10 @@
     </row>
     <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C220" s="7">
         <v>80</v>
@@ -10349,13 +10364,13 @@
         <v>50</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F220" s="7" t="s">
         <v>132</v>
       </c>
       <c r="G220" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H220" s="7" t="s">
         <v>100</v>
@@ -10363,10 +10378,10 @@
     </row>
     <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>522</v>
       </c>
       <c r="C221" s="7">
         <v>859</v>
@@ -10375,24 +10390,24 @@
         <v>650</v>
       </c>
       <c r="E221" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="F221" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="F221" s="7" t="s">
-        <v>524</v>
-      </c>
       <c r="G221" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H221" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C222" s="7">
         <v>150</v>
@@ -10401,13 +10416,13 @@
         <v>100</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G222" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H222" s="7" t="s">
         <v>211</v>
@@ -10415,10 +10430,10 @@
     </row>
     <row r="223" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C223" s="7">
         <v>150</v>
@@ -10427,13 +10442,13 @@
         <v>100</v>
       </c>
       <c r="E223" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="F223" s="7" t="s">
         <v>662</v>
       </c>
-      <c r="F223" s="7" t="s">
-        <v>663</v>
-      </c>
       <c r="G223" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H223" s="7" t="s">
         <v>211</v>
@@ -10441,10 +10456,10 @@
     </row>
     <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C224" s="7">
         <v>150</v>
@@ -10453,13 +10468,13 @@
         <v>100</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G224" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H224" s="7" t="s">
         <v>211</v>
@@ -10467,10 +10482,10 @@
     </row>
     <row r="225" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C225" s="7">
         <v>200</v>
@@ -10479,13 +10494,13 @@
         <v>150</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G225" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H225" s="7" t="s">
         <v>211</v>
@@ -10493,10 +10508,10 @@
     </row>
     <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C226" s="7">
         <v>170</v>
@@ -10519,10 +10534,10 @@
     </row>
     <row r="227" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C227" s="7">
         <v>200</v>
@@ -10537,7 +10552,7 @@
         <v>179</v>
       </c>
       <c r="G227" s="7" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H227" s="7" t="s">
         <v>66</v>
@@ -10545,10 +10560,10 @@
     </row>
     <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>885</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>886</v>
       </c>
       <c r="C228" s="7">
         <v>150</v>
@@ -10557,13 +10572,13 @@
         <v>100</v>
       </c>
       <c r="E228" s="7" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="G228" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H228" s="7" t="s">
         <v>100</v>
@@ -10571,10 +10586,10 @@
     </row>
     <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>864</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>865</v>
       </c>
       <c r="C229" s="7">
         <v>200</v>
@@ -10583,13 +10598,13 @@
         <v>100</v>
       </c>
       <c r="E229" s="8" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F229" s="7" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G229" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H229" s="7" t="s">
         <v>100</v>
@@ -10615,10 +10630,10 @@
         <v>59</v>
       </c>
       <c r="G230" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H230" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -10638,7 +10653,7 @@
         <v>398</v>
       </c>
       <c r="G231" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H231" s="7" t="s">
         <v>12</v>
@@ -10667,7 +10682,7 @@
         <v>294</v>
       </c>
       <c r="H232" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -10690,7 +10705,7 @@
         <v>313</v>
       </c>
       <c r="G233" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H233" s="7" t="s">
         <v>100</v>
@@ -10716,18 +10731,18 @@
         <v>76</v>
       </c>
       <c r="G234" s="7" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H234" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C235" s="7">
         <v>450</v>
@@ -10736,21 +10751,21 @@
         <v>410</v>
       </c>
       <c r="E235" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="F235" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="F235" s="7" t="s">
-        <v>492</v>
-      </c>
       <c r="G235" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H235" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>239</v>
@@ -10762,24 +10777,24 @@
         <v>150</v>
       </c>
       <c r="E236" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="F236" s="7" t="s">
         <v>795</v>
       </c>
-      <c r="F236" s="7" t="s">
-        <v>796</v>
-      </c>
       <c r="G236" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H236" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C237" s="7">
         <v>250</v>
@@ -10788,24 +10803,24 @@
         <v>200</v>
       </c>
       <c r="E237" s="7" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G237" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H237" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C238" s="7">
         <v>550</v>
@@ -10814,24 +10829,24 @@
         <v>450</v>
       </c>
       <c r="E238" s="7" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="F238" s="7" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="G238" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H238" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C239" s="7">
         <v>550</v>
@@ -10840,24 +10855,24 @@
         <v>440</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="F239" s="7" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="G239" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H239" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C240" s="7">
         <v>450</v>
@@ -10866,16 +10881,16 @@
         <v>420</v>
       </c>
       <c r="E240" s="7" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="F240" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="G240" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="H240" s="7" t="s">
         <v>674</v>
-      </c>
-      <c r="G240" s="7" t="s">
-        <v>760</v>
-      </c>
-      <c r="H240" s="7" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -10921,7 +10936,7 @@
         <v>362</v>
       </c>
       <c r="G242" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H242" s="7" t="s">
         <v>12</v>
@@ -10947,15 +10962,15 @@
         <v>237</v>
       </c>
       <c r="G243" s="7" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H243" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>18</v>
@@ -10964,13 +10979,13 @@
         <v>280</v>
       </c>
       <c r="E244" s="7" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F244" s="7" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G244" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H244" s="7" t="s">
         <v>211</v>
@@ -11004,7 +11019,7 @@
     </row>
     <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>18</v>
@@ -11019,7 +11034,7 @@
         <v>134</v>
       </c>
       <c r="G246" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H246" s="7" t="s">
         <v>100</v>
@@ -11042,7 +11057,7 @@
         <v>452</v>
       </c>
       <c r="G247" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H247" s="7" t="s">
         <v>100</v>
@@ -11050,33 +11065,33 @@
     </row>
     <row r="248" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C248" s="7">
         <v>200</v>
       </c>
       <c r="E248" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F248" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G248" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H248" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C249" s="7">
         <v>300</v>
@@ -11085,13 +11100,13 @@
         <v>150</v>
       </c>
       <c r="E249" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F249" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G249" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H249" s="7" t="s">
         <v>211</v>
@@ -11140,7 +11155,7 @@
         <v>137</v>
       </c>
       <c r="G251" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H251" s="7" t="s">
         <v>100</v>
@@ -11166,7 +11181,7 @@
         <v>140</v>
       </c>
       <c r="G252" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H252" s="7" t="s">
         <v>100</v>
@@ -11192,7 +11207,7 @@
         <v>143</v>
       </c>
       <c r="G253" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H253" s="7" t="s">
         <v>100</v>
@@ -11200,10 +11215,10 @@
     </row>
     <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C254" s="7">
         <v>150</v>
@@ -11212,13 +11227,13 @@
         <v>100</v>
       </c>
       <c r="E254" s="7" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F254" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G254" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H254" s="7" t="s">
         <v>211</v>
@@ -11244,7 +11259,7 @@
         <v>401</v>
       </c>
       <c r="G255" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H255" s="7" t="s">
         <v>12</v>
@@ -11252,19 +11267,19 @@
     </row>
     <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C256" s="7">
         <v>150</v>
       </c>
       <c r="E256" s="7" t="s">
+        <v>910</v>
+      </c>
+      <c r="F256" s="7" t="s">
         <v>911</v>
-      </c>
-      <c r="F256" s="7" t="s">
-        <v>912</v>
       </c>
       <c r="G256" s="7" t="s">
         <v>438</v>
@@ -11273,12 +11288,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>1050</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>1051</v>
       </c>
       <c r="C257" s="7">
         <v>895</v>
@@ -11287,19 +11302,19 @@
         <v>550</v>
       </c>
       <c r="E257" s="7" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F257" s="7" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G257" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H257" s="7" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>453</v>
       </c>
@@ -11312,20 +11327,26 @@
       <c r="D258" s="7">
         <v>1300</v>
       </c>
-      <c r="E258" s="7" t="s">
+      <c r="E258" s="12" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F258" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="F258" s="7" t="s">
-        <v>456</v>
-      </c>
       <c r="G258" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H258" s="7" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I258" s="12" t="s">
+        <v>1452</v>
+      </c>
+      <c r="J258" s="12" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>276</v>
       </c>
@@ -11351,30 +11372,30 @@
         <v>66</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>754</v>
       </c>
       <c r="C260" s="7">
         <v>50</v>
       </c>
       <c r="E260" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F260" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G260" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H260" s="7" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>301</v>
       </c>
@@ -11388,7 +11409,7 @@
         <v>600</v>
       </c>
       <c r="E261" s="12" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="G261" s="7" t="s">
         <v>303</v>
@@ -11397,35 +11418,35 @@
         <v>211</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>629</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>630</v>
       </c>
       <c r="C262" s="7">
         <v>240</v>
       </c>
       <c r="E262" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F262" s="7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G262" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H262" s="7" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C263" s="7">
         <v>200</v>
@@ -11434,19 +11455,19 @@
         <v>150</v>
       </c>
       <c r="E263" s="7" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F263" s="7" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G263" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H263" s="7" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>431</v>
       </c>
@@ -11469,12 +11490,12 @@
         <v>31</v>
       </c>
       <c r="H264" s="7" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>18</v>
@@ -11486,21 +11507,21 @@
         <v>200</v>
       </c>
       <c r="E265" s="7" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F265" s="7" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G265" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H265" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>18</v>
@@ -11512,19 +11533,19 @@
         <v>100</v>
       </c>
       <c r="E266" s="7" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F266" s="7" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G266" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H266" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>279</v>
       </c>
@@ -11550,7 +11571,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>262</v>
       </c>
@@ -11576,7 +11597,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>363</v>
       </c>
@@ -11596,59 +11617,59 @@
         <v>365</v>
       </c>
       <c r="G269" s="7" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H269" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="270" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C270" s="7">
         <v>300</v>
       </c>
       <c r="E270" s="7" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F270" s="7" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G270" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H270" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="271" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>968</v>
-      </c>
-      <c r="B271" s="1" t="s">
-        <v>969</v>
       </c>
       <c r="C271" s="7">
         <v>200</v>
       </c>
       <c r="E271" s="7" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F271" s="7" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G271" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H271" s="7" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>266</v>
       </c>
@@ -11673,10 +11694,10 @@
     </row>
     <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>1015</v>
-      </c>
-      <c r="B273" s="1" t="s">
-        <v>1016</v>
       </c>
       <c r="C273" s="7">
         <v>3500</v>
@@ -11685,19 +11706,19 @@
         <v>2500</v>
       </c>
       <c r="E273" s="7" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="F273" s="7" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="G273" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H273" s="7" t="s">
         <v>100</v>
       </c>
       <c r="I273" s="12" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
@@ -11705,7 +11726,7 @@
         <v>435</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C274" s="7">
         <v>200</v>
@@ -11780,10 +11801,10 @@
     </row>
     <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C277" s="7">
         <v>715</v>
@@ -11792,13 +11813,13 @@
         <v>450</v>
       </c>
       <c r="E277" s="7" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F277" s="7" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G277" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H277" s="7" t="s">
         <v>12</v>
@@ -11806,10 +11827,10 @@
     </row>
     <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B278" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="B278" s="1" t="s">
-        <v>463</v>
       </c>
       <c r="C278" s="7">
         <v>806</v>
@@ -11818,13 +11839,13 @@
         <v>380</v>
       </c>
       <c r="E278" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F278" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G278" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H278" s="7" t="s">
         <v>12</v>
@@ -11835,7 +11856,7 @@
         <v>218</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C279" s="7">
         <v>503</v>
@@ -11850,7 +11871,7 @@
         <v>220</v>
       </c>
       <c r="G279" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H279" s="7" t="s">
         <v>12</v>
@@ -11861,7 +11882,7 @@
         <v>224</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C280" s="7">
         <v>570</v>
@@ -11876,7 +11897,7 @@
         <v>226</v>
       </c>
       <c r="G280" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H280" s="7" t="s">
         <v>12</v>
@@ -11884,10 +11905,10 @@
     </row>
     <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C281" s="7">
         <v>298</v>
@@ -11896,13 +11917,13 @@
         <v>200</v>
       </c>
       <c r="E281" s="7" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F281" s="7" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G281" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H281" s="7" t="s">
         <v>66</v>
@@ -11922,13 +11943,13 @@
         <v>220</v>
       </c>
       <c r="E282" s="7" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F282" s="7" t="s">
         <v>368</v>
       </c>
       <c r="G282" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H282" s="7" t="s">
         <v>66</v>
@@ -11948,13 +11969,13 @@
         <v>250</v>
       </c>
       <c r="E283" s="7" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F283" s="7" t="s">
         <v>371</v>
       </c>
       <c r="G283" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H283" s="7" t="s">
         <v>66</v>
@@ -11988,7 +12009,7 @@
     </row>
     <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>145</v>
@@ -12006,7 +12027,7 @@
         <v>147</v>
       </c>
       <c r="G285" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H285" s="7" t="s">
         <v>100</v>
@@ -12014,7 +12035,7 @@
     </row>
     <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>148</v>
@@ -12032,7 +12053,7 @@
         <v>150</v>
       </c>
       <c r="G286" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H286" s="7" t="s">
         <v>100</v>
@@ -12040,7 +12061,7 @@
     </row>
     <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>126</v>
@@ -12058,7 +12079,7 @@
         <v>128</v>
       </c>
       <c r="G287" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H287" s="7" t="s">
         <v>100</v>
@@ -12066,7 +12087,7 @@
     </row>
     <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>148</v>
@@ -12084,7 +12105,7 @@
         <v>152</v>
       </c>
       <c r="G288" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H288" s="7" t="s">
         <v>100</v>
@@ -12092,7 +12113,7 @@
     </row>
     <row r="289" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>108</v>
@@ -12107,7 +12128,7 @@
         <v>144</v>
       </c>
       <c r="G289" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H289" s="7" t="s">
         <v>100</v>
@@ -12115,10 +12136,10 @@
     </row>
     <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>835</v>
-      </c>
-      <c r="B290" s="1" t="s">
-        <v>836</v>
       </c>
       <c r="C290" s="7">
         <v>144</v>
@@ -12133,10 +12154,10 @@
         <v>154</v>
       </c>
       <c r="G290" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H290" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -12159,10 +12180,10 @@
         <v>62</v>
       </c>
       <c r="G291" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H291" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
@@ -12183,7 +12204,7 @@
         <v>374</v>
       </c>
       <c r="G292" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H292" s="7" t="s">
         <v>100</v>
@@ -12209,7 +12230,7 @@
         <v>217</v>
       </c>
       <c r="G293" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H293" s="7" t="s">
         <v>211</v>
@@ -12235,7 +12256,7 @@
         <v>182</v>
       </c>
       <c r="G294" s="7" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H294" s="7" t="s">
         <v>66</v>
@@ -12272,7 +12293,7 @@
         <v>183</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C296" s="7">
         <v>521</v>
@@ -12287,7 +12308,7 @@
         <v>185</v>
       </c>
       <c r="G296" s="7" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H296" s="7" t="s">
         <v>66</v>
@@ -12321,10 +12342,10 @@
     </row>
     <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>623</v>
-      </c>
-      <c r="B298" s="1" t="s">
-        <v>624</v>
       </c>
       <c r="C298" s="7">
         <v>688</v>
@@ -12333,13 +12354,13 @@
         <v>400</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F298" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G298" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H298" s="7" t="s">
         <v>211</v>
@@ -12347,79 +12368,79 @@
     </row>
     <row r="299" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>985</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>986</v>
       </c>
       <c r="C299" s="7">
         <v>200</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F299" s="7" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="G299" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H299" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C300" s="7">
         <v>180</v>
       </c>
       <c r="E300" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F300" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G300" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H300" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C301" s="7">
         <v>200</v>
       </c>
       <c r="E301" s="7" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F301" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G301" s="7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H301" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C302" s="7">
         <v>555</v>
@@ -12428,13 +12449,13 @@
         <v>300</v>
       </c>
       <c r="E302" s="7" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="F302" s="7" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G302" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H302" s="7" t="s">
         <v>12</v>
@@ -12442,10 +12463,10 @@
     </row>
     <row r="303" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C303" s="7">
         <v>622</v>
@@ -12454,13 +12475,13 @@
         <v>350</v>
       </c>
       <c r="E303" s="7" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="F303" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G303" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H303" s="7" t="s">
         <v>12</v>
@@ -12468,10 +12489,10 @@
     </row>
     <row r="304" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>1086</v>
-      </c>
-      <c r="B304" s="1" t="s">
-        <v>1087</v>
       </c>
       <c r="C304" s="7">
         <v>400</v>
@@ -12480,13 +12501,13 @@
         <v>300</v>
       </c>
       <c r="E304" s="7" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="F304" s="7" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G304" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H304" s="7" t="s">
         <v>100</v>
@@ -12494,10 +12515,10 @@
     </row>
     <row r="305" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>1090</v>
-      </c>
-      <c r="B305" s="1" t="s">
-        <v>1091</v>
       </c>
       <c r="C305" s="7">
         <v>300</v>
@@ -12506,13 +12527,13 @@
         <v>250</v>
       </c>
       <c r="E305" s="7" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="F305" s="7" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G305" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H305" s="7" t="s">
         <v>100</v>
@@ -12520,7 +12541,7 @@
     </row>
     <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>27</v>
@@ -12532,13 +12553,13 @@
         <v>270</v>
       </c>
       <c r="E306" s="7" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="F306" s="7" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G306" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H306" s="7" t="s">
         <v>66</v>
@@ -12546,10 +12567,10 @@
     </row>
     <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C307" s="7">
         <v>220</v>
@@ -12558,10 +12579,10 @@
         <v>150</v>
       </c>
       <c r="E307" s="7" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F307" s="7" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G307" s="7" t="s">
         <v>438</v>
@@ -12572,10 +12593,10 @@
     </row>
     <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C308" s="7">
         <v>399</v>
@@ -12584,30 +12605,30 @@
         <v>250</v>
       </c>
       <c r="E308" s="7" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F308" s="7" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G308" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H308" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I308" s="12" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="J308" s="12" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B309" s="1" t="s">
         <v>1103</v>
-      </c>
-      <c r="B309" s="1" t="s">
-        <v>1104</v>
       </c>
       <c r="C309" s="7">
         <v>599</v>
@@ -12616,24 +12637,24 @@
         <v>400</v>
       </c>
       <c r="E309" s="7" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="F309" s="7" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G309" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H309" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="310" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>1107</v>
-      </c>
-      <c r="B310" s="1" t="s">
-        <v>1108</v>
       </c>
       <c r="C310" s="7">
         <v>250</v>
@@ -12642,24 +12663,24 @@
         <v>180</v>
       </c>
       <c r="E310" s="7" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F310" s="7" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G310" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H310" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B311" s="1" t="s">
         <v>1109</v>
-      </c>
-      <c r="B311" s="1" t="s">
-        <v>1110</v>
       </c>
       <c r="C311" s="7">
         <v>598</v>
@@ -12668,10 +12689,10 @@
         <v>300</v>
       </c>
       <c r="E311" s="7" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="F311" s="7" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G311" s="7" t="s">
         <v>438</v>
@@ -12682,10 +12703,10 @@
     </row>
     <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>1115</v>
-      </c>
-      <c r="B312" s="1" t="s">
-        <v>1116</v>
       </c>
       <c r="C312" s="7">
         <v>200</v>
@@ -12694,13 +12715,13 @@
         <v>150</v>
       </c>
       <c r="E312" s="7" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="F312" s="7" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G312" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H312" s="7" t="s">
         <v>12</v>
@@ -12708,10 +12729,10 @@
     </row>
     <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C313" s="7">
         <v>100</v>
@@ -12720,13 +12741,13 @@
         <v>80</v>
       </c>
       <c r="E313" s="7" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="F313" s="7" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G313" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H313" s="7" t="s">
         <v>100</v>
@@ -12734,50 +12755,50 @@
     </row>
     <row r="314" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B314" s="1" t="s">
         <v>1127</v>
-      </c>
-      <c r="B314" s="1" t="s">
-        <v>1128</v>
       </c>
       <c r="C314" s="7">
         <v>200</v>
       </c>
       <c r="E314" s="7" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="F314" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H314" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="315" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C315" s="7">
         <v>200</v>
       </c>
       <c r="E315" s="7" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F315" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H315" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="316" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B316" s="1" t="s">
         <v>1133</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>1134</v>
       </c>
       <c r="C316" s="7">
         <v>820</v>
@@ -12786,53 +12807,53 @@
         <v>575</v>
       </c>
       <c r="E316" s="7" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F316" s="7" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H316" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="317" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B317" s="1" t="s">
         <v>1137</v>
-      </c>
-      <c r="B317" s="1" t="s">
-        <v>1138</v>
       </c>
       <c r="C317" s="7">
         <v>300</v>
       </c>
       <c r="E317" s="7" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="F317" s="7" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H317" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>1141</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>1142</v>
       </c>
       <c r="C318" s="7">
         <v>100</v>
       </c>
       <c r="E318" s="7" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F318" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G318" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H318" s="7" t="s">
         <v>66</v>
@@ -12840,10 +12861,10 @@
     </row>
     <row r="319" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>1145</v>
-      </c>
-      <c r="B319" s="1" t="s">
-        <v>1146</v>
       </c>
       <c r="C319" s="7">
         <v>399</v>
@@ -12852,10 +12873,10 @@
         <v>250</v>
       </c>
       <c r="E319" s="7" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F319" s="7" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H319" s="7" t="s">
         <v>66</v>
@@ -12863,30 +12884,30 @@
     </row>
     <row r="320" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B320" s="1" t="s">
         <v>1149</v>
-      </c>
-      <c r="B320" s="1" t="s">
-        <v>1150</v>
       </c>
       <c r="C320" s="7">
         <v>150</v>
       </c>
       <c r="E320" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F320" s="7" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H320" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C321" s="7">
         <v>299</v>
@@ -12895,24 +12916,24 @@
         <v>150</v>
       </c>
       <c r="E321" s="7" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="F321" s="7" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G321" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H321" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>1156</v>
-      </c>
-      <c r="B322" s="1" t="s">
-        <v>1157</v>
       </c>
       <c r="C322" s="7">
         <v>250</v>
@@ -12921,13 +12942,13 @@
         <v>150</v>
       </c>
       <c r="E322" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="F322" s="7" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G322" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H322" s="7" t="s">
         <v>12</v>
@@ -12935,30 +12956,30 @@
     </row>
     <row r="323" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C323" s="7">
         <v>200</v>
       </c>
       <c r="E323" s="7" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="F323" s="7" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H323" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="324" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>1164</v>
-      </c>
-      <c r="B324" s="1" t="s">
-        <v>1165</v>
       </c>
       <c r="C324" s="7">
         <v>338</v>
@@ -12967,21 +12988,21 @@
         <v>220</v>
       </c>
       <c r="E324" s="7" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="F324" s="7" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H324" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>1168</v>
-      </c>
-      <c r="B325" s="1" t="s">
-        <v>1169</v>
       </c>
       <c r="C325" s="7">
         <v>297</v>
@@ -12990,13 +13011,13 @@
         <v>150</v>
       </c>
       <c r="E325" s="7" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="F325" s="7" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G325" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H325" s="7" t="s">
         <v>12</v>
@@ -13004,10 +13025,10 @@
     </row>
     <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C326" s="7">
         <v>407</v>
@@ -13016,13 +13037,13 @@
         <v>180</v>
       </c>
       <c r="E326" s="7" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="F326" s="7" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G326" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H326" s="7" t="s">
         <v>66</v>
@@ -13030,10 +13051,10 @@
     </row>
     <row r="327" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B327" s="1" t="s">
         <v>1176</v>
-      </c>
-      <c r="B327" s="1" t="s">
-        <v>1177</v>
       </c>
       <c r="C327" s="7">
         <v>499</v>
@@ -13042,18 +13063,18 @@
         <v>200</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="F327" s="7" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H327" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B328" s="1" t="s">
         <v>18</v>
@@ -13065,13 +13086,13 @@
         <v>80</v>
       </c>
       <c r="E328" s="7" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="F328" s="7" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G328" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H328" s="7" t="s">
         <v>66</v>
@@ -13079,7 +13100,7 @@
     </row>
     <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>18</v>
@@ -13088,30 +13109,30 @@
         <v>200</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="F329" s="7" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H329" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C330" s="7">
         <v>300</v>
       </c>
       <c r="E330" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F330" s="7" t="s">
         <v>1186</v>
-      </c>
-      <c r="F330" s="7" t="s">
-        <v>1187</v>
       </c>
       <c r="G330" s="7" t="s">
         <v>438</v>
@@ -13122,10 +13143,10 @@
     </row>
     <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B331" s="1" t="s">
         <v>1189</v>
-      </c>
-      <c r="B331" s="1" t="s">
-        <v>1190</v>
       </c>
       <c r="C331" s="7">
         <v>299</v>
@@ -13134,21 +13155,21 @@
         <v>200</v>
       </c>
       <c r="E331" s="7" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="F331" s="7" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H331" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C332" s="7">
         <v>298</v>
@@ -13157,13 +13178,13 @@
         <v>170</v>
       </c>
       <c r="E332" s="7" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="F332" s="7" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="G332" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H332" s="7" t="s">
         <v>12</v>
@@ -13171,10 +13192,10 @@
     </row>
     <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B333" s="1" t="s">
         <v>1198</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>1199</v>
       </c>
       <c r="C333" s="7">
         <v>298</v>
@@ -13183,10 +13204,10 @@
         <v>200</v>
       </c>
       <c r="E333" s="7" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="F333" s="7" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G333" s="7" t="s">
         <v>438</v>
@@ -13197,10 +13218,10 @@
     </row>
     <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C334" s="7">
         <v>269</v>
@@ -13209,10 +13230,10 @@
         <v>180</v>
       </c>
       <c r="E334" s="7" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="F334" s="7" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G334" s="7" t="s">
         <v>438</v>
@@ -13223,7 +13244,7 @@
     </row>
     <row r="335" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>27</v>
@@ -13235,13 +13256,13 @@
         <v>200</v>
       </c>
       <c r="E335" s="7" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="F335" s="7" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="G335" s="7" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H335" s="7" t="s">
         <v>100</v>
@@ -13249,10 +13270,10 @@
     </row>
     <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C336" s="7">
         <v>608</v>
@@ -13261,21 +13282,21 @@
         <v>395</v>
       </c>
       <c r="E336" s="7" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="F336" s="7" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="H336" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="337" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B337" s="1" t="s">
         <v>1212</v>
-      </c>
-      <c r="B337" s="1" t="s">
-        <v>1213</v>
       </c>
       <c r="C337" s="7">
         <v>956</v>
@@ -13284,10 +13305,10 @@
         <v>482</v>
       </c>
       <c r="E337" s="7" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F337" s="7" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G337" s="7" t="s">
         <v>438</v>
@@ -13298,10 +13319,10 @@
     </row>
     <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>1216</v>
-      </c>
-      <c r="B338" s="1" t="s">
-        <v>1217</v>
       </c>
       <c r="C338" s="7">
         <v>298</v>
@@ -13310,13 +13331,13 @@
         <v>270</v>
       </c>
       <c r="E338" s="7" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F338" s="7" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G338" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H338" s="7" t="s">
         <v>12</v>
@@ -13324,7 +13345,7 @@
     </row>
     <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="B339" s="1" t="s">
         <v>27</v>
@@ -13336,10 +13357,10 @@
         <v>200</v>
       </c>
       <c r="E339" s="7" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F339" s="7" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H339" s="7" t="s">
         <v>100</v>
@@ -13347,7 +13368,7 @@
     </row>
     <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="B340" s="1" t="s">
         <v>27</v>
@@ -13359,44 +13380,44 @@
         <v>1700</v>
       </c>
       <c r="E340" s="12" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="F340" s="7" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="H340" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I340" s="12" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B341" s="1" t="s">
         <v>1224</v>
-      </c>
-      <c r="B341" s="1" t="s">
-        <v>1225</v>
       </c>
       <c r="C341" s="7">
         <v>500</v>
       </c>
       <c r="E341" s="7" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F341" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="H341" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B342" s="1" t="s">
         <v>1229</v>
-      </c>
-      <c r="B342" s="1" t="s">
-        <v>1230</v>
       </c>
       <c r="C342" s="7">
         <v>1665</v>
@@ -13405,24 +13426,24 @@
         <v>1500</v>
       </c>
       <c r="E342" s="7" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="F342" s="7" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H342" s="7" t="s">
         <v>100</v>
       </c>
       <c r="I342" s="12" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B343" s="1" t="s">
         <v>1233</v>
-      </c>
-      <c r="B343" s="1" t="s">
-        <v>1234</v>
       </c>
       <c r="C343" s="7">
         <v>850</v>
@@ -13431,13 +13452,13 @@
         <v>500</v>
       </c>
       <c r="E343" s="7" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F343" s="7" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="G343" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H343" s="7" t="s">
         <v>66</v>
@@ -13445,10 +13466,10 @@
     </row>
     <row r="344" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B344" s="1" t="s">
         <v>1238</v>
-      </c>
-      <c r="B344" s="1" t="s">
-        <v>1239</v>
       </c>
       <c r="C344" s="7">
         <v>200</v>
@@ -13457,21 +13478,21 @@
         <v>150</v>
       </c>
       <c r="E344" s="7" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F344" s="7" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="G344" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H344" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="345" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>18</v>
@@ -13483,10 +13504,10 @@
         <v>130</v>
       </c>
       <c r="E345" s="7" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F345" s="7" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="H345" s="7" t="s">
         <v>100</v>
@@ -13494,7 +13515,7 @@
     </row>
     <row r="346" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>18</v>
@@ -13506,10 +13527,10 @@
         <v>150</v>
       </c>
       <c r="E346" s="7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F346" s="7" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="H346" s="7" t="s">
         <v>100</v>
@@ -13517,10 +13538,10 @@
     </row>
     <row r="347" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C347" s="7">
         <v>729</v>
@@ -13529,10 +13550,10 @@
         <v>350</v>
       </c>
       <c r="E347" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="F347" s="7" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="H347" s="7" t="s">
         <v>211</v>
@@ -13540,10 +13561,10 @@
     </row>
     <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>1253</v>
-      </c>
-      <c r="B348" s="1" t="s">
-        <v>1254</v>
       </c>
       <c r="C348" s="7">
         <v>1299</v>
@@ -13552,10 +13573,10 @@
         <v>650</v>
       </c>
       <c r="E348" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="F348" s="7" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="H348" s="7" t="s">
         <v>66</v>
@@ -13563,10 +13584,10 @@
     </row>
     <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>1255</v>
-      </c>
-      <c r="B349" s="1" t="s">
-        <v>1256</v>
       </c>
       <c r="C349" s="7">
         <v>350</v>
@@ -13575,10 +13596,10 @@
         <v>200</v>
       </c>
       <c r="E349" s="7" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="F349" s="7" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H349" s="7" t="s">
         <v>66</v>
@@ -13586,10 +13607,10 @@
     </row>
     <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C350" s="7">
         <v>247</v>
@@ -13598,13 +13619,13 @@
         <v>170</v>
       </c>
       <c r="E350" s="7" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F350" s="7" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="G350" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H350" s="7" t="s">
         <v>12</v>
@@ -13612,10 +13633,10 @@
     </row>
     <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B351" s="1" t="s">
         <v>1265</v>
-      </c>
-      <c r="B351" s="1" t="s">
-        <v>1266</v>
       </c>
       <c r="C351" s="7">
         <v>150</v>
@@ -13624,10 +13645,10 @@
         <v>100</v>
       </c>
       <c r="E351" s="7" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="F351" s="7" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H351" s="7" t="s">
         <v>66</v>
@@ -13635,10 +13656,10 @@
     </row>
     <row r="352" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B352" s="1" t="s">
         <v>1267</v>
-      </c>
-      <c r="B352" s="1" t="s">
-        <v>1268</v>
       </c>
       <c r="C352" s="7">
         <v>349</v>
@@ -13647,10 +13668,10 @@
         <v>200</v>
       </c>
       <c r="E352" s="7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="F352" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="H352" s="7" t="s">
         <v>66</v>
@@ -13658,10 +13679,10 @@
     </row>
     <row r="353" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C353" s="7">
         <v>800</v>
@@ -13670,21 +13691,21 @@
         <v>750</v>
       </c>
       <c r="E353" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="F353" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H353" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B354" s="1" t="s">
         <v>1277</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>1278</v>
       </c>
       <c r="C354" s="7">
         <v>200</v>
@@ -13693,10 +13714,10 @@
         <v>170</v>
       </c>
       <c r="E354" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="F354" s="7" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H354" s="7" t="s">
         <v>66</v>
@@ -13704,10 +13725,10 @@
     </row>
     <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C355" s="7">
         <v>399</v>
@@ -13716,13 +13737,13 @@
         <v>250</v>
       </c>
       <c r="E355" s="7" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="F355" s="7" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="G355" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H355" s="7" t="s">
         <v>66</v>
@@ -13730,10 +13751,10 @@
     </row>
     <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C356" s="7">
         <v>399</v>
@@ -13742,13 +13763,13 @@
         <v>230</v>
       </c>
       <c r="E356" s="7" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="F356" s="7" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="G356" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H356" s="7" t="s">
         <v>66</v>
@@ -13756,10 +13777,10 @@
     </row>
     <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C357" s="7">
         <v>170</v>
@@ -13768,13 +13789,13 @@
         <v>150</v>
       </c>
       <c r="E357" s="7" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="F357" s="7" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="G357" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H357" s="7" t="s">
         <v>12</v>
@@ -13782,10 +13803,10 @@
     </row>
     <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C358" s="7">
         <v>262</v>
@@ -13794,13 +13815,13 @@
         <v>190</v>
       </c>
       <c r="E358" s="7" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F358" s="7" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="G358" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H358" s="7" t="s">
         <v>12</v>
@@ -13808,10 +13829,10 @@
     </row>
     <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C359" s="7">
         <v>468</v>
@@ -13820,13 +13841,13 @@
         <v>255</v>
       </c>
       <c r="E359" s="7" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="F359" s="7" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="G359" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H359" s="7" t="s">
         <v>12</v>
@@ -13834,7 +13855,7 @@
     </row>
     <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>9</v>
@@ -13846,13 +13867,13 @@
         <v>150</v>
       </c>
       <c r="E360" s="7" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="F360" s="7" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="G360" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H360" s="7" t="s">
         <v>12</v>
@@ -13860,10 +13881,10 @@
     </row>
     <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B361" s="1" t="s">
         <v>1309</v>
-      </c>
-      <c r="B361" s="1" t="s">
-        <v>1310</v>
       </c>
       <c r="C361" s="7">
         <v>447</v>
@@ -13872,13 +13893,13 @@
         <v>250</v>
       </c>
       <c r="E361" s="7" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F361" s="7" t="s">
         <v>1312</v>
       </c>
-      <c r="F361" s="7" t="s">
-        <v>1313</v>
-      </c>
       <c r="G361" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H361" s="7" t="s">
         <v>12</v>
@@ -13886,19 +13907,19 @@
     </row>
     <row r="362" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C362" s="7">
         <v>350</v>
       </c>
       <c r="E362" s="12" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="F362" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H362" s="7" t="s">
         <v>66</v>
@@ -13906,10 +13927,10 @@
     </row>
     <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B363" s="1" t="s">
         <v>1322</v>
-      </c>
-      <c r="B363" s="1" t="s">
-        <v>1323</v>
       </c>
       <c r="C363" s="7">
         <v>200</v>
@@ -13918,10 +13939,10 @@
         <v>120</v>
       </c>
       <c r="E363" s="7" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="F363" s="7" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="G363" s="7" t="s">
         <v>438</v>
@@ -13932,10 +13953,10 @@
     </row>
     <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B364" s="1" t="s">
         <v>1332</v>
-      </c>
-      <c r="B364" s="1" t="s">
-        <v>1333</v>
       </c>
       <c r="C364" s="7">
         <v>147</v>
@@ -13944,10 +13965,10 @@
         <v>100</v>
       </c>
       <c r="E364" s="7" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="F364" s="7" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="G364" s="7" t="s">
         <v>438</v>
@@ -13958,10 +13979,10 @@
     </row>
     <row r="365" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C365" s="7">
         <v>1383</v>
@@ -13970,13 +13991,13 @@
         <v>630</v>
       </c>
       <c r="E365" s="12" t="s">
+        <v>1343</v>
+      </c>
+      <c r="F365" s="12" t="s">
         <v>1344</v>
       </c>
-      <c r="F365" s="12" t="s">
-        <v>1345</v>
-      </c>
       <c r="G365" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H365" s="7" t="s">
         <v>66</v>
@@ -13984,10 +14005,10 @@
     </row>
     <row r="366" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B366" s="1" t="s">
         <v>1346</v>
-      </c>
-      <c r="B366" s="1" t="s">
-        <v>1347</v>
       </c>
       <c r="C366" s="7">
         <v>899</v>
@@ -13996,24 +14017,24 @@
         <v>485</v>
       </c>
       <c r="E366" s="12" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="F366" s="12" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="G366" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H366" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B367" s="1" t="s">
         <v>1350</v>
-      </c>
-      <c r="B367" s="1" t="s">
-        <v>1351</v>
       </c>
       <c r="C367" s="7">
         <v>1050</v>
@@ -14022,24 +14043,24 @@
         <v>600</v>
       </c>
       <c r="E367" s="12" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F367" s="12" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="G367" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H367" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B368" s="1" t="s">
         <v>1354</v>
-      </c>
-      <c r="B368" s="1" t="s">
-        <v>1355</v>
       </c>
       <c r="C368" s="7">
         <v>1084</v>
@@ -14048,24 +14069,24 @@
         <v>650</v>
       </c>
       <c r="E368" s="12" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="F368" s="12" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="G368" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H368" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B369" s="1" t="s">
         <v>1360</v>
-      </c>
-      <c r="B369" s="1" t="s">
-        <v>1361</v>
       </c>
       <c r="C369" s="7">
         <v>1265</v>
@@ -14074,24 +14095,24 @@
         <v>650</v>
       </c>
       <c r="E369" s="12" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F369" s="12" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="G369" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H369" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="370" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="C370" s="7">
         <v>1225</v>
@@ -14100,24 +14121,24 @@
         <v>700</v>
       </c>
       <c r="E370" s="12" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="F370" s="12" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="G370" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H370" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="371" spans="1:8" ht="87" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C371" s="7">
         <v>1225</v>
@@ -14126,24 +14147,24 @@
         <v>700</v>
       </c>
       <c r="E371" s="12" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="F371" s="12" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="G371" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H371" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B372" s="1" t="s">
         <v>1368</v>
-      </c>
-      <c r="B372" s="1" t="s">
-        <v>1369</v>
       </c>
       <c r="C372" s="7">
         <v>535</v>
@@ -14152,13 +14173,13 @@
         <v>400</v>
       </c>
       <c r="E372" s="12" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="F372" s="12" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="G372" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H372" s="7" t="s">
         <v>66</v>
@@ -14166,10 +14187,10 @@
     </row>
     <row r="373" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B373" s="1" t="s">
         <v>1384</v>
-      </c>
-      <c r="B373" s="1" t="s">
-        <v>1385</v>
       </c>
       <c r="C373" s="7">
         <v>1033</v>
@@ -14178,24 +14199,24 @@
         <v>675</v>
       </c>
       <c r="E373" s="12" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="F373" s="12" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="G373" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H373" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="374" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B374" s="1" t="s">
         <v>1386</v>
-      </c>
-      <c r="B374" s="1" t="s">
-        <v>1387</v>
       </c>
       <c r="C374" s="7">
         <v>614</v>
@@ -14204,24 +14225,24 @@
         <v>375</v>
       </c>
       <c r="E374" s="12" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="F374" s="12" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="G374" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H374" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="375" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B375" s="1" t="s">
         <v>1388</v>
-      </c>
-      <c r="B375" s="1" t="s">
-        <v>1389</v>
       </c>
       <c r="C375" s="7">
         <v>946</v>
@@ -14230,24 +14251,24 @@
         <v>575</v>
       </c>
       <c r="E375" s="12" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="F375" s="12" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="G375" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H375" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="376" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B376" s="1" t="s">
         <v>1380</v>
-      </c>
-      <c r="B376" s="1" t="s">
-        <v>1381</v>
       </c>
       <c r="C376" s="7">
         <v>1174</v>
@@ -14256,24 +14277,24 @@
         <v>700</v>
       </c>
       <c r="E376" s="12" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="F376" s="12" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="G376" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H376" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="377" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B377" s="1" t="s">
         <v>1390</v>
-      </c>
-      <c r="B377" s="1" t="s">
-        <v>1391</v>
       </c>
       <c r="C377" s="7">
         <v>1395</v>
@@ -14282,13 +14303,13 @@
         <v>920</v>
       </c>
       <c r="E377" s="12" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="F377" s="12" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="G377" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H377" s="7" t="s">
         <v>66</v>
@@ -14296,10 +14317,10 @@
     </row>
     <row r="378" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B378" s="1" t="s">
         <v>1394</v>
-      </c>
-      <c r="B378" s="1" t="s">
-        <v>1395</v>
       </c>
       <c r="C378" s="7">
         <v>488</v>
@@ -14308,24 +14329,24 @@
         <v>400</v>
       </c>
       <c r="E378" s="12" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="F378" s="12" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="G378" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H378" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C379" s="7">
         <v>554</v>
@@ -14334,13 +14355,13 @@
         <v>200</v>
       </c>
       <c r="E379" s="12" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F379" s="12" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="G379" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H379" s="7" t="s">
         <v>12</v>
@@ -14348,10 +14369,10 @@
     </row>
     <row r="380" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C380" s="7">
         <v>398</v>
@@ -14360,24 +14381,24 @@
         <v>250</v>
       </c>
       <c r="E380" s="12" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="F380" s="12" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="G380" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H380" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B381" s="1" t="s">
         <v>1406</v>
-      </c>
-      <c r="B381" s="1" t="s">
-        <v>1407</v>
       </c>
       <c r="C381" s="7">
         <v>399</v>
@@ -14386,13 +14407,13 @@
         <v>120</v>
       </c>
       <c r="E381" s="12" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="F381" s="12" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="G381" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H381" s="7" t="s">
         <v>66</v>
@@ -14400,10 +14421,10 @@
     </row>
     <row r="382" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B382" s="1" t="s">
         <v>1410</v>
-      </c>
-      <c r="B382" s="1" t="s">
-        <v>1411</v>
       </c>
       <c r="C382" s="7">
         <v>397</v>
@@ -14412,13 +14433,13 @@
         <v>300</v>
       </c>
       <c r="E382" s="12" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="F382" s="12" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="G382" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H382" s="7" t="s">
         <v>211</v>
@@ -14426,10 +14447,10 @@
     </row>
     <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B383" s="1" t="s">
         <v>1414</v>
-      </c>
-      <c r="B383" s="1" t="s">
-        <v>1415</v>
       </c>
       <c r="C383" s="7">
         <v>350</v>
@@ -14438,13 +14459,13 @@
         <v>300</v>
       </c>
       <c r="E383" s="12" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F383" s="12" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="G383" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H383" s="7" t="s">
         <v>66</v>
@@ -14452,10 +14473,10 @@
     </row>
     <row r="384" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B384" s="1" t="s">
         <v>1420</v>
-      </c>
-      <c r="B384" s="1" t="s">
-        <v>1421</v>
       </c>
       <c r="C384" s="7">
         <v>385</v>
@@ -14464,24 +14485,24 @@
         <v>300</v>
       </c>
       <c r="E384" s="12" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="F384" s="12" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="G384" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H384" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="385" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="C385" s="7">
         <v>1690</v>
@@ -14490,24 +14511,27 @@
         <v>1090</v>
       </c>
       <c r="E385" s="12" t="s">
-        <v>1425</v>
+        <v>1455</v>
       </c>
       <c r="F385" s="12" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="G385" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H385" s="7" t="s">
         <v>66</v>
       </c>
+      <c r="I385" s="12" t="s">
+        <v>1456</v>
+      </c>
     </row>
     <row r="386" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="1" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="C386" s="7">
         <v>1999</v>
@@ -14516,13 +14540,13 @@
         <v>800</v>
       </c>
       <c r="E386" s="12" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="F386" s="12" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="G386" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H386" s="7" t="s">
         <v>211</v>
@@ -14530,10 +14554,10 @@
     </row>
     <row r="387" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="1" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="C387" s="7">
         <v>4699</v>
@@ -14542,30 +14566,30 @@
         <v>2832</v>
       </c>
       <c r="E387" s="12" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="F387" s="12" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G387" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H387" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I387" s="12" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="J387" s="12" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="C388" s="7">
         <v>349</v>
@@ -14574,10 +14598,10 @@
         <v>295</v>
       </c>
       <c r="E388" s="12" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="F388" s="12" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="G388" s="7" t="s">
         <v>438</v>
@@ -14638,7 +14662,7 @@
     <hyperlink ref="F384" r:id="rId47"/>
     <hyperlink ref="E384" r:id="rId48"/>
     <hyperlink ref="F385" r:id="rId49"/>
-    <hyperlink ref="E385" r:id="rId50" display="https://http2.mlstatic.com/D_NQ_NP_2X_984373-MLA112451559563_052026-F.webp"/>
+    <hyperlink ref="E385" r:id="rId50"/>
     <hyperlink ref="F386" r:id="rId51"/>
     <hyperlink ref="E386" r:id="rId52"/>
     <hyperlink ref="F387" r:id="rId53"/>
@@ -14658,11 +14682,16 @@
     <hyperlink ref="J387" r:id="rId60"/>
     <hyperlink ref="I387" r:id="rId61"/>
     <hyperlink ref="I342"/>
+    <hyperlink ref="E258" r:id="rId62"/>
+    <hyperlink ref="I258" r:id="rId63"/>
+    <hyperlink ref="J258" r:id="rId64"/>
+    <hyperlink ref="I36" r:id="rId65"/>
+    <hyperlink ref="I385"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId62"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId66"/>
   <tableParts count="1">
-    <tablePart r:id="rId63"/>
+    <tablePart r:id="rId67"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2307" uniqueCount="1457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2325" uniqueCount="1475">
   <si>
     <t>Nombre</t>
   </si>
@@ -4407,6 +4407,60 @@
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_870766-MLA111944165952_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_835091-MLA112882459449_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_865807-MLA113706863262_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_881890-MLA115108214329_072026-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019f1a4ceb3b7612b8229efa46d49f6b/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_650019-MLA112598239078_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_694102-MLA111420836191_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_960139-MLA111232526403_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_654633-MLA111232677355_052026-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_908039-MLA112874706206_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_922341-MLA112874942992_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_668896-MLA114078462461_072026-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_761866-MLA76203783381_052024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_967910-MLA76082310461_042024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_699850-MLA76082339489_042024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_688162-MLA77258607126_072024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_987664-MLA73443046442_122023-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-static-clips.mms.mlstatic.com/62c82f1f923a3f082b72612d/019ec7172f297018bc87b285605c79fd/packaging/static/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_937988-MLA100214376229_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_839463-MLA100214244569_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_878239-MLA100214347283_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_746732-MLA100214337393_122025-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_853469-MLA73479850047_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_636371-MLA72966055893_112023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_647337-MLA74448293715_022024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_843886-MLA73007265330_112023-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_838661-MLA114043475512_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_997422-MLA111845686244_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_946430-MLA112856485647_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_885165-MLA111740080984_062026-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_700050-MLA90330537717_082025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_810830-MLA92985348779_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_611435-MLA103169335415_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_770740-MLA102656875022_122025-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019fbae051fa719da9d306536dceb684/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_972461-MLA108765590667_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_959062-MLA111287287492_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_702439-MLA108999676116_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_991088-MLA108999765964_032026-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_772336-MLA83215360667_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_641687-MLA82926894938_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_686941-MLA80851161221_112024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_788718-MLA101812695971_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_703043-MLA79489338416_102024-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019eedaef42876b0b4c1468e5ea4c162/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_918751-MLA113089268495_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_972829-MLA114388137831_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_739083-MLA113884890489_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_823404-MLA110625955659_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_668792-MLA111243248596_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_665158-MLA114050953663_072026-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_622982-MLA91998379772_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_918567-MLA93316673763_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_951409-MLA93316693351_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_873847-MLA99429346773_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_754609-MLA92520544449_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_981089-MLA107665597095_022026-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019f7cd765587bb9b171a45689bab017/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_860421-MLA111296936608_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_731074-MLA113783205421_062026-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-static-clips.mms.mlstatic.com/62c82f1f923a3f082b72612d/019ed9394d7a72dc8adc7f349c65987a/packaging/static/master.m3u8</t>
   </si>
 </sst>
 </file>
@@ -4569,7 +4623,7 @@
   <autoFilter ref="A1:J388">
     <filterColumn colId="0">
       <filters>
-        <filter val="Bebedero Para mascotas 4.5L, Fuente de Agua Dispensador Automático Silencioso"/>
+        <filter val="Epicentro Max-02 Restaurador De Bajos Para Auto, Ecualizador para sistema de audio_x000a_"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -5300,7 +5354,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>856</v>
       </c>
@@ -5323,7 +5377,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>763</v>
       </c>
@@ -5349,7 +5403,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>578</v>
       </c>
@@ -5372,7 +5426,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>789</v>
       </c>
@@ -5395,7 +5449,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>765</v>
       </c>
@@ -5421,7 +5475,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>533</v>
       </c>
@@ -5444,7 +5498,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>533</v>
       </c>
@@ -5467,7 +5521,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>533</v>
       </c>
@@ -5490,7 +5544,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>495</v>
       </c>
@@ -5516,7 +5570,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>111</v>
       </c>
@@ -5542,7 +5596,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>850</v>
       </c>
@@ -5568,7 +5622,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>839</v>
       </c>
@@ -5594,7 +5648,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>114</v>
       </c>
@@ -5617,7 +5671,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>840</v>
       </c>
@@ -5643,7 +5697,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>849</v>
       </c>
@@ -5669,7 +5723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>841</v>
       </c>
@@ -5693,6 +5747,12 @@
       </c>
       <c r="H32" s="7" t="s">
         <v>100</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>1462</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>1461</v>
       </c>
     </row>
     <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
@@ -6084,7 +6144,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>203</v>
       </c>
@@ -6110,7 +6170,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>337</v>
       </c>
@@ -6136,7 +6196,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>188</v>
       </c>
@@ -6159,7 +6219,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>808</v>
       </c>
@@ -6185,7 +6245,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>807</v>
       </c>
@@ -6211,7 +6271,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>457</v>
       </c>
@@ -6237,7 +6297,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>221</v>
       </c>
@@ -6263,7 +6323,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>813</v>
       </c>
@@ -6289,7 +6349,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>899</v>
       </c>
@@ -6315,7 +6375,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>1328</v>
       </c>
@@ -6341,7 +6401,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>978</v>
       </c>
@@ -6364,7 +6424,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>796</v>
       </c>
@@ -6387,7 +6447,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>1063</v>
       </c>
@@ -6412,8 +6472,14 @@
       <c r="H61" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I61" s="12" t="s">
+        <v>1458</v>
+      </c>
+      <c r="J61" s="12" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>340</v>
       </c>
@@ -6436,7 +6502,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>974</v>
       </c>
@@ -6459,7 +6525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>853</v>
       </c>
@@ -7296,7 +7362,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>646</v>
       </c>
@@ -7322,7 +7388,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>646</v>
       </c>
@@ -7345,7 +7411,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>308</v>
       </c>
@@ -7371,7 +7437,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>208</v>
       </c>
@@ -7397,7 +7463,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>243</v>
       </c>
@@ -7423,7 +7489,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>173</v>
       </c>
@@ -7449,7 +7515,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>176</v>
       </c>
@@ -7472,7 +7538,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>329</v>
       </c>
@@ -7497,8 +7563,11 @@
       <c r="H104" s="7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I104" s="12" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>464</v>
       </c>
@@ -7521,7 +7590,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>918</v>
       </c>
@@ -7547,7 +7616,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>212</v>
       </c>
@@ -7573,7 +7642,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>1003</v>
       </c>
@@ -7599,7 +7668,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>347</v>
       </c>
@@ -7625,7 +7694,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>1004</v>
       </c>
@@ -7651,7 +7720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>1073</v>
       </c>
@@ -7677,7 +7746,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>28</v>
       </c>
@@ -8490,7 +8559,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>486</v>
       </c>
@@ -8513,7 +8582,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>482</v>
       </c>
@@ -8536,7 +8605,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>255</v>
       </c>
@@ -8562,7 +8631,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>97</v>
       </c>
@@ -8585,7 +8654,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>33</v>
       </c>
@@ -8610,8 +8679,11 @@
       <c r="H149" s="7" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I149" s="12" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>36</v>
       </c>
@@ -8637,7 +8709,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>40</v>
       </c>
@@ -8663,7 +8735,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>164</v>
       </c>
@@ -8689,7 +8761,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>167</v>
       </c>
@@ -8715,7 +8787,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>170</v>
       </c>
@@ -8741,7 +8813,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>613</v>
       </c>
@@ -8767,7 +8839,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>391</v>
       </c>
@@ -8793,7 +8865,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>642</v>
       </c>
@@ -8819,7 +8891,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>478</v>
       </c>
@@ -8845,7 +8917,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>351</v>
       </c>
@@ -8868,7 +8940,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>871</v>
       </c>
@@ -10480,7 +10552,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>670</v>
       </c>
@@ -10506,7 +10578,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>723</v>
       </c>
@@ -10532,7 +10604,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>1027</v>
       </c>
@@ -10558,7 +10630,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>884</v>
       </c>
@@ -10584,7 +10656,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>863</v>
       </c>
@@ -10610,7 +10682,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>57</v>
       </c>
@@ -10636,7 +10708,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>395</v>
       </c>
@@ -10659,7 +10731,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>298</v>
       </c>
@@ -10685,7 +10757,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>311</v>
       </c>
@@ -10710,8 +10782,11 @@
       <c r="H233" s="7" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I233" s="12" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>74</v>
       </c>
@@ -10737,7 +10812,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>671</v>
       </c>
@@ -10763,7 +10838,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>793</v>
       </c>
@@ -10789,7 +10864,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>1316</v>
       </c>
@@ -10815,7 +10890,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>1028</v>
       </c>
@@ -10841,7 +10916,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>1031</v>
       </c>
@@ -10867,7 +10942,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>672</v>
       </c>
@@ -10893,7 +10968,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>321</v>
       </c>
@@ -10919,7 +10994,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>360</v>
       </c>
@@ -10942,7 +11017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>235</v>
       </c>
@@ -10968,7 +11043,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>820</v>
       </c>
@@ -10991,7 +11066,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>272</v>
       </c>
@@ -11017,7 +11092,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>1018</v>
       </c>
@@ -11040,7 +11115,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>450</v>
       </c>
@@ -11063,7 +11138,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>542</v>
       </c>
@@ -11086,7 +11161,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="249" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>656</v>
       </c>
@@ -11112,7 +11187,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>259</v>
       </c>
@@ -11135,7 +11210,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>135</v>
       </c>
@@ -11161,7 +11236,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>138</v>
       </c>
@@ -11186,8 +11261,11 @@
       <c r="H252" s="7" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I252" s="12" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>141</v>
       </c>
@@ -11213,7 +11291,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>720</v>
       </c>
@@ -11239,7 +11317,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>399</v>
       </c>
@@ -11265,7 +11343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>913</v>
       </c>
@@ -13677,7 +13755,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="353" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>1270</v>
       </c>
@@ -13699,8 +13777,14 @@
       <c r="H353" s="7" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I353" s="12" t="s">
+        <v>1467</v>
+      </c>
+      <c r="J353" s="12" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>1276</v>
       </c>
@@ -13723,7 +13807,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>1326</v>
       </c>
@@ -13749,7 +13833,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>1327</v>
       </c>
@@ -13775,7 +13859,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>1292</v>
       </c>
@@ -13801,7 +13885,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>1295</v>
       </c>
@@ -13827,7 +13911,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>1300</v>
       </c>
@@ -13853,7 +13937,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>1303</v>
       </c>
@@ -13879,7 +13963,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>1308</v>
       </c>
@@ -13905,7 +13989,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="362" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>1313</v>
       </c>
@@ -13925,7 +14009,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>1321</v>
       </c>
@@ -13951,7 +14035,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>1331</v>
       </c>
@@ -13977,7 +14061,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="365" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>1342</v>
       </c>
@@ -14003,7 +14087,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="366" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>1345</v>
       </c>
@@ -14029,7 +14113,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>1349</v>
       </c>
@@ -14055,7 +14139,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>1353</v>
       </c>
@@ -14081,7 +14165,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>1359</v>
       </c>
@@ -14107,7 +14191,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="370" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:10" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>1378</v>
       </c>
@@ -14132,8 +14216,14 @@
       <c r="H370" s="7" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="371" spans="1:8" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I370" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="J370" s="12" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>1377</v>
       </c>
@@ -14158,8 +14248,14 @@
       <c r="H371" s="7" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I371" s="12" t="s">
+        <v>1473</v>
+      </c>
+      <c r="J371" s="12" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
         <v>1367</v>
       </c>
@@ -14185,7 +14281,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="373" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>1383</v>
       </c>
@@ -14211,7 +14307,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="374" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>1385</v>
       </c>
@@ -14237,7 +14333,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="375" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:10" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
         <v>1387</v>
       </c>
@@ -14263,7 +14359,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="376" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>1379</v>
       </c>
@@ -14288,8 +14384,14 @@
       <c r="H376" s="7" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="377" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I376" s="12" t="s">
+        <v>1470</v>
+      </c>
+      <c r="J376" s="12" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>1389</v>
       </c>
@@ -14314,8 +14416,11 @@
       <c r="H377" s="7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="378" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I377" s="12" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
         <v>1393</v>
       </c>
@@ -14341,7 +14446,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
         <v>1397</v>
       </c>
@@ -14367,7 +14472,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="380" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
         <v>1401</v>
       </c>
@@ -14393,7 +14498,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="1" t="s">
         <v>1405</v>
       </c>
@@ -14419,7 +14524,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="382" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="1" t="s">
         <v>1409</v>
       </c>
@@ -14445,7 +14550,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="1" t="s">
         <v>1413</v>
       </c>
@@ -14471,7 +14576,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="384" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
         <v>1419</v>
       </c>
@@ -14497,7 +14602,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="385" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
         <v>1422</v>
       </c>
@@ -14550,6 +14655,9 @@
       </c>
       <c r="H386" s="7" t="s">
         <v>211</v>
+      </c>
+      <c r="I386" s="12" t="s">
+        <v>1464</v>
       </c>
     </row>
     <row r="387" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
@@ -14687,11 +14795,29 @@
     <hyperlink ref="J258" r:id="rId64"/>
     <hyperlink ref="I36" r:id="rId65"/>
     <hyperlink ref="I385"/>
+    <hyperlink ref="J61" r:id="rId66"/>
+    <hyperlink ref="I61"/>
+    <hyperlink ref="I377" r:id="rId67"/>
+    <hyperlink ref="I233"/>
+    <hyperlink ref="J32" r:id="rId68"/>
+    <hyperlink ref="I32"/>
+    <hyperlink ref="I104"/>
+    <hyperlink ref="I386"/>
+    <hyperlink ref="I149"/>
+    <hyperlink ref="J353" r:id="rId69"/>
+    <hyperlink ref="I353"/>
+    <hyperlink ref="I252"/>
+    <hyperlink ref="J376" r:id="rId70"/>
+    <hyperlink ref="I376"/>
+    <hyperlink ref="J370" r:id="rId71"/>
+    <hyperlink ref="I370"/>
+    <hyperlink ref="I371" r:id="rId72"/>
+    <hyperlink ref="J371" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId66"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId74"/>
   <tableParts count="1">
-    <tablePart r:id="rId67"/>
+    <tablePart r:id="rId75"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2325" uniqueCount="1475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2331" uniqueCount="1483">
   <si>
     <t>Nombre</t>
   </si>
@@ -4054,18 +4054,6 @@
     <t>https://panchochacharas.netlify.app/imagenes/4aaa7507c541c0dc0aac5e2393fb2c31.jpeg</t>
   </si>
   <si>
-    <t>Aluminio Negro con Mango de Madera, Set de 3 Unidades (24 y 28 cm)</t>
-  </si>
-  <si>
-    <t>Pack de Sartenes Antiadherentes</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_718669-MLA109014019546_032026-F.webp</t>
-  </si>
-  <si>
-    <t>https://www.mercadolibre.com.mx/pack-de-sartenes-antiadherentes-xinest-de-aluminio-negro-con-mango-de-madera-set-de-3-unidades-24-y-28-cm/p/MLM67441876?pdp_filters=item_id%3AMLM5595517674#&amp;gid=1&amp;pid=1</t>
-  </si>
-  <si>
     <t>Pistola Para Pintar Eléctrica</t>
   </si>
   <si>
@@ -4391,9 +4379,6 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_704682-MLA112632086794_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648062-MLA114215908179_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_721338-MLA112631444306_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_666014-MLA110019279904_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_747141-MLA110928994963_042026-F.webp</t>
   </si>
   <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_885715-MLA103257094455_122025-F.webp;</t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_679078-MLA106513626675_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_867289-MLA106513332881_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_837213-MLA106512862341_022026-F.webp</t>
   </si>
   <si>
@@ -4403,9 +4388,6 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_877039-MLA114231711531_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_669195-MLA111691242302_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_694108-MLA111868098195_052026-F.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">https://http2.mlstatic.com/D_NQ_NP_2X_984373-MLA112451559563_052026-F.webp; </t>
-  </si>
-  <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_870766-MLA111944165952_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_835091-MLA112882459449_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_865807-MLA113706863262_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_881890-MLA115108214329_072026-F.webp</t>
   </si>
   <si>
@@ -4461,6 +4443,48 @@
   </si>
   <si>
     <t>https://video-static-clips.mms.mlstatic.com/62c82f1f923a3f082b72612d/019ed9394d7a72dc8adc7f349c65987a/packaging/static/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019f6363325b7280806cc57c579f2933/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_630634-MLA83929492736_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_826427-MLA83875691856_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_778506-MLA83875632066_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_734315-MLA83875642068_042025-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_601798-MLA74779553000_032024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_784677-MLA71729912500_092023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_982997-MLA73375012815_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_982999-MLA70028199790_062023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_830261-MLA70048397883_062023-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019f29451c3876a8969ca32011081a6b/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_743943-MLA113720575198_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_652343-MLA98742656086_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_688496-MLA89833143459_082025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_980015-MLA111245266119_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_676086-MLA108251244515_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_743943-MLA113720575198_072026-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019eec50ebdc7581aaf884c109615b29/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_842998-MLA109635418200_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_655182-MLA88058609951_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_931498-MLA73993836353_012024-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_892154-MLA114436130385_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_641144-MLA114436417313_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_829930-MLA114436306203_072026-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_726152-MLA113045385176_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_848969-MLA113204126664_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_715603-MLA113204126666_072026-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_854442-MLA81845510730_012025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_966885-MLA81845471952_012025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_982348-MLA81845471950_012025-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_933354-MLA113160110934_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_644822-MLA114391216509_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_679253-MLA114391531429_072026-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019f9f72c531799fa159fcfdf4ceaee9/master.m3u8</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_885715-MLA103257094455_122025-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_984373-MLA112451559563_052026-F.webp</t>
   </si>
 </sst>
 </file>
@@ -4619,14 +4643,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J388" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J388">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Epicentro Max-02 Restaurador De Bajos Para Auto, Ecualizador para sistema de audio_x000a_"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J387" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J387"/>
   <sortState ref="A2:H342">
     <sortCondition ref="A1:A342"/>
   </sortState>
@@ -4931,7 +4949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J388"/>
+  <dimension ref="A1:J387"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" style="1" customWidth="1"/>
@@ -4971,13 +4989,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>1437</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1082</v>
       </c>
@@ -5005,7 +5023,7 @@
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1084</v>
       </c>
@@ -5031,7 +5049,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>588</v>
       </c>
@@ -5054,7 +5072,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>155</v>
       </c>
@@ -5080,7 +5098,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>406</v>
       </c>
@@ -5103,7 +5121,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>862</v>
       </c>
@@ -5129,7 +5147,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>104</v>
       </c>
@@ -5155,7 +5173,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>693</v>
       </c>
@@ -5181,7 +5199,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>861</v>
       </c>
@@ -5207,7 +5225,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>238</v>
       </c>
@@ -5233,7 +5251,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>750</v>
       </c>
@@ -5259,7 +5277,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>971</v>
       </c>
@@ -5282,7 +5300,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>632</v>
       </c>
@@ -5308,7 +5326,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>992</v>
       </c>
@@ -5331,7 +5349,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>109</v>
       </c>
@@ -5354,7 +5372,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>856</v>
       </c>
@@ -5377,7 +5395,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>763</v>
       </c>
@@ -5403,7 +5421,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>578</v>
       </c>
@@ -5426,7 +5444,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>789</v>
       </c>
@@ -5449,7 +5467,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>765</v>
       </c>
@@ -5475,7 +5493,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>533</v>
       </c>
@@ -5498,7 +5516,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>533</v>
       </c>
@@ -5521,7 +5539,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>533</v>
       </c>
@@ -5544,7 +5562,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>495</v>
       </c>
@@ -5570,7 +5588,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>111</v>
       </c>
@@ -5596,7 +5614,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>850</v>
       </c>
@@ -5622,7 +5640,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>839</v>
       </c>
@@ -5648,7 +5666,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>114</v>
       </c>
@@ -5671,7 +5689,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>840</v>
       </c>
@@ -5697,7 +5715,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>849</v>
       </c>
@@ -5723,7 +5741,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>841</v>
       </c>
@@ -5749,13 +5767,13 @@
         <v>100</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>1461</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>844</v>
       </c>
@@ -5781,7 +5799,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>842</v>
       </c>
@@ -5807,7 +5825,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>843</v>
       </c>
@@ -5830,7 +5848,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>1061</v>
       </c>
@@ -5856,10 +5874,10 @@
         <v>66</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>1454</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>1329</v>
       </c>
@@ -5885,7 +5903,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>1000</v>
       </c>
@@ -5908,7 +5926,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>598</v>
       </c>
@@ -5931,7 +5949,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>922</v>
       </c>
@@ -5957,7 +5975,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>77</v>
       </c>
@@ -5977,7 +5995,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>186</v>
       </c>
@@ -6000,7 +6018,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>159</v>
       </c>
@@ -6026,7 +6044,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>929</v>
       </c>
@@ -6049,7 +6067,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>934</v>
       </c>
@@ -6072,7 +6090,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>930</v>
       </c>
@@ -6095,7 +6113,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>930</v>
       </c>
@@ -6118,7 +6136,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>468</v>
       </c>
@@ -6144,7 +6162,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>203</v>
       </c>
@@ -6170,7 +6188,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>337</v>
       </c>
@@ -6196,7 +6214,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>188</v>
       </c>
@@ -6219,7 +6237,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>808</v>
       </c>
@@ -6245,7 +6263,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>807</v>
       </c>
@@ -6271,7 +6289,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>457</v>
       </c>
@@ -6297,7 +6315,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>221</v>
       </c>
@@ -6323,7 +6341,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>813</v>
       </c>
@@ -6348,8 +6366,14 @@
       <c r="H56" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I56" s="12" t="s">
+        <v>1475</v>
+      </c>
+      <c r="J56" s="12" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>899</v>
       </c>
@@ -6375,7 +6399,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>1328</v>
       </c>
@@ -6401,7 +6425,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>978</v>
       </c>
@@ -6424,7 +6448,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>796</v>
       </c>
@@ -6447,7 +6471,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>1063</v>
       </c>
@@ -6473,13 +6497,13 @@
         <v>12</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>1458</v>
+        <v>1452</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>1457</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>340</v>
       </c>
@@ -6502,7 +6526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>974</v>
       </c>
@@ -6525,7 +6549,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>853</v>
       </c>
@@ -6551,7 +6575,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>942</v>
       </c>
@@ -6577,7 +6601,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>944</v>
       </c>
@@ -6603,7 +6627,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>1077</v>
       </c>
@@ -6629,13 +6653,13 @@
         <v>100</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>120</v>
       </c>
@@ -6661,10 +6685,10 @@
         <v>100</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>1445</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>746</v>
       </c>
@@ -6687,7 +6711,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>676</v>
       </c>
@@ -6713,7 +6737,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>344</v>
       </c>
@@ -6736,7 +6760,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>410</v>
       </c>
@@ -6762,7 +6786,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>895</v>
       </c>
@@ -6788,10 +6812,10 @@
         <v>66</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>1438</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>379</v>
       </c>
@@ -6814,7 +6838,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>375</v>
       </c>
@@ -6837,7 +6861,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>413</v>
       </c>
@@ -6863,7 +6887,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>786</v>
       </c>
@@ -6889,7 +6913,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>774</v>
       </c>
@@ -6912,7 +6936,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>785</v>
       </c>
@@ -6935,7 +6959,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>1034</v>
       </c>
@@ -6961,7 +6985,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>771</v>
       </c>
@@ -6987,7 +7011,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>575</v>
       </c>
@@ -7010,7 +7034,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>569</v>
       </c>
@@ -7033,7 +7057,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>1040</v>
       </c>
@@ -7059,7 +7083,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>1048</v>
       </c>
@@ -7085,7 +7109,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>314</v>
       </c>
@@ -7111,7 +7135,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>601</v>
       </c>
@@ -7134,7 +7158,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>381</v>
       </c>
@@ -7160,7 +7184,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>1318</v>
       </c>
@@ -7186,7 +7210,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>906</v>
       </c>
@@ -7212,7 +7236,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>651</v>
       </c>
@@ -7238,7 +7262,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>682</v>
       </c>
@@ -7264,7 +7288,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>731</v>
       </c>
@@ -7287,7 +7311,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>231</v>
       </c>
@@ -7313,7 +7337,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>611</v>
       </c>
@@ -7339,7 +7363,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>648</v>
       </c>
@@ -7362,7 +7386,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>646</v>
       </c>
@@ -7388,7 +7412,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>646</v>
       </c>
@@ -7411,7 +7435,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>308</v>
       </c>
@@ -7437,7 +7461,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>208</v>
       </c>
@@ -7463,7 +7487,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>243</v>
       </c>
@@ -7489,7 +7513,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>173</v>
       </c>
@@ -7515,7 +7539,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>176</v>
       </c>
@@ -7538,7 +7562,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>329</v>
       </c>
@@ -7564,10 +7588,10 @@
         <v>66</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>1463</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>464</v>
       </c>
@@ -7590,7 +7614,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>918</v>
       </c>
@@ -7616,7 +7640,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>212</v>
       </c>
@@ -7642,7 +7666,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>1003</v>
       </c>
@@ -7668,7 +7692,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>347</v>
       </c>
@@ -7694,7 +7718,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>1004</v>
       </c>
@@ -7720,7 +7744,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>1073</v>
       </c>
@@ -7746,7 +7770,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>28</v>
       </c>
@@ -7769,7 +7793,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>30</v>
       </c>
@@ -7792,7 +7816,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>508</v>
       </c>
@@ -7815,7 +7839,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>524</v>
       </c>
@@ -7838,7 +7862,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>417</v>
       </c>
@@ -7864,7 +7888,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>875</v>
       </c>
@@ -7890,7 +7914,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>867</v>
       </c>
@@ -7916,7 +7940,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>421</v>
       </c>
@@ -7942,7 +7966,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>79</v>
       </c>
@@ -7968,7 +7992,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>700</v>
       </c>
@@ -7994,7 +8018,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>734</v>
       </c>
@@ -8020,7 +8044,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>686</v>
       </c>
@@ -8046,7 +8070,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>708</v>
       </c>
@@ -8069,7 +8093,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>8</v>
       </c>
@@ -8095,7 +8119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>512</v>
       </c>
@@ -8118,7 +8142,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>695</v>
       </c>
@@ -8141,7 +8165,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>565</v>
       </c>
@@ -8164,7 +8188,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>246</v>
       </c>
@@ -8187,7 +8211,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>249</v>
       </c>
@@ -8213,7 +8237,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>252</v>
       </c>
@@ -8239,7 +8263,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>384</v>
       </c>
@@ -8265,7 +8289,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>388</v>
       </c>
@@ -8291,7 +8315,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>82</v>
       </c>
@@ -8314,10 +8338,10 @@
         <v>530</v>
       </c>
       <c r="I134" s="12" t="s">
-        <v>1442</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>1024</v>
       </c>
@@ -8342,8 +8366,11 @@
       <c r="H135" s="7" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="136" spans="1:9" ht="58" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I135" s="12" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>989</v>
       </c>
@@ -8366,7 +8393,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>446</v>
       </c>
@@ -8392,7 +8419,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>85</v>
       </c>
@@ -8415,7 +8442,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>288</v>
       </c>
@@ -8441,7 +8468,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>1319</v>
       </c>
@@ -8467,7 +8494,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>88</v>
       </c>
@@ -8490,7 +8517,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>91</v>
       </c>
@@ -8513,7 +8540,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>94</v>
       </c>
@@ -8536,7 +8563,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>472</v>
       </c>
@@ -8559,7 +8586,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>486</v>
       </c>
@@ -8582,7 +8609,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>482</v>
       </c>
@@ -8605,7 +8632,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>255</v>
       </c>
@@ -8631,7 +8658,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>97</v>
       </c>
@@ -8654,7 +8681,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>33</v>
       </c>
@@ -8680,10 +8707,10 @@
         <v>531</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>1465</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>36</v>
       </c>
@@ -8709,7 +8736,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>40</v>
       </c>
@@ -8735,7 +8762,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>164</v>
       </c>
@@ -8761,7 +8788,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>167</v>
       </c>
@@ -8787,7 +8814,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>170</v>
       </c>
@@ -8813,7 +8840,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>613</v>
       </c>
@@ -8839,7 +8866,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>391</v>
       </c>
@@ -8865,7 +8892,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>642</v>
       </c>
@@ -8891,7 +8918,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>478</v>
       </c>
@@ -8917,7 +8944,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>351</v>
       </c>
@@ -8940,7 +8967,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>871</v>
       </c>
@@ -8966,7 +8993,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>607</v>
       </c>
@@ -8989,7 +9016,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>43</v>
       </c>
@@ -9012,7 +9039,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>714</v>
       </c>
@@ -9038,7 +9065,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>712</v>
       </c>
@@ -9061,7 +9088,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>704</v>
       </c>
@@ -9084,7 +9111,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>291</v>
       </c>
@@ -9110,7 +9137,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>498</v>
       </c>
@@ -9133,7 +9160,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>304</v>
       </c>
@@ -9159,7 +9186,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>124</v>
       </c>
@@ -9182,7 +9209,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>1080</v>
       </c>
@@ -9205,7 +9232,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>67</v>
       </c>
@@ -9228,7 +9255,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>318</v>
       </c>
@@ -9254,7 +9281,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>71</v>
       </c>
@@ -9279,8 +9306,14 @@
       <c r="H173" s="7" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I173" s="12" t="s">
+        <v>1470</v>
+      </c>
+      <c r="J173" s="12" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>760</v>
       </c>
@@ -9306,7 +9339,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>775</v>
       </c>
@@ -9329,7 +9362,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>504</v>
       </c>
@@ -9352,7 +9385,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>47</v>
       </c>
@@ -9375,7 +9408,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>50</v>
       </c>
@@ -9401,7 +9434,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>639</v>
       </c>
@@ -9427,7 +9460,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>54</v>
       </c>
@@ -9453,7 +9486,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>557</v>
       </c>
@@ -9476,7 +9509,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>557</v>
       </c>
@@ -9499,7 +9532,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>995</v>
       </c>
@@ -9522,7 +9555,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>1065</v>
       </c>
@@ -9548,7 +9581,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>955</v>
       </c>
@@ -9571,7 +9604,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>742</v>
       </c>
@@ -9597,7 +9630,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>554</v>
       </c>
@@ -9620,7 +9653,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>425</v>
       </c>
@@ -9646,7 +9679,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>836</v>
       </c>
@@ -9672,7 +9705,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>190</v>
       </c>
@@ -9698,7 +9731,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>193</v>
       </c>
@@ -9724,7 +9757,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>196</v>
       </c>
@@ -9750,7 +9783,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>354</v>
       </c>
@@ -9773,7 +9806,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>939</v>
       </c>
@@ -9799,7 +9832,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>227</v>
       </c>
@@ -9825,10 +9858,10 @@
         <v>100</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>1441</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>577</v>
       </c>
@@ -9851,7 +9884,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>577</v>
       </c>
@@ -9874,7 +9907,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>959</v>
       </c>
@@ -9897,7 +9930,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>961</v>
       </c>
@@ -9920,7 +9953,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>594</v>
       </c>
@@ -9943,7 +9976,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>269</v>
       </c>
@@ -9969,7 +10002,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>1009</v>
       </c>
@@ -9995,7 +10028,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>199</v>
       </c>
@@ -10021,7 +10054,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>724</v>
       </c>
@@ -10044,7 +10077,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>17</v>
       </c>
@@ -10070,7 +10103,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>1047</v>
       </c>
@@ -10096,7 +10129,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>617</v>
       </c>
@@ -10122,7 +10155,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>737</v>
       </c>
@@ -10148,7 +10181,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>621</v>
       </c>
@@ -10174,7 +10207,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>780</v>
       </c>
@@ -10197,7 +10230,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>21</v>
       </c>
@@ -10223,7 +10256,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>357</v>
       </c>
@@ -10249,7 +10282,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>604</v>
       </c>
@@ -10272,7 +10305,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>295</v>
       </c>
@@ -10298,7 +10331,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>428</v>
       </c>
@@ -10321,7 +10354,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>950</v>
       </c>
@@ -10347,7 +10380,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>516</v>
       </c>
@@ -10373,7 +10406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>13</v>
       </c>
@@ -10399,7 +10432,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>129</v>
       </c>
@@ -10422,7 +10455,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>832</v>
       </c>
@@ -10448,7 +10481,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>520</v>
       </c>
@@ -10474,7 +10507,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>660</v>
       </c>
@@ -10500,7 +10533,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>660</v>
       </c>
@@ -10526,7 +10559,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>660</v>
       </c>
@@ -10552,7 +10585,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>670</v>
       </c>
@@ -10578,7 +10611,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>723</v>
       </c>
@@ -10604,7 +10637,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>1027</v>
       </c>
@@ -10630,7 +10663,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>884</v>
       </c>
@@ -10656,7 +10689,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>863</v>
       </c>
@@ -10682,7 +10715,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>57</v>
       </c>
@@ -10708,7 +10741,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>395</v>
       </c>
@@ -10731,7 +10764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>298</v>
       </c>
@@ -10757,7 +10790,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>311</v>
       </c>
@@ -10783,10 +10816,10 @@
         <v>100</v>
       </c>
       <c r="I233" s="12" t="s">
-        <v>1460</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>74</v>
       </c>
@@ -10812,7 +10845,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>671</v>
       </c>
@@ -10838,7 +10871,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>793</v>
       </c>
@@ -10864,7 +10897,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>1316</v>
       </c>
@@ -10890,7 +10923,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>1028</v>
       </c>
@@ -10916,7 +10949,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>1031</v>
       </c>
@@ -10942,7 +10975,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>672</v>
       </c>
@@ -10968,7 +11001,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>321</v>
       </c>
@@ -10994,7 +11027,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>360</v>
       </c>
@@ -11017,7 +11050,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>235</v>
       </c>
@@ -11043,7 +11076,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>820</v>
       </c>
@@ -11066,7 +11099,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>272</v>
       </c>
@@ -11092,7 +11125,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>1018</v>
       </c>
@@ -11115,7 +11148,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>450</v>
       </c>
@@ -11138,7 +11171,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>542</v>
       </c>
@@ -11161,7 +11194,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>656</v>
       </c>
@@ -11187,7 +11220,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>259</v>
       </c>
@@ -11210,7 +11243,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>135</v>
       </c>
@@ -11236,7 +11269,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>138</v>
       </c>
@@ -11262,10 +11295,10 @@
         <v>100</v>
       </c>
       <c r="I252" s="12" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>141</v>
       </c>
@@ -11291,7 +11324,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>720</v>
       </c>
@@ -11317,7 +11350,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>399</v>
       </c>
@@ -11343,7 +11376,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>913</v>
       </c>
@@ -11366,7 +11399,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>1049</v>
       </c>
@@ -11392,7 +11425,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>453</v>
       </c>
@@ -11406,7 +11439,7 @@
         <v>1300</v>
       </c>
       <c r="E258" s="12" t="s">
-        <v>1451</v>
+        <v>1481</v>
       </c>
       <c r="F258" s="7" t="s">
         <v>455</v>
@@ -11418,13 +11451,13 @@
         <v>211</v>
       </c>
       <c r="I258" s="12" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="J258" s="12" t="s">
-        <v>1453</v>
-      </c>
-    </row>
-    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>276</v>
       </c>
@@ -11450,7 +11483,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>752</v>
       </c>
@@ -11473,7 +11506,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>301</v>
       </c>
@@ -11496,7 +11529,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>628</v>
       </c>
@@ -11519,7 +11552,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>756</v>
       </c>
@@ -11545,7 +11578,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>431</v>
       </c>
@@ -11571,7 +11604,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>1019</v>
       </c>
@@ -11597,7 +11630,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>879</v>
       </c>
@@ -11623,7 +11656,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>279</v>
       </c>
@@ -11649,7 +11682,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>262</v>
       </c>
@@ -11675,7 +11708,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>363</v>
       </c>
@@ -11701,7 +11734,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>1290</v>
       </c>
@@ -11724,7 +11757,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="271" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>967</v>
       </c>
@@ -11747,7 +11780,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>266</v>
       </c>
@@ -11770,7 +11803,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>1014</v>
       </c>
@@ -11796,10 +11829,10 @@
         <v>100</v>
       </c>
       <c r="I273" s="12" t="s">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>435</v>
       </c>
@@ -11825,7 +11858,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>282</v>
       </c>
@@ -11851,7 +11884,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>285</v>
       </c>
@@ -11877,7 +11910,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>817</v>
       </c>
@@ -11903,7 +11936,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>461</v>
       </c>
@@ -11929,7 +11962,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>218</v>
       </c>
@@ -11955,7 +11988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>224</v>
       </c>
@@ -11981,7 +12014,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>1070</v>
       </c>
@@ -12007,7 +12040,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>366</v>
       </c>
@@ -12033,7 +12066,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>369</v>
       </c>
@@ -12059,7 +12092,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>439</v>
       </c>
@@ -12085,7 +12118,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>1023</v>
       </c>
@@ -12111,7 +12144,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>1022</v>
       </c>
@@ -12137,7 +12170,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>1021</v>
       </c>
@@ -12163,7 +12196,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>833</v>
       </c>
@@ -12189,7 +12222,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" ht="16" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>1020</v>
       </c>
@@ -12212,7 +12245,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>834</v>
       </c>
@@ -12238,7 +12271,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>60</v>
       </c>
@@ -12264,7 +12297,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>372</v>
       </c>
@@ -12288,7 +12321,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
         <v>215</v>
       </c>
@@ -12314,7 +12347,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
         <v>180</v>
       </c>
@@ -12340,7 +12373,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="295" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>325</v>
       </c>
@@ -12365,8 +12398,11 @@
       <c r="H295" s="7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="296" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I295" s="12" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A296" s="1" t="s">
         <v>183</v>
       </c>
@@ -12392,7 +12428,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
         <v>443</v>
       </c>
@@ -12418,7 +12454,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>622</v>
       </c>
@@ -12444,7 +12480,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="299" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>984</v>
       </c>
@@ -12467,7 +12503,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>562</v>
       </c>
@@ -12490,7 +12526,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
         <v>585</v>
       </c>
@@ -12513,7 +12549,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>800</v>
       </c>
@@ -12539,7 +12575,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>1291</v>
       </c>
@@ -12565,7 +12601,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="304" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>1085</v>
       </c>
@@ -12591,7 +12627,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="305" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>1089</v>
       </c>
@@ -12617,7 +12653,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>1093</v>
       </c>
@@ -12643,7 +12679,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
         <v>1193</v>
       </c>
@@ -12669,7 +12705,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>1098</v>
       </c>
@@ -12695,13 +12731,13 @@
         <v>532</v>
       </c>
       <c r="I308" s="12" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="J308" s="12" t="s">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
         <v>1102</v>
       </c>
@@ -12727,7 +12763,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="310" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>1106</v>
       </c>
@@ -12753,7 +12789,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
         <v>1108</v>
       </c>
@@ -12779,7 +12815,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>1114</v>
       </c>
@@ -12805,7 +12841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
         <v>1118</v>
       </c>
@@ -12831,7 +12867,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="314" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
         <v>1126</v>
       </c>
@@ -12851,7 +12887,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="315" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
         <v>1128</v>
       </c>
@@ -12871,7 +12907,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="316" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
         <v>1132</v>
       </c>
@@ -12894,7 +12930,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="317" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
         <v>1136</v>
       </c>
@@ -12914,7 +12950,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
         <v>1140</v>
       </c>
@@ -12937,7 +12973,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="319" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
         <v>1144</v>
       </c>
@@ -12960,7 +12996,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="320" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
         <v>1148</v>
       </c>
@@ -12980,7 +13016,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
         <v>1288</v>
       </c>
@@ -13006,7 +13042,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
         <v>1155</v>
       </c>
@@ -13032,7 +13068,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="323" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
         <v>1159</v>
       </c>
@@ -13052,7 +13088,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="324" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>1163</v>
       </c>
@@ -13075,7 +13111,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
         <v>1167</v>
       </c>
@@ -13101,7 +13137,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>1171</v>
       </c>
@@ -13127,7 +13163,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="327" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>1175</v>
       </c>
@@ -13150,7 +13186,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
         <v>1179</v>
       </c>
@@ -13176,7 +13212,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
         <v>1182</v>
       </c>
@@ -13196,7 +13232,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
         <v>1317</v>
       </c>
@@ -13219,7 +13255,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
         <v>1188</v>
       </c>
@@ -13242,7 +13278,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
         <v>1284</v>
       </c>
@@ -13268,7 +13304,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
         <v>1197</v>
       </c>
@@ -13294,7 +13330,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
         <v>1201</v>
       </c>
@@ -13320,7 +13356,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="335" spans="1:8" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
         <v>1204</v>
       </c>
@@ -13346,7 +13382,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
         <v>1208</v>
       </c>
@@ -13369,7 +13405,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>1211</v>
       </c>
@@ -13395,7 +13431,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>1215</v>
       </c>
@@ -13421,7 +13457,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
         <v>1220</v>
       </c>
@@ -13444,7 +13480,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
         <v>1222</v>
       </c>
@@ -13467,10 +13503,10 @@
         <v>530</v>
       </c>
       <c r="I340" s="12" t="s">
-        <v>1447</v>
-      </c>
-    </row>
-    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
         <v>1223</v>
       </c>
@@ -13490,7 +13526,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
         <v>1228</v>
       </c>
@@ -13513,10 +13549,10 @@
         <v>100</v>
       </c>
       <c r="I342" s="12" t="s">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
         <v>1232</v>
       </c>
@@ -13542,7 +13578,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
         <v>1237</v>
       </c>
@@ -13568,7 +13604,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>1240</v>
       </c>
@@ -13591,7 +13627,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
         <v>1241</v>
       </c>
@@ -13614,7 +13650,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>1246</v>
       </c>
@@ -13637,7 +13673,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>1252</v>
       </c>
@@ -13660,7 +13696,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
         <v>1254</v>
       </c>
@@ -13683,7 +13719,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
         <v>1258</v>
       </c>
@@ -13709,7 +13745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
         <v>1264</v>
       </c>
@@ -13732,7 +13768,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
         <v>1266</v>
       </c>
@@ -13755,7 +13791,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="353" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>1270</v>
       </c>
@@ -13778,13 +13814,13 @@
         <v>530</v>
       </c>
       <c r="I353" s="12" t="s">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="J353" s="12" t="s">
-        <v>1466</v>
-      </c>
-    </row>
-    <row r="354" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>1276</v>
       </c>
@@ -13807,7 +13843,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>1326</v>
       </c>
@@ -13833,7 +13869,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>1327</v>
       </c>
@@ -13859,7 +13895,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>1292</v>
       </c>
@@ -13885,7 +13921,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>1295</v>
       </c>
@@ -13911,7 +13947,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>1300</v>
       </c>
@@ -13937,7 +13973,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>1303</v>
       </c>
@@ -13963,7 +13999,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>1308</v>
       </c>
@@ -13989,7 +14025,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="362" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>1313</v>
       </c>
@@ -14009,7 +14045,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>1321</v>
       </c>
@@ -14035,7 +14071,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>1331</v>
       </c>
@@ -14061,33 +14097,33 @@
         <v>66</v>
       </c>
     </row>
-    <row r="365" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B365" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="B365" s="1" t="s">
-        <v>1341</v>
-      </c>
       <c r="C365" s="7">
-        <v>1383</v>
+        <v>899</v>
       </c>
       <c r="D365" s="7">
-        <v>630</v>
+        <v>485</v>
       </c>
       <c r="E365" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F365" s="12" t="s">
         <v>1343</v>
-      </c>
-      <c r="F365" s="12" t="s">
-        <v>1344</v>
       </c>
       <c r="G365" s="7" t="s">
         <v>891</v>
       </c>
       <c r="H365" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>1345</v>
       </c>
@@ -14095,10 +14131,10 @@
         <v>1346</v>
       </c>
       <c r="C366" s="7">
-        <v>899</v>
+        <v>1050</v>
       </c>
       <c r="D366" s="7">
-        <v>485</v>
+        <v>600</v>
       </c>
       <c r="E366" s="12" t="s">
         <v>1348</v>
@@ -14112,8 +14148,14 @@
       <c r="H366" s="7" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I366" s="12" t="s">
+        <v>1479</v>
+      </c>
+      <c r="J366" s="12" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>1349</v>
       </c>
@@ -14121,10 +14163,10 @@
         <v>1350</v>
       </c>
       <c r="C367" s="7">
-        <v>1050</v>
+        <v>1084</v>
       </c>
       <c r="D367" s="7">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="E367" s="12" t="s">
         <v>1352</v>
@@ -14136,27 +14178,30 @@
         <v>891</v>
       </c>
       <c r="H367" s="7" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+      <c r="I367" s="12" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="C368" s="7">
-        <v>1084</v>
+        <v>1265</v>
       </c>
       <c r="D368" s="7">
         <v>650</v>
       </c>
       <c r="E368" s="12" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="F368" s="12" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="G368" s="7" t="s">
         <v>891</v>
@@ -14164,19 +14209,22 @@
       <c r="H368" s="7" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I368" s="12" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
-        <v>1359</v>
+        <v>1374</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>1360</v>
+        <v>1371</v>
       </c>
       <c r="C369" s="7">
-        <v>1265</v>
+        <v>1225</v>
       </c>
       <c r="D369" s="7">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="E369" s="12" t="s">
         <v>1358</v>
@@ -14188,15 +14236,21 @@
         <v>891</v>
       </c>
       <c r="H369" s="7" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="370" spans="1:10" ht="58" hidden="1" x14ac:dyDescent="0.35">
+        <v>531</v>
+      </c>
+      <c r="I369" s="12" t="s">
+        <v>1465</v>
+      </c>
+      <c r="J369" s="12" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="C370" s="7">
         <v>1225</v>
@@ -14205,10 +14259,10 @@
         <v>700</v>
       </c>
       <c r="E370" s="12" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="F370" s="12" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="G370" s="7" t="s">
         <v>891</v>
@@ -14217,56 +14271,50 @@
         <v>531</v>
       </c>
       <c r="I370" s="12" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
       <c r="J370" s="12" t="s">
-        <v>1472</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
-        <v>1377</v>
+        <v>1363</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>1376</v>
+        <v>1364</v>
       </c>
       <c r="C371" s="7">
-        <v>1225</v>
+        <v>535</v>
       </c>
       <c r="D371" s="7">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="E371" s="12" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="F371" s="12" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="G371" s="7" t="s">
         <v>891</v>
       </c>
       <c r="H371" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="I371" s="12" t="s">
-        <v>1473</v>
-      </c>
-      <c r="J371" s="12" t="s">
-        <v>1474</v>
-      </c>
-    </row>
-    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
-        <v>1367</v>
+        <v>1379</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>1368</v>
+        <v>1380</v>
       </c>
       <c r="C372" s="7">
-        <v>535</v>
+        <v>1033</v>
       </c>
       <c r="D372" s="7">
-        <v>400</v>
+        <v>675</v>
       </c>
       <c r="E372" s="12" t="s">
         <v>1366</v>
@@ -14278,27 +14326,33 @@
         <v>891</v>
       </c>
       <c r="H372" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="373" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>531</v>
+      </c>
+      <c r="I372" s="12" t="s">
+        <v>1473</v>
+      </c>
+      <c r="J372" s="12" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="C373" s="7">
-        <v>1033</v>
+        <v>614</v>
       </c>
       <c r="D373" s="7">
-        <v>675</v>
+        <v>375</v>
       </c>
       <c r="E373" s="12" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="F373" s="12" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="G373" s="7" t="s">
         <v>891</v>
@@ -14307,24 +14361,24 @@
         <v>531</v>
       </c>
     </row>
-    <row r="374" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="C374" s="7">
-        <v>614</v>
+        <v>946</v>
       </c>
       <c r="D374" s="7">
-        <v>375</v>
+        <v>575</v>
       </c>
       <c r="E374" s="12" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="F374" s="12" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="G374" s="7" t="s">
         <v>891</v>
@@ -14333,24 +14387,24 @@
         <v>531</v>
       </c>
     </row>
-    <row r="375" spans="1:10" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
-        <v>1387</v>
+        <v>1375</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>1388</v>
+        <v>1376</v>
       </c>
       <c r="C375" s="7">
-        <v>946</v>
+        <v>1174</v>
       </c>
       <c r="D375" s="7">
-        <v>575</v>
+        <v>700</v>
       </c>
       <c r="E375" s="12" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="F375" s="12" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="G375" s="7" t="s">
         <v>891</v>
@@ -14358,40 +14412,43 @@
       <c r="H375" s="7" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="376" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I375" s="12" t="s">
+        <v>1464</v>
+      </c>
+      <c r="J375" s="12" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="C376" s="7">
-        <v>1174</v>
+        <v>1395</v>
       </c>
       <c r="D376" s="7">
-        <v>700</v>
+        <v>920</v>
       </c>
       <c r="E376" s="12" t="s">
-        <v>1382</v>
+        <v>1388</v>
       </c>
       <c r="F376" s="12" t="s">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="G376" s="7" t="s">
         <v>891</v>
       </c>
       <c r="H376" s="7" t="s">
-        <v>531</v>
+        <v>66</v>
       </c>
       <c r="I376" s="12" t="s">
-        <v>1470</v>
-      </c>
-      <c r="J376" s="12" t="s">
-        <v>1469</v>
-      </c>
-    </row>
-    <row r="377" spans="1:10" ht="58" hidden="1" x14ac:dyDescent="0.35">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>1389</v>
       </c>
@@ -14399,10 +14456,10 @@
         <v>1390</v>
       </c>
       <c r="C377" s="7">
-        <v>1395</v>
+        <v>488</v>
       </c>
       <c r="D377" s="7">
-        <v>920</v>
+        <v>400</v>
       </c>
       <c r="E377" s="12" t="s">
         <v>1392</v>
@@ -14414,39 +14471,36 @@
         <v>891</v>
       </c>
       <c r="H377" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I377" s="12" t="s">
-        <v>1459</v>
-      </c>
-    </row>
-    <row r="378" spans="1:10" ht="58" hidden="1" x14ac:dyDescent="0.35">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
         <v>1393</v>
       </c>
       <c r="B378" s="1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C378" s="7">
+        <v>554</v>
+      </c>
+      <c r="D378" s="7">
+        <v>200</v>
+      </c>
+      <c r="E378" s="12" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F378" s="12" t="s">
         <v>1394</v>
-      </c>
-      <c r="C378" s="7">
-        <v>488</v>
-      </c>
-      <c r="D378" s="7">
-        <v>400</v>
-      </c>
-      <c r="E378" s="12" t="s">
-        <v>1396</v>
-      </c>
-      <c r="F378" s="12" t="s">
-        <v>1395</v>
       </c>
       <c r="G378" s="7" t="s">
         <v>891</v>
       </c>
       <c r="H378" s="7" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="379" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
         <v>1397</v>
       </c>
@@ -14454,10 +14508,10 @@
         <v>1400</v>
       </c>
       <c r="C379" s="7">
-        <v>554</v>
+        <v>398</v>
       </c>
       <c r="D379" s="7">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E379" s="12" t="s">
         <v>1399</v>
@@ -14469,36 +14523,36 @@
         <v>891</v>
       </c>
       <c r="H379" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="380" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
         <v>1401</v>
       </c>
       <c r="B380" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C380" s="7">
+        <v>399</v>
+      </c>
+      <c r="D380" s="7">
+        <v>120</v>
+      </c>
+      <c r="E380" s="12" t="s">
         <v>1404</v>
       </c>
-      <c r="C380" s="7">
-        <v>398</v>
-      </c>
-      <c r="D380" s="7">
-        <v>250</v>
-      </c>
-      <c r="E380" s="12" t="s">
+      <c r="F380" s="12" t="s">
         <v>1403</v>
-      </c>
-      <c r="F380" s="12" t="s">
-        <v>1402</v>
       </c>
       <c r="G380" s="7" t="s">
         <v>891</v>
       </c>
       <c r="H380" s="7" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A381" s="1" t="s">
         <v>1405</v>
       </c>
@@ -14506,10 +14560,10 @@
         <v>1406</v>
       </c>
       <c r="C381" s="7">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D381" s="7">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="E381" s="12" t="s">
         <v>1408</v>
@@ -14521,10 +14575,10 @@
         <v>891</v>
       </c>
       <c r="H381" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="382" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A382" s="1" t="s">
         <v>1409</v>
       </c>
@@ -14532,7 +14586,7 @@
         <v>1410</v>
       </c>
       <c r="C382" s="7">
-        <v>397</v>
+        <v>350</v>
       </c>
       <c r="D382" s="7">
         <v>300</v>
@@ -14547,27 +14601,27 @@
         <v>891</v>
       </c>
       <c r="H382" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="383" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A383" s="1" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="C383" s="7">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="D383" s="7">
         <v>300</v>
       </c>
       <c r="E383" s="12" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="F383" s="12" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="G383" s="7" t="s">
         <v>891</v>
@@ -14576,24 +14630,24 @@
         <v>66</v>
       </c>
     </row>
-    <row r="384" spans="1:10" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C384" s="7">
+        <v>1690</v>
+      </c>
+      <c r="D384" s="7">
+        <v>1090</v>
+      </c>
+      <c r="E384" s="12" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F384" s="12" t="s">
         <v>1419</v>
-      </c>
-      <c r="B384" s="1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C384" s="7">
-        <v>385</v>
-      </c>
-      <c r="D384" s="7">
-        <v>300</v>
-      </c>
-      <c r="E384" s="12" t="s">
-        <v>1418</v>
-      </c>
-      <c r="F384" s="12" t="s">
-        <v>1417</v>
       </c>
       <c r="G384" s="7" t="s">
         <v>891</v>
@@ -14601,48 +14655,51 @@
       <c r="H384" s="7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="385" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="I384" s="12" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
         <v>1422</v>
       </c>
       <c r="B385" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C385" s="7">
+        <v>1999</v>
+      </c>
+      <c r="D385" s="7">
+        <v>800</v>
+      </c>
+      <c r="E385" s="12" t="s">
         <v>1421</v>
       </c>
-      <c r="C385" s="7">
-        <v>1690</v>
-      </c>
-      <c r="D385" s="7">
-        <v>1090</v>
-      </c>
-      <c r="E385" s="12" t="s">
-        <v>1455</v>
-      </c>
       <c r="F385" s="12" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="G385" s="7" t="s">
         <v>891</v>
       </c>
       <c r="H385" s="7" t="s">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="I385" s="12" t="s">
-        <v>1456</v>
-      </c>
-    </row>
-    <row r="386" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A386" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B386" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="B386" s="1" t="s">
-        <v>1427</v>
-      </c>
       <c r="C386" s="7">
-        <v>1999</v>
+        <v>4699</v>
       </c>
       <c r="D386" s="7">
-        <v>800</v>
+        <v>2832</v>
       </c>
       <c r="E386" s="12" t="s">
         <v>1425</v>
@@ -14654,67 +14711,38 @@
         <v>891</v>
       </c>
       <c r="H386" s="7" t="s">
-        <v>211</v>
+        <v>530</v>
       </c>
       <c r="I386" s="12" t="s">
-        <v>1464</v>
-      </c>
-    </row>
-    <row r="387" spans="1:10" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+        <v>1445</v>
+      </c>
+      <c r="J386" s="12" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A387" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C387" s="7">
+        <v>349</v>
+      </c>
+      <c r="D387" s="7">
+        <v>295</v>
+      </c>
+      <c r="E387" s="12" t="s">
         <v>1431</v>
       </c>
-      <c r="B387" s="1" t="s">
+      <c r="F387" s="12" t="s">
         <v>1430</v>
       </c>
-      <c r="C387" s="7">
-        <v>4699</v>
-      </c>
-      <c r="D387" s="7">
-        <v>2832</v>
-      </c>
-      <c r="E387" s="12" t="s">
-        <v>1429</v>
-      </c>
-      <c r="F387" s="12" t="s">
-        <v>1428</v>
-      </c>
       <c r="G387" s="7" t="s">
-        <v>891</v>
+        <v>438</v>
       </c>
       <c r="H387" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="I387" s="12" t="s">
-        <v>1449</v>
-      </c>
-      <c r="J387" s="12" t="s">
-        <v>1448</v>
-      </c>
-    </row>
-    <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A388" s="1" t="s">
-        <v>1432</v>
-      </c>
-      <c r="B388" s="1" t="s">
-        <v>1433</v>
-      </c>
-      <c r="C388" s="7">
-        <v>349</v>
-      </c>
-      <c r="D388" s="7">
-        <v>295</v>
-      </c>
-      <c r="E388" s="12" t="s">
-        <v>1435</v>
-      </c>
-      <c r="F388" s="12" t="s">
-        <v>1434</v>
-      </c>
-      <c r="G388" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="H388" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -14729,19 +14757,19 @@
     <hyperlink ref="E261" r:id="rId7"/>
     <hyperlink ref="E340" r:id="rId8"/>
     <hyperlink ref="E155" r:id="rId9"/>
-    <hyperlink ref="E365" r:id="rId10"/>
-    <hyperlink ref="F365" r:id="rId11" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="F365" r:id="rId10" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="E365" r:id="rId11"/>
     <hyperlink ref="F366" r:id="rId12" location="&amp;gid=1&amp;pid=1"/>
     <hyperlink ref="E366" r:id="rId13"/>
     <hyperlink ref="F367" r:id="rId14" location="&amp;gid=1&amp;pid=1"/>
     <hyperlink ref="E367" r:id="rId15"/>
-    <hyperlink ref="F368" r:id="rId16" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="F368" r:id="rId16"/>
     <hyperlink ref="E368" r:id="rId17"/>
     <hyperlink ref="F369" r:id="rId18"/>
     <hyperlink ref="E369" r:id="rId19"/>
-    <hyperlink ref="F370" r:id="rId20"/>
-    <hyperlink ref="E370" r:id="rId21"/>
-    <hyperlink ref="F371" display="https://www.mercadolibre.com.mx/epicentro-audishako-max-02-restaurador-de-bajos-para-auto-subwoofer-para-carro-pickups-y-suv-accesorios-para-auto-audio-diseno-en-relieve-3d-incluye-dash-remoto-control-de-bajos/p/MLM64640099?pdp_filters=item_id:MLM46970202"/>
+    <hyperlink ref="F370" display="https://www.mercadolibre.com.mx/epicentro-audishako-max-02-restaurador-de-bajos-para-auto-subwoofer-para-carro-pickups-y-suv-accesorios-para-auto-audio-diseno-en-relieve-3d-incluye-dash-remoto-control-de-bajos/p/MLM64640099?pdp_filters=item_id:MLM46970202"/>
+    <hyperlink ref="E370" r:id="rId20"/>
+    <hyperlink ref="F371" r:id="rId21"/>
     <hyperlink ref="E371" r:id="rId22"/>
     <hyperlink ref="F372" r:id="rId23"/>
     <hyperlink ref="E372" r:id="rId24"/>
@@ -14753,9 +14781,9 @@
     <hyperlink ref="E375" r:id="rId30"/>
     <hyperlink ref="F376" r:id="rId31"/>
     <hyperlink ref="E376" r:id="rId32"/>
-    <hyperlink ref="F377" r:id="rId33"/>
+    <hyperlink ref="F377" r:id="rId33" location="reviews"/>
     <hyperlink ref="E377" r:id="rId34"/>
-    <hyperlink ref="F378" r:id="rId35" location="reviews"/>
+    <hyperlink ref="F378" r:id="rId35"/>
     <hyperlink ref="E378" r:id="rId36"/>
     <hyperlink ref="F379" r:id="rId37"/>
     <hyperlink ref="E379" r:id="rId38"/>
@@ -14775,49 +14803,59 @@
     <hyperlink ref="E386" r:id="rId52"/>
     <hyperlink ref="F387" r:id="rId53"/>
     <hyperlink ref="E387" r:id="rId54"/>
-    <hyperlink ref="F388" r:id="rId55"/>
-    <hyperlink ref="E388" r:id="rId56"/>
-    <hyperlink ref="I73"/>
-    <hyperlink ref="I308" r:id="rId57"/>
-    <hyperlink ref="J308" r:id="rId58"/>
-    <hyperlink ref="I195"/>
-    <hyperlink ref="I134"/>
-    <hyperlink ref="I67"/>
-    <hyperlink ref="J67" r:id="rId59"/>
-    <hyperlink ref="I68"/>
-    <hyperlink ref="I273"/>
-    <hyperlink ref="I340"/>
-    <hyperlink ref="J387" r:id="rId60"/>
-    <hyperlink ref="I387" r:id="rId61"/>
-    <hyperlink ref="I342"/>
-    <hyperlink ref="E258" r:id="rId62"/>
-    <hyperlink ref="I258" r:id="rId63"/>
-    <hyperlink ref="J258" r:id="rId64"/>
-    <hyperlink ref="I36" r:id="rId65"/>
-    <hyperlink ref="I385"/>
-    <hyperlink ref="J61" r:id="rId66"/>
-    <hyperlink ref="I61"/>
-    <hyperlink ref="I377" r:id="rId67"/>
-    <hyperlink ref="I233"/>
-    <hyperlink ref="J32" r:id="rId68"/>
-    <hyperlink ref="I32"/>
-    <hyperlink ref="I104"/>
-    <hyperlink ref="I386"/>
-    <hyperlink ref="I149"/>
-    <hyperlink ref="J353" r:id="rId69"/>
-    <hyperlink ref="I353"/>
-    <hyperlink ref="I252"/>
-    <hyperlink ref="J376" r:id="rId70"/>
-    <hyperlink ref="I376"/>
+    <hyperlink ref="I73" display="https://http2.mlstatic.com/D_NQ_NP_2X_977864-MLA82522530268_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728802-MLA82808708997_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_714871-MLA82808836891_032025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="I308" r:id="rId55"/>
+    <hyperlink ref="J308" r:id="rId56"/>
+    <hyperlink ref="I195" display="https://http2.mlstatic.com/D_NQ_NP_2X_881622-MLA100107482214_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_853470-MLA83211986807_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_889429-MLA82708797484_032025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
+    <hyperlink ref="I134" display="https://http2.mlstatic.com/D_NQ_NP_2X_691159-MLA74393127536_022024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_797614-MLA74213272750_012024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_768655-MLA74336317695_012024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="I67" display="https://http2.mlstatic.com/D_NQ_NP_2X_665383-MLA110622349795_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_998155-MLA109812957268_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_967066-MLA109813016698_042026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J67" r:id="rId57"/>
+    <hyperlink ref="I68" display="https://http2.mlstatic.com/D_NQ_NP_2X_754117-MLA87918629604_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_955266-MLA88256438081_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_924778-MLA88256272783_072025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="I273" display="https://http2.mlstatic.com/D_NQ_NP_2X_651538-MLA109474609027_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_786870-MLA109384870397_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_877937-MLA109385877631_032026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I340" display="https://http2.mlstatic.com/D_NQ_NP_2X_659872-MLA110558100656_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_654212-MLA110558217136_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728798-MLA110558100602_052026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J386" r:id="rId58"/>
+    <hyperlink ref="I386" r:id="rId59"/>
+    <hyperlink ref="I342" display="https://http2.mlstatic.com/D_NQ_NP_2X_704682-MLA112632086794_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648062-MLA114215908179_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_721338-MLA112631444306_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="E258" r:id="rId60"/>
+    <hyperlink ref="I258" r:id="rId61"/>
+    <hyperlink ref="J258" r:id="rId62"/>
+    <hyperlink ref="I36" r:id="rId63"/>
+    <hyperlink ref="I384" display="https://http2.mlstatic.com/D_NQ_NP_2X_870766-MLA111944165952_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_835091-MLA112882459449_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J61" r:id="rId64"/>
+    <hyperlink ref="I61" display="https://http2.mlstatic.com/D_NQ_NP_2X_650019-MLA112598239078_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_694102-MLA111420836191_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_960139-MLA111232526403_052026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I376" r:id="rId65"/>
+    <hyperlink ref="I233" display="https://http2.mlstatic.com/D_NQ_NP_2X_761866-MLA76203783381_052024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_967910-MLA76082310461_042024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_699850-MLA76082339489_042024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="J32" r:id="rId66"/>
+    <hyperlink ref="I32" display="https://http2.mlstatic.com/D_NQ_NP_2X_937988-MLA100214376229_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_839463-MLA100214244569_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_878239-MLA100214347283_122025-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I104" display="https://http2.mlstatic.com/D_NQ_NP_2X_853469-MLA73479850047_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_636371-MLA72966055893_112023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_647337-MLA74448293715_022024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="I385" display="https://http2.mlstatic.com/D_NQ_NP_2X_838661-MLA114043475512_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_997422-MLA111845686244_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_946430-MLA112856485647_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I149" display="https://http2.mlstatic.com/D_NQ_NP_2X_700050-MLA90330537717_082025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_810830-MLA92985348779_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_611435-MLA103169335415_122025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
+    <hyperlink ref="J353" r:id="rId67"/>
+    <hyperlink ref="I353" display="https://http2.mlstatic.com/D_NQ_NP_2X_972461-MLA108765590667_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_959062-MLA111287287492_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_702439-MLA108999676116_032026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I252" display="https://http2.mlstatic.com/D_NQ_NP_2X_772336-MLA83215360667_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_641687-MLA82926894938_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_686941-MLA80851161221_112024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="J375" r:id="rId68"/>
+    <hyperlink ref="I375" display="https://http2.mlstatic.com/D_NQ_NP_2X_918751-MLA113089268495_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_972829-MLA114388137831_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_739083-MLA113884890489_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J369" r:id="rId69"/>
+    <hyperlink ref="I369" display="https://http2.mlstatic.com/D_NQ_NP_2X_622982-MLA91998379772_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_918567-MLA93316673763_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_951409-MLA93316693351_092025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="I370" r:id="rId70"/>
     <hyperlink ref="J370" r:id="rId71"/>
-    <hyperlink ref="I370"/>
-    <hyperlink ref="I371" r:id="rId72"/>
-    <hyperlink ref="J371" r:id="rId73"/>
+    <hyperlink ref="J173" r:id="rId72"/>
+    <hyperlink ref="I173" display="https://http2.mlstatic.com/D_NQ_NP_2X_630634-MLA83929492736_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_826427-MLA83875691856_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_778506-MLA83875632066_042025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="I295" display="https://http2.mlstatic.com/D_NQ_NP_2X_601798-MLA74779553000_032024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_784677-MLA71729912500_092023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_982997-MLA73375012815_122023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="J372" r:id="rId73"/>
+    <hyperlink ref="I372" display="https://http2.mlstatic.com/D_NQ_NP_2X_743943-MLA113720575198_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_652343-MLA98742656086_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_688496-MLA89833143459_082025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
+    <hyperlink ref="J56" r:id="rId74"/>
+    <hyperlink ref="I56" r:id="rId75"/>
+    <hyperlink ref="I367" r:id="rId76"/>
+    <hyperlink ref="I368" r:id="rId77"/>
+    <hyperlink ref="I135" r:id="rId78"/>
+    <hyperlink ref="I366" r:id="rId79"/>
+    <hyperlink ref="J366" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId74"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId81"/>
   <tableParts count="1">
-    <tablePart r:id="rId75"/>
+    <tablePart r:id="rId82"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2403" uniqueCount="1580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2412" uniqueCount="1587">
   <si>
     <t>Nombre</t>
   </si>
@@ -4776,6 +4776,27 @@
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_973200-MLA111559842713_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_705535-MLA110612658098_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_743702-MLA110611090138_052026-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_701490-MLA108653774761_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_910611-MLA87584829978_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_761367-MLA87718920709_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_607798-MLA107642299882_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_656127-MLA114825035763_072026-F.webp</t>
+  </si>
+  <si>
+    <t>Espejo De Baño Led Tri Color Tira De Luz</t>
+  </si>
+  <si>
+    <t>Radio: 50cm</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_861035-MLM110725392715_042026-F-espejo-de-bano-led-tri-color-tira-de-luz-defogging-time5050.webp</t>
+  </si>
+  <si>
+    <t>https://articulo.mercadolibre.com.mx/MLM-2900477235-espejo-de-bano-led-tri-color-tira-de-luz-defogging-time5050-_JM?quantity=1&amp;sid=purchases</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_957897-MLA114152946760_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_988648-MLA114781488773_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_938364-MLA113693419924_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_714728-MLA115205021849_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_675499-MLA115386756969_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_808617-MLA114152032962_082026-F.webp</t>
+  </si>
+  <si>
+    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019f90e3cbb27ae8a7448a824f49eed7/master.m3u8</t>
   </si>
 </sst>
 </file>
@@ -4934,8 +4955,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J375" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J375"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J376" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J376"/>
   <sortState ref="A2:H342">
     <sortCondition ref="A1:A342"/>
   </sortState>
@@ -5240,7 +5261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J375"/>
+  <dimension ref="A1:J376"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" style="1" customWidth="1"/>
@@ -7906,6 +7927,9 @@
       <c r="H102" s="7" t="s">
         <v>198</v>
       </c>
+      <c r="I102" s="12" t="s">
+        <v>1580</v>
+      </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
@@ -14656,22 +14680,22 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
-        <v>1315</v>
+        <v>1581</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>1316</v>
+        <v>1582</v>
       </c>
       <c r="C359" s="7">
-        <v>535</v>
+        <v>590</v>
       </c>
       <c r="D359" s="7">
         <v>400</v>
       </c>
       <c r="E359" s="12" t="s">
-        <v>1314</v>
+        <v>1583</v>
       </c>
       <c r="F359" s="12" t="s">
-        <v>1313</v>
+        <v>1584</v>
       </c>
       <c r="G359" s="7" t="s">
         <v>861</v>
@@ -14680,62 +14704,62 @@
         <v>66</v>
       </c>
       <c r="I359" s="12" t="s">
-        <v>1552</v>
+        <v>1585</v>
       </c>
       <c r="J359" s="12" t="s">
-        <v>1551</v>
-      </c>
-    </row>
-    <row r="360" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
-        <v>1331</v>
+        <v>1315</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>1332</v>
+        <v>1316</v>
       </c>
       <c r="C360" s="7">
-        <v>1033</v>
+        <v>535</v>
       </c>
       <c r="D360" s="7">
-        <v>675</v>
+        <v>400</v>
       </c>
       <c r="E360" s="12" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="F360" s="12" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="G360" s="7" t="s">
         <v>861</v>
       </c>
       <c r="H360" s="7" t="s">
-        <v>512</v>
+        <v>66</v>
       </c>
       <c r="I360" s="12" t="s">
-        <v>1424</v>
+        <v>1552</v>
       </c>
       <c r="J360" s="12" t="s">
-        <v>1423</v>
-      </c>
-    </row>
-    <row r="361" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C361" s="7">
-        <v>614</v>
+        <v>1033</v>
       </c>
       <c r="D361" s="7">
-        <v>375</v>
+        <v>675</v>
       </c>
       <c r="E361" s="12" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="F361" s="12" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="G361" s="7" t="s">
         <v>861</v>
@@ -14743,25 +14767,31 @@
       <c r="H361" s="7" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="362" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="I361" s="12" t="s">
+        <v>1424</v>
+      </c>
+      <c r="J361" s="12" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="C362" s="7">
-        <v>946</v>
+        <v>614</v>
       </c>
       <c r="D362" s="7">
-        <v>575</v>
+        <v>375</v>
       </c>
       <c r="E362" s="12" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="F362" s="12" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="G362" s="7" t="s">
         <v>861</v>
@@ -14769,31 +14799,25 @@
       <c r="H362" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="I362" s="12" t="s">
-        <v>1534</v>
-      </c>
-      <c r="J362" s="12" t="s">
-        <v>1533</v>
-      </c>
-    </row>
-    <row r="363" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="363" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
       <c r="C363" s="7">
-        <v>1174</v>
+        <v>946</v>
       </c>
       <c r="D363" s="7">
-        <v>700</v>
+        <v>575</v>
       </c>
       <c r="E363" s="12" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
       <c r="F363" s="12" t="s">
-        <v>1329</v>
+        <v>1321</v>
       </c>
       <c r="G363" s="7" t="s">
         <v>861</v>
@@ -14802,242 +14826,242 @@
         <v>512</v>
       </c>
       <c r="I363" s="12" t="s">
-        <v>1415</v>
+        <v>1534</v>
       </c>
       <c r="J363" s="12" t="s">
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="364" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
-        <v>1337</v>
+        <v>1327</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>1338</v>
+        <v>1328</v>
       </c>
       <c r="C364" s="7">
-        <v>1395</v>
+        <v>1174</v>
       </c>
       <c r="D364" s="7">
-        <v>920</v>
+        <v>700</v>
       </c>
       <c r="E364" s="12" t="s">
-        <v>1340</v>
+        <v>1330</v>
       </c>
       <c r="F364" s="12" t="s">
-        <v>1339</v>
+        <v>1329</v>
       </c>
       <c r="G364" s="7" t="s">
         <v>861</v>
       </c>
       <c r="H364" s="7" t="s">
-        <v>66</v>
+        <v>512</v>
       </c>
       <c r="I364" s="12" t="s">
-        <v>1404</v>
+        <v>1415</v>
+      </c>
+      <c r="J364" s="12" t="s">
+        <v>1414</v>
       </c>
     </row>
     <row r="365" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
-        <v>1527</v>
+        <v>1337</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="C365" s="7">
-        <v>488</v>
+        <v>1395</v>
       </c>
       <c r="D365" s="7">
-        <v>400</v>
+        <v>920</v>
       </c>
       <c r="E365" s="12" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="F365" s="12" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="G365" s="7" t="s">
         <v>861</v>
       </c>
       <c r="H365" s="7" t="s">
-        <v>512</v>
+        <v>66</v>
       </c>
       <c r="I365" s="12" t="s">
-        <v>1482</v>
-      </c>
-      <c r="J365" s="12" t="s">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
-        <v>1344</v>
+        <v>1527</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="C366" s="7">
-        <v>554</v>
+        <v>488</v>
       </c>
       <c r="D366" s="7">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E366" s="12" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="F366" s="12" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="G366" s="7" t="s">
         <v>861</v>
       </c>
       <c r="H366" s="7" t="s">
-        <v>12</v>
+        <v>512</v>
       </c>
       <c r="I366" s="12" t="s">
-        <v>1458</v>
+        <v>1482</v>
       </c>
       <c r="J366" s="12" t="s">
-        <v>1457</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="C367" s="7">
-        <v>398</v>
+        <v>554</v>
       </c>
       <c r="D367" s="7">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E367" s="12" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="F367" s="12" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="G367" s="7" t="s">
         <v>861</v>
       </c>
       <c r="H367" s="7" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I367" s="12" t="s">
+        <v>1458</v>
+      </c>
+      <c r="J367" s="12" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C368" s="7">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D368" s="7">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E368" s="12" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="F368" s="12" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="G368" s="7" t="s">
         <v>861</v>
       </c>
       <c r="H368" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I368" s="12" t="s">
-        <v>1548</v>
-      </c>
-    </row>
-    <row r="369" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="C369" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D369" s="7">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E369" s="12" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="F369" s="12" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="G369" s="7" t="s">
         <v>861</v>
       </c>
       <c r="H369" s="7" t="s">
-        <v>198</v>
+        <v>66</v>
       </c>
       <c r="I369" s="12" t="s">
-        <v>1438</v>
-      </c>
-      <c r="J369" s="12" t="s">
-        <v>1439</v>
-      </c>
-    </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="C370" s="7">
-        <v>350</v>
+        <v>397</v>
       </c>
       <c r="D370" s="7">
         <v>300</v>
       </c>
       <c r="E370" s="12" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F370" s="12" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="G370" s="7" t="s">
         <v>861</v>
       </c>
       <c r="H370" s="7" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="I370" s="12" t="s">
-        <v>1543</v>
+        <v>1438</v>
       </c>
       <c r="J370" s="12" t="s">
-        <v>1542</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="C371" s="7">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="D371" s="7">
         <v>300</v>
       </c>
       <c r="E371" s="12" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="F371" s="12" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="G371" s="7" t="s">
         <v>861</v>
@@ -15046,27 +15070,30 @@
         <v>66</v>
       </c>
       <c r="I371" s="12" t="s">
-        <v>1434</v>
-      </c>
-    </row>
-    <row r="372" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>1543</v>
+      </c>
+      <c r="J371" s="12" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="C372" s="7">
-        <v>1690</v>
+        <v>385</v>
       </c>
       <c r="D372" s="7">
-        <v>1090</v>
+        <v>300</v>
       </c>
       <c r="E372" s="12" t="s">
-        <v>1433</v>
+        <v>1365</v>
       </c>
       <c r="F372" s="12" t="s">
-        <v>1370</v>
+        <v>1364</v>
       </c>
       <c r="G372" s="7" t="s">
         <v>861</v>
@@ -15075,99 +15102,128 @@
         <v>66</v>
       </c>
       <c r="I372" s="12" t="s">
-        <v>1401</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="373" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>1374</v>
+        <v>1368</v>
       </c>
       <c r="C373" s="7">
-        <v>1999</v>
+        <v>1690</v>
       </c>
       <c r="D373" s="7">
-        <v>800</v>
+        <v>1090</v>
       </c>
       <c r="E373" s="12" t="s">
-        <v>1372</v>
+        <v>1433</v>
       </c>
       <c r="F373" s="12" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="G373" s="7" t="s">
         <v>861</v>
       </c>
       <c r="H373" s="7" t="s">
-        <v>198</v>
+        <v>66</v>
       </c>
       <c r="I373" s="12" t="s">
-        <v>1409</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="C374" s="7">
-        <v>4699</v>
+        <v>1999</v>
       </c>
       <c r="D374" s="7">
-        <v>2832</v>
+        <v>800</v>
       </c>
       <c r="E374" s="12" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="F374" s="12" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="G374" s="7" t="s">
         <v>861</v>
       </c>
       <c r="H374" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="I374" s="12" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A375" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C375" s="7">
+        <v>4699</v>
+      </c>
+      <c r="D375" s="7">
+        <v>2832</v>
+      </c>
+      <c r="E375" s="12" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F375" s="12" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G375" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="H375" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="I374" s="12" t="s">
+      <c r="I375" s="12" t="s">
         <v>1396</v>
       </c>
-      <c r="J374" s="12" t="s">
+      <c r="J375" s="12" t="s">
         <v>1395</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A375" s="1" t="s">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A376" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="B375" s="1" t="s">
+      <c r="B376" s="1" t="s">
         <v>1380</v>
       </c>
-      <c r="C375" s="7">
+      <c r="C376" s="7">
         <v>349</v>
       </c>
-      <c r="D375" s="7">
+      <c r="D376" s="7">
         <v>295</v>
       </c>
-      <c r="E375" s="12" t="s">
+      <c r="E376" s="12" t="s">
         <v>1382</v>
       </c>
-      <c r="F375" s="12" t="s">
+      <c r="F376" s="12" t="s">
         <v>1381</v>
       </c>
-      <c r="G375" s="7" t="s">
+      <c r="G376" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="H375" s="7" t="s">
+      <c r="H376" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I375" s="12" t="s">
+      <c r="I376" s="12" t="s">
         <v>1493</v>
       </c>
-      <c r="J375" s="12" t="s">
+      <c r="J376" s="12" t="s">
         <v>1492</v>
       </c>
     </row>
@@ -15194,40 +15250,40 @@
     <hyperlink ref="E357" r:id="rId19"/>
     <hyperlink ref="F358" display="https://www.mercadolibre.com.mx/epicentro-audishako-max-02-restaurador-de-bajos-para-auto-subwoofer-para-carro-pickups-y-suv-accesorios-para-auto-audio-diseno-en-relieve-3d-incluye-dash-remoto-control-de-bajos/p/MLM64640099?pdp_filters=item_id:MLM46970202"/>
     <hyperlink ref="E358" r:id="rId20"/>
-    <hyperlink ref="F359" r:id="rId21"/>
-    <hyperlink ref="E359" r:id="rId22"/>
-    <hyperlink ref="F360" r:id="rId23"/>
-    <hyperlink ref="E360" r:id="rId24"/>
-    <hyperlink ref="F361" r:id="rId25"/>
-    <hyperlink ref="E361" r:id="rId26"/>
-    <hyperlink ref="F362" r:id="rId27"/>
-    <hyperlink ref="E362" r:id="rId28"/>
-    <hyperlink ref="F363" r:id="rId29"/>
-    <hyperlink ref="E363" r:id="rId30"/>
-    <hyperlink ref="F364" r:id="rId31"/>
-    <hyperlink ref="E364" r:id="rId32"/>
-    <hyperlink ref="F365" r:id="rId33" location="reviews"/>
-    <hyperlink ref="E365" r:id="rId34"/>
-    <hyperlink ref="F366" r:id="rId35"/>
-    <hyperlink ref="E366" r:id="rId36"/>
-    <hyperlink ref="F367" r:id="rId37"/>
-    <hyperlink ref="E367" r:id="rId38"/>
-    <hyperlink ref="F368" r:id="rId39"/>
-    <hyperlink ref="E368" r:id="rId40"/>
-    <hyperlink ref="F369" r:id="rId41"/>
-    <hyperlink ref="E369" r:id="rId42"/>
-    <hyperlink ref="F370" r:id="rId43"/>
-    <hyperlink ref="E370" r:id="rId44"/>
-    <hyperlink ref="F371" r:id="rId45"/>
-    <hyperlink ref="E371" r:id="rId46"/>
-    <hyperlink ref="F372" r:id="rId47"/>
-    <hyperlink ref="E372" r:id="rId48"/>
-    <hyperlink ref="F373" r:id="rId49"/>
-    <hyperlink ref="E373" r:id="rId50"/>
-    <hyperlink ref="F374" r:id="rId51"/>
-    <hyperlink ref="E374" r:id="rId52"/>
-    <hyperlink ref="F375" r:id="rId53"/>
-    <hyperlink ref="E375" r:id="rId54"/>
+    <hyperlink ref="F360" r:id="rId21"/>
+    <hyperlink ref="E360" r:id="rId22"/>
+    <hyperlink ref="F361" r:id="rId23"/>
+    <hyperlink ref="E361" r:id="rId24"/>
+    <hyperlink ref="F362" r:id="rId25"/>
+    <hyperlink ref="E362" r:id="rId26"/>
+    <hyperlink ref="F363" r:id="rId27"/>
+    <hyperlink ref="E363" r:id="rId28"/>
+    <hyperlink ref="F364" r:id="rId29"/>
+    <hyperlink ref="E364" r:id="rId30"/>
+    <hyperlink ref="F365" r:id="rId31"/>
+    <hyperlink ref="E365" r:id="rId32"/>
+    <hyperlink ref="F366" r:id="rId33" location="reviews"/>
+    <hyperlink ref="E366" r:id="rId34"/>
+    <hyperlink ref="F367" r:id="rId35"/>
+    <hyperlink ref="E367" r:id="rId36"/>
+    <hyperlink ref="F368" r:id="rId37"/>
+    <hyperlink ref="E368" r:id="rId38"/>
+    <hyperlink ref="F369" r:id="rId39"/>
+    <hyperlink ref="E369" r:id="rId40"/>
+    <hyperlink ref="F370" r:id="rId41"/>
+    <hyperlink ref="E370" r:id="rId42"/>
+    <hyperlink ref="F371" r:id="rId43"/>
+    <hyperlink ref="E371" r:id="rId44"/>
+    <hyperlink ref="F372" r:id="rId45"/>
+    <hyperlink ref="E372" r:id="rId46"/>
+    <hyperlink ref="F373" r:id="rId47"/>
+    <hyperlink ref="E373" r:id="rId48"/>
+    <hyperlink ref="F374" r:id="rId49"/>
+    <hyperlink ref="E374" r:id="rId50"/>
+    <hyperlink ref="F375" r:id="rId51"/>
+    <hyperlink ref="E375" r:id="rId52"/>
+    <hyperlink ref="F376" r:id="rId53"/>
+    <hyperlink ref="E376" r:id="rId54"/>
     <hyperlink ref="I72" display="https://http2.mlstatic.com/D_NQ_NP_2X_977864-MLA82522530268_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728802-MLA82808708997_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_714871-MLA82808836891_032025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I299" r:id="rId55"/>
     <hyperlink ref="J299" r:id="rId56"/>
@@ -15238,28 +15294,28 @@
     <hyperlink ref="I67" display="https://http2.mlstatic.com/D_NQ_NP_2X_754117-MLA87918629604_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_955266-MLA88256438081_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_924778-MLA88256272783_072025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I265" display="https://http2.mlstatic.com/D_NQ_NP_2X_651538-MLA109474609027_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_786870-MLA109384870397_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_877937-MLA109385877631_032026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I328" display="https://http2.mlstatic.com/D_NQ_NP_2X_659872-MLA110558100656_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_654212-MLA110558217136_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728798-MLA110558100602_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J374" r:id="rId58"/>
-    <hyperlink ref="I374" r:id="rId59"/>
+    <hyperlink ref="J375" r:id="rId58"/>
+    <hyperlink ref="I375" r:id="rId59"/>
     <hyperlink ref="I330" display="https://http2.mlstatic.com/D_NQ_NP_2X_704682-MLA112632086794_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648062-MLA114215908179_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_721338-MLA112631444306_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="E250" r:id="rId60"/>
     <hyperlink ref="I250" r:id="rId61"/>
     <hyperlink ref="J250" r:id="rId62"/>
     <hyperlink ref="I36" r:id="rId63"/>
-    <hyperlink ref="I372" display="https://http2.mlstatic.com/D_NQ_NP_2X_870766-MLA111944165952_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_835091-MLA112882459449_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I373" display="https://http2.mlstatic.com/D_NQ_NP_2X_870766-MLA111944165952_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_835091-MLA112882459449_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="J60" r:id="rId64"/>
     <hyperlink ref="I60" display="https://http2.mlstatic.com/D_NQ_NP_2X_650019-MLA112598239078_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_694102-MLA111420836191_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_960139-MLA111232526403_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I364" r:id="rId65"/>
+    <hyperlink ref="I365" r:id="rId65"/>
     <hyperlink ref="I225" display="https://http2.mlstatic.com/D_NQ_NP_2X_761866-MLA76203783381_052024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_967910-MLA76082310461_042024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_699850-MLA76082339489_042024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="J32" r:id="rId66"/>
     <hyperlink ref="I32" display="https://http2.mlstatic.com/D_NQ_NP_2X_937988-MLA100214376229_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_839463-MLA100214244569_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_878239-MLA100214347283_122025-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I101" display="https://http2.mlstatic.com/D_NQ_NP_2X_853469-MLA73479850047_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_636371-MLA72966055893_112023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_647337-MLA74448293715_022024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I373" display="https://http2.mlstatic.com/D_NQ_NP_2X_838661-MLA114043475512_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_997422-MLA111845686244_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_946430-MLA112856485647_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I374" display="https://http2.mlstatic.com/D_NQ_NP_2X_838661-MLA114043475512_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_997422-MLA111845686244_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_946430-MLA112856485647_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I146" display="https://http2.mlstatic.com/D_NQ_NP_2X_700050-MLA90330537717_082025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_810830-MLA92985348779_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_611435-MLA103169335415_122025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
     <hyperlink ref="J341" r:id="rId67"/>
     <hyperlink ref="I341" display="https://http2.mlstatic.com/D_NQ_NP_2X_972461-MLA108765590667_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_959062-MLA111287287492_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_702439-MLA108999676116_032026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I244" display="https://http2.mlstatic.com/D_NQ_NP_2X_772336-MLA83215360667_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_641687-MLA82926894938_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_686941-MLA80851161221_112024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J363" r:id="rId68"/>
-    <hyperlink ref="I363" display="https://http2.mlstatic.com/D_NQ_NP_2X_918751-MLA113089268495_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_972829-MLA114388137831_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_739083-MLA113884890489_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J364" r:id="rId68"/>
+    <hyperlink ref="I364" display="https://http2.mlstatic.com/D_NQ_NP_2X_918751-MLA113089268495_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_972829-MLA114388137831_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_739083-MLA113884890489_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="J357" r:id="rId69"/>
     <hyperlink ref="I357" display="https://http2.mlstatic.com/D_NQ_NP_2X_622982-MLA91998379772_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_918567-MLA93316673763_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_951409-MLA93316693351_092025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I358" r:id="rId70"/>
@@ -15267,8 +15323,8 @@
     <hyperlink ref="J169" r:id="rId72"/>
     <hyperlink ref="I169" display="https://http2.mlstatic.com/D_NQ_NP_2X_630634-MLA83929492736_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_826427-MLA83875691856_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_778506-MLA83875632066_042025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I286" display="https://http2.mlstatic.com/D_NQ_NP_2X_601798-MLA74779553000_032024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_784677-MLA71729912500_092023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_982997-MLA73375012815_122023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J360" r:id="rId73"/>
-    <hyperlink ref="I360" display="https://http2.mlstatic.com/D_NQ_NP_2X_743943-MLA113720575198_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_652343-MLA98742656086_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_688496-MLA89833143459_082025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
+    <hyperlink ref="J361" r:id="rId73"/>
+    <hyperlink ref="I361" display="https://http2.mlstatic.com/D_NQ_NP_2X_743943-MLA113720575198_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_652343-MLA98742656086_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_688496-MLA89833143459_082025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
     <hyperlink ref="J56" r:id="rId74"/>
     <hyperlink ref="I56" r:id="rId75"/>
     <hyperlink ref="I355" r:id="rId76"/>
@@ -15276,12 +15332,12 @@
     <hyperlink ref="I132" r:id="rId78"/>
     <hyperlink ref="I354" r:id="rId79"/>
     <hyperlink ref="J354" r:id="rId80"/>
-    <hyperlink ref="I371" display="https://http2.mlstatic.com/D_NQ_NP_2X_730160-MLA112550162587_062026-F.webp;http://http2.mlstatic.com/D_NQ_NP_2X_748872-MLA113290799753_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_824232-MLA112954608093_062026-F.webp;https://http2.mlstatic.com/D_NQ"/>
+    <hyperlink ref="I372" display="https://http2.mlstatic.com/D_NQ_NP_2X_730160-MLA112550162587_062026-F.webp;http://http2.mlstatic.com/D_NQ_NP_2X_748872-MLA113290799753_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_824232-MLA112954608093_062026-F.webp;https://http2.mlstatic.com/D_NQ"/>
     <hyperlink ref="I107" r:id="rId81"/>
     <hyperlink ref="I2" display="https://http2.mlstatic.com/D_NQ_NP_2X_644970-MLA111138624893_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_618974-MLA113557256809_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_849248-MLA111414716285_052026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I11" r:id="rId82"/>
-    <hyperlink ref="I369" r:id="rId83"/>
-    <hyperlink ref="J369" r:id="rId84"/>
+    <hyperlink ref="I370" r:id="rId83"/>
+    <hyperlink ref="J370" r:id="rId84"/>
     <hyperlink ref="E145" r:id="rId85"/>
     <hyperlink ref="I145" r:id="rId86"/>
     <hyperlink ref="J180" r:id="rId87"/>
@@ -15301,8 +15357,8 @@
     <hyperlink ref="I54" r:id="rId101"/>
     <hyperlink ref="I353" r:id="rId102"/>
     <hyperlink ref="I325" r:id="rId103"/>
-    <hyperlink ref="J366" r:id="rId104"/>
-    <hyperlink ref="I366" r:id="rId105"/>
+    <hyperlink ref="J367" r:id="rId104"/>
+    <hyperlink ref="I367" r:id="rId105"/>
     <hyperlink ref="I337" display="https://http2.mlstatic.com/D_NQ_NP_2X_871513-MLA105683275105_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_921467-MLA106225093215_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_768089-MLA111241397693_052026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I273" r:id="rId106"/>
     <hyperlink ref="J268" r:id="rId107"/>
@@ -15326,7 +15382,7 @@
     <hyperlink ref="I197" display="https://http2.mlstatic.com/D_NQ_NP_2X_882824-MLA78038279945_072024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_628505-MLA80605999965_112024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_605405-MLA79717879214_102024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="J108" r:id="rId121"/>
     <hyperlink ref="I108" r:id="rId122"/>
-    <hyperlink ref="I365" r:id="rId123"/>
+    <hyperlink ref="I366" r:id="rId123"/>
     <hyperlink ref="I174" display="https://http2.mlstatic.com/D_NQ_NP_2X_671282-MLA88303913955_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_751626-MLA88304056333_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_928886-MLA111461620111_052026-F.webp;https://http2.mlstatic.com/D_NQ_"/>
     <hyperlink ref="I85" r:id="rId124"/>
     <hyperlink ref="I212" r:id="rId125"/>
@@ -15336,8 +15392,8 @@
     <hyperlink ref="J271" r:id="rId128"/>
     <hyperlink ref="I271" r:id="rId129"/>
     <hyperlink ref="I324" r:id="rId130"/>
-    <hyperlink ref="J375" r:id="rId131"/>
-    <hyperlink ref="I375" r:id="rId132"/>
+    <hyperlink ref="J376" r:id="rId131"/>
+    <hyperlink ref="I376" r:id="rId132"/>
     <hyperlink ref="J53" r:id="rId133"/>
     <hyperlink ref="I53" r:id="rId134"/>
     <hyperlink ref="I222" display="https://http2.mlstatic.com/D_NQ_NP_2X_931197-MLA111097282025_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_647752-MLA86304062244_062025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_697099-MLA86808814199_062025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
@@ -15371,13 +15427,13 @@
     <hyperlink ref="J143" r:id="rId148"/>
     <hyperlink ref="J87" r:id="rId149"/>
     <hyperlink ref="I87" r:id="rId150"/>
-    <hyperlink ref="J365" r:id="rId151"/>
+    <hyperlink ref="J366" r:id="rId151"/>
     <hyperlink ref="J235" r:id="rId152"/>
     <hyperlink ref="I235" display="https://http2.mlstatic.com/D_NQ_NP_2X_786831-MLA112508605409_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_945451-MLA106951088919_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_942407-MLA79868078780_102024-F.webp;https://http2.mlstatic.com/D_NQ"/>
     <hyperlink ref="J25" r:id="rId153"/>
     <hyperlink ref="I156" r:id="rId154"/>
-    <hyperlink ref="J362" r:id="rId155"/>
-    <hyperlink ref="I362" display="https://http2.mlstatic.com/D_NQ_NP_2X_654570-MLA114163554383_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_820669-MLA112176540320_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_827402-MLA113697495744_072026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J363" r:id="rId155"/>
+    <hyperlink ref="I363" display="https://http2.mlstatic.com/D_NQ_NP_2X_654570-MLA114163554383_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_820669-MLA112176540320_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_827402-MLA113697495744_072026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="J283" r:id="rId156"/>
     <hyperlink ref="I283" r:id="rId157"/>
     <hyperlink ref="I147" r:id="rId158"/>
@@ -15385,48 +15441,53 @@
     <hyperlink ref="I167" display="https://http2.mlstatic.com/D_NQ_NP_2X_949414-MLA115597206229_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_781530-MLA115596590455_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_794977-MLA113865153424_072026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I242" r:id="rId160"/>
     <hyperlink ref="I336" r:id="rId161"/>
-    <hyperlink ref="J370" r:id="rId162"/>
-    <hyperlink ref="I370" r:id="rId163"/>
+    <hyperlink ref="J371" r:id="rId162"/>
+    <hyperlink ref="I371" r:id="rId163"/>
     <hyperlink ref="I113" display="https://http2.mlstatic.com/D_NQ_NP_2X_602967-MLA106207657120_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_937184-MLA99857184303_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_615655-MLA93805615686_102025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
     <hyperlink ref="J113" r:id="rId164"/>
     <hyperlink ref="I274" display="https://http2.mlstatic.com/D_NQ_NP_2X_811367-MLA96964641173_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_724534-MLA95972455447_102025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_862711-MLA94582890276_102025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I188" r:id="rId165"/>
-    <hyperlink ref="I368" r:id="rId166"/>
+    <hyperlink ref="I369" r:id="rId166"/>
     <hyperlink ref="I112" display="https://http2.mlstatic.com/D_NQ_NP_2X_832809-MLA100859657141_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_651615-MLA104572148023_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_683702-MLA104248384382_012026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I321" r:id="rId167"/>
-    <hyperlink ref="J359" r:id="rId168"/>
-    <hyperlink ref="I359" display="https://http2.mlstatic.com/D_NQ_NP_2X_986254-MLA113898749317_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_998498-MLA115220256263_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_611119-MLA113912677208_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I297"/>
+    <hyperlink ref="J360" r:id="rId168"/>
+    <hyperlink ref="I360" display="https://http2.mlstatic.com/D_NQ_NP_2X_986254-MLA113898749317_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_998498-MLA115220256263_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_611119-MLA113912677208_072026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I297" display="https://http2.mlstatic.com/D_NQ_NP_2X_672294-MLA110281902509_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_995715-MLA110918042491_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_936537-MLA110364709430_052026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="J297" r:id="rId169"/>
     <hyperlink ref="J326" r:id="rId170"/>
-    <hyperlink ref="I326"/>
+    <hyperlink ref="I326" display="https://http2.mlstatic.com/D_NQ_NP_2X_623123-MLA111040290746_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_934760-MLA111878498611_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_790070-MLA112661729675_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="J338" r:id="rId171"/>
-    <hyperlink ref="I338"/>
+    <hyperlink ref="I338" display="https://http2.mlstatic.com/D_NQ_NP_2X_637815-MLA110916194519_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_643077-MLA110749031212_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_708016-MLA112321199072_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I320" r:id="rId172"/>
     <hyperlink ref="I122" r:id="rId173"/>
     <hyperlink ref="J55" r:id="rId174"/>
-    <hyperlink ref="I55"/>
+    <hyperlink ref="I55" display="https://http2.mlstatic.com/D_NQ_NP_2X_707272-MLA81406001662_122024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_992452-MLA71699440818_092023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_616985-MLA84032409756_052025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="J293" r:id="rId175"/>
-    <hyperlink ref="I293"/>
+    <hyperlink ref="I293" display="https://http2.mlstatic.com/D_NQ_NP_2X_699847-MLA83204192108_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_847455-MLA79932861627_102024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_823994-MLA70105011582_062023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="J247" r:id="rId176"/>
-    <hyperlink ref="I247"/>
+    <hyperlink ref="I247" display="https://http2.mlstatic.com/D_NQ_NP_2X_896395-MLA74651133358_022024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_757231-MLA73307952803_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_773664-MLA113844190574_072026-F.webp;https://http2.mlstatic.com/D_NQ_"/>
     <hyperlink ref="I269" r:id="rId177"/>
     <hyperlink ref="J214" r:id="rId178"/>
-    <hyperlink ref="I214"/>
+    <hyperlink ref="I214" display="https://http2.mlstatic.com/D_NQ_NP_2X_857704-MLA105910693631_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_785878-MLA115684445439_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_732723-MLA114610870605_072026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I124" r:id="rId179"/>
-    <hyperlink ref="I139"/>
-    <hyperlink ref="I151"/>
+    <hyperlink ref="I139" display="https://http2.mlstatic.com/D_NQ_NP_2X_731885-MLA81735782871_012025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_877502-MLA81736505623_012025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_739624-MLA81735782869_012025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="I151" display="https://http2.mlstatic.com/D_NQ_NP_2X_852777-MLA73231184100_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_953229-MLA74068746840_012024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_727505-MLA74823139724_032024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I163" r:id="rId180"/>
     <hyperlink ref="J163" r:id="rId181"/>
     <hyperlink ref="F111" r:id="rId182" location="reviews"/>
     <hyperlink ref="I111" r:id="rId183"/>
     <hyperlink ref="I323" r:id="rId184"/>
     <hyperlink ref="I327" r:id="rId185"/>
+    <hyperlink ref="I102"/>
+    <hyperlink ref="E359" r:id="rId186"/>
+    <hyperlink ref="F359" r:id="rId187"/>
+    <hyperlink ref="I359"/>
+    <hyperlink ref="J359" r:id="rId188"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId186"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId189"/>
   <tableParts count="1">
-    <tablePart r:id="rId187"/>
+    <tablePart r:id="rId190"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="1602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="1596">
   <si>
     <t>Nombre</t>
   </si>
@@ -3973,12 +3973,6 @@
     <t>Altura: 52.5 cm, Ancho: 37.5 cm</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.mx/inversor-hzero-600w-de-onda-senoidal-modificada-para-auto-con-2-salidas-ac-y-2-usb/p/MLM52856540?pdp_filters=item_id:MLM2587727551</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_996228-MLA110110565683_042026-F.webp</t>
-  </si>
-  <si>
     <t>https://www.mercadolibre.com.mx/hzero-inversor-de-corriente-1000w-12v-a-110v-transformador-portatil-para-coche-con-2-ac-y-2-usb-ideal-para-respaldo-electrico-hogar-proteccion-electrica-multiple/p/MLM57806893?pdp_filters=item_id:MLM2587781837</t>
   </si>
   <si>
@@ -4017,13 +4011,6 @@
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_824026-MLA102603004510_122025-F.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">Inversor convertidor de corriente 600W
-</t>
-  </si>
-  <si>
-    <t>Marca: Hzero Descripcion: Onda Senoidal Modificada para Auto con 2 Salidas AC y 2 USB</t>
-  </si>
-  <si>
     <t xml:space="preserve">Inversor Convertidor De Corriente 1000W 12v A 110v
 </t>
   </si>
@@ -4296,12 +4283,6 @@
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_601798-MLA74779553000_032024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_784677-MLA71729912500_092023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_982997-MLA73375012815_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_982999-MLA70028199790_062023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_830261-MLA70048397883_062023-F.webp</t>
-  </si>
-  <si>
-    <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019f29451c3876a8969ca32011081a6b/master.m3u8</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_743943-MLA113720575198_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_652343-MLA98742656086_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_688496-MLA89833143459_082025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_980015-MLA111245266119_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_676086-MLA108251244515_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_743943-MLA113720575198_072026-F.webp</t>
   </si>
   <si>
     <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019eec50ebdc7581aaf884c109615b29/master.m3u8</t>
@@ -5009,8 +4990,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J377" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J377"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J376" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J376"/>
   <sortState ref="A2:H342">
     <sortCondition ref="A1:A342"/>
   </sortState>
@@ -5315,7 +5296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J377"/>
+  <dimension ref="A1:J376"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" style="1" customWidth="1"/>
@@ -5355,10 +5336,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -5387,7 +5368,7 @@
         <v>66</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>1433</v>
+        <v>1427</v>
       </c>
       <c r="J2" s="12"/>
     </row>
@@ -5417,7 +5398,7 @@
         <v>66</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>1509</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -5469,7 +5450,7 @@
         <v>510</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -5625,7 +5606,7 @@
         <v>66</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
@@ -5965,7 +5946,7 @@
         <v>511</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
@@ -5994,7 +5975,7 @@
         <v>99</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>1468</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
@@ -6063,7 +6044,7 @@
         <v>114</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>1587</v>
+        <v>1581</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>912</v>
@@ -6150,10 +6131,10 @@
         <v>99</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
@@ -6257,7 +6238,7 @@
         <v>66</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
@@ -6545,10 +6526,10 @@
         <v>512</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>1502</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
@@ -6652,10 +6633,10 @@
         <v>12</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>1511</v>
+        <v>1505</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>1510</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
@@ -6684,10 +6665,10 @@
         <v>12</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>1489</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
@@ -6716,10 +6697,10 @@
         <v>12</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>1451</v>
+        <v>1445</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>1450</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
@@ -6748,10 +6729,10 @@
         <v>12</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
@@ -6780,10 +6761,10 @@
         <v>12</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>1423</v>
+        <v>1417</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>1422</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
@@ -6884,10 +6865,10 @@
         <v>12</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
@@ -7017,7 +6998,7 @@
         <v>512</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>1514</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -7046,10 +7027,10 @@
         <v>99</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -7078,7 +7059,7 @@
         <v>99</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
@@ -7153,10 +7134,10 @@
         <v>197</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
@@ -7211,7 +7192,7 @@
         <v>66</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
@@ -7260,10 +7241,10 @@
         <v>12</v>
       </c>
       <c r="I74" s="12" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>1445</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
@@ -7292,7 +7273,7 @@
         <v>405</v>
       </c>
       <c r="I75" s="12" t="s">
-        <v>1496</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.35">
@@ -7543,7 +7524,7 @@
         <v>99</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>1479</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
@@ -7560,7 +7541,7 @@
         <v>579</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>1600</v>
+        <v>1594</v>
       </c>
       <c r="G86" s="7" t="s">
         <v>990</v>
@@ -7569,10 +7550,10 @@
         <v>510</v>
       </c>
       <c r="I86" s="12" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.35">
@@ -7601,10 +7582,10 @@
         <v>66</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>1521</v>
+        <v>1515</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>1520</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
@@ -7962,7 +7943,7 @@
         <v>66</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.35">
@@ -7988,7 +7969,7 @@
         <v>197</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>1575</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
@@ -8095,7 +8076,7 @@
         <v>12</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>1459</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
@@ -8124,7 +8105,7 @@
         <v>12</v>
       </c>
       <c r="I107" s="12" t="s">
-        <v>1432</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.35">
@@ -8153,10 +8134,10 @@
         <v>511</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>1475</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.35">
@@ -8219,7 +8200,7 @@
         <v>491</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>1570</v>
+        <v>1564</v>
       </c>
       <c r="G111" s="7" t="s">
         <v>879</v>
@@ -8228,7 +8209,7 @@
         <v>510</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>1571</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.35">
@@ -8254,7 +8235,7 @@
         <v>66</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>1544</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.35">
@@ -8283,10 +8264,10 @@
         <v>66</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>1540</v>
+        <v>1534</v>
       </c>
       <c r="J113" s="12" t="s">
-        <v>1539</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.35">
@@ -8367,10 +8348,10 @@
         <v>66</v>
       </c>
       <c r="I116" s="12" t="s">
-        <v>1493</v>
+        <v>1487</v>
       </c>
       <c r="J116" s="12" t="s">
-        <v>1492</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.35">
@@ -8526,7 +8507,7 @@
         <v>12</v>
       </c>
       <c r="I122" s="12" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.35">
@@ -8575,7 +8556,7 @@
         <v>510</v>
       </c>
       <c r="I124" s="12" t="s">
-        <v>1565</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -8751,7 +8732,7 @@
         <v>510</v>
       </c>
       <c r="I131" s="12" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.35">
@@ -8780,7 +8761,7 @@
         <v>511</v>
       </c>
       <c r="I132" s="12" t="s">
-        <v>1426</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="58" x14ac:dyDescent="0.35">
@@ -8855,7 +8836,7 @@
         <v>510</v>
       </c>
       <c r="I135" s="12" t="s">
-        <v>1501</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.35">
@@ -8910,10 +8891,10 @@
         <v>66</v>
       </c>
       <c r="I137" s="12" t="s">
-        <v>1470</v>
+        <v>1464</v>
       </c>
       <c r="J137" s="12" t="s">
-        <v>1469</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.35">
@@ -8962,7 +8943,7 @@
         <v>510</v>
       </c>
       <c r="I139" s="12" t="s">
-        <v>1566</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.35">
@@ -9011,7 +8992,7 @@
         <v>197</v>
       </c>
       <c r="I141" s="12" t="s">
-        <v>1594</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.35">
@@ -9037,10 +9018,10 @@
         <v>197</v>
       </c>
       <c r="I142" s="12" t="s">
-        <v>1596</v>
+        <v>1590</v>
       </c>
       <c r="J142" s="12" t="s">
-        <v>1595</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.35">
@@ -9066,10 +9047,10 @@
         <v>197</v>
       </c>
       <c r="I143" s="12" t="s">
-        <v>1519</v>
+        <v>1513</v>
       </c>
       <c r="J143" s="12" t="s">
-        <v>1518</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.35">
@@ -9109,7 +9090,7 @@
         <v>250</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="F145" s="7" t="s">
         <v>98</v>
@@ -9121,7 +9102,7 @@
         <v>510</v>
       </c>
       <c r="I145" s="12" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.35">
@@ -9150,7 +9131,7 @@
         <v>511</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.35">
@@ -9179,7 +9160,7 @@
         <v>511</v>
       </c>
       <c r="I147" s="12" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.35">
@@ -9208,7 +9189,7 @@
         <v>511</v>
       </c>
       <c r="I148" s="12" t="s">
-        <v>1458</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.35">
@@ -9237,7 +9218,7 @@
         <v>510</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>1467</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.35">
@@ -9292,7 +9273,7 @@
         <v>510</v>
       </c>
       <c r="I151" s="12" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.35">
@@ -9422,7 +9403,7 @@
         <v>511</v>
       </c>
       <c r="I156" s="12" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="29" x14ac:dyDescent="0.35">
@@ -9569,10 +9550,10 @@
         <v>510</v>
       </c>
       <c r="I162" s="12" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="J162" s="12" t="s">
-        <v>1593</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.35">
@@ -9598,10 +9579,10 @@
         <v>510</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="J163" s="12" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.35">
@@ -9699,10 +9680,10 @@
         <v>511</v>
       </c>
       <c r="I167" s="12" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
       <c r="J167" s="12" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.35">
@@ -9757,10 +9738,10 @@
         <v>511</v>
       </c>
       <c r="I169" s="12" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="J169" s="12" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.35">
@@ -9884,7 +9865,7 @@
         <v>511</v>
       </c>
       <c r="I174" s="12" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
@@ -10034,10 +10015,10 @@
         <v>66</v>
       </c>
       <c r="I180" s="12" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="J180" s="12" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -10164,7 +10145,7 @@
         <v>99</v>
       </c>
       <c r="I185" s="12" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.35">
@@ -10242,7 +10223,7 @@
         <v>66</v>
       </c>
       <c r="I188" s="12" t="s">
-        <v>1542</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.35">
@@ -10297,7 +10278,7 @@
         <v>99</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -10441,7 +10422,7 @@
         <v>66</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>1483</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.35">
@@ -10470,10 +10451,10 @@
         <v>12</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>1474</v>
+        <v>1468</v>
       </c>
       <c r="J197" s="12" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -10681,7 +10662,7 @@
         <v>12</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>1515</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.35">
@@ -10808,7 +10789,7 @@
         <v>511</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>1513</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.35">
@@ -10863,7 +10844,7 @@
         <v>12</v>
       </c>
       <c r="I212" s="12" t="s">
-        <v>1480</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.35">
@@ -10915,10 +10896,10 @@
         <v>510</v>
       </c>
       <c r="I214" s="12" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="J214" s="12" t="s">
-        <v>1563</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -11129,7 +11110,7 @@
         <v>511</v>
       </c>
       <c r="I222" s="12" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.35">
@@ -11207,7 +11188,7 @@
         <v>99</v>
       </c>
       <c r="I225" s="12" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.35">
@@ -11354,7 +11335,7 @@
         <v>440</v>
       </c>
       <c r="E231" s="12" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
       <c r="F231" s="7" t="s">
         <v>997</v>
@@ -11366,7 +11347,7 @@
         <v>653</v>
       </c>
       <c r="I231" s="12" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.35">
@@ -11473,10 +11454,10 @@
         <v>511</v>
       </c>
       <c r="I235" s="12" t="s">
-        <v>1525</v>
+        <v>1519</v>
       </c>
       <c r="J235" s="12" t="s">
-        <v>1524</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.35">
@@ -11551,7 +11532,7 @@
         <v>99</v>
       </c>
       <c r="I238" s="12" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.35">
@@ -11649,7 +11630,7 @@
         <v>66</v>
       </c>
       <c r="I242" s="12" t="s">
-        <v>1535</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.35">
@@ -11704,7 +11685,7 @@
         <v>99</v>
       </c>
       <c r="I244" s="12" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.35">
@@ -11733,10 +11714,10 @@
         <v>99</v>
       </c>
       <c r="I245" s="12" t="s">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="J245" s="12" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.35">
@@ -11791,10 +11772,10 @@
         <v>12</v>
       </c>
       <c r="I247" s="12" t="s">
-        <v>1561</v>
+        <v>1555</v>
       </c>
       <c r="J247" s="12" t="s">
-        <v>1560</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.35">
@@ -11860,7 +11841,7 @@
         <v>1300</v>
       </c>
       <c r="E250" s="12" t="s">
-        <v>1429</v>
+        <v>1423</v>
       </c>
       <c r="F250" s="7" t="s">
         <v>436</v>
@@ -11872,10 +11853,10 @@
         <v>197</v>
       </c>
       <c r="I250" s="12" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="J250" s="12" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.35">
@@ -12103,7 +12084,7 @@
         <v>99</v>
       </c>
       <c r="I259" s="12" t="s">
-        <v>1441</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.35">
@@ -12132,10 +12113,10 @@
         <v>66</v>
       </c>
       <c r="I260" s="12" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="J260" s="12" t="s">
-        <v>1494</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.35">
@@ -12259,7 +12240,7 @@
         <v>99</v>
       </c>
       <c r="I265" s="12" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.35">
@@ -12314,7 +12295,7 @@
         <v>99</v>
       </c>
       <c r="I267" s="12" t="s">
-        <v>1447</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.35">
@@ -12343,10 +12324,10 @@
         <v>99</v>
       </c>
       <c r="I268" s="12" t="s">
-        <v>1457</v>
+        <v>1451</v>
       </c>
       <c r="J268" s="12" t="s">
-        <v>1456</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.35">
@@ -12375,7 +12356,7 @@
         <v>12</v>
       </c>
       <c r="I269" s="12" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.35">
@@ -12430,10 +12411,10 @@
         <v>12</v>
       </c>
       <c r="I271" s="12" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
       <c r="J271" s="12" t="s">
-        <v>1484</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.35">
@@ -12462,7 +12443,7 @@
         <v>12</v>
       </c>
       <c r="I272" s="12" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.35">
@@ -12491,7 +12472,7 @@
         <v>66</v>
       </c>
       <c r="I273" s="12" t="s">
-        <v>1455</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.35">
@@ -12520,7 +12501,7 @@
         <v>66</v>
       </c>
       <c r="I274" s="12" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.35">
@@ -12549,7 +12530,7 @@
         <v>66</v>
       </c>
       <c r="I275" s="12" t="s">
-        <v>1504</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.35">
@@ -12630,7 +12611,7 @@
         <v>99</v>
       </c>
       <c r="I278" s="12" t="s">
-        <v>1586</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.35">
@@ -12659,10 +12640,10 @@
         <v>99</v>
       </c>
       <c r="I279" s="12" t="s">
-        <v>1591</v>
+        <v>1585</v>
       </c>
       <c r="J279" s="12" t="s">
-        <v>1590</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.35">
@@ -12766,10 +12747,10 @@
         <v>511</v>
       </c>
       <c r="I283" s="12" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="J283" s="12" t="s">
-        <v>1530</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.35">
@@ -12822,7 +12803,7 @@
         <v>197</v>
       </c>
       <c r="I285" s="12" t="s">
-        <v>1508</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="286" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -12851,7 +12832,7 @@
         <v>66</v>
       </c>
       <c r="I286" s="12" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="287" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -12906,7 +12887,7 @@
         <v>197</v>
       </c>
       <c r="I288" s="12" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.35">
@@ -13030,10 +13011,10 @@
         <v>12</v>
       </c>
       <c r="I293" s="12" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
       <c r="J293" s="12" t="s">
-        <v>1558</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="294" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
@@ -13114,10 +13095,10 @@
         <v>99</v>
       </c>
       <c r="I296" s="12" t="s">
-        <v>1507</v>
+        <v>1501</v>
       </c>
       <c r="J296" s="12" t="s">
-        <v>1601</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.35">
@@ -13146,10 +13127,10 @@
         <v>66</v>
       </c>
       <c r="I297" s="12" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="J297" s="12" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.35">
@@ -13178,10 +13159,10 @@
         <v>66</v>
       </c>
       <c r="I298" s="12" t="s">
-        <v>1482</v>
+        <v>1476</v>
       </c>
       <c r="J298" s="12" t="s">
-        <v>1481</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.35">
@@ -13210,10 +13191,10 @@
         <v>512</v>
       </c>
       <c r="I299" s="12" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="J299" s="12" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.35">
@@ -13242,10 +13223,10 @@
         <v>510</v>
       </c>
       <c r="I300" s="12" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="J300" s="12" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="301" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -13274,7 +13255,7 @@
         <v>510</v>
       </c>
       <c r="I301" s="12" t="s">
-        <v>1498</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.35">
@@ -13329,10 +13310,10 @@
         <v>12</v>
       </c>
       <c r="I303" s="12" t="s">
-        <v>1500</v>
+        <v>1494</v>
       </c>
       <c r="J303" s="12" t="s">
-        <v>1499</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.35">
@@ -13726,7 +13707,7 @@
         <v>12</v>
       </c>
       <c r="I320" s="12" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.35">
@@ -13755,7 +13736,7 @@
         <v>66</v>
       </c>
       <c r="I321" s="12" t="s">
-        <v>1545</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.35">
@@ -13784,10 +13765,10 @@
         <v>66</v>
       </c>
       <c r="I322" s="12" t="s">
-        <v>1449</v>
+        <v>1443</v>
       </c>
       <c r="J322" s="12" t="s">
-        <v>1448</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="323" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -13816,7 +13797,7 @@
         <v>99</v>
       </c>
       <c r="I323" s="12" t="s">
-        <v>1573</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.35">
@@ -13842,7 +13823,7 @@
         <v>512</v>
       </c>
       <c r="I324" s="12" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="325" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -13871,7 +13852,7 @@
         <v>66</v>
       </c>
       <c r="I325" s="12" t="s">
-        <v>1453</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.35">
@@ -13900,10 +13881,10 @@
         <v>12</v>
       </c>
       <c r="I326" s="12" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="J326" s="12" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.35">
@@ -13929,7 +13910,7 @@
         <v>99</v>
       </c>
       <c r="I327" s="12" t="s">
-        <v>1574</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.35">
@@ -13955,7 +13936,7 @@
         <v>510</v>
       </c>
       <c r="I328" s="12" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.35">
@@ -13978,7 +13959,7 @@
         <v>66</v>
       </c>
       <c r="I329" s="12" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="330" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
@@ -14004,7 +13985,7 @@
         <v>99</v>
       </c>
       <c r="I330" s="12" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.35">
@@ -14033,7 +14014,7 @@
         <v>66</v>
       </c>
       <c r="I331" s="12" t="s">
-        <v>1512</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="332" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -14062,10 +14043,10 @@
         <v>510</v>
       </c>
       <c r="I332" s="12" t="s">
-        <v>1517</v>
+        <v>1511</v>
       </c>
       <c r="J332" s="12" t="s">
-        <v>1516</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="333" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -14091,10 +14072,10 @@
         <v>99</v>
       </c>
       <c r="I333" s="12" t="s">
-        <v>1588</v>
+        <v>1582</v>
       </c>
       <c r="J333" s="12" t="s">
-        <v>1589</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="334" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
@@ -14120,10 +14101,10 @@
         <v>99</v>
       </c>
       <c r="I334" s="12" t="s">
-        <v>1506</v>
+        <v>1500</v>
       </c>
       <c r="J334" s="12" t="s">
-        <v>1505</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="335" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -14172,7 +14153,7 @@
         <v>66</v>
       </c>
       <c r="I336" s="12" t="s">
-        <v>1536</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.35">
@@ -14198,7 +14179,7 @@
         <v>66</v>
       </c>
       <c r="I337" s="12" t="s">
-        <v>1454</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.35">
@@ -14227,10 +14208,10 @@
         <v>12</v>
       </c>
       <c r="I338" s="12" t="s">
-        <v>1553</v>
+        <v>1547</v>
       </c>
       <c r="J338" s="12" t="s">
-        <v>1552</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.35">
@@ -14302,10 +14283,10 @@
         <v>510</v>
       </c>
       <c r="I341" s="12" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="J341" s="12" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.35">
@@ -14331,10 +14312,10 @@
         <v>66</v>
       </c>
       <c r="I342" s="12" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="J342" s="12" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.35">
@@ -14617,7 +14598,7 @@
         <v>511</v>
       </c>
       <c r="I353" s="12" t="s">
-        <v>1452</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.35">
@@ -14646,10 +14627,10 @@
         <v>511</v>
       </c>
       <c r="I354" s="12" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="J354" s="12" t="s">
-        <v>1428</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.35">
@@ -14678,7 +14659,7 @@
         <v>510</v>
       </c>
       <c r="I355" s="12" t="s">
-        <v>1424</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.35">
@@ -14707,15 +14688,15 @@
         <v>510</v>
       </c>
       <c r="I356" s="12" t="s">
-        <v>1425</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="357" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C357" s="7">
         <v>1225</v>
@@ -14736,18 +14717,18 @@
         <v>511</v>
       </c>
       <c r="I357" s="12" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="J357" s="12" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="358" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="C358" s="7">
         <v>1225</v>
@@ -14768,18 +14749,18 @@
         <v>511</v>
       </c>
       <c r="I358" s="12" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="J358" s="12" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
-        <v>1576</v>
+        <v>1570</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>1577</v>
+        <v>1571</v>
       </c>
       <c r="C359" s="7">
         <v>590</v>
@@ -14788,10 +14769,10 @@
         <v>400</v>
       </c>
       <c r="E359" s="12" t="s">
-        <v>1578</v>
+        <v>1572</v>
       </c>
       <c r="F359" s="12" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="G359" s="7" t="s">
         <v>859</v>
@@ -14800,10 +14781,10 @@
         <v>66</v>
       </c>
       <c r="I359" s="12" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="J359" s="12" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.35">
@@ -14832,24 +14813,24 @@
         <v>66</v>
       </c>
       <c r="I360" s="12" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="J360" s="12" t="s">
-        <v>1546</v>
-      </c>
-    </row>
-    <row r="361" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="C361" s="7">
-        <v>1033</v>
+        <v>614</v>
       </c>
       <c r="D361" s="7">
-        <v>675</v>
+        <v>375</v>
       </c>
       <c r="E361" s="12" t="s">
         <v>1315</v>
@@ -14863,25 +14844,19 @@
       <c r="H361" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="I361" s="12" t="s">
-        <v>1421</v>
-      </c>
-      <c r="J361" s="12" t="s">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="362" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="362" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C362" s="7">
-        <v>614</v>
+        <v>946</v>
       </c>
       <c r="D362" s="7">
-        <v>375</v>
+        <v>575</v>
       </c>
       <c r="E362" s="12" t="s">
         <v>1317</v>
@@ -14895,25 +14870,31 @@
       <c r="H362" s="7" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="363" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="I362" s="12" t="s">
+        <v>1523</v>
+      </c>
+      <c r="J362" s="12" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
-        <v>1332</v>
+        <v>1322</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>1333</v>
+        <v>1323</v>
       </c>
       <c r="C363" s="7">
-        <v>946</v>
+        <v>1174</v>
       </c>
       <c r="D363" s="7">
-        <v>575</v>
+        <v>700</v>
       </c>
       <c r="E363" s="12" t="s">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="F363" s="12" t="s">
-        <v>1318</v>
+        <v>1324</v>
       </c>
       <c r="G363" s="7" t="s">
         <v>859</v>
@@ -14922,106 +14903,106 @@
         <v>511</v>
       </c>
       <c r="I363" s="12" t="s">
-        <v>1529</v>
+        <v>1408</v>
       </c>
       <c r="J363" s="12" t="s">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="364" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="C364" s="7">
-        <v>1174</v>
+        <v>1395</v>
       </c>
       <c r="D364" s="7">
-        <v>700</v>
+        <v>920</v>
       </c>
       <c r="E364" s="12" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="F364" s="12" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="G364" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H364" s="7" t="s">
-        <v>511</v>
+        <v>66</v>
       </c>
       <c r="I364" s="12" t="s">
-        <v>1412</v>
-      </c>
-      <c r="J364" s="12" t="s">
-        <v>1411</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="365" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B365" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="B365" s="1" t="s">
+      <c r="C365" s="7">
+        <v>488</v>
+      </c>
+      <c r="D365" s="7">
+        <v>400</v>
+      </c>
+      <c r="E365" s="12" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F365" s="12" t="s">
         <v>1335</v>
-      </c>
-      <c r="C365" s="7">
-        <v>1395</v>
-      </c>
-      <c r="D365" s="7">
-        <v>920</v>
-      </c>
-      <c r="E365" s="12" t="s">
-        <v>1337</v>
-      </c>
-      <c r="F365" s="12" t="s">
-        <v>1336</v>
       </c>
       <c r="G365" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H365" s="7" t="s">
-        <v>66</v>
+        <v>511</v>
       </c>
       <c r="I365" s="12" t="s">
-        <v>1401</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>1471</v>
+      </c>
+      <c r="J365" s="12" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
-        <v>1522</v>
+        <v>1337</v>
       </c>
       <c r="B366" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C366" s="7">
+        <v>554</v>
+      </c>
+      <c r="D366" s="7">
+        <v>200</v>
+      </c>
+      <c r="E366" s="12" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F366" s="12" t="s">
         <v>1338</v>
-      </c>
-      <c r="C366" s="7">
-        <v>488</v>
-      </c>
-      <c r="D366" s="7">
-        <v>400</v>
-      </c>
-      <c r="E366" s="12" t="s">
-        <v>1340</v>
-      </c>
-      <c r="F366" s="12" t="s">
-        <v>1339</v>
       </c>
       <c r="G366" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H366" s="7" t="s">
-        <v>511</v>
+        <v>12</v>
       </c>
       <c r="I366" s="12" t="s">
-        <v>1477</v>
+        <v>1579</v>
       </c>
       <c r="J366" s="12" t="s">
-        <v>1523</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>1341</v>
       </c>
@@ -15029,10 +15010,10 @@
         <v>1344</v>
       </c>
       <c r="C367" s="7">
-        <v>554</v>
+        <v>398</v>
       </c>
       <c r="D367" s="7">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E367" s="12" t="s">
         <v>1343</v>
@@ -15044,42 +15025,39 @@
         <v>859</v>
       </c>
       <c r="H367" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I367" s="12" t="s">
-        <v>1585</v>
-      </c>
-      <c r="J367" s="12" t="s">
-        <v>1584</v>
-      </c>
-    </row>
-    <row r="368" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>1345</v>
       </c>
       <c r="B368" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C368" s="7">
+        <v>399</v>
+      </c>
+      <c r="D368" s="7">
+        <v>100</v>
+      </c>
+      <c r="E368" s="12" t="s">
         <v>1348</v>
       </c>
-      <c r="C368" s="7">
-        <v>398</v>
-      </c>
-      <c r="D368" s="7">
-        <v>250</v>
-      </c>
-      <c r="E368" s="12" t="s">
+      <c r="F368" s="12" t="s">
         <v>1347</v>
-      </c>
-      <c r="F368" s="12" t="s">
-        <v>1346</v>
       </c>
       <c r="G368" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H368" s="7" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="I368" s="12" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>1349</v>
       </c>
@@ -15087,10 +15065,10 @@
         <v>1350</v>
       </c>
       <c r="C369" s="7">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D369" s="7">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E369" s="12" t="s">
         <v>1352</v>
@@ -15102,13 +15080,16 @@
         <v>859</v>
       </c>
       <c r="H369" s="7" t="s">
-        <v>66</v>
+        <v>197</v>
       </c>
       <c r="I369" s="12" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="370" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>1429</v>
+      </c>
+      <c r="J369" s="12" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>1353</v>
       </c>
@@ -15116,7 +15097,7 @@
         <v>1354</v>
       </c>
       <c r="C370" s="7">
-        <v>397</v>
+        <v>350</v>
       </c>
       <c r="D370" s="7">
         <v>300</v>
@@ -15131,33 +15112,33 @@
         <v>859</v>
       </c>
       <c r="H370" s="7" t="s">
-        <v>197</v>
+        <v>66</v>
       </c>
       <c r="I370" s="12" t="s">
-        <v>1435</v>
+        <v>1532</v>
       </c>
       <c r="J370" s="12" t="s">
-        <v>1436</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="C371" s="7">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="D371" s="7">
         <v>300</v>
       </c>
       <c r="E371" s="12" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="F371" s="12" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="G371" s="7" t="s">
         <v>859</v>
@@ -15166,30 +15147,27 @@
         <v>66</v>
       </c>
       <c r="I371" s="12" t="s">
-        <v>1538</v>
-      </c>
-      <c r="J371" s="12" t="s">
-        <v>1537</v>
-      </c>
-    </row>
-    <row r="372" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C372" s="7">
+        <v>1690</v>
+      </c>
+      <c r="D372" s="7">
+        <v>1090</v>
+      </c>
+      <c r="E372" s="12" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F372" s="12" t="s">
         <v>1363</v>
-      </c>
-      <c r="B372" s="1" t="s">
-        <v>1364</v>
-      </c>
-      <c r="C372" s="7">
-        <v>385</v>
-      </c>
-      <c r="D372" s="7">
-        <v>300</v>
-      </c>
-      <c r="E372" s="12" t="s">
-        <v>1362</v>
-      </c>
-      <c r="F372" s="12" t="s">
-        <v>1361</v>
       </c>
       <c r="G372" s="7" t="s">
         <v>859</v>
@@ -15198,7 +15176,7 @@
         <v>66</v>
       </c>
       <c r="I372" s="12" t="s">
-        <v>1431</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="373" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -15206,42 +15184,42 @@
         <v>1366</v>
       </c>
       <c r="B373" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C373" s="7">
+        <v>1999</v>
+      </c>
+      <c r="D373" s="7">
+        <v>800</v>
+      </c>
+      <c r="E373" s="12" t="s">
         <v>1365</v>
       </c>
-      <c r="C373" s="7">
-        <v>1690</v>
-      </c>
-      <c r="D373" s="7">
-        <v>1090</v>
-      </c>
-      <c r="E373" s="12" t="s">
-        <v>1430</v>
-      </c>
       <c r="F373" s="12" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="G373" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H373" s="7" t="s">
-        <v>66</v>
+        <v>197</v>
       </c>
       <c r="I373" s="12" t="s">
-        <v>1398</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B374" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="B374" s="1" t="s">
-        <v>1371</v>
-      </c>
       <c r="C374" s="7">
-        <v>1999</v>
+        <v>4699</v>
       </c>
       <c r="D374" s="7">
-        <v>800</v>
+        <v>2832</v>
       </c>
       <c r="E374" s="12" t="s">
         <v>1369</v>
@@ -15253,81 +15231,52 @@
         <v>859</v>
       </c>
       <c r="H374" s="7" t="s">
-        <v>197</v>
+        <v>510</v>
       </c>
       <c r="I374" s="12" t="s">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="375" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1389</v>
+      </c>
+      <c r="J374" s="12" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C375" s="7">
+        <v>349</v>
+      </c>
+      <c r="D375" s="7">
+        <v>295</v>
+      </c>
+      <c r="E375" s="12" t="s">
         <v>1375</v>
       </c>
-      <c r="B375" s="1" t="s">
+      <c r="F375" s="12" t="s">
         <v>1374</v>
       </c>
-      <c r="C375" s="7">
-        <v>4699</v>
-      </c>
-      <c r="D375" s="7">
-        <v>2832</v>
-      </c>
-      <c r="E375" s="12" t="s">
-        <v>1373</v>
-      </c>
-      <c r="F375" s="12" t="s">
-        <v>1372</v>
-      </c>
       <c r="G375" s="7" t="s">
-        <v>859</v>
+        <v>419</v>
       </c>
       <c r="H375" s="7" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="I375" s="12" t="s">
-        <v>1393</v>
+        <v>1482</v>
       </c>
       <c r="J375" s="12" t="s">
-        <v>1392</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A376" s="1" t="s">
-        <v>1376</v>
-      </c>
-      <c r="B376" s="1" t="s">
-        <v>1377</v>
-      </c>
-      <c r="C376" s="7">
-        <v>349</v>
-      </c>
-      <c r="D376" s="7">
-        <v>295</v>
-      </c>
-      <c r="E376" s="12" t="s">
-        <v>1379</v>
-      </c>
-      <c r="F376" s="12" t="s">
-        <v>1378</v>
-      </c>
-      <c r="G376" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="H376" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I376" s="12" t="s">
-        <v>1488</v>
-      </c>
-      <c r="J376" s="12" t="s">
-        <v>1487</v>
-      </c>
-    </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A377" s="13" t="s">
-        <v>1597</v>
-      </c>
-      <c r="B377" s="1"/>
+      <c r="A376" s="13" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B376" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15358,255 +15307,247 @@
     <hyperlink ref="E361" r:id="rId24"/>
     <hyperlink ref="F362" r:id="rId25"/>
     <hyperlink ref="E362" r:id="rId26"/>
-    <hyperlink ref="F363" r:id="rId27"/>
-    <hyperlink ref="E363" r:id="rId28"/>
-    <hyperlink ref="F364" r:id="rId29"/>
-    <hyperlink ref="E364" r:id="rId30"/>
-    <hyperlink ref="F365" r:id="rId31"/>
-    <hyperlink ref="E365" r:id="rId32"/>
-    <hyperlink ref="F366" r:id="rId33" location="reviews"/>
-    <hyperlink ref="E366" r:id="rId34"/>
-    <hyperlink ref="F367" r:id="rId35"/>
-    <hyperlink ref="E367" r:id="rId36"/>
-    <hyperlink ref="F368" r:id="rId37"/>
-    <hyperlink ref="E368" r:id="rId38"/>
-    <hyperlink ref="F369" r:id="rId39"/>
-    <hyperlink ref="E369" r:id="rId40"/>
-    <hyperlink ref="F370" r:id="rId41"/>
-    <hyperlink ref="E370" r:id="rId42"/>
-    <hyperlink ref="F371" r:id="rId43"/>
-    <hyperlink ref="E371" r:id="rId44"/>
-    <hyperlink ref="F372" r:id="rId45"/>
-    <hyperlink ref="E372" r:id="rId46"/>
-    <hyperlink ref="F373" r:id="rId47"/>
-    <hyperlink ref="E373" r:id="rId48"/>
-    <hyperlink ref="F374" r:id="rId49"/>
-    <hyperlink ref="E374" r:id="rId50"/>
-    <hyperlink ref="F375" r:id="rId51"/>
-    <hyperlink ref="E375" r:id="rId52"/>
-    <hyperlink ref="F376" r:id="rId53"/>
-    <hyperlink ref="E376" r:id="rId54"/>
+    <hyperlink ref="F364" r:id="rId27"/>
+    <hyperlink ref="E364" r:id="rId28"/>
+    <hyperlink ref="F365" r:id="rId29" location="reviews"/>
+    <hyperlink ref="E365" r:id="rId30"/>
+    <hyperlink ref="F366" r:id="rId31"/>
+    <hyperlink ref="E366" r:id="rId32"/>
+    <hyperlink ref="F367" r:id="rId33"/>
+    <hyperlink ref="E367" r:id="rId34"/>
+    <hyperlink ref="F368" r:id="rId35"/>
+    <hyperlink ref="E368" r:id="rId36"/>
+    <hyperlink ref="F369" r:id="rId37"/>
+    <hyperlink ref="E369" r:id="rId38"/>
+    <hyperlink ref="F370" r:id="rId39"/>
+    <hyperlink ref="E370" r:id="rId40"/>
+    <hyperlink ref="F371" r:id="rId41"/>
+    <hyperlink ref="E371" r:id="rId42"/>
+    <hyperlink ref="F372" r:id="rId43"/>
+    <hyperlink ref="E372" r:id="rId44"/>
+    <hyperlink ref="F373" r:id="rId45"/>
+    <hyperlink ref="E373" r:id="rId46"/>
+    <hyperlink ref="F374" r:id="rId47"/>
+    <hyperlink ref="E374" r:id="rId48"/>
+    <hyperlink ref="F375" r:id="rId49"/>
+    <hyperlink ref="E375" r:id="rId50"/>
     <hyperlink ref="I72" display="https://http2.mlstatic.com/D_NQ_NP_2X_977864-MLA82522530268_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728802-MLA82808708997_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_714871-MLA82808836891_032025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I299" r:id="rId55"/>
-    <hyperlink ref="J299" r:id="rId56"/>
+    <hyperlink ref="I299" r:id="rId51"/>
+    <hyperlink ref="J299" r:id="rId52"/>
     <hyperlink ref="I190" display="https://http2.mlstatic.com/D_NQ_NP_2X_881622-MLA100107482214_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_853470-MLA83211986807_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_889429-MLA82708797484_032025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
     <hyperlink ref="I131" display="https://http2.mlstatic.com/D_NQ_NP_2X_691159-MLA74393127536_022024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_797614-MLA74213272750_012024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_768655-MLA74336317695_012024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I66" display="https://http2.mlstatic.com/D_NQ_NP_2X_665383-MLA110622349795_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_998155-MLA109812957268_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_967066-MLA109813016698_042026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J66" r:id="rId57"/>
+    <hyperlink ref="J66" r:id="rId53"/>
     <hyperlink ref="I67" display="https://http2.mlstatic.com/D_NQ_NP_2X_754117-MLA87918629604_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_955266-MLA88256438081_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_924778-MLA88256272783_072025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I265" display="https://http2.mlstatic.com/D_NQ_NP_2X_651538-MLA109474609027_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_786870-MLA109384870397_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_877937-MLA109385877631_032026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I328" display="https://http2.mlstatic.com/D_NQ_NP_2X_659872-MLA110558100656_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_654212-MLA110558217136_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728798-MLA110558100602_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J375" r:id="rId58"/>
-    <hyperlink ref="I375" r:id="rId59"/>
+    <hyperlink ref="J374" r:id="rId54"/>
+    <hyperlink ref="I374" r:id="rId55"/>
     <hyperlink ref="I330" display="https://http2.mlstatic.com/D_NQ_NP_2X_704682-MLA112632086794_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648062-MLA114215908179_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_721338-MLA112631444306_062026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="E250" r:id="rId60"/>
-    <hyperlink ref="I250" r:id="rId61"/>
-    <hyperlink ref="J250" r:id="rId62"/>
-    <hyperlink ref="I36" r:id="rId63"/>
-    <hyperlink ref="I373" display="https://http2.mlstatic.com/D_NQ_NP_2X_870766-MLA111944165952_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_835091-MLA112882459449_062026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J60" r:id="rId64"/>
+    <hyperlink ref="E250" r:id="rId56"/>
+    <hyperlink ref="I250" r:id="rId57"/>
+    <hyperlink ref="J250" r:id="rId58"/>
+    <hyperlink ref="I36" r:id="rId59"/>
+    <hyperlink ref="I372" display="https://http2.mlstatic.com/D_NQ_NP_2X_870766-MLA111944165952_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_835091-MLA112882459449_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J60" r:id="rId60"/>
     <hyperlink ref="I60" display="https://http2.mlstatic.com/D_NQ_NP_2X_650019-MLA112598239078_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_694102-MLA111420836191_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_960139-MLA111232526403_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I365" r:id="rId65"/>
+    <hyperlink ref="I364" r:id="rId61"/>
     <hyperlink ref="I225" display="https://http2.mlstatic.com/D_NQ_NP_2X_761866-MLA76203783381_052024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_967910-MLA76082310461_042024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_699850-MLA76082339489_042024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J32" r:id="rId66"/>
+    <hyperlink ref="J32" r:id="rId62"/>
     <hyperlink ref="I32" display="https://http2.mlstatic.com/D_NQ_NP_2X_937988-MLA100214376229_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_839463-MLA100214244569_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_878239-MLA100214347283_122025-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I101" display="https://http2.mlstatic.com/D_NQ_NP_2X_853469-MLA73479850047_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_636371-MLA72966055893_112023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_647337-MLA74448293715_022024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I374" display="https://http2.mlstatic.com/D_NQ_NP_2X_838661-MLA114043475512_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_997422-MLA111845686244_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_946430-MLA112856485647_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I373" display="https://http2.mlstatic.com/D_NQ_NP_2X_838661-MLA114043475512_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_997422-MLA111845686244_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_946430-MLA112856485647_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I146" display="https://http2.mlstatic.com/D_NQ_NP_2X_700050-MLA90330537717_082025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_810830-MLA92985348779_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_611435-MLA103169335415_122025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="J341" r:id="rId67"/>
+    <hyperlink ref="J341" r:id="rId63"/>
     <hyperlink ref="I341" display="https://http2.mlstatic.com/D_NQ_NP_2X_972461-MLA108765590667_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_959062-MLA111287287492_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_702439-MLA108999676116_032026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I244" display="https://http2.mlstatic.com/D_NQ_NP_2X_772336-MLA83215360667_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_641687-MLA82926894938_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_686941-MLA80851161221_112024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J364" r:id="rId68"/>
-    <hyperlink ref="I364" display="https://http2.mlstatic.com/D_NQ_NP_2X_918751-MLA113089268495_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_972829-MLA114388137831_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_739083-MLA113884890489_062026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J357" r:id="rId69"/>
+    <hyperlink ref="J362" r:id="rId64"/>
+    <hyperlink ref="I362" display="https://http2.mlstatic.com/D_NQ_NP_2X_654570-MLA114163554383_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_820669-MLA112176540320_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_827402-MLA113697495744_072026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J357" r:id="rId65"/>
     <hyperlink ref="I357" display="https://http2.mlstatic.com/D_NQ_NP_2X_622982-MLA91998379772_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_918567-MLA93316673763_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_951409-MLA93316693351_092025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I358" r:id="rId70"/>
-    <hyperlink ref="J358" r:id="rId71"/>
-    <hyperlink ref="J169" r:id="rId72"/>
+    <hyperlink ref="I358" r:id="rId66"/>
+    <hyperlink ref="J358" r:id="rId67"/>
+    <hyperlink ref="J169" r:id="rId68"/>
     <hyperlink ref="I169" display="https://http2.mlstatic.com/D_NQ_NP_2X_630634-MLA83929492736_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_826427-MLA83875691856_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_778506-MLA83875632066_042025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I286" display="https://http2.mlstatic.com/D_NQ_NP_2X_601798-MLA74779553000_032024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_784677-MLA71729912500_092023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_982997-MLA73375012815_122023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J361" r:id="rId73"/>
-    <hyperlink ref="I361" display="https://http2.mlstatic.com/D_NQ_NP_2X_743943-MLA113720575198_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_652343-MLA98742656086_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_688496-MLA89833143459_082025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="J56" r:id="rId74"/>
-    <hyperlink ref="I56" r:id="rId75"/>
-    <hyperlink ref="I355" r:id="rId76"/>
-    <hyperlink ref="I356" r:id="rId77"/>
-    <hyperlink ref="I132" r:id="rId78"/>
-    <hyperlink ref="I354" r:id="rId79"/>
-    <hyperlink ref="J354" r:id="rId80"/>
-    <hyperlink ref="I372" display="https://http2.mlstatic.com/D_NQ_NP_2X_730160-MLA112550162587_062026-F.webp;http://http2.mlstatic.com/D_NQ_NP_2X_748872-MLA113290799753_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_824232-MLA112954608093_062026-F.webp;https://http2.mlstatic.com/D_NQ"/>
-    <hyperlink ref="I107" r:id="rId81"/>
+    <hyperlink ref="J56" r:id="rId69"/>
+    <hyperlink ref="I56" r:id="rId70"/>
+    <hyperlink ref="I355" r:id="rId71"/>
+    <hyperlink ref="I356" r:id="rId72"/>
+    <hyperlink ref="I132" r:id="rId73"/>
+    <hyperlink ref="I354" r:id="rId74"/>
+    <hyperlink ref="J354" r:id="rId75"/>
+    <hyperlink ref="I371" display="https://http2.mlstatic.com/D_NQ_NP_2X_730160-MLA112550162587_062026-F.webp;http://http2.mlstatic.com/D_NQ_NP_2X_748872-MLA113290799753_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_824232-MLA112954608093_062026-F.webp;https://http2.mlstatic.com/D_NQ"/>
+    <hyperlink ref="I107" r:id="rId76"/>
     <hyperlink ref="I2" display="https://http2.mlstatic.com/D_NQ_NP_2X_644970-MLA111138624893_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_618974-MLA113557256809_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_849248-MLA111414716285_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I11" r:id="rId82"/>
-    <hyperlink ref="I370" r:id="rId83"/>
-    <hyperlink ref="J370" r:id="rId84"/>
-    <hyperlink ref="E145" r:id="rId85"/>
-    <hyperlink ref="I145" r:id="rId86"/>
-    <hyperlink ref="J180" r:id="rId87"/>
-    <hyperlink ref="I180" r:id="rId88"/>
-    <hyperlink ref="I272" r:id="rId89"/>
-    <hyperlink ref="I259" r:id="rId90"/>
-    <hyperlink ref="I238" r:id="rId91"/>
-    <hyperlink ref="J70" r:id="rId92"/>
-    <hyperlink ref="I70" r:id="rId93"/>
-    <hyperlink ref="J74" r:id="rId94"/>
-    <hyperlink ref="I74" r:id="rId95"/>
-    <hyperlink ref="I267" r:id="rId96"/>
-    <hyperlink ref="E251" r:id="rId97"/>
-    <hyperlink ref="J322" r:id="rId98"/>
-    <hyperlink ref="I322" r:id="rId99"/>
-    <hyperlink ref="J54" r:id="rId100"/>
-    <hyperlink ref="I54" r:id="rId101"/>
-    <hyperlink ref="I353" r:id="rId102"/>
-    <hyperlink ref="I325" r:id="rId103"/>
-    <hyperlink ref="J367" r:id="rId104"/>
-    <hyperlink ref="I367"/>
+    <hyperlink ref="I11" r:id="rId77"/>
+    <hyperlink ref="I369" r:id="rId78"/>
+    <hyperlink ref="J369" r:id="rId79"/>
+    <hyperlink ref="E145" r:id="rId80"/>
+    <hyperlink ref="I145" r:id="rId81"/>
+    <hyperlink ref="J180" r:id="rId82"/>
+    <hyperlink ref="I180" r:id="rId83"/>
+    <hyperlink ref="I272" r:id="rId84"/>
+    <hyperlink ref="I259" r:id="rId85"/>
+    <hyperlink ref="I238" r:id="rId86"/>
+    <hyperlink ref="J70" r:id="rId87"/>
+    <hyperlink ref="I70" r:id="rId88"/>
+    <hyperlink ref="J74" r:id="rId89"/>
+    <hyperlink ref="I74" r:id="rId90"/>
+    <hyperlink ref="I267" r:id="rId91"/>
+    <hyperlink ref="E251" r:id="rId92"/>
+    <hyperlink ref="J322" r:id="rId93"/>
+    <hyperlink ref="I322" r:id="rId94"/>
+    <hyperlink ref="J54" r:id="rId95"/>
+    <hyperlink ref="I54" r:id="rId96"/>
+    <hyperlink ref="I353" r:id="rId97"/>
+    <hyperlink ref="I325" r:id="rId98"/>
+    <hyperlink ref="J366" r:id="rId99"/>
+    <hyperlink ref="I366" display="https://http2.mlstatic.com/D_NQ_NP_2X_967252-MLA112857017004_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_802434-MLA114058497103_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_904877-MLA112857136140_072026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I337" display="https://http2.mlstatic.com/D_NQ_NP_2X_871513-MLA105683275105_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_921467-MLA106225093215_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_768089-MLA111241397693_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I273" r:id="rId105"/>
-    <hyperlink ref="J268" r:id="rId106"/>
+    <hyperlink ref="I273" r:id="rId100"/>
+    <hyperlink ref="J268" r:id="rId101"/>
     <hyperlink ref="I268" display="https://http2.mlstatic.com/D_NQ_NP_2X_723996-MLA101839595031_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648298-MLA100279286785_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_899562-MLA105452243109_012026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I148" r:id="rId107"/>
+    <hyperlink ref="I148" r:id="rId102"/>
     <hyperlink ref="I106" display="https://http2.mlstatic.com/D_NQ_NP_2X_986480-MLA92403239851_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_992851-MLA91999385090_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_790783-MLA94732447073_102025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I185" display="https://http2.mlstatic.com/D_NQ_NP_2X_714527-MLA94159366454_102025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_847366-MLA97737335743_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_618907-MLA100261323194_122025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="I288" r:id="rId108"/>
-    <hyperlink ref="J342" r:id="rId109"/>
-    <hyperlink ref="I342" r:id="rId110"/>
-    <hyperlink ref="J300" r:id="rId111"/>
-    <hyperlink ref="I300" r:id="rId112"/>
+    <hyperlink ref="I288" r:id="rId103"/>
+    <hyperlink ref="J342" r:id="rId104"/>
+    <hyperlink ref="I342" r:id="rId105"/>
+    <hyperlink ref="J300" r:id="rId106"/>
+    <hyperlink ref="I300" r:id="rId107"/>
     <hyperlink ref="I329" display="https://http2.mlstatic.com/D_NQ_NP_2X_886751-MLA110760597980_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_722285-MLA111072136212_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_745568-MLA111456288976_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I149" r:id="rId113"/>
-    <hyperlink ref="I26" r:id="rId114"/>
-    <hyperlink ref="J137" r:id="rId115"/>
-    <hyperlink ref="I137" r:id="rId116"/>
-    <hyperlink ref="I245" r:id="rId117"/>
-    <hyperlink ref="J245" r:id="rId118"/>
-    <hyperlink ref="J197" r:id="rId119"/>
+    <hyperlink ref="I149" r:id="rId108"/>
+    <hyperlink ref="I26" r:id="rId109"/>
+    <hyperlink ref="J137" r:id="rId110"/>
+    <hyperlink ref="I137" r:id="rId111"/>
+    <hyperlink ref="I245" r:id="rId112"/>
+    <hyperlink ref="J245" r:id="rId113"/>
+    <hyperlink ref="J197" r:id="rId114"/>
     <hyperlink ref="I197" display="https://http2.mlstatic.com/D_NQ_NP_2X_882824-MLA78038279945_072024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_628505-MLA80605999965_112024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_605405-MLA79717879214_102024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J108" r:id="rId120"/>
-    <hyperlink ref="I108" r:id="rId121"/>
-    <hyperlink ref="I366" r:id="rId122"/>
+    <hyperlink ref="J108" r:id="rId115"/>
+    <hyperlink ref="I108" r:id="rId116"/>
+    <hyperlink ref="I365" r:id="rId117"/>
     <hyperlink ref="I174" display="https://http2.mlstatic.com/D_NQ_NP_2X_671282-MLA88303913955_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_751626-MLA88304056333_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_928886-MLA111461620111_052026-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="I85" r:id="rId123"/>
-    <hyperlink ref="I212" r:id="rId124"/>
-    <hyperlink ref="J298" r:id="rId125"/>
+    <hyperlink ref="I85" r:id="rId118"/>
+    <hyperlink ref="I212" r:id="rId119"/>
+    <hyperlink ref="J298" r:id="rId120"/>
     <hyperlink ref="I298" display="https://http2.mlstatic.com/D_NQ_NP_2X_700210-MLA112568199673_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_802525-MLA112567847565_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_792468-MLA109485788846_042026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I196" r:id="rId126"/>
-    <hyperlink ref="J271" r:id="rId127"/>
-    <hyperlink ref="I271" r:id="rId128"/>
-    <hyperlink ref="I324" r:id="rId129"/>
-    <hyperlink ref="J376" r:id="rId130"/>
-    <hyperlink ref="I376" r:id="rId131"/>
-    <hyperlink ref="J53" r:id="rId132"/>
-    <hyperlink ref="I53" r:id="rId133"/>
+    <hyperlink ref="I196" r:id="rId121"/>
+    <hyperlink ref="J271" r:id="rId122"/>
+    <hyperlink ref="I271" r:id="rId123"/>
+    <hyperlink ref="I324" r:id="rId124"/>
+    <hyperlink ref="J375" r:id="rId125"/>
+    <hyperlink ref="I375" r:id="rId126"/>
+    <hyperlink ref="J53" r:id="rId127"/>
+    <hyperlink ref="I53" r:id="rId128"/>
     <hyperlink ref="I222" display="https://http2.mlstatic.com/D_NQ_NP_2X_931197-MLA111097282025_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_647752-MLA86304062244_062025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_697099-MLA86808814199_062025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="J116" r:id="rId134"/>
+    <hyperlink ref="J116" r:id="rId129"/>
     <hyperlink ref="I116" display="https://http2.mlstatic.com/D_NQ_NP_2X_745425-MLA103761528641_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_974089-MLA111955152709_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_981681-MLA94488043029_102025-F.webp;https://http2.mlstatic.com/D_NQ"/>
-    <hyperlink ref="J260" r:id="rId135"/>
+    <hyperlink ref="J260" r:id="rId130"/>
     <hyperlink ref="I260" display="https://http2.mlstatic.com/D_NQ_NP_2X_990444-MLA85056951766_052025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_988969-MLA85056892306_052025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_982610-MLA112201389146_062026-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="I75" r:id="rId136"/>
+    <hyperlink ref="I75" r:id="rId131"/>
     <hyperlink ref="I5" display="https://http2.mlstatic.com/D_NQ_NP_2X_694398-MLA79165334679_092024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_601148-MLA79165686217_092024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_993833-MLA78690991305_082024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I301" display="https://http2.mlstatic.com/D_NQ_NP_2X_767186-MLA109412110946_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_863859-MLA110084692769_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_611180-MLA109193207080_042026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J303" r:id="rId137"/>
-    <hyperlink ref="I303" r:id="rId138"/>
+    <hyperlink ref="J303" r:id="rId132"/>
+    <hyperlink ref="I303" r:id="rId133"/>
     <hyperlink ref="I135" display="https://http2.mlstatic.com/D_NQ_NP_2X_839510-MLA85369833245_052025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_984239-MLA85369833247_052025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_909408-MLA85370025445_052025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J48" r:id="rId139"/>
+    <hyperlink ref="J48" r:id="rId134"/>
     <hyperlink ref="I48" display="https://http2.mlstatic.com/D_NQ_NP_2X_615383-MLA106283983813_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637244-MLA106762003457_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_647036-MLA106069021004_022026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I275" r:id="rId140"/>
-    <hyperlink ref="J334" r:id="rId141"/>
+    <hyperlink ref="I275" r:id="rId135"/>
+    <hyperlink ref="J334" r:id="rId136"/>
     <hyperlink ref="I334" display="https://http2.mlstatic.com/D_NQ_NP_2X_694390-MLA103915605591_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_901157-MLA112027651816_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_930408-MLA112027361550_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I296" display="https://http2.mlstatic.com/D_NQ_NP_2X_877410-MLA86700953698_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_621602-MLA110823348827_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_945418-MLA86701516062_072025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="I285" r:id="rId142"/>
+    <hyperlink ref="I285" r:id="rId137"/>
     <hyperlink ref="I3" display="https://http2.mlstatic.com/D_NQ_NP_2X_652387-MLA81262109420_122024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_964100-MLA74205385415_012024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_663926-MLA71594815900_092023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J52" r:id="rId143"/>
+    <hyperlink ref="J52" r:id="rId138"/>
     <hyperlink ref="I52" display="https://http2.mlstatic.com/D_NQ_NP_2X_787566-MLA112208805453_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_610420-MLA108420590498_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_778316-MLA108420330866_032026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I331" display="https://http2.mlstatic.com/D_NQ_NP_2X_811172-MLA108871819192_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_673692-MLA109653928111_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_807085-MLA109742422391_032026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I210" display="https://http2.mlstatic.com/D_NQ_NP_2X_787733-MLA73258839528_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_702415-MLA111282425851_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_934591-MLA108763618671_032026-F.webp;https://http2.mlstatic.com/D_NQ"/>
     <hyperlink ref="I65" display="https://http2.mlstatic.com/D_NQ_NP_2X_822004-MLA83792590685_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_922399-MLA83499949924_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_741644-MLA73913804094_012024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I205" r:id="rId144"/>
-    <hyperlink ref="J332" r:id="rId145"/>
-    <hyperlink ref="I332" r:id="rId146"/>
+    <hyperlink ref="I205" r:id="rId139"/>
+    <hyperlink ref="J332" r:id="rId140"/>
+    <hyperlink ref="I332" r:id="rId141"/>
     <hyperlink ref="I143" display="https://http2.mlstatic.com/D_NQ_NP_2X_951908-MLA106095526036_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_697058-MLA92029170496_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_770689-MLA112170606647_052026-F.webp;https://http2.mlstatic.com/D_NQ"/>
-    <hyperlink ref="J143" r:id="rId147"/>
-    <hyperlink ref="J87" r:id="rId148"/>
-    <hyperlink ref="I87" r:id="rId149"/>
-    <hyperlink ref="J366" r:id="rId150"/>
-    <hyperlink ref="J235" r:id="rId151"/>
+    <hyperlink ref="J143" r:id="rId142"/>
+    <hyperlink ref="J87" r:id="rId143"/>
+    <hyperlink ref="I87" r:id="rId144"/>
+    <hyperlink ref="J365" r:id="rId145"/>
+    <hyperlink ref="J235" r:id="rId146"/>
     <hyperlink ref="I235" display="https://http2.mlstatic.com/D_NQ_NP_2X_786831-MLA112508605409_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_945451-MLA106951088919_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_942407-MLA79868078780_102024-F.webp;https://http2.mlstatic.com/D_NQ"/>
-    <hyperlink ref="J25" r:id="rId152"/>
-    <hyperlink ref="I156" r:id="rId153"/>
-    <hyperlink ref="J363" r:id="rId154"/>
-    <hyperlink ref="I363" display="https://http2.mlstatic.com/D_NQ_NP_2X_654570-MLA114163554383_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_820669-MLA112176540320_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_827402-MLA113697495744_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J283" r:id="rId155"/>
-    <hyperlink ref="I283" r:id="rId156"/>
-    <hyperlink ref="I147" r:id="rId157"/>
-    <hyperlink ref="J167" r:id="rId158"/>
+    <hyperlink ref="J25" r:id="rId147"/>
+    <hyperlink ref="I156" r:id="rId148"/>
+    <hyperlink ref="J283" r:id="rId149"/>
+    <hyperlink ref="I283" r:id="rId150"/>
+    <hyperlink ref="I147" r:id="rId151"/>
+    <hyperlink ref="J167" r:id="rId152"/>
     <hyperlink ref="I167" display="https://http2.mlstatic.com/D_NQ_NP_2X_949414-MLA115597206229_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_781530-MLA115596590455_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_794977-MLA113865153424_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I242" r:id="rId159"/>
-    <hyperlink ref="I336" r:id="rId160"/>
-    <hyperlink ref="J371" r:id="rId161"/>
-    <hyperlink ref="I371" r:id="rId162"/>
+    <hyperlink ref="I242" r:id="rId153"/>
+    <hyperlink ref="I336" r:id="rId154"/>
+    <hyperlink ref="J370" r:id="rId155"/>
+    <hyperlink ref="I370" r:id="rId156"/>
     <hyperlink ref="I113" display="https://http2.mlstatic.com/D_NQ_NP_2X_602967-MLA106207657120_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_937184-MLA99857184303_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_615655-MLA93805615686_102025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="J113" r:id="rId163"/>
+    <hyperlink ref="J113" r:id="rId157"/>
     <hyperlink ref="I274" display="https://http2.mlstatic.com/D_NQ_NP_2X_811367-MLA96964641173_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_724534-MLA95972455447_102025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_862711-MLA94582890276_102025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I188" r:id="rId164"/>
-    <hyperlink ref="I369" r:id="rId165"/>
+    <hyperlink ref="I188" r:id="rId158"/>
+    <hyperlink ref="I368" r:id="rId159"/>
     <hyperlink ref="I112" display="https://http2.mlstatic.com/D_NQ_NP_2X_832809-MLA100859657141_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_651615-MLA104572148023_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_683702-MLA104248384382_012026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I321" r:id="rId166"/>
-    <hyperlink ref="J360" r:id="rId167"/>
+    <hyperlink ref="I321" r:id="rId160"/>
+    <hyperlink ref="J360" r:id="rId161"/>
     <hyperlink ref="I360" display="https://http2.mlstatic.com/D_NQ_NP_2X_986254-MLA113898749317_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_998498-MLA115220256263_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_611119-MLA113912677208_072026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I297" display="https://http2.mlstatic.com/D_NQ_NP_2X_672294-MLA110281902509_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_995715-MLA110918042491_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_936537-MLA110364709430_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J297" r:id="rId168"/>
-    <hyperlink ref="J326" r:id="rId169"/>
+    <hyperlink ref="J297" r:id="rId162"/>
+    <hyperlink ref="J326" r:id="rId163"/>
     <hyperlink ref="I326" display="https://http2.mlstatic.com/D_NQ_NP_2X_623123-MLA111040290746_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_934760-MLA111878498611_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_790070-MLA112661729675_062026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J338" r:id="rId170"/>
+    <hyperlink ref="J338" r:id="rId164"/>
     <hyperlink ref="I338" display="https://http2.mlstatic.com/D_NQ_NP_2X_637815-MLA110916194519_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_643077-MLA110749031212_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_708016-MLA112321199072_062026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I320" r:id="rId171"/>
-    <hyperlink ref="I122" r:id="rId172"/>
-    <hyperlink ref="J55" r:id="rId173"/>
+    <hyperlink ref="I320" r:id="rId165"/>
+    <hyperlink ref="I122" r:id="rId166"/>
+    <hyperlink ref="J55" r:id="rId167"/>
     <hyperlink ref="I55" display="https://http2.mlstatic.com/D_NQ_NP_2X_707272-MLA81406001662_122024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_992452-MLA71699440818_092023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_616985-MLA84032409756_052025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J293" r:id="rId174"/>
+    <hyperlink ref="J293" r:id="rId168"/>
     <hyperlink ref="I293" display="https://http2.mlstatic.com/D_NQ_NP_2X_699847-MLA83204192108_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_847455-MLA79932861627_102024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_823994-MLA70105011582_062023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J247" r:id="rId175"/>
+    <hyperlink ref="J247" r:id="rId169"/>
     <hyperlink ref="I247" display="https://http2.mlstatic.com/D_NQ_NP_2X_896395-MLA74651133358_022024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_757231-MLA73307952803_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_773664-MLA113844190574_072026-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="I269" r:id="rId176"/>
-    <hyperlink ref="J214" r:id="rId177"/>
+    <hyperlink ref="I269" r:id="rId170"/>
+    <hyperlink ref="J214" r:id="rId171"/>
     <hyperlink ref="I214" display="https://http2.mlstatic.com/D_NQ_NP_2X_857704-MLA105910693631_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_785878-MLA115684445439_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_732723-MLA114610870605_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I124" r:id="rId178"/>
+    <hyperlink ref="I124" r:id="rId172"/>
     <hyperlink ref="I139" display="https://http2.mlstatic.com/D_NQ_NP_2X_731885-MLA81735782871_012025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_877502-MLA81736505623_012025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_739624-MLA81735782869_012025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I151" display="https://http2.mlstatic.com/D_NQ_NP_2X_852777-MLA73231184100_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_953229-MLA74068746840_012024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_727505-MLA74823139724_032024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I163" r:id="rId179"/>
-    <hyperlink ref="J163" r:id="rId180"/>
-    <hyperlink ref="F111" r:id="rId181" location="reviews"/>
-    <hyperlink ref="I111" r:id="rId182"/>
-    <hyperlink ref="I323" r:id="rId183"/>
-    <hyperlink ref="I327" r:id="rId184"/>
+    <hyperlink ref="I163" r:id="rId173"/>
+    <hyperlink ref="J163" r:id="rId174"/>
+    <hyperlink ref="F111" r:id="rId175" location="reviews"/>
+    <hyperlink ref="I111" r:id="rId176"/>
+    <hyperlink ref="I323" r:id="rId177"/>
+    <hyperlink ref="I327" r:id="rId178"/>
     <hyperlink ref="I102" display="https://http2.mlstatic.com/D_NQ_NP_2X_701490-MLA108653774761_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_910611-MLA87584829978_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_761367-MLA87718920709_072025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="E359" r:id="rId185"/>
-    <hyperlink ref="F359" r:id="rId186"/>
+    <hyperlink ref="E359" r:id="rId179"/>
+    <hyperlink ref="F359" r:id="rId180"/>
     <hyperlink ref="I359" display="https://http2.mlstatic.com/D_NQ_NP_2X_957897-MLA114152946760_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_988648-MLA114781488773_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_938364-MLA113693419924_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J359" r:id="rId187"/>
-    <hyperlink ref="E231" r:id="rId188"/>
-    <hyperlink ref="I231" r:id="rId189"/>
-    <hyperlink ref="I278" r:id="rId190"/>
-    <hyperlink ref="F29" r:id="rId191"/>
-    <hyperlink ref="I333"/>
-    <hyperlink ref="J333" r:id="rId192"/>
-    <hyperlink ref="J279" r:id="rId193"/>
-    <hyperlink ref="I279"/>
-    <hyperlink ref="I162" r:id="rId194"/>
-    <hyperlink ref="J162" r:id="rId195"/>
-    <hyperlink ref="I141" r:id="rId196"/>
-    <hyperlink ref="J142" r:id="rId197"/>
-    <hyperlink ref="I142"/>
-    <hyperlink ref="J86" r:id="rId198"/>
-    <hyperlink ref="I86"/>
-    <hyperlink ref="F86" r:id="rId199"/>
-    <hyperlink ref="J296" r:id="rId200"/>
+    <hyperlink ref="J359" r:id="rId181"/>
+    <hyperlink ref="E231" r:id="rId182"/>
+    <hyperlink ref="I231" r:id="rId183"/>
+    <hyperlink ref="I278" r:id="rId184"/>
+    <hyperlink ref="F29" r:id="rId185"/>
+    <hyperlink ref="I333" display="https://http2.mlstatic.com/D_NQ_NP_2X_661292-MLA98293086467_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_907390-MLA106707175024_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_876338-MLA108047534008_032026-F.webp;https://http2.mlstatic.com/D_NQ"/>
+    <hyperlink ref="J333" r:id="rId186"/>
+    <hyperlink ref="J279" r:id="rId187"/>
+    <hyperlink ref="I279" display="https://http2.mlstatic.com/D_NQ_NP_2X_609731-MLA83282009211_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_965155-MLA83841127402_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_758965-MLA85304541601_052025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="I162" r:id="rId188"/>
+    <hyperlink ref="J162" r:id="rId189"/>
+    <hyperlink ref="I141" r:id="rId190"/>
+    <hyperlink ref="J142" r:id="rId191"/>
+    <hyperlink ref="I142" display="https://http2.mlstatic.com/D_NQ_NP_2X_863418-MLA109994960812_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_927650-MLA105811665406_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_743624-MLA105810281830_022026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J86" r:id="rId192"/>
+    <hyperlink ref="I86" display="https://http2.mlstatic.com/D_NQ_NP_2X_929447-MLA114868215933_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_688697-MLA113791320300_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_631693-MLA113790881904_072026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="F86" r:id="rId193"/>
+    <hyperlink ref="J296" r:id="rId194"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId201"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId195"/>
   <tableParts count="1">
-    <tablePart r:id="rId202"/>
+    <tablePart r:id="rId196"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="1596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2412" uniqueCount="1591">
   <si>
     <t>Nombre</t>
   </si>
@@ -3603,20 +3603,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Transmisor Y Receptor Auxiliar Bluetooth 5.3 Laptop Y Coche C25 Plug C25 Negro , Adaptado Inalámbric Estéreo, Audi Alta Calidad, Conexió 3.5mm
-</t>
-  </si>
-  <si>
     <t>https://www.mercadolibre.com.mx/adaptador-bluetooth-auto-llamadas-y-musica-para-movil/up/MLMU3814435585</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_987611-MLM107926464043_032026-F.webp</t>
-  </si>
-  <si>
-    <t>https://www.mercadolibre.com.mx/naiwant-transmisor-y-receptor-auxiliar-bluetooth-53-laptop-y-coche-c25-plug-c25-negro-adaptado-inalambric-estereo-audi-alta-calidad-conexio-35mm/p/MLM65201623?pdp_filters=item_id:MLM2843434933#&amp;gid=1&amp;pid=1</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_983873-MLA109780349159_032026-F.webp</t>
   </si>
   <si>
     <t xml:space="preserve">Gafas De Sol Polarizadas Con Montura Cuadrada Para Hombre
@@ -4532,12 +4522,6 @@
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_841625-MLA90322371395_082025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_931928-MLA90286123036_082025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_613327-MLA90322341537_082025-F.webp</t>
-  </si>
-  <si>
-    <t>https://video-static-clips.mms.mlstatic.com/62c82f1f923a3f082b72612d/019e8b58f7327dada9733a33bdb6d5be/packaging/static/master.m3u8</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_694390-MLA103915605591_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_901157-MLA112027651816_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_930408-MLA112027361550_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648399-MLA112027885812_062026-F.webp</t>
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_877410-MLA86700953698_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_621602-MLA110823348827_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_945418-MLA86701516062_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_924886-MLA109781041828_042026-F.webp</t>
@@ -4990,8 +4974,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J376" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J376"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J375" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J375"/>
   <sortState ref="A2:H342">
     <sortCondition ref="A1:A342"/>
   </sortState>
@@ -5296,7 +5280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J376"/>
+  <dimension ref="A1:J375"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" style="1" customWidth="1"/>
@@ -5336,10 +5320,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -5362,13 +5346,13 @@
         <v>1017</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="J2" s="12"/>
     </row>
@@ -5398,7 +5382,7 @@
         <v>66</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -5450,7 +5434,7 @@
         <v>510</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -5559,7 +5543,7 @@
         <v>834</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="C10" s="7">
         <v>300</v>
@@ -5606,7 +5590,7 @@
         <v>66</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
@@ -5946,7 +5930,7 @@
         <v>511</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
@@ -5975,7 +5959,7 @@
         <v>99</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
@@ -6044,7 +6028,7 @@
         <v>114</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>912</v>
@@ -6131,10 +6115,10 @@
         <v>99</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
@@ -6238,15 +6222,15 @@
         <v>66</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="C37" s="7">
         <v>300</v>
@@ -6261,7 +6245,7 @@
         <v>390</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>66</v>
@@ -6526,10 +6510,10 @@
         <v>512</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="J48" s="12" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
@@ -6633,10 +6617,10 @@
         <v>12</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
@@ -6665,10 +6649,10 @@
         <v>12</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
@@ -6697,10 +6681,10 @@
         <v>12</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
@@ -6708,7 +6692,7 @@
         <v>207</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="C55" s="7">
         <v>652</v>
@@ -6729,10 +6713,10 @@
         <v>12</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
@@ -6761,10 +6745,10 @@
         <v>12</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
@@ -6787,7 +6771,7 @@
         <v>869</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>66</v>
@@ -6853,7 +6837,7 @@
         <v>1000</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F60" s="12" t="s">
         <v>1028</v>
@@ -6865,10 +6849,10 @@
         <v>12</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
@@ -6998,7 +6982,7 @@
         <v>512</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -7027,10 +7011,10 @@
         <v>99</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -7059,7 +7043,7 @@
         <v>99</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
@@ -7134,10 +7118,10 @@
         <v>197</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
@@ -7192,7 +7176,7 @@
         <v>66</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
@@ -7241,10 +7225,10 @@
         <v>12</v>
       </c>
       <c r="I74" s="12" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
@@ -7273,7 +7257,7 @@
         <v>405</v>
       </c>
       <c r="I75" s="12" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.35">
@@ -7524,7 +7508,7 @@
         <v>99</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
@@ -7541,7 +7525,7 @@
         <v>579</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="G86" s="7" t="s">
         <v>990</v>
@@ -7550,15 +7534,15 @@
         <v>510</v>
       </c>
       <c r="I86" s="12" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>667</v>
@@ -7582,10 +7566,10 @@
         <v>66</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
@@ -7943,7 +7927,7 @@
         <v>66</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.35">
@@ -7969,7 +7953,7 @@
         <v>197</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
@@ -8076,7 +8060,7 @@
         <v>12</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
@@ -8105,7 +8089,7 @@
         <v>12</v>
       </c>
       <c r="I107" s="12" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.35">
@@ -8134,10 +8118,10 @@
         <v>511</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.35">
@@ -8200,7 +8184,7 @@
         <v>491</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="G111" s="7" t="s">
         <v>879</v>
@@ -8209,7 +8193,7 @@
         <v>510</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.35">
@@ -8235,7 +8219,7 @@
         <v>66</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.35">
@@ -8264,10 +8248,10 @@
         <v>66</v>
       </c>
       <c r="I113" s="12" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
       <c r="J113" s="12" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.35">
@@ -8348,10 +8332,10 @@
         <v>66</v>
       </c>
       <c r="I116" s="12" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="J116" s="12" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.35">
@@ -8507,7 +8491,7 @@
         <v>12</v>
       </c>
       <c r="I122" s="12" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.35">
@@ -8556,7 +8540,7 @@
         <v>510</v>
       </c>
       <c r="I124" s="12" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -8732,7 +8716,7 @@
         <v>510</v>
       </c>
       <c r="I131" s="12" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.35">
@@ -8761,7 +8745,7 @@
         <v>511</v>
       </c>
       <c r="I132" s="12" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="58" x14ac:dyDescent="0.35">
@@ -8836,7 +8820,7 @@
         <v>510</v>
       </c>
       <c r="I135" s="12" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.35">
@@ -8867,7 +8851,7 @@
     </row>
     <row r="137" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>1032</v>
@@ -8891,10 +8875,10 @@
         <v>66</v>
       </c>
       <c r="I137" s="12" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="J137" s="12" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.35">
@@ -8943,7 +8927,7 @@
         <v>510</v>
       </c>
       <c r="I139" s="12" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.35">
@@ -8992,7 +8976,7 @@
         <v>197</v>
       </c>
       <c r="I141" s="12" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.35">
@@ -9018,10 +9002,10 @@
         <v>197</v>
       </c>
       <c r="I142" s="12" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="J142" s="12" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.35">
@@ -9047,10 +9031,10 @@
         <v>197</v>
       </c>
       <c r="I143" s="12" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="J143" s="12" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.35">
@@ -9090,7 +9074,7 @@
         <v>250</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="F145" s="7" t="s">
         <v>98</v>
@@ -9102,7 +9086,7 @@
         <v>510</v>
       </c>
       <c r="I145" s="12" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.35">
@@ -9131,7 +9115,7 @@
         <v>511</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.35">
@@ -9160,7 +9144,7 @@
         <v>511</v>
       </c>
       <c r="I147" s="12" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.35">
@@ -9189,7 +9173,7 @@
         <v>511</v>
       </c>
       <c r="I148" s="12" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.35">
@@ -9218,7 +9202,7 @@
         <v>510</v>
       </c>
       <c r="I149" s="12" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.35">
@@ -9273,7 +9257,7 @@
         <v>510</v>
       </c>
       <c r="I151" s="12" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.35">
@@ -9290,7 +9274,7 @@
         <v>150</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="F152" s="7" t="s">
         <v>593</v>
@@ -9374,7 +9358,7 @@
         <v>462</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H155" s="7" t="s">
         <v>66</v>
@@ -9403,7 +9387,7 @@
         <v>511</v>
       </c>
       <c r="I156" s="12" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="29" x14ac:dyDescent="0.35">
@@ -9550,10 +9534,10 @@
         <v>510</v>
       </c>
       <c r="I162" s="12" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="J162" s="12" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.35">
@@ -9579,10 +9563,10 @@
         <v>510</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="J163" s="12" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.35">
@@ -9680,10 +9664,10 @@
         <v>511</v>
       </c>
       <c r="I167" s="12" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="J167" s="12" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.35">
@@ -9738,10 +9722,10 @@
         <v>511</v>
       </c>
       <c r="I169" s="12" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="J169" s="12" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.35">
@@ -9865,7 +9849,7 @@
         <v>511</v>
       </c>
       <c r="I174" s="12" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
@@ -10015,10 +9999,10 @@
         <v>66</v>
       </c>
       <c r="I180" s="12" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="J180" s="12" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -10145,7 +10129,7 @@
         <v>99</v>
       </c>
       <c r="I185" s="12" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.35">
@@ -10223,7 +10207,7 @@
         <v>66</v>
       </c>
       <c r="I188" s="12" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.35">
@@ -10278,7 +10262,7 @@
         <v>99</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -10422,7 +10406,7 @@
         <v>66</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.35">
@@ -10451,10 +10435,10 @@
         <v>12</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="J197" s="12" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="198" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -10662,7 +10646,7 @@
         <v>12</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.35">
@@ -10789,7 +10773,7 @@
         <v>511</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.35">
@@ -10844,7 +10828,7 @@
         <v>12</v>
       </c>
       <c r="I212" s="12" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.35">
@@ -10896,10 +10880,10 @@
         <v>510</v>
       </c>
       <c r="I214" s="12" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="J214" s="12" t="s">
-        <v>1557</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="215" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -11110,7 +11094,7 @@
         <v>511</v>
       </c>
       <c r="I222" s="12" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.35">
@@ -11188,7 +11172,7 @@
         <v>99</v>
       </c>
       <c r="I225" s="12" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.35">
@@ -11271,7 +11255,7 @@
     </row>
     <row r="229" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>799</v>
@@ -11335,7 +11319,7 @@
         <v>440</v>
       </c>
       <c r="E231" s="12" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="F231" s="7" t="s">
         <v>997</v>
@@ -11347,7 +11331,7 @@
         <v>653</v>
       </c>
       <c r="I231" s="12" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.35">
@@ -11454,10 +11438,10 @@
         <v>511</v>
       </c>
       <c r="I235" s="12" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="J235" s="12" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.35">
@@ -11532,7 +11516,7 @@
         <v>99</v>
       </c>
       <c r="I238" s="12" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.35">
@@ -11630,7 +11614,7 @@
         <v>66</v>
       </c>
       <c r="I242" s="12" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.35">
@@ -11685,7 +11669,7 @@
         <v>99</v>
       </c>
       <c r="I244" s="12" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.35">
@@ -11714,10 +11698,10 @@
         <v>99</v>
       </c>
       <c r="I245" s="12" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="J245" s="12" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.35">
@@ -11772,10 +11756,10 @@
         <v>12</v>
       </c>
       <c r="I247" s="12" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="J247" s="12" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.35">
@@ -11841,7 +11825,7 @@
         <v>1300</v>
       </c>
       <c r="E250" s="12" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="F250" s="7" t="s">
         <v>436</v>
@@ -11853,10 +11837,10 @@
         <v>197</v>
       </c>
       <c r="I250" s="12" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="J250" s="12" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.35">
@@ -11922,7 +11906,7 @@
         <v>600</v>
       </c>
       <c r="E253" s="12" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="G253" s="7" t="s">
         <v>289</v>
@@ -11959,7 +11943,7 @@
         <v>729</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="C255" s="7">
         <v>200</v>
@@ -12084,7 +12068,7 @@
         <v>99</v>
       </c>
       <c r="I259" s="12" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.35">
@@ -12113,10 +12097,10 @@
         <v>66</v>
       </c>
       <c r="I260" s="12" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="J260" s="12" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.35">
@@ -12147,7 +12131,7 @@
     </row>
     <row r="262" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>946</v>
@@ -12240,7 +12224,7 @@
         <v>99</v>
       </c>
       <c r="I265" s="12" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.35">
@@ -12295,7 +12279,7 @@
         <v>99</v>
       </c>
       <c r="I267" s="12" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.35">
@@ -12324,10 +12308,10 @@
         <v>99</v>
       </c>
       <c r="I268" s="12" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="J268" s="12" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.35">
@@ -12356,7 +12340,7 @@
         <v>12</v>
       </c>
       <c r="I269" s="12" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.35">
@@ -12373,7 +12357,7 @@
         <v>380</v>
       </c>
       <c r="E270" s="7" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="F270" s="7" t="s">
         <v>444</v>
@@ -12390,7 +12374,7 @@
         <v>204</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="C271" s="7">
         <v>503</v>
@@ -12411,10 +12395,10 @@
         <v>12</v>
       </c>
       <c r="I271" s="12" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="J271" s="12" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.35">
@@ -12422,7 +12406,7 @@
         <v>210</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="C272" s="7">
         <v>570</v>
@@ -12443,7 +12427,7 @@
         <v>12</v>
       </c>
       <c r="I272" s="12" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.35">
@@ -12466,13 +12450,13 @@
         <v>1035</v>
       </c>
       <c r="G273" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H273" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I273" s="12" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.35">
@@ -12495,13 +12479,13 @@
         <v>354</v>
       </c>
       <c r="G274" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H274" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I274" s="12" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.35">
@@ -12524,13 +12508,13 @@
         <v>357</v>
       </c>
       <c r="G275" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H275" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I275" s="12" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.35">
@@ -12611,7 +12595,7 @@
         <v>99</v>
       </c>
       <c r="I278" s="12" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.35">
@@ -12640,10 +12624,10 @@
         <v>99</v>
       </c>
       <c r="I279" s="12" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="J279" s="12" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.35">
@@ -12747,10 +12731,10 @@
         <v>511</v>
       </c>
       <c r="I283" s="12" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="J283" s="12" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.35">
@@ -12803,7 +12787,7 @@
         <v>197</v>
       </c>
       <c r="I285" s="12" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="286" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -12832,7 +12816,7 @@
         <v>66</v>
       </c>
       <c r="I286" s="12" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="287" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -12887,7 +12871,7 @@
         <v>197</v>
       </c>
       <c r="I288" s="12" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.35">
@@ -13011,15 +12995,15 @@
         <v>12</v>
       </c>
       <c r="I293" s="12" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
       <c r="J293" s="12" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="294" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>1085</v>
@@ -13095,10 +13079,10 @@
         <v>99</v>
       </c>
       <c r="I296" s="12" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="J296" s="12" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.35">
@@ -13121,16 +13105,16 @@
         <v>1058</v>
       </c>
       <c r="G297" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H297" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I297" s="12" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="J297" s="12" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.35">
@@ -13159,10 +13143,10 @@
         <v>66</v>
       </c>
       <c r="I298" s="12" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="J298" s="12" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.35">
@@ -13191,10 +13175,10 @@
         <v>512</v>
       </c>
       <c r="I299" s="12" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="J299" s="12" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.35">
@@ -13223,10 +13207,10 @@
         <v>510</v>
       </c>
       <c r="I300" s="12" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="J300" s="12" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="301" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -13255,7 +13239,7 @@
         <v>510</v>
       </c>
       <c r="I301" s="12" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.35">
@@ -13310,10 +13294,10 @@
         <v>12</v>
       </c>
       <c r="I303" s="12" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="J303" s="12" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.35">
@@ -13442,7 +13426,7 @@
         <v>1106</v>
       </c>
       <c r="G309" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H309" s="7" t="s">
         <v>66</v>
@@ -13470,7 +13454,7 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>1114</v>
@@ -13560,7 +13544,7 @@
         <v>1124</v>
       </c>
       <c r="G314" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H314" s="7" t="s">
         <v>66</v>
@@ -13609,7 +13593,7 @@
         <v>1132</v>
       </c>
       <c r="G316" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H316" s="7" t="s">
         <v>66</v>
@@ -13637,7 +13621,7 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="B318" s="1" t="s">
         <v>1139</v>
@@ -13683,7 +13667,7 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>1146</v>
@@ -13707,7 +13691,7 @@
         <v>12</v>
       </c>
       <c r="I320" s="12" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.35">
@@ -13736,7 +13720,7 @@
         <v>66</v>
       </c>
       <c r="I321" s="12" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.35">
@@ -13744,7 +13728,7 @@
         <v>1153</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="C322" s="7">
         <v>269</v>
@@ -13765,10 +13749,10 @@
         <v>66</v>
       </c>
       <c r="I322" s="12" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="J322" s="12" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="323" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -13797,7 +13781,7 @@
         <v>99</v>
       </c>
       <c r="I323" s="12" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.35">
@@ -13823,7 +13807,7 @@
         <v>512</v>
       </c>
       <c r="I324" s="12" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="325" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -13852,7 +13836,7 @@
         <v>66</v>
       </c>
       <c r="I325" s="12" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.35">
@@ -13881,10 +13865,10 @@
         <v>12</v>
       </c>
       <c r="I326" s="12" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="J326" s="12" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.35">
@@ -13901,7 +13885,7 @@
         <v>200</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="F327" s="7" t="s">
         <v>1170</v>
@@ -13910,7 +13894,7 @@
         <v>99</v>
       </c>
       <c r="I327" s="12" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.35">
@@ -13927,7 +13911,7 @@
         <v>1700</v>
       </c>
       <c r="E328" s="12" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="F328" s="7" t="s">
         <v>1172</v>
@@ -13936,7 +13920,7 @@
         <v>510</v>
       </c>
       <c r="I328" s="12" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.35">
@@ -13959,7 +13943,7 @@
         <v>66</v>
       </c>
       <c r="I329" s="12" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="330" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
@@ -13985,7 +13969,7 @@
         <v>99</v>
       </c>
       <c r="I330" s="12" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.35">
@@ -14008,13 +13992,13 @@
         <v>1185</v>
       </c>
       <c r="G331" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H331" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I331" s="12" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="332" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -14043,10 +14027,10 @@
         <v>510</v>
       </c>
       <c r="I332" s="12" t="s">
-        <v>1511</v>
+        <v>1506</v>
       </c>
       <c r="J332" s="12" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="333" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -14063,33 +14047,33 @@
         <v>130</v>
       </c>
       <c r="E333" s="7" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="F333" s="7" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="H333" s="7" t="s">
         <v>99</v>
       </c>
       <c r="I333" s="12" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="J333" s="12" t="s">
-        <v>1583</v>
-      </c>
-    </row>
-    <row r="334" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>18</v>
+        <v>1197</v>
       </c>
       <c r="C334" s="7">
-        <v>269</v>
+        <v>729</v>
       </c>
       <c r="D334" s="7">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="E334" s="7" t="s">
         <v>1196</v>
@@ -14098,27 +14082,21 @@
         <v>1195</v>
       </c>
       <c r="H334" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I334" s="12" t="s">
-        <v>1500</v>
-      </c>
-      <c r="J334" s="12" t="s">
-        <v>1499</v>
-      </c>
-    </row>
-    <row r="335" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C335" s="7">
-        <v>729</v>
+        <v>1299</v>
       </c>
       <c r="D335" s="7">
-        <v>350</v>
+        <v>650</v>
       </c>
       <c r="E335" s="7" t="s">
         <v>1199</v>
@@ -14127,47 +14105,50 @@
         <v>1198</v>
       </c>
       <c r="H335" s="7" t="s">
-        <v>197</v>
+        <v>66</v>
+      </c>
+      <c r="I335" s="12" t="s">
+        <v>1525</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B336" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="B336" s="1" t="s">
+      <c r="C336" s="7">
+        <v>350</v>
+      </c>
+      <c r="D336" s="7">
+        <v>200</v>
+      </c>
+      <c r="E336" s="7" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F336" s="7" t="s">
         <v>1204</v>
-      </c>
-      <c r="C336" s="7">
-        <v>1299</v>
-      </c>
-      <c r="D336" s="7">
-        <v>650</v>
-      </c>
-      <c r="E336" s="7" t="s">
-        <v>1202</v>
-      </c>
-      <c r="F336" s="7" t="s">
-        <v>1201</v>
       </c>
       <c r="H336" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I336" s="12" t="s">
-        <v>1530</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B337" s="1" t="s">
         <v>1206</v>
       </c>
+      <c r="B337" s="1">
+        <v>126</v>
+      </c>
       <c r="C337" s="7">
-        <v>350</v>
+        <v>247</v>
       </c>
       <c r="D337" s="7">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E337" s="7" t="s">
         <v>1208</v>
@@ -14175,80 +14156,77 @@
       <c r="F337" s="7" t="s">
         <v>1207</v>
       </c>
+      <c r="G337" s="7" t="s">
+        <v>917</v>
+      </c>
       <c r="H337" s="7" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="I337" s="12" t="s">
-        <v>1448</v>
+        <v>1542</v>
+      </c>
+      <c r="J337" s="12" t="s">
+        <v>1541</v>
       </c>
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C338" s="7">
+        <v>150</v>
+      </c>
+      <c r="D338" s="7">
+        <v>100</v>
+      </c>
+      <c r="E338" s="7" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F338" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="B338" s="1">
-        <v>126</v>
-      </c>
-      <c r="C338" s="7">
-        <v>247</v>
-      </c>
-      <c r="D338" s="7">
-        <v>120</v>
-      </c>
-      <c r="E338" s="7" t="s">
-        <v>1211</v>
-      </c>
-      <c r="F338" s="7" t="s">
-        <v>1210</v>
-      </c>
-      <c r="G338" s="7" t="s">
-        <v>917</v>
-      </c>
       <c r="H338" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I338" s="12" t="s">
-        <v>1547</v>
-      </c>
-      <c r="J338" s="12" t="s">
-        <v>1546</v>
-      </c>
-    </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="B339" s="1" t="s">
+      <c r="C339" s="7">
+        <v>349</v>
+      </c>
+      <c r="D339" s="7">
+        <v>200</v>
+      </c>
+      <c r="E339" s="7" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F339" s="7" t="s">
         <v>1215</v>
-      </c>
-      <c r="C339" s="7">
-        <v>150</v>
-      </c>
-      <c r="D339" s="7">
-        <v>100</v>
-      </c>
-      <c r="E339" s="7" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F339" s="7" t="s">
-        <v>1212</v>
       </c>
       <c r="H339" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="340" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="C340" s="7">
-        <v>349</v>
+        <v>800</v>
       </c>
       <c r="D340" s="7">
-        <v>200</v>
+        <v>750</v>
       </c>
       <c r="E340" s="7" t="s">
         <v>1219</v>
@@ -14257,21 +14235,27 @@
         <v>1218</v>
       </c>
       <c r="H340" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="341" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>510</v>
+      </c>
+      <c r="I340" s="12" t="s">
+        <v>1402</v>
+      </c>
+      <c r="J340" s="12" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C341" s="7">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="D341" s="7">
-        <v>750</v>
+        <v>170</v>
       </c>
       <c r="E341" s="7" t="s">
         <v>1222</v>
@@ -14280,65 +14264,62 @@
         <v>1221</v>
       </c>
       <c r="H341" s="7" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="I341" s="12" t="s">
-        <v>1405</v>
+        <v>1454</v>
       </c>
       <c r="J341" s="12" t="s">
-        <v>1404</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B342" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="B342" s="1" t="s">
+      <c r="C342" s="7">
+        <v>399</v>
+      </c>
+      <c r="D342" s="7">
+        <v>250</v>
+      </c>
+      <c r="E342" s="7" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F342" s="7" t="s">
         <v>1227</v>
       </c>
-      <c r="C342" s="7">
-        <v>200</v>
-      </c>
-      <c r="D342" s="7">
-        <v>170</v>
-      </c>
-      <c r="E342" s="7" t="s">
-        <v>1225</v>
-      </c>
-      <c r="F342" s="7" t="s">
-        <v>1224</v>
+      <c r="G342" s="7" t="s">
+        <v>1272</v>
       </c>
       <c r="H342" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I342" s="12" t="s">
-        <v>1457</v>
-      </c>
-      <c r="J342" s="12" t="s">
-        <v>1456</v>
-      </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="C343" s="7">
         <v>399</v>
       </c>
       <c r="D343" s="7">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E343" s="7" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="F343" s="7" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="G343" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="H343" s="7" t="s">
         <v>66</v>
@@ -14346,28 +14327,28 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
-        <v>1277</v>
+        <v>1239</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>1228</v>
+        <v>1245</v>
       </c>
       <c r="C344" s="7">
-        <v>399</v>
+        <v>170</v>
       </c>
       <c r="D344" s="7">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="E344" s="7" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="F344" s="7" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="G344" s="7" t="s">
-        <v>1275</v>
+        <v>917</v>
       </c>
       <c r="H344" s="7" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.35">
@@ -14375,13 +14356,13 @@
         <v>1242</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C345" s="7">
-        <v>170</v>
+        <v>262</v>
       </c>
       <c r="D345" s="7">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="E345" s="7" t="s">
         <v>1244</v>
@@ -14398,22 +14379,22 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="B346" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C346" s="7">
+        <v>468</v>
+      </c>
+      <c r="D346" s="7">
+        <v>255</v>
+      </c>
+      <c r="E346" s="7" t="s">
         <v>1249</v>
       </c>
-      <c r="C346" s="7">
-        <v>262</v>
-      </c>
-      <c r="D346" s="7">
-        <v>190</v>
-      </c>
-      <c r="E346" s="7" t="s">
-        <v>1247</v>
-      </c>
       <c r="F346" s="7" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="G346" s="7" t="s">
         <v>917</v>
@@ -14427,13 +14408,13 @@
         <v>1250</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>1260</v>
+        <v>9</v>
       </c>
       <c r="C347" s="7">
-        <v>468</v>
+        <v>299</v>
       </c>
       <c r="D347" s="7">
-        <v>255</v>
+        <v>150</v>
       </c>
       <c r="E347" s="7" t="s">
         <v>1252</v>
@@ -14450,22 +14431,22 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>9</v>
+        <v>1256</v>
       </c>
       <c r="C348" s="7">
-        <v>299</v>
+        <v>447</v>
       </c>
       <c r="D348" s="7">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E348" s="7" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="F348" s="7" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="G348" s="7" t="s">
         <v>917</v>
@@ -14474,47 +14455,47 @@
         <v>12</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>1259</v>
+        <v>1283</v>
       </c>
       <c r="C349" s="7">
-        <v>447</v>
-      </c>
-      <c r="D349" s="7">
-        <v>250</v>
-      </c>
-      <c r="E349" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="E349" s="12" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F349" s="7" t="s">
         <v>1261</v>
       </c>
-      <c r="F349" s="7" t="s">
-        <v>1262</v>
-      </c>
-      <c r="G349" s="7" t="s">
-        <v>917</v>
-      </c>
       <c r="H349" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="350" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>1286</v>
+        <v>1269</v>
       </c>
       <c r="C350" s="7">
-        <v>350</v>
-      </c>
-      <c r="E350" s="12" t="s">
-        <v>1285</v>
+        <v>200</v>
+      </c>
+      <c r="D350" s="7">
+        <v>120</v>
+      </c>
+      <c r="E350" s="7" t="s">
+        <v>1271</v>
       </c>
       <c r="F350" s="7" t="s">
-        <v>1264</v>
+        <v>1270</v>
+      </c>
+      <c r="G350" s="7" t="s">
+        <v>419</v>
       </c>
       <c r="H350" s="7" t="s">
         <v>66</v>
@@ -14522,22 +14503,22 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="C351" s="7">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="D351" s="7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E351" s="7" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="F351" s="7" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="G351" s="7" t="s">
         <v>419</v>
@@ -14546,50 +14527,53 @@
         <v>66</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
-        <v>1280</v>
+        <v>1287</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>1281</v>
+        <v>1288</v>
       </c>
       <c r="C352" s="7">
-        <v>147</v>
+        <v>899</v>
       </c>
       <c r="D352" s="7">
-        <v>100</v>
-      </c>
-      <c r="E352" s="7" t="s">
-        <v>1283</v>
-      </c>
-      <c r="F352" s="7" t="s">
-        <v>1282</v>
+        <v>485</v>
+      </c>
+      <c r="E352" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F352" s="12" t="s">
+        <v>1289</v>
       </c>
       <c r="G352" s="7" t="s">
-        <v>419</v>
+        <v>859</v>
       </c>
       <c r="H352" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="353" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>511</v>
+      </c>
+      <c r="I352" s="12" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="C353" s="7">
-        <v>899</v>
+        <v>1050</v>
       </c>
       <c r="D353" s="7">
-        <v>485</v>
+        <v>600</v>
       </c>
       <c r="E353" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F353" s="12" t="s">
         <v>1293</v>
-      </c>
-      <c r="F353" s="12" t="s">
-        <v>1292</v>
       </c>
       <c r="G353" s="7" t="s">
         <v>859</v>
@@ -14598,59 +14582,59 @@
         <v>511</v>
       </c>
       <c r="I353" s="12" t="s">
-        <v>1446</v>
+        <v>1418</v>
+      </c>
+      <c r="J353" s="12" t="s">
+        <v>1419</v>
       </c>
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C354" s="7">
-        <v>1050</v>
+        <v>1084</v>
       </c>
       <c r="D354" s="7">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="E354" s="12" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F354" s="12" t="s">
         <v>1297</v>
-      </c>
-      <c r="F354" s="12" t="s">
-        <v>1296</v>
       </c>
       <c r="G354" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H354" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I354" s="12" t="s">
-        <v>1421</v>
-      </c>
-      <c r="J354" s="12" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="C355" s="7">
-        <v>1084</v>
+        <v>1265</v>
       </c>
       <c r="D355" s="7">
         <v>650</v>
       </c>
       <c r="E355" s="12" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="F355" s="12" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="G355" s="7" t="s">
         <v>859</v>
@@ -14659,44 +14643,47 @@
         <v>510</v>
       </c>
       <c r="I355" s="12" t="s">
-        <v>1418</v>
-      </c>
-    </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C356" s="7">
+        <v>1225</v>
+      </c>
+      <c r="D356" s="7">
+        <v>700</v>
+      </c>
+      <c r="E356" s="12" t="s">
         <v>1304</v>
       </c>
-      <c r="B356" s="1" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C356" s="7">
-        <v>1265</v>
-      </c>
-      <c r="D356" s="7">
-        <v>650</v>
-      </c>
-      <c r="E356" s="12" t="s">
+      <c r="F356" s="12" t="s">
         <v>1303</v>
-      </c>
-      <c r="F356" s="12" t="s">
-        <v>1302</v>
       </c>
       <c r="G356" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H356" s="7" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I356" s="12" t="s">
-        <v>1419</v>
-      </c>
-    </row>
-    <row r="357" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>1406</v>
+      </c>
+      <c r="J356" s="12" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="C357" s="7">
         <v>1225</v>
@@ -14705,10 +14692,10 @@
         <v>700</v>
       </c>
       <c r="E357" s="12" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="F357" s="12" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="G357" s="7" t="s">
         <v>859</v>
@@ -14717,62 +14704,62 @@
         <v>511</v>
       </c>
       <c r="I357" s="12" t="s">
+        <v>1408</v>
+      </c>
+      <c r="J357" s="12" t="s">
         <v>1409</v>
       </c>
-      <c r="J357" s="12" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="358" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+    </row>
+    <row r="358" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
-        <v>1320</v>
+        <v>1565</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>1319</v>
+        <v>1566</v>
       </c>
       <c r="C358" s="7">
-        <v>1225</v>
+        <v>590</v>
       </c>
       <c r="D358" s="7">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="E358" s="12" t="s">
-        <v>1309</v>
+        <v>1567</v>
       </c>
       <c r="F358" s="12" t="s">
-        <v>1308</v>
+        <v>1568</v>
       </c>
       <c r="G358" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H358" s="7" t="s">
-        <v>511</v>
+        <v>66</v>
       </c>
       <c r="I358" s="12" t="s">
-        <v>1411</v>
+        <v>1569</v>
       </c>
       <c r="J358" s="12" t="s">
-        <v>1412</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
-        <v>1570</v>
+        <v>1309</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>1571</v>
+        <v>1310</v>
       </c>
       <c r="C359" s="7">
-        <v>590</v>
+        <v>535</v>
       </c>
       <c r="D359" s="7">
         <v>400</v>
       </c>
       <c r="E359" s="12" t="s">
-        <v>1572</v>
+        <v>1308</v>
       </c>
       <c r="F359" s="12" t="s">
-        <v>1573</v>
+        <v>1307</v>
       </c>
       <c r="G359" s="7" t="s">
         <v>859</v>
@@ -14781,62 +14768,56 @@
         <v>66</v>
       </c>
       <c r="I359" s="12" t="s">
-        <v>1574</v>
+        <v>1536</v>
       </c>
       <c r="J359" s="12" t="s">
-        <v>1575</v>
-      </c>
-    </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C360" s="7">
+        <v>614</v>
+      </c>
+      <c r="D360" s="7">
+        <v>375</v>
+      </c>
+      <c r="E360" s="12" t="s">
         <v>1312</v>
       </c>
-      <c r="B360" s="1" t="s">
-        <v>1313</v>
-      </c>
-      <c r="C360" s="7">
-        <v>535</v>
-      </c>
-      <c r="D360" s="7">
-        <v>400</v>
-      </c>
-      <c r="E360" s="12" t="s">
+      <c r="F360" s="12" t="s">
         <v>1311</v>
-      </c>
-      <c r="F360" s="12" t="s">
-        <v>1310</v>
       </c>
       <c r="G360" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H360" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I360" s="12" t="s">
-        <v>1541</v>
-      </c>
-      <c r="J360" s="12" t="s">
-        <v>1540</v>
-      </c>
-    </row>
-    <row r="361" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B361" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="B361" s="1" t="s">
-        <v>1327</v>
-      </c>
       <c r="C361" s="7">
-        <v>614</v>
+        <v>946</v>
       </c>
       <c r="D361" s="7">
-        <v>375</v>
+        <v>575</v>
       </c>
       <c r="E361" s="12" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="F361" s="12" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="G361" s="7" t="s">
         <v>859</v>
@@ -14844,25 +14825,31 @@
       <c r="H361" s="7" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="362" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="I361" s="12" t="s">
+        <v>1518</v>
+      </c>
+      <c r="J361" s="12" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
-        <v>1328</v>
+        <v>1319</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>1329</v>
+        <v>1320</v>
       </c>
       <c r="C362" s="7">
-        <v>946</v>
+        <v>1174</v>
       </c>
       <c r="D362" s="7">
-        <v>575</v>
+        <v>700</v>
       </c>
       <c r="E362" s="12" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
       <c r="F362" s="12" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="G362" s="7" t="s">
         <v>859</v>
@@ -14871,56 +14858,53 @@
         <v>511</v>
       </c>
       <c r="I362" s="12" t="s">
-        <v>1523</v>
+        <v>1405</v>
       </c>
       <c r="J362" s="12" t="s">
-        <v>1522</v>
-      </c>
-    </row>
-    <row r="363" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
-        <v>1322</v>
+        <v>1327</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>1323</v>
+        <v>1328</v>
       </c>
       <c r="C363" s="7">
-        <v>1174</v>
+        <v>1395</v>
       </c>
       <c r="D363" s="7">
-        <v>700</v>
+        <v>920</v>
       </c>
       <c r="E363" s="12" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
       <c r="F363" s="12" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
       <c r="G363" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H363" s="7" t="s">
-        <v>511</v>
+        <v>66</v>
       </c>
       <c r="I363" s="12" t="s">
-        <v>1408</v>
-      </c>
-      <c r="J363" s="12" t="s">
-        <v>1407</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="364" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
-        <v>1330</v>
+        <v>1511</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>1331</v>
       </c>
       <c r="C364" s="7">
-        <v>1395</v>
+        <v>488</v>
       </c>
       <c r="D364" s="7">
-        <v>920</v>
+        <v>400</v>
       </c>
       <c r="E364" s="12" t="s">
         <v>1333</v>
@@ -14932,24 +14916,27 @@
         <v>859</v>
       </c>
       <c r="H364" s="7" t="s">
-        <v>66</v>
+        <v>511</v>
       </c>
       <c r="I364" s="12" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="365" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>1468</v>
+      </c>
+      <c r="J364" s="12" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
-        <v>1516</v>
+        <v>1334</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="C365" s="7">
-        <v>488</v>
+        <v>554</v>
       </c>
       <c r="D365" s="7">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E365" s="12" t="s">
         <v>1336</v>
@@ -14961,152 +14948,152 @@
         <v>859</v>
       </c>
       <c r="H365" s="7" t="s">
-        <v>511</v>
+        <v>12</v>
       </c>
       <c r="I365" s="12" t="s">
-        <v>1471</v>
+        <v>1574</v>
       </c>
       <c r="J365" s="12" t="s">
-        <v>1517</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B366" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C366" s="7">
+        <v>398</v>
+      </c>
+      <c r="D366" s="7">
+        <v>250</v>
+      </c>
+      <c r="E366" s="12" t="s">
         <v>1340</v>
       </c>
-      <c r="C366" s="7">
-        <v>554</v>
-      </c>
-      <c r="D366" s="7">
-        <v>200</v>
-      </c>
-      <c r="E366" s="12" t="s">
+      <c r="F366" s="12" t="s">
         <v>1339</v>
-      </c>
-      <c r="F366" s="12" t="s">
-        <v>1338</v>
       </c>
       <c r="G366" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H366" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I366" s="12" t="s">
-        <v>1579</v>
-      </c>
-      <c r="J366" s="12" t="s">
-        <v>1578</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B367" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C367" s="7">
+        <v>399</v>
+      </c>
+      <c r="D367" s="7">
+        <v>100</v>
+      </c>
+      <c r="E367" s="12" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F367" s="12" t="s">
         <v>1344</v>
-      </c>
-      <c r="C367" s="7">
-        <v>398</v>
-      </c>
-      <c r="D367" s="7">
-        <v>250</v>
-      </c>
-      <c r="E367" s="12" t="s">
-        <v>1343</v>
-      </c>
-      <c r="F367" s="12" t="s">
-        <v>1342</v>
       </c>
       <c r="G367" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H367" s="7" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="I367" s="12" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="C368" s="7">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D368" s="7">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E368" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F368" s="12" t="s">
         <v>1348</v>
-      </c>
-      <c r="F368" s="12" t="s">
-        <v>1347</v>
       </c>
       <c r="G368" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H368" s="7" t="s">
-        <v>66</v>
+        <v>197</v>
       </c>
       <c r="I368" s="12" t="s">
-        <v>1537</v>
-      </c>
-    </row>
-    <row r="369" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>1426</v>
+      </c>
+      <c r="J368" s="12" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="C369" s="7">
-        <v>397</v>
+        <v>350</v>
       </c>
       <c r="D369" s="7">
         <v>300</v>
       </c>
       <c r="E369" s="12" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F369" s="12" t="s">
         <v>1352</v>
-      </c>
-      <c r="F369" s="12" t="s">
-        <v>1351</v>
       </c>
       <c r="G369" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H369" s="7" t="s">
-        <v>197</v>
+        <v>66</v>
       </c>
       <c r="I369" s="12" t="s">
-        <v>1429</v>
+        <v>1527</v>
       </c>
       <c r="J369" s="12" t="s">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="C370" s="7">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="D370" s="7">
         <v>300</v>
       </c>
       <c r="E370" s="12" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="F370" s="12" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="G370" s="7" t="s">
         <v>859</v>
@@ -15115,30 +15102,27 @@
         <v>66</v>
       </c>
       <c r="I370" s="12" t="s">
-        <v>1532</v>
-      </c>
-      <c r="J370" s="12" t="s">
-        <v>1531</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>1359</v>
       </c>
       <c r="B371" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C371" s="7">
+        <v>1690</v>
+      </c>
+      <c r="D371" s="7">
+        <v>1090</v>
+      </c>
+      <c r="E371" s="12" t="s">
+        <v>1421</v>
+      </c>
+      <c r="F371" s="12" t="s">
         <v>1360</v>
-      </c>
-      <c r="C371" s="7">
-        <v>385</v>
-      </c>
-      <c r="D371" s="7">
-        <v>300</v>
-      </c>
-      <c r="E371" s="12" t="s">
-        <v>1358</v>
-      </c>
-      <c r="F371" s="12" t="s">
-        <v>1357</v>
       </c>
       <c r="G371" s="7" t="s">
         <v>859</v>
@@ -15147,136 +15131,107 @@
         <v>66</v>
       </c>
       <c r="I371" s="12" t="s">
-        <v>1425</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="372" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C372" s="7">
+        <v>1999</v>
+      </c>
+      <c r="D372" s="7">
+        <v>800</v>
+      </c>
+      <c r="E372" s="12" t="s">
         <v>1362</v>
       </c>
-      <c r="B372" s="1" t="s">
+      <c r="F372" s="12" t="s">
         <v>1361</v>
-      </c>
-      <c r="C372" s="7">
-        <v>1690</v>
-      </c>
-      <c r="D372" s="7">
-        <v>1090</v>
-      </c>
-      <c r="E372" s="12" t="s">
-        <v>1424</v>
-      </c>
-      <c r="F372" s="12" t="s">
-        <v>1363</v>
       </c>
       <c r="G372" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H372" s="7" t="s">
-        <v>66</v>
+        <v>197</v>
       </c>
       <c r="I372" s="12" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="373" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>1367</v>
       </c>
       <c r="C373" s="7">
-        <v>1999</v>
+        <v>4699</v>
       </c>
       <c r="D373" s="7">
-        <v>800</v>
+        <v>2832</v>
       </c>
       <c r="E373" s="12" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F373" s="12" t="s">
         <v>1365</v>
-      </c>
-      <c r="F373" s="12" t="s">
-        <v>1364</v>
       </c>
       <c r="G373" s="7" t="s">
         <v>859</v>
       </c>
       <c r="H373" s="7" t="s">
-        <v>197</v>
+        <v>510</v>
       </c>
       <c r="I373" s="12" t="s">
-        <v>1402</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1386</v>
+      </c>
+      <c r="J373" s="12" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>1370</v>
       </c>
       <c r="C374" s="7">
-        <v>4699</v>
+        <v>349</v>
       </c>
       <c r="D374" s="7">
-        <v>2832</v>
+        <v>295</v>
       </c>
       <c r="E374" s="12" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="F374" s="12" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="G374" s="7" t="s">
-        <v>859</v>
+        <v>419</v>
       </c>
       <c r="H374" s="7" t="s">
-        <v>510</v>
+        <v>66</v>
       </c>
       <c r="I374" s="12" t="s">
-        <v>1389</v>
+        <v>1479</v>
       </c>
       <c r="J374" s="12" t="s">
-        <v>1388</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A375" s="1" t="s">
-        <v>1372</v>
-      </c>
-      <c r="B375" s="1" t="s">
-        <v>1373</v>
-      </c>
-      <c r="C375" s="7">
-        <v>349</v>
-      </c>
-      <c r="D375" s="7">
-        <v>295</v>
-      </c>
-      <c r="E375" s="12" t="s">
-        <v>1375</v>
-      </c>
-      <c r="F375" s="12" t="s">
-        <v>1374</v>
-      </c>
-      <c r="G375" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="H375" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I375" s="12" t="s">
-        <v>1482</v>
-      </c>
-      <c r="J375" s="12" t="s">
-        <v>1481</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A376" s="13" t="s">
-        <v>1591</v>
-      </c>
-      <c r="B376" s="1"/>
+      <c r="A375" s="13" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B375" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15285,52 +15240,52 @@
     <hyperlink ref="F60" r:id="rId3"/>
     <hyperlink ref="E271" r:id="rId4"/>
     <hyperlink ref="E60" r:id="rId5"/>
-    <hyperlink ref="E350" r:id="rId6"/>
+    <hyperlink ref="E349" r:id="rId6"/>
     <hyperlink ref="E253" r:id="rId7"/>
     <hyperlink ref="E328" r:id="rId8"/>
     <hyperlink ref="E152" r:id="rId9"/>
-    <hyperlink ref="F353" r:id="rId10" location="&amp;gid=1&amp;pid=1"/>
-    <hyperlink ref="E353" r:id="rId11"/>
-    <hyperlink ref="F354" r:id="rId12" location="&amp;gid=1&amp;pid=1"/>
-    <hyperlink ref="E354" r:id="rId13"/>
-    <hyperlink ref="F355" r:id="rId14" location="&amp;gid=1&amp;pid=1"/>
-    <hyperlink ref="E355" r:id="rId15"/>
-    <hyperlink ref="F356" r:id="rId16"/>
-    <hyperlink ref="E356" r:id="rId17"/>
-    <hyperlink ref="F357" r:id="rId18"/>
-    <hyperlink ref="E357" r:id="rId19"/>
-    <hyperlink ref="F358" display="https://www.mercadolibre.com.mx/epicentro-audishako-max-02-restaurador-de-bajos-para-auto-subwoofer-para-carro-pickups-y-suv-accesorios-para-auto-audio-diseno-en-relieve-3d-incluye-dash-remoto-control-de-bajos/p/MLM64640099?pdp_filters=item_id:MLM46970202"/>
-    <hyperlink ref="E358" r:id="rId20"/>
-    <hyperlink ref="F360" r:id="rId21"/>
-    <hyperlink ref="E360" r:id="rId22"/>
-    <hyperlink ref="F361" r:id="rId23"/>
-    <hyperlink ref="E361" r:id="rId24"/>
-    <hyperlink ref="F362" r:id="rId25"/>
-    <hyperlink ref="E362" r:id="rId26"/>
-    <hyperlink ref="F364" r:id="rId27"/>
-    <hyperlink ref="E364" r:id="rId28"/>
-    <hyperlink ref="F365" r:id="rId29" location="reviews"/>
-    <hyperlink ref="E365" r:id="rId30"/>
-    <hyperlink ref="F366" r:id="rId31"/>
-    <hyperlink ref="E366" r:id="rId32"/>
-    <hyperlink ref="F367" r:id="rId33"/>
-    <hyperlink ref="E367" r:id="rId34"/>
-    <hyperlink ref="F368" r:id="rId35"/>
-    <hyperlink ref="E368" r:id="rId36"/>
-    <hyperlink ref="F369" r:id="rId37"/>
-    <hyperlink ref="E369" r:id="rId38"/>
-    <hyperlink ref="F370" r:id="rId39"/>
-    <hyperlink ref="E370" r:id="rId40"/>
-    <hyperlink ref="F371" r:id="rId41"/>
-    <hyperlink ref="E371" r:id="rId42"/>
-    <hyperlink ref="F372" r:id="rId43"/>
-    <hyperlink ref="E372" r:id="rId44"/>
-    <hyperlink ref="F373" r:id="rId45"/>
-    <hyperlink ref="E373" r:id="rId46"/>
-    <hyperlink ref="F374" r:id="rId47"/>
-    <hyperlink ref="E374" r:id="rId48"/>
-    <hyperlink ref="F375" r:id="rId49"/>
-    <hyperlink ref="E375" r:id="rId50"/>
+    <hyperlink ref="F352" r:id="rId10" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="E352" r:id="rId11"/>
+    <hyperlink ref="F353" r:id="rId12" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="E353" r:id="rId13"/>
+    <hyperlink ref="F354" r:id="rId14" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="E354" r:id="rId15"/>
+    <hyperlink ref="F355" r:id="rId16"/>
+    <hyperlink ref="E355" r:id="rId17"/>
+    <hyperlink ref="F356" r:id="rId18"/>
+    <hyperlink ref="E356" r:id="rId19"/>
+    <hyperlink ref="F357" display="https://www.mercadolibre.com.mx/epicentro-audishako-max-02-restaurador-de-bajos-para-auto-subwoofer-para-carro-pickups-y-suv-accesorios-para-auto-audio-diseno-en-relieve-3d-incluye-dash-remoto-control-de-bajos/p/MLM64640099?pdp_filters=item_id:MLM46970202"/>
+    <hyperlink ref="E357" r:id="rId20"/>
+    <hyperlink ref="F359" r:id="rId21"/>
+    <hyperlink ref="E359" r:id="rId22"/>
+    <hyperlink ref="F360" r:id="rId23"/>
+    <hyperlink ref="E360" r:id="rId24"/>
+    <hyperlink ref="F361" r:id="rId25"/>
+    <hyperlink ref="E361" r:id="rId26"/>
+    <hyperlink ref="F363" r:id="rId27"/>
+    <hyperlink ref="E363" r:id="rId28"/>
+    <hyperlink ref="F364" r:id="rId29" location="reviews"/>
+    <hyperlink ref="E364" r:id="rId30"/>
+    <hyperlink ref="F365" r:id="rId31"/>
+    <hyperlink ref="E365" r:id="rId32"/>
+    <hyperlink ref="F366" r:id="rId33"/>
+    <hyperlink ref="E366" r:id="rId34"/>
+    <hyperlink ref="F367" r:id="rId35"/>
+    <hyperlink ref="E367" r:id="rId36"/>
+    <hyperlink ref="F368" r:id="rId37"/>
+    <hyperlink ref="E368" r:id="rId38"/>
+    <hyperlink ref="F369" r:id="rId39"/>
+    <hyperlink ref="E369" r:id="rId40"/>
+    <hyperlink ref="F370" r:id="rId41"/>
+    <hyperlink ref="E370" r:id="rId42"/>
+    <hyperlink ref="F371" r:id="rId43"/>
+    <hyperlink ref="E371" r:id="rId44"/>
+    <hyperlink ref="F372" r:id="rId45"/>
+    <hyperlink ref="E372" r:id="rId46"/>
+    <hyperlink ref="F373" r:id="rId47"/>
+    <hyperlink ref="E373" r:id="rId48"/>
+    <hyperlink ref="F374" r:id="rId49"/>
+    <hyperlink ref="E374" r:id="rId50"/>
     <hyperlink ref="I72" display="https://http2.mlstatic.com/D_NQ_NP_2X_977864-MLA82522530268_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728802-MLA82808708997_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_714871-MLA82808836891_032025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I299" r:id="rId51"/>
     <hyperlink ref="J299" r:id="rId52"/>
@@ -15341,48 +15296,48 @@
     <hyperlink ref="I67" display="https://http2.mlstatic.com/D_NQ_NP_2X_754117-MLA87918629604_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_955266-MLA88256438081_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_924778-MLA88256272783_072025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I265" display="https://http2.mlstatic.com/D_NQ_NP_2X_651538-MLA109474609027_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_786870-MLA109384870397_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_877937-MLA109385877631_032026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I328" display="https://http2.mlstatic.com/D_NQ_NP_2X_659872-MLA110558100656_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_654212-MLA110558217136_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728798-MLA110558100602_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J374" r:id="rId54"/>
-    <hyperlink ref="I374" r:id="rId55"/>
+    <hyperlink ref="J373" r:id="rId54"/>
+    <hyperlink ref="I373" r:id="rId55"/>
     <hyperlink ref="I330" display="https://http2.mlstatic.com/D_NQ_NP_2X_704682-MLA112632086794_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648062-MLA114215908179_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_721338-MLA112631444306_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="E250" r:id="rId56"/>
     <hyperlink ref="I250" r:id="rId57"/>
     <hyperlink ref="J250" r:id="rId58"/>
     <hyperlink ref="I36" r:id="rId59"/>
-    <hyperlink ref="I372" display="https://http2.mlstatic.com/D_NQ_NP_2X_870766-MLA111944165952_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_835091-MLA112882459449_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I371" display="https://http2.mlstatic.com/D_NQ_NP_2X_870766-MLA111944165952_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_835091-MLA112882459449_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="J60" r:id="rId60"/>
     <hyperlink ref="I60" display="https://http2.mlstatic.com/D_NQ_NP_2X_650019-MLA112598239078_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_694102-MLA111420836191_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_960139-MLA111232526403_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I364" r:id="rId61"/>
+    <hyperlink ref="I363" r:id="rId61"/>
     <hyperlink ref="I225" display="https://http2.mlstatic.com/D_NQ_NP_2X_761866-MLA76203783381_052024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_967910-MLA76082310461_042024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_699850-MLA76082339489_042024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="J32" r:id="rId62"/>
     <hyperlink ref="I32" display="https://http2.mlstatic.com/D_NQ_NP_2X_937988-MLA100214376229_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_839463-MLA100214244569_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_878239-MLA100214347283_122025-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I101" display="https://http2.mlstatic.com/D_NQ_NP_2X_853469-MLA73479850047_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_636371-MLA72966055893_112023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_647337-MLA74448293715_022024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I373" display="https://http2.mlstatic.com/D_NQ_NP_2X_838661-MLA114043475512_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_997422-MLA111845686244_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_946430-MLA112856485647_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I372" display="https://http2.mlstatic.com/D_NQ_NP_2X_838661-MLA114043475512_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_997422-MLA111845686244_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_946430-MLA112856485647_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I146" display="https://http2.mlstatic.com/D_NQ_NP_2X_700050-MLA90330537717_082025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_810830-MLA92985348779_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_611435-MLA103169335415_122025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="J341" r:id="rId63"/>
-    <hyperlink ref="I341" display="https://http2.mlstatic.com/D_NQ_NP_2X_972461-MLA108765590667_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_959062-MLA111287287492_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_702439-MLA108999676116_032026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J340" r:id="rId63"/>
+    <hyperlink ref="I340" display="https://http2.mlstatic.com/D_NQ_NP_2X_972461-MLA108765590667_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_959062-MLA111287287492_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_702439-MLA108999676116_032026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I244" display="https://http2.mlstatic.com/D_NQ_NP_2X_772336-MLA83215360667_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_641687-MLA82926894938_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_686941-MLA80851161221_112024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J362" r:id="rId64"/>
-    <hyperlink ref="I362" display="https://http2.mlstatic.com/D_NQ_NP_2X_654570-MLA114163554383_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_820669-MLA112176540320_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_827402-MLA113697495744_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J357" r:id="rId65"/>
-    <hyperlink ref="I357" display="https://http2.mlstatic.com/D_NQ_NP_2X_622982-MLA91998379772_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_918567-MLA93316673763_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_951409-MLA93316693351_092025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I358" r:id="rId66"/>
-    <hyperlink ref="J358" r:id="rId67"/>
+    <hyperlink ref="J361" r:id="rId64"/>
+    <hyperlink ref="I361" display="https://http2.mlstatic.com/D_NQ_NP_2X_654570-MLA114163554383_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_820669-MLA112176540320_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_827402-MLA113697495744_072026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J356" r:id="rId65"/>
+    <hyperlink ref="I356" display="https://http2.mlstatic.com/D_NQ_NP_2X_622982-MLA91998379772_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_918567-MLA93316673763_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_951409-MLA93316693351_092025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="I357" r:id="rId66"/>
+    <hyperlink ref="J357" r:id="rId67"/>
     <hyperlink ref="J169" r:id="rId68"/>
     <hyperlink ref="I169" display="https://http2.mlstatic.com/D_NQ_NP_2X_630634-MLA83929492736_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_826427-MLA83875691856_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_778506-MLA83875632066_042025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I286" display="https://http2.mlstatic.com/D_NQ_NP_2X_601798-MLA74779553000_032024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_784677-MLA71729912500_092023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_982997-MLA73375012815_122023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="J56" r:id="rId69"/>
     <hyperlink ref="I56" r:id="rId70"/>
-    <hyperlink ref="I355" r:id="rId71"/>
-    <hyperlink ref="I356" r:id="rId72"/>
+    <hyperlink ref="I354" r:id="rId71"/>
+    <hyperlink ref="I355" r:id="rId72"/>
     <hyperlink ref="I132" r:id="rId73"/>
-    <hyperlink ref="I354" r:id="rId74"/>
-    <hyperlink ref="J354" r:id="rId75"/>
-    <hyperlink ref="I371" display="https://http2.mlstatic.com/D_NQ_NP_2X_730160-MLA112550162587_062026-F.webp;http://http2.mlstatic.com/D_NQ_NP_2X_748872-MLA113290799753_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_824232-MLA112954608093_062026-F.webp;https://http2.mlstatic.com/D_NQ"/>
+    <hyperlink ref="I353" r:id="rId74"/>
+    <hyperlink ref="J353" r:id="rId75"/>
+    <hyperlink ref="I370" display="https://http2.mlstatic.com/D_NQ_NP_2X_730160-MLA112550162587_062026-F.webp;http://http2.mlstatic.com/D_NQ_NP_2X_748872-MLA113290799753_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_824232-MLA112954608093_062026-F.webp;https://http2.mlstatic.com/D_NQ"/>
     <hyperlink ref="I107" r:id="rId76"/>
     <hyperlink ref="I2" display="https://http2.mlstatic.com/D_NQ_NP_2X_644970-MLA111138624893_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_618974-MLA113557256809_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_849248-MLA111414716285_052026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I11" r:id="rId77"/>
-    <hyperlink ref="I369" r:id="rId78"/>
-    <hyperlink ref="J369" r:id="rId79"/>
+    <hyperlink ref="I368" r:id="rId78"/>
+    <hyperlink ref="J368" r:id="rId79"/>
     <hyperlink ref="E145" r:id="rId80"/>
     <hyperlink ref="I145" r:id="rId81"/>
     <hyperlink ref="J180" r:id="rId82"/>
@@ -15400,11 +15355,11 @@
     <hyperlink ref="I322" r:id="rId94"/>
     <hyperlink ref="J54" r:id="rId95"/>
     <hyperlink ref="I54" r:id="rId96"/>
-    <hyperlink ref="I353" r:id="rId97"/>
+    <hyperlink ref="I352" r:id="rId97"/>
     <hyperlink ref="I325" r:id="rId98"/>
-    <hyperlink ref="J366" r:id="rId99"/>
-    <hyperlink ref="I366" display="https://http2.mlstatic.com/D_NQ_NP_2X_967252-MLA112857017004_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_802434-MLA114058497103_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_904877-MLA112857136140_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I337" display="https://http2.mlstatic.com/D_NQ_NP_2X_871513-MLA105683275105_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_921467-MLA106225093215_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_768089-MLA111241397693_052026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J365" r:id="rId99"/>
+    <hyperlink ref="I365" display="https://http2.mlstatic.com/D_NQ_NP_2X_967252-MLA112857017004_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_802434-MLA114058497103_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_904877-MLA112857136140_072026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I336" display="https://http2.mlstatic.com/D_NQ_NP_2X_871513-MLA105683275105_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_921467-MLA106225093215_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_768089-MLA111241397693_052026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I273" r:id="rId100"/>
     <hyperlink ref="J268" r:id="rId101"/>
     <hyperlink ref="I268" display="https://http2.mlstatic.com/D_NQ_NP_2X_723996-MLA101839595031_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648298-MLA100279286785_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_899562-MLA105452243109_012026-F.webp;https://http2.mlstatic.com/D_N"/>
@@ -15412,8 +15367,8 @@
     <hyperlink ref="I106" display="https://http2.mlstatic.com/D_NQ_NP_2X_986480-MLA92403239851_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_992851-MLA91999385090_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_790783-MLA94732447073_102025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I185" display="https://http2.mlstatic.com/D_NQ_NP_2X_714527-MLA94159366454_102025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_847366-MLA97737335743_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_618907-MLA100261323194_122025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
     <hyperlink ref="I288" r:id="rId103"/>
-    <hyperlink ref="J342" r:id="rId104"/>
-    <hyperlink ref="I342" r:id="rId105"/>
+    <hyperlink ref="J341" r:id="rId104"/>
+    <hyperlink ref="I341" r:id="rId105"/>
     <hyperlink ref="J300" r:id="rId106"/>
     <hyperlink ref="I300" r:id="rId107"/>
     <hyperlink ref="I329" display="https://http2.mlstatic.com/D_NQ_NP_2X_886751-MLA110760597980_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_722285-MLA111072136212_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_745568-MLA111456288976_052026-F.webp;https://http2.mlstatic.com/D_N"/>
@@ -15427,7 +15382,7 @@
     <hyperlink ref="I197" display="https://http2.mlstatic.com/D_NQ_NP_2X_882824-MLA78038279945_072024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_628505-MLA80605999965_112024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_605405-MLA79717879214_102024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="J108" r:id="rId115"/>
     <hyperlink ref="I108" r:id="rId116"/>
-    <hyperlink ref="I365" r:id="rId117"/>
+    <hyperlink ref="I364" r:id="rId117"/>
     <hyperlink ref="I174" display="https://http2.mlstatic.com/D_NQ_NP_2X_671282-MLA88303913955_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_751626-MLA88304056333_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_928886-MLA111461620111_052026-F.webp;https://http2.mlstatic.com/D_NQ_"/>
     <hyperlink ref="I85" r:id="rId118"/>
     <hyperlink ref="I212" r:id="rId119"/>
@@ -15437,8 +15392,8 @@
     <hyperlink ref="J271" r:id="rId122"/>
     <hyperlink ref="I271" r:id="rId123"/>
     <hyperlink ref="I324" r:id="rId124"/>
-    <hyperlink ref="J375" r:id="rId125"/>
-    <hyperlink ref="I375" r:id="rId126"/>
+    <hyperlink ref="J374" r:id="rId125"/>
+    <hyperlink ref="I374" r:id="rId126"/>
     <hyperlink ref="J53" r:id="rId127"/>
     <hyperlink ref="I53" r:id="rId128"/>
     <hyperlink ref="I222" display="https://http2.mlstatic.com/D_NQ_NP_2X_931197-MLA111097282025_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_647752-MLA86304062244_062025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_697099-MLA86808814199_062025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
@@ -15455,99 +15410,97 @@
     <hyperlink ref="J48" r:id="rId134"/>
     <hyperlink ref="I48" display="https://http2.mlstatic.com/D_NQ_NP_2X_615383-MLA106283983813_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637244-MLA106762003457_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_647036-MLA106069021004_022026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I275" r:id="rId135"/>
-    <hyperlink ref="J334" r:id="rId136"/>
-    <hyperlink ref="I334" display="https://http2.mlstatic.com/D_NQ_NP_2X_694390-MLA103915605591_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_901157-MLA112027651816_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_930408-MLA112027361550_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I296" display="https://http2.mlstatic.com/D_NQ_NP_2X_877410-MLA86700953698_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_621602-MLA110823348827_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_945418-MLA86701516062_072025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="I285" r:id="rId137"/>
+    <hyperlink ref="I285" r:id="rId136"/>
     <hyperlink ref="I3" display="https://http2.mlstatic.com/D_NQ_NP_2X_652387-MLA81262109420_122024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_964100-MLA74205385415_012024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_663926-MLA71594815900_092023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J52" r:id="rId138"/>
+    <hyperlink ref="J52" r:id="rId137"/>
     <hyperlink ref="I52" display="https://http2.mlstatic.com/D_NQ_NP_2X_787566-MLA112208805453_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_610420-MLA108420590498_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_778316-MLA108420330866_032026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I331" display="https://http2.mlstatic.com/D_NQ_NP_2X_811172-MLA108871819192_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_673692-MLA109653928111_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_807085-MLA109742422391_032026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I210" display="https://http2.mlstatic.com/D_NQ_NP_2X_787733-MLA73258839528_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_702415-MLA111282425851_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_934591-MLA108763618671_032026-F.webp;https://http2.mlstatic.com/D_NQ"/>
     <hyperlink ref="I65" display="https://http2.mlstatic.com/D_NQ_NP_2X_822004-MLA83792590685_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_922399-MLA83499949924_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_741644-MLA73913804094_012024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I205" r:id="rId139"/>
-    <hyperlink ref="J332" r:id="rId140"/>
-    <hyperlink ref="I332" r:id="rId141"/>
+    <hyperlink ref="I205" r:id="rId138"/>
+    <hyperlink ref="J332" r:id="rId139"/>
+    <hyperlink ref="I332" r:id="rId140"/>
     <hyperlink ref="I143" display="https://http2.mlstatic.com/D_NQ_NP_2X_951908-MLA106095526036_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_697058-MLA92029170496_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_770689-MLA112170606647_052026-F.webp;https://http2.mlstatic.com/D_NQ"/>
-    <hyperlink ref="J143" r:id="rId142"/>
-    <hyperlink ref="J87" r:id="rId143"/>
-    <hyperlink ref="I87" r:id="rId144"/>
-    <hyperlink ref="J365" r:id="rId145"/>
-    <hyperlink ref="J235" r:id="rId146"/>
+    <hyperlink ref="J143" r:id="rId141"/>
+    <hyperlink ref="J87" r:id="rId142"/>
+    <hyperlink ref="I87" r:id="rId143"/>
+    <hyperlink ref="J364" r:id="rId144"/>
+    <hyperlink ref="J235" r:id="rId145"/>
     <hyperlink ref="I235" display="https://http2.mlstatic.com/D_NQ_NP_2X_786831-MLA112508605409_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_945451-MLA106951088919_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_942407-MLA79868078780_102024-F.webp;https://http2.mlstatic.com/D_NQ"/>
-    <hyperlink ref="J25" r:id="rId147"/>
-    <hyperlink ref="I156" r:id="rId148"/>
-    <hyperlink ref="J283" r:id="rId149"/>
-    <hyperlink ref="I283" r:id="rId150"/>
-    <hyperlink ref="I147" r:id="rId151"/>
-    <hyperlink ref="J167" r:id="rId152"/>
+    <hyperlink ref="J25" r:id="rId146"/>
+    <hyperlink ref="I156" r:id="rId147"/>
+    <hyperlink ref="J283" r:id="rId148"/>
+    <hyperlink ref="I283" r:id="rId149"/>
+    <hyperlink ref="I147" r:id="rId150"/>
+    <hyperlink ref="J167" r:id="rId151"/>
     <hyperlink ref="I167" display="https://http2.mlstatic.com/D_NQ_NP_2X_949414-MLA115597206229_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_781530-MLA115596590455_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_794977-MLA113865153424_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I242" r:id="rId153"/>
-    <hyperlink ref="I336" r:id="rId154"/>
-    <hyperlink ref="J370" r:id="rId155"/>
-    <hyperlink ref="I370" r:id="rId156"/>
+    <hyperlink ref="I242" r:id="rId152"/>
+    <hyperlink ref="I335" r:id="rId153"/>
+    <hyperlink ref="J369" r:id="rId154"/>
+    <hyperlink ref="I369" r:id="rId155"/>
     <hyperlink ref="I113" display="https://http2.mlstatic.com/D_NQ_NP_2X_602967-MLA106207657120_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_937184-MLA99857184303_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_615655-MLA93805615686_102025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="J113" r:id="rId157"/>
+    <hyperlink ref="J113" r:id="rId156"/>
     <hyperlink ref="I274" display="https://http2.mlstatic.com/D_NQ_NP_2X_811367-MLA96964641173_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_724534-MLA95972455447_102025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_862711-MLA94582890276_102025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I188" r:id="rId158"/>
-    <hyperlink ref="I368" r:id="rId159"/>
+    <hyperlink ref="I188" r:id="rId157"/>
+    <hyperlink ref="I367" r:id="rId158"/>
     <hyperlink ref="I112" display="https://http2.mlstatic.com/D_NQ_NP_2X_832809-MLA100859657141_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_651615-MLA104572148023_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_683702-MLA104248384382_012026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I321" r:id="rId160"/>
-    <hyperlink ref="J360" r:id="rId161"/>
-    <hyperlink ref="I360" display="https://http2.mlstatic.com/D_NQ_NP_2X_986254-MLA113898749317_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_998498-MLA115220256263_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_611119-MLA113912677208_072026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I321" r:id="rId159"/>
+    <hyperlink ref="J359" r:id="rId160"/>
+    <hyperlink ref="I359" display="https://http2.mlstatic.com/D_NQ_NP_2X_986254-MLA113898749317_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_998498-MLA115220256263_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_611119-MLA113912677208_072026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I297" display="https://http2.mlstatic.com/D_NQ_NP_2X_672294-MLA110281902509_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_995715-MLA110918042491_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_936537-MLA110364709430_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J297" r:id="rId162"/>
-    <hyperlink ref="J326" r:id="rId163"/>
+    <hyperlink ref="J297" r:id="rId161"/>
+    <hyperlink ref="J326" r:id="rId162"/>
     <hyperlink ref="I326" display="https://http2.mlstatic.com/D_NQ_NP_2X_623123-MLA111040290746_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_934760-MLA111878498611_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_790070-MLA112661729675_062026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J338" r:id="rId164"/>
-    <hyperlink ref="I338" display="https://http2.mlstatic.com/D_NQ_NP_2X_637815-MLA110916194519_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_643077-MLA110749031212_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_708016-MLA112321199072_062026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I320" r:id="rId165"/>
-    <hyperlink ref="I122" r:id="rId166"/>
-    <hyperlink ref="J55" r:id="rId167"/>
+    <hyperlink ref="J337" r:id="rId163"/>
+    <hyperlink ref="I337" display="https://http2.mlstatic.com/D_NQ_NP_2X_637815-MLA110916194519_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_643077-MLA110749031212_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_708016-MLA112321199072_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I320" r:id="rId164"/>
+    <hyperlink ref="I122" r:id="rId165"/>
+    <hyperlink ref="J55" r:id="rId166"/>
     <hyperlink ref="I55" display="https://http2.mlstatic.com/D_NQ_NP_2X_707272-MLA81406001662_122024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_992452-MLA71699440818_092023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_616985-MLA84032409756_052025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J293" r:id="rId168"/>
+    <hyperlink ref="J293" r:id="rId167"/>
     <hyperlink ref="I293" display="https://http2.mlstatic.com/D_NQ_NP_2X_699847-MLA83204192108_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_847455-MLA79932861627_102024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_823994-MLA70105011582_062023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J247" r:id="rId169"/>
+    <hyperlink ref="J247" r:id="rId168"/>
     <hyperlink ref="I247" display="https://http2.mlstatic.com/D_NQ_NP_2X_896395-MLA74651133358_022024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_757231-MLA73307952803_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_773664-MLA113844190574_072026-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="I269" r:id="rId170"/>
-    <hyperlink ref="J214" r:id="rId171"/>
+    <hyperlink ref="I269" r:id="rId169"/>
+    <hyperlink ref="J214" r:id="rId170"/>
     <hyperlink ref="I214" display="https://http2.mlstatic.com/D_NQ_NP_2X_857704-MLA105910693631_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_785878-MLA115684445439_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_732723-MLA114610870605_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I124" r:id="rId172"/>
+    <hyperlink ref="I124" r:id="rId171"/>
     <hyperlink ref="I139" display="https://http2.mlstatic.com/D_NQ_NP_2X_731885-MLA81735782871_012025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_877502-MLA81736505623_012025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_739624-MLA81735782869_012025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I151" display="https://http2.mlstatic.com/D_NQ_NP_2X_852777-MLA73231184100_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_953229-MLA74068746840_012024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_727505-MLA74823139724_032024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I163" r:id="rId173"/>
-    <hyperlink ref="J163" r:id="rId174"/>
-    <hyperlink ref="F111" r:id="rId175" location="reviews"/>
-    <hyperlink ref="I111" r:id="rId176"/>
-    <hyperlink ref="I323" r:id="rId177"/>
-    <hyperlink ref="I327" r:id="rId178"/>
+    <hyperlink ref="I163" r:id="rId172"/>
+    <hyperlink ref="J163" r:id="rId173"/>
+    <hyperlink ref="F111" r:id="rId174" location="reviews"/>
+    <hyperlink ref="I111" r:id="rId175"/>
+    <hyperlink ref="I323" r:id="rId176"/>
+    <hyperlink ref="I327" r:id="rId177"/>
     <hyperlink ref="I102" display="https://http2.mlstatic.com/D_NQ_NP_2X_701490-MLA108653774761_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_910611-MLA87584829978_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_761367-MLA87718920709_072025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="E359" r:id="rId179"/>
-    <hyperlink ref="F359" r:id="rId180"/>
-    <hyperlink ref="I359" display="https://http2.mlstatic.com/D_NQ_NP_2X_957897-MLA114152946760_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_988648-MLA114781488773_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_938364-MLA113693419924_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J359" r:id="rId181"/>
-    <hyperlink ref="E231" r:id="rId182"/>
-    <hyperlink ref="I231" r:id="rId183"/>
-    <hyperlink ref="I278" r:id="rId184"/>
-    <hyperlink ref="F29" r:id="rId185"/>
+    <hyperlink ref="E358" r:id="rId178"/>
+    <hyperlink ref="F358" r:id="rId179"/>
+    <hyperlink ref="I358" display="https://http2.mlstatic.com/D_NQ_NP_2X_957897-MLA114152946760_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_988648-MLA114781488773_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_938364-MLA113693419924_072026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J358" r:id="rId180"/>
+    <hyperlink ref="E231" r:id="rId181"/>
+    <hyperlink ref="I231" r:id="rId182"/>
+    <hyperlink ref="I278" r:id="rId183"/>
+    <hyperlink ref="F29" r:id="rId184"/>
     <hyperlink ref="I333" display="https://http2.mlstatic.com/D_NQ_NP_2X_661292-MLA98293086467_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_907390-MLA106707175024_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_876338-MLA108047534008_032026-F.webp;https://http2.mlstatic.com/D_NQ"/>
-    <hyperlink ref="J333" r:id="rId186"/>
-    <hyperlink ref="J279" r:id="rId187"/>
+    <hyperlink ref="J333" r:id="rId185"/>
+    <hyperlink ref="J279" r:id="rId186"/>
     <hyperlink ref="I279" display="https://http2.mlstatic.com/D_NQ_NP_2X_609731-MLA83282009211_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_965155-MLA83841127402_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_758965-MLA85304541601_052025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I162" r:id="rId188"/>
-    <hyperlink ref="J162" r:id="rId189"/>
-    <hyperlink ref="I141" r:id="rId190"/>
-    <hyperlink ref="J142" r:id="rId191"/>
+    <hyperlink ref="I162" r:id="rId187"/>
+    <hyperlink ref="J162" r:id="rId188"/>
+    <hyperlink ref="I141" r:id="rId189"/>
+    <hyperlink ref="J142" r:id="rId190"/>
     <hyperlink ref="I142" display="https://http2.mlstatic.com/D_NQ_NP_2X_863418-MLA109994960812_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_927650-MLA105811665406_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_743624-MLA105810281830_022026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J86" r:id="rId192"/>
+    <hyperlink ref="J86" r:id="rId191"/>
     <hyperlink ref="I86" display="https://http2.mlstatic.com/D_NQ_NP_2X_929447-MLA114868215933_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_688697-MLA113791320300_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_631693-MLA113790881904_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="F86" r:id="rId193"/>
-    <hyperlink ref="J296" r:id="rId194"/>
+    <hyperlink ref="F86" r:id="rId192"/>
+    <hyperlink ref="J296" r:id="rId193"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId195"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId194"/>
   <tableParts count="1">
-    <tablePart r:id="rId196"/>
+    <tablePart r:id="rId195"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="1621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="1616">
   <si>
     <t>Nombre</t>
   </si>
@@ -3428,18 +3428,6 @@
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_861484-MLM111005189078_052026-F.webp</t>
-  </si>
-  <si>
-    <t>Batidora Licuadora Juguera Portátil Usb</t>
-  </si>
-  <si>
-    <t>Recargable, 400ml rosa</t>
-  </si>
-  <si>
-    <t>https://articulo.mercadolibre.com.mx/MLM-4768514924-batidora-licuadora-juguera-portatil-usb-recargable-400mlrosa-_JM?quantity=1</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_883925-CBT110729694168_052026-F-batidora-licuadora-juguera-portatil-usb-recargable-400mlrosa.webp</t>
   </si>
   <si>
     <t>Lámpara Mata Mosquitos Eléctrica Con Luz Nocturna</t>
@@ -4516,9 +4504,6 @@
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_832809-MLA100859657141_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_651615-MLA104572148023_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_683702-MLA104248384382_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_619507-MLA106020998787_012026-F.webp</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_657542-MLA111312545960_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_606173-MLA112222407989_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_794095-MLA112462249195_052026-F.webp</t>
   </si>
   <si>
     <t>https://video-vod-clips.mms.mlstatic.com/v1/video/hls/cli_04xzu0y81ntclips/019fb0f6ab517b269630675668626b35/master.m3u8</t>
@@ -5057,8 +5042,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J381" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J381"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J380" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J380"/>
   <sortState ref="A2:H342">
     <sortCondition ref="A1:A342"/>
   </sortState>
@@ -5363,7 +5348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J381"/>
+  <dimension ref="A1:J380"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" style="1" customWidth="1"/>
@@ -5403,18 +5388,18 @@
         <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="11.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="C2" s="7">
         <v>2699</v>
@@ -5423,10 +5408,10 @@
         <v>2000</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>590</v>
@@ -5435,7 +5420,7 @@
         <v>66</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -5458,13 +5443,13 @@
         <v>1008</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="J3" s="12"/>
     </row>
@@ -5494,7 +5479,7 @@
         <v>66</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -5546,7 +5531,7 @@
         <v>507</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -5655,7 +5640,7 @@
         <v>828</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="C11" s="7">
         <v>300</v>
@@ -5702,7 +5687,7 @@
         <v>66</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
@@ -6042,7 +6027,7 @@
         <v>508</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
@@ -6071,7 +6056,7 @@
         <v>99</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
@@ -6140,7 +6125,7 @@
         <v>114</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>903</v>
@@ -6227,10 +6212,10 @@
         <v>99</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
@@ -6334,15 +6319,15 @@
         <v>66</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="C38" s="7">
         <v>300</v>
@@ -6357,7 +6342,7 @@
         <v>390</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>66</v>
@@ -6622,10 +6607,10 @@
         <v>509</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
@@ -6729,10 +6714,10 @@
         <v>12</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
@@ -6761,10 +6746,10 @@
         <v>12</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
@@ -6793,10 +6778,10 @@
         <v>12</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
@@ -6804,7 +6789,7 @@
         <v>207</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="C56" s="7">
         <v>652</v>
@@ -6825,10 +6810,10 @@
         <v>12</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
@@ -6857,10 +6842,10 @@
         <v>12</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
@@ -6883,7 +6868,7 @@
         <v>863</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>66</v>
@@ -6949,7 +6934,7 @@
         <v>1000</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="F61" s="12" t="s">
         <v>1019</v>
@@ -6961,10 +6946,10 @@
         <v>12</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.35">
@@ -7082,7 +7067,7 @@
         <v>3500</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>1030</v>
@@ -7094,10 +7079,10 @@
         <v>99</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -7126,7 +7111,7 @@
         <v>99</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.35">
@@ -7201,10 +7186,10 @@
         <v>197</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
@@ -7259,7 +7244,7 @@
         <v>66</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
@@ -7308,10 +7293,10 @@
         <v>12</v>
       </c>
       <c r="I74" s="12" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
@@ -7340,7 +7325,7 @@
         <v>405</v>
       </c>
       <c r="I75" s="12" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.35">
@@ -7591,7 +7576,7 @@
         <v>99</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
@@ -7608,7 +7593,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="G86" s="7" t="s">
         <v>981</v>
@@ -7617,15 +7602,15 @@
         <v>507</v>
       </c>
       <c r="I86" s="12" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>664</v>
@@ -7649,10 +7634,10 @@
         <v>66</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
@@ -8010,7 +7995,7 @@
         <v>66</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.35">
@@ -8036,7 +8021,7 @@
         <v>197</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
@@ -8143,7 +8128,7 @@
         <v>12</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
@@ -8172,7 +8157,7 @@
         <v>12</v>
       </c>
       <c r="I107" s="12" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.35">
@@ -8235,7 +8220,7 @@
         <v>491</v>
       </c>
       <c r="F110" s="12" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="G110" s="7" t="s">
         <v>873</v>
@@ -8244,7 +8229,7 @@
         <v>507</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.35">
@@ -8270,7 +8255,7 @@
         <v>66</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.35">
@@ -8299,10 +8284,10 @@
         <v>66</v>
       </c>
       <c r="I112" s="12" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="J112" s="12" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.35">
@@ -8383,10 +8368,10 @@
         <v>66</v>
       </c>
       <c r="I115" s="12" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="J115" s="12" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.35">
@@ -8542,7 +8527,7 @@
         <v>12</v>
       </c>
       <c r="I121" s="12" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.35">
@@ -8591,7 +8576,7 @@
         <v>507</v>
       </c>
       <c r="I123" s="12" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -8767,7 +8752,7 @@
         <v>507</v>
       </c>
       <c r="I130" s="12" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.35">
@@ -8796,7 +8781,7 @@
         <v>508</v>
       </c>
       <c r="I131" s="12" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="58" x14ac:dyDescent="0.35">
@@ -8871,7 +8856,7 @@
         <v>507</v>
       </c>
       <c r="I134" s="12" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.35">
@@ -8902,7 +8887,7 @@
     </row>
     <row r="136" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>1023</v>
@@ -8926,10 +8911,10 @@
         <v>66</v>
       </c>
       <c r="I136" s="12" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="J136" s="12" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.35">
@@ -8978,7 +8963,7 @@
         <v>507</v>
       </c>
       <c r="I138" s="12" t="s">
-        <v>1511</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.35">
@@ -9027,7 +9012,7 @@
         <v>197</v>
       </c>
       <c r="I140" s="12" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.35">
@@ -9053,10 +9038,10 @@
         <v>197</v>
       </c>
       <c r="I141" s="12" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.35">
@@ -9082,10 +9067,10 @@
         <v>197</v>
       </c>
       <c r="I142" s="12" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
       <c r="J142" s="12" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.35">
@@ -9125,7 +9110,7 @@
         <v>250</v>
       </c>
       <c r="E144" s="12" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="F144" s="7" t="s">
         <v>98</v>
@@ -9137,7 +9122,7 @@
         <v>507</v>
       </c>
       <c r="I144" s="12" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.35">
@@ -9166,7 +9151,7 @@
         <v>508</v>
       </c>
       <c r="I145" s="12" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.35">
@@ -9195,7 +9180,7 @@
         <v>508</v>
       </c>
       <c r="I146" s="12" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.35">
@@ -9224,7 +9209,7 @@
         <v>508</v>
       </c>
       <c r="I147" s="12" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.35">
@@ -9253,7 +9238,7 @@
         <v>507</v>
       </c>
       <c r="I148" s="12" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.35">
@@ -9308,7 +9293,7 @@
         <v>507</v>
       </c>
       <c r="I150" s="12" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.35">
@@ -9325,7 +9310,7 @@
         <v>150</v>
       </c>
       <c r="E151" s="12" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="F151" s="7" t="s">
         <v>590</v>
@@ -9409,7 +9394,7 @@
         <v>462</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="H154" s="7" t="s">
         <v>66</v>
@@ -9438,7 +9423,7 @@
         <v>508</v>
       </c>
       <c r="I155" s="12" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="29" x14ac:dyDescent="0.35">
@@ -9585,10 +9570,10 @@
         <v>507</v>
       </c>
       <c r="I161" s="12" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="J161" s="12" t="s">
-        <v>1532</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.35">
@@ -9614,10 +9599,10 @@
         <v>507</v>
       </c>
       <c r="I162" s="12" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="J162" s="12" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.35">
@@ -9692,10 +9677,10 @@
         <v>508</v>
       </c>
       <c r="I165" s="12" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="J165" s="12" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.35">
@@ -9750,10 +9735,10 @@
         <v>508</v>
       </c>
       <c r="I167" s="12" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="J167" s="12" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.35">
@@ -9877,7 +9862,7 @@
         <v>508</v>
       </c>
       <c r="I172" s="12" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
@@ -10027,10 +10012,10 @@
         <v>66</v>
       </c>
       <c r="I178" s="12" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="J178" s="12" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="179" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -10157,7 +10142,7 @@
         <v>99</v>
       </c>
       <c r="I183" s="12" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.35">
@@ -10235,7 +10220,7 @@
         <v>66</v>
       </c>
       <c r="I186" s="12" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.35">
@@ -10290,7 +10275,7 @@
         <v>99</v>
       </c>
       <c r="I188" s="12" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="189" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -10434,7 +10419,7 @@
         <v>66</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.35">
@@ -10463,10 +10448,10 @@
         <v>12</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="J195" s="12" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="196" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -10674,7 +10659,7 @@
         <v>12</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.35">
@@ -10801,7 +10786,7 @@
         <v>508</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.35">
@@ -10856,7 +10841,7 @@
         <v>12</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.35">
@@ -10908,10 +10893,10 @@
         <v>507</v>
       </c>
       <c r="I212" s="12" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
       <c r="J212" s="12" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -11122,7 +11107,7 @@
         <v>508</v>
       </c>
       <c r="I220" s="12" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.35">
@@ -11200,7 +11185,7 @@
         <v>99</v>
       </c>
       <c r="I223" s="12" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.35">
@@ -11283,7 +11268,7 @@
     </row>
     <row r="227" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>793</v>
@@ -11347,7 +11332,7 @@
         <v>440</v>
       </c>
       <c r="E229" s="12" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="F229" s="7" t="s">
         <v>988</v>
@@ -11359,7 +11344,7 @@
         <v>650</v>
       </c>
       <c r="I229" s="12" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.35">
@@ -11466,10 +11451,10 @@
         <v>508</v>
       </c>
       <c r="I233" s="12" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="J233" s="12" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.35">
@@ -11521,7 +11506,7 @@
         <v>99</v>
       </c>
       <c r="I235" s="12" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.35">
@@ -11619,7 +11604,7 @@
         <v>66</v>
       </c>
       <c r="I239" s="12" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.35">
@@ -11674,7 +11659,7 @@
         <v>99</v>
       </c>
       <c r="I241" s="12" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.35">
@@ -11703,10 +11688,10 @@
         <v>99</v>
       </c>
       <c r="I242" s="12" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
       <c r="J242" s="12" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.35">
@@ -11761,10 +11746,10 @@
         <v>12</v>
       </c>
       <c r="I244" s="12" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
       <c r="J244" s="12" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.35">
@@ -11830,7 +11815,7 @@
         <v>1300</v>
       </c>
       <c r="E247" s="12" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="F247" s="7" t="s">
         <v>436</v>
@@ -11842,10 +11827,10 @@
         <v>197</v>
       </c>
       <c r="I247" s="12" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="J247" s="12" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.35">
@@ -11911,7 +11896,7 @@
         <v>600</v>
       </c>
       <c r="E250" s="12" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="G250" s="7" t="s">
         <v>289</v>
@@ -11948,7 +11933,7 @@
         <v>726</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="C252" s="7">
         <v>200</v>
@@ -12073,7 +12058,7 @@
         <v>99</v>
       </c>
       <c r="I256" s="12" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.35">
@@ -12102,10 +12087,10 @@
         <v>66</v>
       </c>
       <c r="I257" s="12" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="J257" s="12" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.35">
@@ -12136,7 +12121,7 @@
     </row>
     <row r="259" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>937</v>
@@ -12229,7 +12214,7 @@
         <v>99</v>
       </c>
       <c r="I262" s="12" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.35">
@@ -12284,7 +12269,7 @@
         <v>99</v>
       </c>
       <c r="I264" s="12" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.35">
@@ -12313,10 +12298,10 @@
         <v>99</v>
       </c>
       <c r="I265" s="12" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="J265" s="12" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.35">
@@ -12345,7 +12330,7 @@
         <v>12</v>
       </c>
       <c r="I266" s="12" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.35">
@@ -12362,7 +12347,7 @@
         <v>380</v>
       </c>
       <c r="E267" s="7" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="F267" s="7" t="s">
         <v>444</v>
@@ -12379,7 +12364,7 @@
         <v>204</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="C268" s="7">
         <v>503</v>
@@ -12400,10 +12385,10 @@
         <v>12</v>
       </c>
       <c r="I268" s="12" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="J268" s="12" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.35">
@@ -12411,7 +12396,7 @@
         <v>210</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C269" s="7">
         <v>570</v>
@@ -12432,7 +12417,7 @@
         <v>12</v>
       </c>
       <c r="I269" s="12" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.35">
@@ -12455,13 +12440,13 @@
         <v>1026</v>
       </c>
       <c r="G270" s="7" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="H270" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I270" s="12" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.35">
@@ -12484,13 +12469,13 @@
         <v>354</v>
       </c>
       <c r="G271" s="7" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="H271" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I271" s="12" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.35">
@@ -12513,13 +12498,13 @@
         <v>357</v>
       </c>
       <c r="G272" s="7" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="H272" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I272" s="12" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.35">
@@ -12600,7 +12585,7 @@
         <v>99</v>
       </c>
       <c r="I275" s="12" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.35">
@@ -12629,10 +12614,10 @@
         <v>99</v>
       </c>
       <c r="I276" s="12" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="J276" s="12" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.35">
@@ -12736,10 +12721,10 @@
         <v>508</v>
       </c>
       <c r="I280" s="12" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="J280" s="12" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.35">
@@ -12792,7 +12777,7 @@
         <v>197</v>
       </c>
       <c r="I282" s="12" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="283" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -12821,7 +12806,7 @@
         <v>66</v>
       </c>
       <c r="I283" s="12" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="284" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -12876,7 +12861,7 @@
         <v>197</v>
       </c>
       <c r="I285" s="12" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.35">
@@ -13000,15 +12985,15 @@
         <v>12</v>
       </c>
       <c r="I290" s="12" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="J290" s="12" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="291" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>1071</v>
@@ -13084,10 +13069,10 @@
         <v>99</v>
       </c>
       <c r="I293" s="12" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="J293" s="12" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.35">
@@ -13110,16 +13095,16 @@
         <v>1044</v>
       </c>
       <c r="G294" s="7" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="H294" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I294" s="12" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="J294" s="12" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.35">
@@ -13148,10 +13133,10 @@
         <v>66</v>
       </c>
       <c r="I295" s="12" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="J295" s="12" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.35">
@@ -13180,10 +13165,10 @@
         <v>509</v>
       </c>
       <c r="I296" s="12" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="J296" s="12" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.35">
@@ -13212,10 +13197,10 @@
         <v>507</v>
       </c>
       <c r="I297" s="12" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
       <c r="J297" s="12" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="298" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -13244,7 +13229,7 @@
         <v>507</v>
       </c>
       <c r="I298" s="12" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.35">
@@ -13299,10 +13284,10 @@
         <v>12</v>
       </c>
       <c r="I300" s="12" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="J300" s="12" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.35">
@@ -13431,7 +13416,7 @@
         <v>1092</v>
       </c>
       <c r="G306" s="7" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="H306" s="7" t="s">
         <v>66</v>
@@ -13459,7 +13444,7 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="B308" s="1" t="s">
         <v>1100</v>
@@ -13549,7 +13534,7 @@
         <v>1110</v>
       </c>
       <c r="G311" s="7" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="H311" s="7" t="s">
         <v>66</v>
@@ -13598,7 +13583,7 @@
         <v>1118</v>
       </c>
       <c r="G313" s="7" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="H313" s="7" t="s">
         <v>66</v>
@@ -13626,7 +13611,7 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>1125</v>
@@ -13672,7 +13657,7 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="B317" s="1" t="s">
         <v>1132</v>
@@ -13696,7 +13681,7 @@
         <v>12</v>
       </c>
       <c r="I317" s="12" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.35">
@@ -13704,19 +13689,19 @@
         <v>1135</v>
       </c>
       <c r="B318" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C318" s="7">
+        <v>269</v>
+      </c>
+      <c r="D318" s="7">
+        <v>180</v>
+      </c>
+      <c r="E318" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F318" s="7" t="s">
         <v>1136</v>
-      </c>
-      <c r="C318" s="7">
-        <v>298</v>
-      </c>
-      <c r="D318" s="7">
-        <v>200</v>
-      </c>
-      <c r="E318" s="7" t="s">
-        <v>1138</v>
-      </c>
-      <c r="F318" s="7" t="s">
-        <v>1137</v>
       </c>
       <c r="G318" s="7" t="s">
         <v>419</v>
@@ -13725,82 +13710,79 @@
         <v>66</v>
       </c>
       <c r="I318" s="12" t="s">
-        <v>1494</v>
-      </c>
-    </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1404</v>
+      </c>
+      <c r="J318" s="12" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C319" s="7">
+        <v>299</v>
+      </c>
+      <c r="D319" s="7">
+        <v>200</v>
+      </c>
+      <c r="E319" s="7" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F319" s="7" t="s">
         <v>1139</v>
       </c>
-      <c r="B319" s="1" t="s">
-        <v>1246</v>
-      </c>
-      <c r="C319" s="7">
-        <v>269</v>
-      </c>
-      <c r="D319" s="7">
-        <v>180</v>
-      </c>
-      <c r="E319" s="7" t="s">
+      <c r="G319" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="H319" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I319" s="12" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A320" s="1" t="s">
         <v>1141</v>
       </c>
-      <c r="F319" s="7" t="s">
-        <v>1140</v>
-      </c>
-      <c r="G319" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="H319" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I319" s="12" t="s">
-        <v>1408</v>
-      </c>
-      <c r="J319" s="12" t="s">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="320" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A320" s="1" t="s">
+      <c r="B320" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="C320" s="7">
+        <v>608</v>
+      </c>
+      <c r="D320" s="7">
+        <v>395</v>
+      </c>
+      <c r="E320" s="7" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F320" s="7" t="s">
         <v>1142</v>
       </c>
-      <c r="B320" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C320" s="7">
-        <v>299</v>
-      </c>
-      <c r="D320" s="7">
-        <v>200</v>
-      </c>
-      <c r="E320" s="7" t="s">
-        <v>1144</v>
-      </c>
-      <c r="F320" s="7" t="s">
-        <v>1143</v>
-      </c>
-      <c r="G320" s="7" t="s">
-        <v>590</v>
-      </c>
       <c r="H320" s="7" t="s">
-        <v>99</v>
+        <v>509</v>
       </c>
       <c r="I320" s="12" t="s">
-        <v>1518</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>1145</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>871</v>
-      </c>
       <c r="C321" s="7">
-        <v>608</v>
+        <v>298</v>
       </c>
       <c r="D321" s="7">
-        <v>395</v>
+        <v>270</v>
       </c>
       <c r="E321" s="7" t="s">
         <v>1147</v>
@@ -13808,121 +13790,121 @@
       <c r="F321" s="7" t="s">
         <v>1146</v>
       </c>
+      <c r="G321" s="7" t="s">
+        <v>908</v>
+      </c>
       <c r="H321" s="7" t="s">
-        <v>509</v>
+        <v>12</v>
       </c>
       <c r="I321" s="12" t="s">
-        <v>1441</v>
+        <v>1493</v>
+      </c>
+      <c r="J321" s="12" t="s">
+        <v>1492</v>
       </c>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C322" s="7">
+        <v>299</v>
+      </c>
+      <c r="D322" s="7">
+        <v>200</v>
+      </c>
+      <c r="E322" s="7" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F322" s="7" t="s">
         <v>1148</v>
       </c>
-      <c r="B322" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C322" s="7">
-        <v>298</v>
-      </c>
-      <c r="D322" s="7">
-        <v>270</v>
-      </c>
-      <c r="E322" s="7" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F322" s="7" t="s">
-        <v>1150</v>
-      </c>
-      <c r="G322" s="7" t="s">
-        <v>908</v>
-      </c>
       <c r="H322" s="7" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="I322" s="12" t="s">
-        <v>1498</v>
-      </c>
-      <c r="J322" s="12" t="s">
-        <v>1497</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C323" s="7">
-        <v>299</v>
+        <v>2791</v>
       </c>
       <c r="D323" s="7">
-        <v>200</v>
-      </c>
-      <c r="E323" s="7" t="s">
-        <v>1233</v>
+        <v>1700</v>
+      </c>
+      <c r="E323" s="12" t="s">
+        <v>1260</v>
       </c>
       <c r="F323" s="7" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="H323" s="7" t="s">
-        <v>99</v>
+        <v>507</v>
       </c>
       <c r="I323" s="12" t="s">
-        <v>1519</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C324" s="7">
+        <v>500</v>
+      </c>
+      <c r="E324" s="7" t="s">
         <v>1155</v>
-      </c>
-      <c r="B324" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C324" s="7">
-        <v>2791</v>
-      </c>
-      <c r="D324" s="7">
-        <v>1700</v>
-      </c>
-      <c r="E324" s="12" t="s">
-        <v>1264</v>
       </c>
       <c r="F324" s="7" t="s">
         <v>1154</v>
       </c>
       <c r="H324" s="7" t="s">
-        <v>507</v>
+        <v>66</v>
       </c>
       <c r="I324" s="12" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C325" s="7">
-        <v>500</v>
+        <v>1665</v>
+      </c>
+      <c r="D325" s="7">
+        <v>1500</v>
       </c>
       <c r="E325" s="7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F325" s="7" t="s">
         <v>1159</v>
       </c>
-      <c r="F325" s="7" t="s">
-        <v>1158</v>
-      </c>
       <c r="H325" s="7" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="I325" s="12" t="s">
-        <v>1424</v>
-      </c>
-    </row>
-    <row r="326" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>1161</v>
       </c>
@@ -13930,10 +13912,10 @@
         <v>1162</v>
       </c>
       <c r="C326" s="7">
-        <v>1665</v>
+        <v>850</v>
       </c>
       <c r="D326" s="7">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="E326" s="7" t="s">
         <v>1164</v>
@@ -13941,303 +13923,303 @@
       <c r="F326" s="7" t="s">
         <v>1163</v>
       </c>
+      <c r="G326" s="7" t="s">
+        <v>1247</v>
+      </c>
       <c r="H326" s="7" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="I326" s="12" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="C327" s="7">
-        <v>850</v>
+        <v>200</v>
       </c>
       <c r="D327" s="7">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="E327" s="7" t="s">
         <v>1168</v>
       </c>
       <c r="F327" s="7" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="G327" s="7" t="s">
-        <v>1251</v>
+        <v>873</v>
       </c>
       <c r="H327" s="7" t="s">
-        <v>66</v>
+        <v>507</v>
       </c>
       <c r="I327" s="12" t="s">
         <v>1465</v>
       </c>
+      <c r="J327" s="12" t="s">
+        <v>1464</v>
+      </c>
     </row>
     <row r="328" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C328" s="7">
+        <v>239</v>
+      </c>
+      <c r="D328" s="7">
+        <v>130</v>
+      </c>
+      <c r="E328" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F328" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C328" s="7">
-        <v>200</v>
-      </c>
-      <c r="D328" s="7">
-        <v>150</v>
-      </c>
-      <c r="E328" s="7" t="s">
-        <v>1172</v>
-      </c>
-      <c r="F328" s="7" t="s">
-        <v>1169</v>
-      </c>
-      <c r="G328" s="7" t="s">
-        <v>873</v>
-      </c>
       <c r="H328" s="7" t="s">
-        <v>507</v>
+        <v>99</v>
       </c>
       <c r="I328" s="12" t="s">
-        <v>1469</v>
+        <v>1522</v>
       </c>
       <c r="J328" s="12" t="s">
-        <v>1468</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="329" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C329" s="7">
+        <v>729</v>
+      </c>
+      <c r="D329" s="7">
+        <v>350</v>
+      </c>
+      <c r="E329" s="7" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F329" s="7" t="s">
         <v>1173</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C329" s="7">
-        <v>239</v>
-      </c>
-      <c r="D329" s="7">
-        <v>130</v>
-      </c>
-      <c r="E329" s="7" t="s">
-        <v>1175</v>
-      </c>
-      <c r="F329" s="7" t="s">
-        <v>1174</v>
-      </c>
       <c r="H329" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I329" s="12" t="s">
-        <v>1527</v>
-      </c>
-      <c r="J329" s="12" t="s">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="330" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>1179</v>
       </c>
       <c r="C330" s="7">
-        <v>729</v>
+        <v>1299</v>
       </c>
       <c r="D330" s="7">
-        <v>350</v>
+        <v>650</v>
       </c>
       <c r="E330" s="7" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="F330" s="7" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H330" s="7" t="s">
-        <v>197</v>
+        <v>66</v>
+      </c>
+      <c r="I330" s="12" t="s">
+        <v>1482</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C331" s="7">
+        <v>350</v>
+      </c>
+      <c r="D331" s="7">
+        <v>200</v>
+      </c>
+      <c r="E331" s="7" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F331" s="7" t="s">
         <v>1182</v>
-      </c>
-      <c r="B331" s="1" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C331" s="7">
-        <v>1299</v>
-      </c>
-      <c r="D331" s="7">
-        <v>650</v>
-      </c>
-      <c r="E331" s="7" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F331" s="7" t="s">
-        <v>1180</v>
       </c>
       <c r="H331" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I331" s="12" t="s">
-        <v>1486</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C332" s="7">
+        <v>150</v>
+      </c>
+      <c r="D332" s="7">
+        <v>100</v>
+      </c>
+      <c r="E332" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F332" s="7" t="s">
         <v>1184</v>
-      </c>
-      <c r="B332" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C332" s="7">
-        <v>350</v>
-      </c>
-      <c r="D332" s="7">
-        <v>200</v>
-      </c>
-      <c r="E332" s="7" t="s">
-        <v>1187</v>
-      </c>
-      <c r="F332" s="7" t="s">
-        <v>1186</v>
       </c>
       <c r="H332" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I332" s="12" t="s">
-        <v>1412</v>
-      </c>
-    </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="333" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C333" s="7">
+        <v>349</v>
+      </c>
+      <c r="D333" s="7">
+        <v>200</v>
+      </c>
+      <c r="E333" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F333" s="7" t="s">
         <v>1190</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C333" s="7">
-        <v>150</v>
-      </c>
-      <c r="D333" s="7">
-        <v>100</v>
-      </c>
-      <c r="E333" s="7" t="s">
-        <v>1189</v>
-      </c>
-      <c r="F333" s="7" t="s">
-        <v>1188</v>
       </c>
       <c r="H333" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="334" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
         <v>1192</v>
       </c>
       <c r="B334" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C334" s="7">
+        <v>800</v>
+      </c>
+      <c r="D334" s="7">
+        <v>750</v>
+      </c>
+      <c r="E334" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F334" s="7" t="s">
         <v>1193</v>
       </c>
-      <c r="C334" s="7">
-        <v>349</v>
-      </c>
-      <c r="D334" s="7">
-        <v>200</v>
-      </c>
-      <c r="E334" s="7" t="s">
-        <v>1195</v>
-      </c>
-      <c r="F334" s="7" t="s">
-        <v>1194</v>
-      </c>
       <c r="H334" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="335" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>507</v>
+      </c>
+      <c r="I334" s="12" t="s">
+        <v>1366</v>
+      </c>
+      <c r="J334" s="12" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>1199</v>
       </c>
       <c r="C335" s="7">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="D335" s="7">
-        <v>750</v>
+        <v>170</v>
       </c>
       <c r="E335" s="7" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="F335" s="7" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="H335" s="7" t="s">
-        <v>507</v>
+        <v>66</v>
       </c>
       <c r="I335" s="12" t="s">
-        <v>1370</v>
+        <v>1417</v>
       </c>
       <c r="J335" s="12" t="s">
-        <v>1369</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C336" s="7">
+        <v>399</v>
+      </c>
+      <c r="D336" s="7">
+        <v>250</v>
+      </c>
+      <c r="E336" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F336" s="7" t="s">
         <v>1202</v>
       </c>
-      <c r="B336" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="C336" s="7">
-        <v>200</v>
-      </c>
-      <c r="D336" s="7">
-        <v>170</v>
-      </c>
-      <c r="E336" s="7" t="s">
-        <v>1201</v>
-      </c>
-      <c r="F336" s="7" t="s">
-        <v>1200</v>
+      <c r="G336" s="7" t="s">
+        <v>1247</v>
       </c>
       <c r="H336" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I336" s="12" t="s">
-        <v>1421</v>
-      </c>
-      <c r="J336" s="12" t="s">
-        <v>1420</v>
-      </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="C337" s="7">
         <v>399</v>
       </c>
       <c r="D337" s="7">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E337" s="7" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="F337" s="7" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="G337" s="7" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="H337" s="7" t="s">
         <v>66</v>
@@ -14245,48 +14227,48 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
-        <v>1253</v>
+        <v>1214</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>1204</v>
+        <v>1220</v>
       </c>
       <c r="C338" s="7">
-        <v>399</v>
+        <v>170</v>
       </c>
       <c r="D338" s="7">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="E338" s="7" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="F338" s="7" t="s">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="G338" s="7" t="s">
-        <v>1251</v>
+        <v>908</v>
       </c>
       <c r="H338" s="7" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C339" s="7">
+        <v>262</v>
+      </c>
+      <c r="D339" s="7">
+        <v>190</v>
+      </c>
+      <c r="E339" s="7" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F339" s="7" t="s">
         <v>1218</v>
-      </c>
-      <c r="B339" s="1" t="s">
-        <v>1224</v>
-      </c>
-      <c r="C339" s="7">
-        <v>170</v>
-      </c>
-      <c r="D339" s="7">
-        <v>150</v>
-      </c>
-      <c r="E339" s="7" t="s">
-        <v>1220</v>
-      </c>
-      <c r="F339" s="7" t="s">
-        <v>1219</v>
       </c>
       <c r="G339" s="7" t="s">
         <v>908</v>
@@ -14297,22 +14279,22 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="C340" s="7">
-        <v>262</v>
+        <v>468</v>
       </c>
       <c r="D340" s="7">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="E340" s="7" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F340" s="7" t="s">
         <v>1223</v>
-      </c>
-      <c r="F340" s="7" t="s">
-        <v>1222</v>
       </c>
       <c r="G340" s="7" t="s">
         <v>908</v>
@@ -14323,22 +14305,22 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C341" s="7">
+        <v>299</v>
+      </c>
+      <c r="D341" s="7">
+        <v>150</v>
+      </c>
+      <c r="E341" s="7" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F341" s="7" t="s">
         <v>1226</v>
-      </c>
-      <c r="B341" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="C341" s="7">
-        <v>468</v>
-      </c>
-      <c r="D341" s="7">
-        <v>255</v>
-      </c>
-      <c r="E341" s="7" t="s">
-        <v>1228</v>
-      </c>
-      <c r="F341" s="7" t="s">
-        <v>1227</v>
       </c>
       <c r="G341" s="7" t="s">
         <v>908</v>
@@ -14349,22 +14331,22 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>9</v>
+        <v>1231</v>
       </c>
       <c r="C342" s="7">
-        <v>299</v>
+        <v>447</v>
       </c>
       <c r="D342" s="7">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E342" s="7" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="F342" s="7" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="G342" s="7" t="s">
         <v>908</v>
@@ -14373,47 +14355,47 @@
         <v>12</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>1235</v>
+        <v>1258</v>
       </c>
       <c r="C343" s="7">
-        <v>447</v>
-      </c>
-      <c r="D343" s="7">
-        <v>250</v>
-      </c>
-      <c r="E343" s="7" t="s">
-        <v>1237</v>
+        <v>350</v>
+      </c>
+      <c r="E343" s="12" t="s">
+        <v>1257</v>
       </c>
       <c r="F343" s="7" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G343" s="7" t="s">
-        <v>908</v>
+        <v>1236</v>
       </c>
       <c r="H343" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="344" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>1262</v>
+        <v>1244</v>
       </c>
       <c r="C344" s="7">
-        <v>350</v>
-      </c>
-      <c r="E344" s="12" t="s">
-        <v>1261</v>
+        <v>200</v>
+      </c>
+      <c r="D344" s="7">
+        <v>120</v>
+      </c>
+      <c r="E344" s="7" t="s">
+        <v>1246</v>
       </c>
       <c r="F344" s="7" t="s">
-        <v>1240</v>
+        <v>1245</v>
+      </c>
+      <c r="G344" s="7" t="s">
+        <v>419</v>
       </c>
       <c r="H344" s="7" t="s">
         <v>66</v>
@@ -14421,22 +14403,22 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="C345" s="7">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="D345" s="7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E345" s="7" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="F345" s="7" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="G345" s="7" t="s">
         <v>419</v>
@@ -14445,33 +14427,36 @@
         <v>66</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="C346" s="7">
-        <v>147</v>
+        <v>899</v>
       </c>
       <c r="D346" s="7">
-        <v>100</v>
-      </c>
-      <c r="E346" s="7" t="s">
-        <v>1259</v>
-      </c>
-      <c r="F346" s="7" t="s">
-        <v>1258</v>
+        <v>485</v>
+      </c>
+      <c r="E346" s="12" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F346" s="12" t="s">
+        <v>1264</v>
       </c>
       <c r="G346" s="7" t="s">
-        <v>419</v>
+        <v>853</v>
       </c>
       <c r="H346" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="347" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>508</v>
+      </c>
+      <c r="I346" s="12" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>1266</v>
       </c>
@@ -14479,10 +14464,10 @@
         <v>1267</v>
       </c>
       <c r="C347" s="7">
-        <v>899</v>
+        <v>1050</v>
       </c>
       <c r="D347" s="7">
-        <v>485</v>
+        <v>600</v>
       </c>
       <c r="E347" s="12" t="s">
         <v>1269</v>
@@ -14497,7 +14482,10 @@
         <v>508</v>
       </c>
       <c r="I347" s="12" t="s">
-        <v>1411</v>
+        <v>1382</v>
+      </c>
+      <c r="J347" s="12" t="s">
+        <v>1383</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.35">
@@ -14508,10 +14496,10 @@
         <v>1271</v>
       </c>
       <c r="C348" s="7">
-        <v>1050</v>
+        <v>1084</v>
       </c>
       <c r="D348" s="7">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="E348" s="12" t="s">
         <v>1273</v>
@@ -14523,33 +14511,30 @@
         <v>853</v>
       </c>
       <c r="H348" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="I348" s="12" t="s">
-        <v>1386</v>
-      </c>
-      <c r="J348" s="12" t="s">
-        <v>1387</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="C349" s="7">
-        <v>1084</v>
+        <v>1265</v>
       </c>
       <c r="D349" s="7">
         <v>650</v>
       </c>
       <c r="E349" s="12" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="F349" s="12" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="G349" s="7" t="s">
         <v>853</v>
@@ -14558,21 +14543,21 @@
         <v>507</v>
       </c>
       <c r="I349" s="12" t="s">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
-        <v>1280</v>
+        <v>1289</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="C350" s="7">
-        <v>1265</v>
+        <v>1225</v>
       </c>
       <c r="D350" s="7">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="E350" s="12" t="s">
         <v>1279</v>
@@ -14584,18 +14569,21 @@
         <v>853</v>
       </c>
       <c r="H350" s="7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I350" s="12" t="s">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="351" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>1370</v>
+      </c>
+      <c r="J350" s="12" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="C351" s="7">
         <v>1225</v>
@@ -14604,10 +14592,10 @@
         <v>700</v>
       </c>
       <c r="E351" s="12" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="F351" s="12" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="G351" s="7" t="s">
         <v>853</v>
@@ -14616,30 +14604,30 @@
         <v>508</v>
       </c>
       <c r="I351" s="12" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="J351" s="12" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="352" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="C352" s="7">
-        <v>1225</v>
+        <v>614</v>
       </c>
       <c r="D352" s="7">
-        <v>700</v>
+        <v>375</v>
       </c>
       <c r="E352" s="12" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F352" s="12" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="G352" s="7" t="s">
         <v>853</v>
@@ -14647,31 +14635,25 @@
       <c r="H352" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="I352" s="12" t="s">
-        <v>1376</v>
-      </c>
-      <c r="J352" s="12" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="353" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="353" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="C353" s="7">
-        <v>614</v>
+        <v>946</v>
       </c>
       <c r="D353" s="7">
-        <v>375</v>
+        <v>575</v>
       </c>
       <c r="E353" s="12" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="F353" s="12" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="G353" s="7" t="s">
         <v>853</v>
@@ -14679,25 +14661,31 @@
       <c r="H353" s="7" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="354" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="I353" s="12" t="s">
+        <v>1475</v>
+      </c>
+      <c r="J353" s="12" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
-        <v>1300</v>
+        <v>1290</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>1301</v>
+        <v>1291</v>
       </c>
       <c r="C354" s="7">
-        <v>946</v>
+        <v>1174</v>
       </c>
       <c r="D354" s="7">
-        <v>575</v>
+        <v>700</v>
       </c>
       <c r="E354" s="12" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="F354" s="12" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="G354" s="7" t="s">
         <v>853</v>
@@ -14706,74 +14694,74 @@
         <v>508</v>
       </c>
       <c r="I354" s="12" t="s">
-        <v>1479</v>
+        <v>1369</v>
       </c>
       <c r="J354" s="12" t="s">
-        <v>1478</v>
-      </c>
-    </row>
-    <row r="355" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="C355" s="7">
-        <v>1174</v>
+        <v>1395</v>
       </c>
       <c r="D355" s="7">
-        <v>700</v>
+        <v>920</v>
       </c>
       <c r="E355" s="12" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="F355" s="12" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="G355" s="7" t="s">
         <v>853</v>
       </c>
       <c r="H355" s="7" t="s">
-        <v>508</v>
+        <v>66</v>
       </c>
       <c r="I355" s="12" t="s">
-        <v>1373</v>
-      </c>
-      <c r="J355" s="12" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="356" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>1302</v>
       </c>
       <c r="B356" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C356" s="7">
+        <v>554</v>
+      </c>
+      <c r="D356" s="7">
+        <v>200</v>
+      </c>
+      <c r="E356" s="12" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F356" s="12" t="s">
         <v>1303</v>
-      </c>
-      <c r="C356" s="7">
-        <v>1395</v>
-      </c>
-      <c r="D356" s="7">
-        <v>920</v>
-      </c>
-      <c r="E356" s="12" t="s">
-        <v>1305</v>
-      </c>
-      <c r="F356" s="12" t="s">
-        <v>1304</v>
       </c>
       <c r="G356" s="7" t="s">
         <v>853</v>
       </c>
       <c r="H356" s="7" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="I356" s="12" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1519</v>
+      </c>
+      <c r="J356" s="12" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>1306</v>
       </c>
@@ -14781,10 +14769,10 @@
         <v>1309</v>
       </c>
       <c r="C357" s="7">
-        <v>554</v>
+        <v>398</v>
       </c>
       <c r="D357" s="7">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E357" s="12" t="s">
         <v>1308</v>
@@ -14796,13 +14784,7 @@
         <v>853</v>
       </c>
       <c r="H357" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I357" s="12" t="s">
-        <v>1524</v>
-      </c>
-      <c r="J357" s="12" t="s">
-        <v>1523</v>
+        <v>508</v>
       </c>
     </row>
     <row r="358" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -14810,28 +14792,34 @@
         <v>1310</v>
       </c>
       <c r="B358" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C358" s="7">
+        <v>397</v>
+      </c>
+      <c r="D358" s="7">
+        <v>300</v>
+      </c>
+      <c r="E358" s="12" t="s">
         <v>1313</v>
       </c>
-      <c r="C358" s="7">
-        <v>398</v>
-      </c>
-      <c r="D358" s="7">
-        <v>250</v>
-      </c>
-      <c r="E358" s="12" t="s">
+      <c r="F358" s="12" t="s">
         <v>1312</v>
-      </c>
-      <c r="F358" s="12" t="s">
-        <v>1311</v>
       </c>
       <c r="G358" s="7" t="s">
         <v>853</v>
       </c>
       <c r="H358" s="7" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="359" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+      <c r="I358" s="12" t="s">
+        <v>1390</v>
+      </c>
+      <c r="J358" s="12" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>1314</v>
       </c>
@@ -14839,7 +14827,7 @@
         <v>1315</v>
       </c>
       <c r="C359" s="7">
-        <v>397</v>
+        <v>350</v>
       </c>
       <c r="D359" s="7">
         <v>300</v>
@@ -14854,33 +14842,33 @@
         <v>853</v>
       </c>
       <c r="H359" s="7" t="s">
-        <v>197</v>
+        <v>66</v>
       </c>
       <c r="I359" s="12" t="s">
-        <v>1394</v>
+        <v>1484</v>
       </c>
       <c r="J359" s="12" t="s">
-        <v>1395</v>
-      </c>
-    </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="C360" s="7">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="D360" s="7">
         <v>300</v>
       </c>
       <c r="E360" s="12" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="F360" s="12" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="G360" s="7" t="s">
         <v>853</v>
@@ -14889,30 +14877,27 @@
         <v>66</v>
       </c>
       <c r="I360" s="12" t="s">
-        <v>1488</v>
-      </c>
-      <c r="J360" s="12" t="s">
-        <v>1487</v>
-      </c>
-    </row>
-    <row r="361" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C361" s="7">
+        <v>1690</v>
+      </c>
+      <c r="D361" s="7">
+        <v>1090</v>
+      </c>
+      <c r="E361" s="12" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F361" s="12" t="s">
         <v>1324</v>
-      </c>
-      <c r="B361" s="1" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C361" s="7">
-        <v>385</v>
-      </c>
-      <c r="D361" s="7">
-        <v>300</v>
-      </c>
-      <c r="E361" s="12" t="s">
-        <v>1323</v>
-      </c>
-      <c r="F361" s="12" t="s">
-        <v>1322</v>
       </c>
       <c r="G361" s="7" t="s">
         <v>853</v>
@@ -14921,7 +14906,7 @@
         <v>66</v>
       </c>
       <c r="I361" s="12" t="s">
-        <v>1390</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="362" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -14929,42 +14914,42 @@
         <v>1327</v>
       </c>
       <c r="B362" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C362" s="7">
+        <v>1999</v>
+      </c>
+      <c r="D362" s="7">
+        <v>800</v>
+      </c>
+      <c r="E362" s="12" t="s">
         <v>1326</v>
       </c>
-      <c r="C362" s="7">
-        <v>1690</v>
-      </c>
-      <c r="D362" s="7">
-        <v>1090</v>
-      </c>
-      <c r="E362" s="12" t="s">
-        <v>1389</v>
-      </c>
       <c r="F362" s="12" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="G362" s="7" t="s">
         <v>853</v>
       </c>
       <c r="H362" s="7" t="s">
-        <v>66</v>
+        <v>197</v>
       </c>
       <c r="I362" s="12" t="s">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="363" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B363" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="B363" s="1" t="s">
-        <v>1332</v>
-      </c>
       <c r="C363" s="7">
-        <v>1999</v>
+        <v>4699</v>
       </c>
       <c r="D363" s="7">
-        <v>800</v>
+        <v>2832</v>
       </c>
       <c r="E363" s="12" t="s">
         <v>1330</v>
@@ -14976,77 +14961,77 @@
         <v>853</v>
       </c>
       <c r="H363" s="7" t="s">
-        <v>197</v>
+        <v>507</v>
       </c>
       <c r="I363" s="12" t="s">
-        <v>1367</v>
-      </c>
-    </row>
-    <row r="364" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1350</v>
+      </c>
+      <c r="J363" s="12" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C364" s="7">
+        <v>349</v>
+      </c>
+      <c r="D364" s="7">
+        <v>295</v>
+      </c>
+      <c r="E364" s="12" t="s">
         <v>1336</v>
       </c>
-      <c r="B364" s="1" t="s">
+      <c r="F364" s="12" t="s">
         <v>1335</v>
       </c>
-      <c r="C364" s="7">
-        <v>4699</v>
-      </c>
-      <c r="D364" s="7">
-        <v>2832</v>
-      </c>
-      <c r="E364" s="12" t="s">
-        <v>1334</v>
-      </c>
-      <c r="F364" s="12" t="s">
-        <v>1333</v>
-      </c>
       <c r="G364" s="7" t="s">
-        <v>853</v>
+        <v>419</v>
       </c>
       <c r="H364" s="7" t="s">
-        <v>507</v>
+        <v>66</v>
       </c>
       <c r="I364" s="12" t="s">
-        <v>1354</v>
+        <v>1439</v>
       </c>
       <c r="J364" s="12" t="s">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
-        <v>1337</v>
+        <v>1540</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>1338</v>
+        <v>1541</v>
       </c>
       <c r="C365" s="7">
-        <v>349</v>
+        <v>2549</v>
       </c>
       <c r="D365" s="7">
-        <v>295</v>
+        <v>1800</v>
       </c>
       <c r="E365" s="12" t="s">
-        <v>1340</v>
+        <v>1544</v>
       </c>
       <c r="F365" s="12" t="s">
-        <v>1339</v>
+        <v>1542</v>
       </c>
       <c r="G365" s="7" t="s">
-        <v>419</v>
+        <v>590</v>
       </c>
       <c r="H365" s="7" t="s">
         <v>66</v>
       </c>
       <c r="I365" s="12" t="s">
-        <v>1443</v>
-      </c>
-      <c r="J365" s="12" t="s">
-        <v>1442</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>1545</v>
       </c>
@@ -15054,16 +15039,16 @@
         <v>1546</v>
       </c>
       <c r="C366" s="7">
-        <v>2549</v>
+        <v>298</v>
       </c>
       <c r="D366" s="7">
-        <v>1800</v>
+        <v>220</v>
       </c>
       <c r="E366" s="12" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="F366" s="12" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="G366" s="7" t="s">
         <v>590</v>
@@ -15071,34 +15056,34 @@
       <c r="H366" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I366" s="12" t="s">
-        <v>1548</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="367" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B367" s="1" t="s">
         <v>1550</v>
       </c>
-      <c r="B367" s="1" t="s">
+      <c r="C367" s="7">
+        <v>999</v>
+      </c>
+      <c r="D367" s="7">
+        <v>635</v>
+      </c>
+      <c r="E367" s="12" t="s">
         <v>1551</v>
       </c>
-      <c r="C367" s="7">
-        <v>298</v>
-      </c>
-      <c r="D367" s="7">
-        <v>220</v>
-      </c>
-      <c r="E367" s="12" t="s">
+      <c r="F367" s="12" t="s">
         <v>1552</v>
-      </c>
-      <c r="F367" s="12" t="s">
-        <v>1553</v>
       </c>
       <c r="G367" s="7" t="s">
         <v>590</v>
       </c>
       <c r="H367" s="7" t="s">
-        <v>66</v>
+        <v>507</v>
+      </c>
+      <c r="I367" s="12" t="s">
+        <v>1553</v>
       </c>
     </row>
     <row r="368" spans="1:10" ht="29" x14ac:dyDescent="0.35">
@@ -15109,126 +15094,126 @@
         <v>1555</v>
       </c>
       <c r="C368" s="7">
-        <v>999</v>
+        <v>798</v>
       </c>
       <c r="D368" s="7">
-        <v>635</v>
+        <v>250</v>
       </c>
       <c r="E368" s="12" t="s">
         <v>1556</v>
       </c>
       <c r="F368" s="12" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="G368" s="7" t="s">
         <v>590</v>
       </c>
       <c r="H368" s="7" t="s">
-        <v>507</v>
+        <v>66</v>
       </c>
       <c r="I368" s="12" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="369" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B369" s="1" t="s">
         <v>1559</v>
       </c>
-      <c r="B369" s="1" t="s">
-        <v>1560</v>
-      </c>
       <c r="C369" s="7">
-        <v>798</v>
+        <v>309</v>
       </c>
       <c r="D369" s="7">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="E369" s="12" t="s">
         <v>1561</v>
       </c>
       <c r="F369" s="12" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="G369" s="7" t="s">
         <v>590</v>
       </c>
       <c r="H369" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I369" s="12" t="s">
-        <v>1562</v>
+        <v>12</v>
       </c>
     </row>
     <row r="370" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="C370" s="7">
-        <v>309</v>
+        <v>509</v>
       </c>
       <c r="D370" s="7">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="E370" s="12" t="s">
         <v>1566</v>
       </c>
       <c r="F370" s="12" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="G370" s="7" t="s">
         <v>590</v>
       </c>
       <c r="H370" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="I370" s="12" t="s">
+        <v>1567</v>
+      </c>
+      <c r="J370" s="12" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B371" s="1" t="s">
         <v>1569</v>
       </c>
-      <c r="B371" s="1" t="s">
-        <v>1568</v>
-      </c>
       <c r="C371" s="7">
-        <v>509</v>
+        <v>277</v>
       </c>
       <c r="D371" s="7">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="E371" s="12" t="s">
+        <v>1572</v>
+      </c>
+      <c r="F371" s="12" t="s">
         <v>1571</v>
-      </c>
-      <c r="F371" s="12" t="s">
-        <v>1570</v>
       </c>
       <c r="G371" s="7" t="s">
         <v>590</v>
       </c>
       <c r="H371" s="7" t="s">
-        <v>66</v>
+        <v>509</v>
       </c>
       <c r="I371" s="12" t="s">
-        <v>1572</v>
-      </c>
-      <c r="J371" s="12" t="s">
         <v>1573</v>
       </c>
     </row>
-    <row r="372" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B372" s="1" t="s">
         <v>1575</v>
       </c>
-      <c r="B372" s="1" t="s">
-        <v>1574</v>
-      </c>
       <c r="C372" s="7">
-        <v>277</v>
+        <v>399</v>
       </c>
       <c r="D372" s="7">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E372" s="12" t="s">
         <v>1577</v>
@@ -15240,41 +15225,41 @@
         <v>590</v>
       </c>
       <c r="H372" s="7" t="s">
-        <v>509</v>
+        <v>66</v>
       </c>
       <c r="I372" s="12" t="s">
         <v>1578</v>
       </c>
+      <c r="J372" s="12" t="s">
+        <v>1579</v>
+      </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="C373" s="7">
-        <v>399</v>
+        <v>509</v>
       </c>
       <c r="D373" s="7">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="E373" s="12" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F373" s="12" t="s">
         <v>1582</v>
-      </c>
-      <c r="F373" s="12" t="s">
-        <v>1581</v>
       </c>
       <c r="G373" s="7" t="s">
         <v>590</v>
       </c>
       <c r="H373" s="7" t="s">
-        <v>66</v>
+        <v>507</v>
       </c>
       <c r="I373" s="12" t="s">
-        <v>1583</v>
-      </c>
-      <c r="J373" s="12" t="s">
         <v>1584</v>
       </c>
     </row>
@@ -15286,10 +15271,10 @@
         <v>1586</v>
       </c>
       <c r="C374" s="7">
-        <v>509</v>
+        <v>247</v>
       </c>
       <c r="D374" s="7">
-        <v>350</v>
+        <v>139</v>
       </c>
       <c r="E374" s="12" t="s">
         <v>1588</v>
@@ -15301,30 +15286,27 @@
         <v>590</v>
       </c>
       <c r="H374" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="I374" s="12" t="s">
-        <v>1589</v>
+        <v>99</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B375" s="1" t="s">
         <v>1590</v>
       </c>
-      <c r="B375" s="1" t="s">
+      <c r="C375" s="7">
+        <v>282</v>
+      </c>
+      <c r="D375" s="7">
+        <v>200</v>
+      </c>
+      <c r="E375" s="12" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F375" s="12" t="s">
         <v>1591</v>
-      </c>
-      <c r="C375" s="7">
-        <v>247</v>
-      </c>
-      <c r="D375" s="7">
-        <v>139</v>
-      </c>
-      <c r="E375" s="12" t="s">
-        <v>1593</v>
-      </c>
-      <c r="F375" s="12" t="s">
-        <v>1592</v>
       </c>
       <c r="G375" s="7" t="s">
         <v>590</v>
@@ -15335,48 +15317,48 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C376" s="7">
+        <v>580</v>
+      </c>
+      <c r="D376" s="7">
+        <v>400</v>
+      </c>
+      <c r="E376" s="12" t="s">
         <v>1594</v>
       </c>
-      <c r="B376" s="1" t="s">
-        <v>1595</v>
-      </c>
-      <c r="C376" s="7">
-        <v>282</v>
-      </c>
-      <c r="D376" s="7">
-        <v>200</v>
-      </c>
-      <c r="E376" s="12" t="s">
-        <v>1597</v>
-      </c>
       <c r="F376" s="12" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="G376" s="7" t="s">
         <v>590</v>
       </c>
       <c r="H376" s="7" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
-        <v>1600</v>
+        <v>1596</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="C377" s="7">
-        <v>580</v>
+        <v>300</v>
       </c>
       <c r="D377" s="7">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E377" s="12" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="F377" s="12" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="G377" s="7" t="s">
         <v>590</v>
@@ -15390,25 +15372,28 @@
         <v>1601</v>
       </c>
       <c r="B378" s="1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C378" s="7">
+        <v>1104</v>
+      </c>
+      <c r="D378" s="7">
+        <v>775</v>
+      </c>
+      <c r="E378" s="12" t="s">
         <v>1604</v>
       </c>
-      <c r="C378" s="7">
-        <v>300</v>
-      </c>
-      <c r="D378" s="7">
-        <v>200</v>
-      </c>
-      <c r="E378" s="12" t="s">
+      <c r="F378" s="12" t="s">
         <v>1603</v>
-      </c>
-      <c r="F378" s="12" t="s">
-        <v>1602</v>
       </c>
       <c r="G378" s="7" t="s">
         <v>590</v>
       </c>
       <c r="H378" s="7" t="s">
-        <v>12</v>
+        <v>66</v>
+      </c>
+      <c r="I378" s="12" t="s">
+        <v>1605</v>
       </c>
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.35">
@@ -15419,10 +15404,10 @@
         <v>1607</v>
       </c>
       <c r="C379" s="7">
-        <v>1104</v>
+        <v>852</v>
       </c>
       <c r="D379" s="7">
-        <v>775</v>
+        <v>350</v>
       </c>
       <c r="E379" s="12" t="s">
         <v>1609</v>
@@ -15434,24 +15419,27 @@
         <v>590</v>
       </c>
       <c r="H379" s="7" t="s">
-        <v>66</v>
+        <v>507</v>
       </c>
       <c r="I379" s="12" t="s">
+        <v>1611</v>
+      </c>
+      <c r="J379" s="12" t="s">
         <v>1610</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="C380" s="7">
-        <v>852</v>
+        <v>1274</v>
       </c>
       <c r="D380" s="7">
-        <v>350</v>
+        <v>770</v>
       </c>
       <c r="E380" s="12" t="s">
         <v>1614</v>
@@ -15463,38 +15451,6 @@
         <v>590</v>
       </c>
       <c r="H380" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="I380" s="12" t="s">
-        <v>1616</v>
-      </c>
-      <c r="J380" s="12" t="s">
-        <v>1615</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A381" s="1" t="s">
-        <v>1617</v>
-      </c>
-      <c r="B381" s="1" t="s">
-        <v>1620</v>
-      </c>
-      <c r="C381" s="7">
-        <v>1274</v>
-      </c>
-      <c r="D381" s="7">
-        <v>770</v>
-      </c>
-      <c r="E381" s="12" t="s">
-        <v>1619</v>
-      </c>
-      <c r="F381" s="12" t="s">
-        <v>1618</v>
-      </c>
-      <c r="G381" s="7" t="s">
-        <v>590</v>
-      </c>
-      <c r="H381" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -15505,46 +15461,46 @@
     <hyperlink ref="F61" r:id="rId3"/>
     <hyperlink ref="E268" r:id="rId4"/>
     <hyperlink ref="E61" r:id="rId5"/>
-    <hyperlink ref="E344" r:id="rId6"/>
+    <hyperlink ref="E343" r:id="rId6"/>
     <hyperlink ref="E250" r:id="rId7"/>
-    <hyperlink ref="E324" r:id="rId8"/>
+    <hyperlink ref="E323" r:id="rId8"/>
     <hyperlink ref="E151" r:id="rId9"/>
-    <hyperlink ref="F347" r:id="rId10" location="&amp;gid=1&amp;pid=1"/>
-    <hyperlink ref="E347" r:id="rId11"/>
-    <hyperlink ref="F348" r:id="rId12" location="&amp;gid=1&amp;pid=1"/>
-    <hyperlink ref="E348" r:id="rId13"/>
-    <hyperlink ref="F349" r:id="rId14" location="&amp;gid=1&amp;pid=1"/>
-    <hyperlink ref="E349" r:id="rId15"/>
-    <hyperlink ref="F350" r:id="rId16"/>
-    <hyperlink ref="E350" r:id="rId17"/>
-    <hyperlink ref="F351" r:id="rId18"/>
-    <hyperlink ref="E351" r:id="rId19"/>
-    <hyperlink ref="F352" display="https://www.mercadolibre.com.mx/epicentro-audishako-max-02-restaurador-de-bajos-para-auto-subwoofer-para-carro-pickups-y-suv-accesorios-para-auto-audio-diseno-en-relieve-3d-incluye-dash-remoto-control-de-bajos/p/MLM64640099?pdp_filters=item_id:MLM46970202"/>
-    <hyperlink ref="E352" r:id="rId20"/>
-    <hyperlink ref="F353" r:id="rId21"/>
-    <hyperlink ref="E353" r:id="rId22"/>
-    <hyperlink ref="F354" r:id="rId23"/>
-    <hyperlink ref="E354" r:id="rId24"/>
-    <hyperlink ref="F356" r:id="rId25"/>
-    <hyperlink ref="E356" r:id="rId26"/>
-    <hyperlink ref="F357" r:id="rId27"/>
-    <hyperlink ref="E357" r:id="rId28"/>
-    <hyperlink ref="F358" r:id="rId29"/>
-    <hyperlink ref="E358" r:id="rId30"/>
-    <hyperlink ref="F359" r:id="rId31"/>
-    <hyperlink ref="E359" r:id="rId32"/>
-    <hyperlink ref="F360" r:id="rId33"/>
-    <hyperlink ref="E360" r:id="rId34"/>
-    <hyperlink ref="F361" r:id="rId35"/>
-    <hyperlink ref="E361" r:id="rId36"/>
-    <hyperlink ref="F362" r:id="rId37"/>
-    <hyperlink ref="E362" r:id="rId38"/>
-    <hyperlink ref="F363" r:id="rId39"/>
-    <hyperlink ref="E363" r:id="rId40"/>
-    <hyperlink ref="F364" r:id="rId41"/>
-    <hyperlink ref="E364" r:id="rId42"/>
-    <hyperlink ref="F365" r:id="rId43"/>
-    <hyperlink ref="E365" r:id="rId44"/>
+    <hyperlink ref="F346" r:id="rId10" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="E346" r:id="rId11"/>
+    <hyperlink ref="F347" r:id="rId12" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="E347" r:id="rId13"/>
+    <hyperlink ref="F348" r:id="rId14" location="&amp;gid=1&amp;pid=1"/>
+    <hyperlink ref="E348" r:id="rId15"/>
+    <hyperlink ref="F349" r:id="rId16"/>
+    <hyperlink ref="E349" r:id="rId17"/>
+    <hyperlink ref="F350" r:id="rId18"/>
+    <hyperlink ref="E350" r:id="rId19"/>
+    <hyperlink ref="F351" display="https://www.mercadolibre.com.mx/epicentro-audishako-max-02-restaurador-de-bajos-para-auto-subwoofer-para-carro-pickups-y-suv-accesorios-para-auto-audio-diseno-en-relieve-3d-incluye-dash-remoto-control-de-bajos/p/MLM64640099?pdp_filters=item_id:MLM46970202"/>
+    <hyperlink ref="E351" r:id="rId20"/>
+    <hyperlink ref="F352" r:id="rId21"/>
+    <hyperlink ref="E352" r:id="rId22"/>
+    <hyperlink ref="F353" r:id="rId23"/>
+    <hyperlink ref="E353" r:id="rId24"/>
+    <hyperlink ref="F355" r:id="rId25"/>
+    <hyperlink ref="E355" r:id="rId26"/>
+    <hyperlink ref="F356" r:id="rId27"/>
+    <hyperlink ref="E356" r:id="rId28"/>
+    <hyperlink ref="F357" r:id="rId29"/>
+    <hyperlink ref="E357" r:id="rId30"/>
+    <hyperlink ref="F358" r:id="rId31"/>
+    <hyperlink ref="E358" r:id="rId32"/>
+    <hyperlink ref="F359" r:id="rId33"/>
+    <hyperlink ref="E359" r:id="rId34"/>
+    <hyperlink ref="F360" r:id="rId35"/>
+    <hyperlink ref="E360" r:id="rId36"/>
+    <hyperlink ref="F361" r:id="rId37"/>
+    <hyperlink ref="E361" r:id="rId38"/>
+    <hyperlink ref="F362" r:id="rId39"/>
+    <hyperlink ref="E362" r:id="rId40"/>
+    <hyperlink ref="F363" r:id="rId41"/>
+    <hyperlink ref="E363" r:id="rId42"/>
+    <hyperlink ref="F364" r:id="rId43"/>
+    <hyperlink ref="E364" r:id="rId44"/>
     <hyperlink ref="I72" display="https://http2.mlstatic.com/D_NQ_NP_2X_977864-MLA82522530268_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728802-MLA82808708997_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_714871-MLA82808836891_032025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I296" r:id="rId45"/>
     <hyperlink ref="J296" r:id="rId46"/>
@@ -15554,49 +15510,49 @@
     <hyperlink ref="J66" r:id="rId47"/>
     <hyperlink ref="I67" display="https://http2.mlstatic.com/D_NQ_NP_2X_754117-MLA87918629604_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_955266-MLA88256438081_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_924778-MLA88256272783_072025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I262" display="https://http2.mlstatic.com/D_NQ_NP_2X_651538-MLA109474609027_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_786870-MLA109384870397_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_877937-MLA109385877631_032026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I324" display="https://http2.mlstatic.com/D_NQ_NP_2X_659872-MLA110558100656_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_654212-MLA110558217136_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728798-MLA110558100602_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J364" r:id="rId48"/>
-    <hyperlink ref="I364" r:id="rId49"/>
-    <hyperlink ref="I326" display="https://http2.mlstatic.com/D_NQ_NP_2X_704682-MLA112632086794_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648062-MLA114215908179_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_721338-MLA112631444306_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I323" display="https://http2.mlstatic.com/D_NQ_NP_2X_659872-MLA110558100656_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_654212-MLA110558217136_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_728798-MLA110558100602_052026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J363" r:id="rId48"/>
+    <hyperlink ref="I363" r:id="rId49"/>
+    <hyperlink ref="I325" display="https://http2.mlstatic.com/D_NQ_NP_2X_704682-MLA112632086794_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648062-MLA114215908179_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_721338-MLA112631444306_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="E247" r:id="rId50"/>
     <hyperlink ref="I247" r:id="rId51"/>
     <hyperlink ref="J247" r:id="rId52"/>
     <hyperlink ref="I37" r:id="rId53"/>
-    <hyperlink ref="I362" display="https://http2.mlstatic.com/D_NQ_NP_2X_870766-MLA111944165952_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_835091-MLA112882459449_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I361" display="https://http2.mlstatic.com/D_NQ_NP_2X_870766-MLA111944165952_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_637261-MLA111944285568_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_835091-MLA112882459449_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="J61" r:id="rId54"/>
     <hyperlink ref="I61" display="https://http2.mlstatic.com/D_NQ_NP_2X_650019-MLA112598239078_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_694102-MLA111420836191_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_960139-MLA111232526403_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I356" r:id="rId55"/>
+    <hyperlink ref="I355" r:id="rId55"/>
     <hyperlink ref="I223" display="https://http2.mlstatic.com/D_NQ_NP_2X_761866-MLA76203783381_052024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_967910-MLA76082310461_042024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_699850-MLA76082339489_042024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="J33" r:id="rId56"/>
     <hyperlink ref="I33" display="https://http2.mlstatic.com/D_NQ_NP_2X_937988-MLA100214376229_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_839463-MLA100214244569_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_878239-MLA100214347283_122025-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I101" display="https://http2.mlstatic.com/D_NQ_NP_2X_853469-MLA73479850047_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_636371-MLA72966055893_112023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_647337-MLA74448293715_022024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I363" display="https://http2.mlstatic.com/D_NQ_NP_2X_838661-MLA114043475512_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_997422-MLA111845686244_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_946430-MLA112856485647_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I362" display="https://http2.mlstatic.com/D_NQ_NP_2X_838661-MLA114043475512_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_997422-MLA111845686244_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_946430-MLA112856485647_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I145" display="https://http2.mlstatic.com/D_NQ_NP_2X_700050-MLA90330537717_082025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_810830-MLA92985348779_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_611435-MLA103169335415_122025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="J335" r:id="rId57"/>
-    <hyperlink ref="I335" display="https://http2.mlstatic.com/D_NQ_NP_2X_972461-MLA108765590667_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_959062-MLA111287287492_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_702439-MLA108999676116_032026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J334" r:id="rId57"/>
+    <hyperlink ref="I334" display="https://http2.mlstatic.com/D_NQ_NP_2X_972461-MLA108765590667_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_959062-MLA111287287492_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_702439-MLA108999676116_032026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I241" display="https://http2.mlstatic.com/D_NQ_NP_2X_772336-MLA83215360667_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_641687-MLA82926894938_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_686941-MLA80851161221_112024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J354" r:id="rId58"/>
-    <hyperlink ref="I354" display="https://http2.mlstatic.com/D_NQ_NP_2X_654570-MLA114163554383_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_820669-MLA112176540320_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_827402-MLA113697495744_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J351" r:id="rId59"/>
-    <hyperlink ref="I351" display="https://http2.mlstatic.com/D_NQ_NP_2X_622982-MLA91998379772_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_918567-MLA93316673763_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_951409-MLA93316693351_092025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I352" r:id="rId60"/>
-    <hyperlink ref="J352" r:id="rId61"/>
+    <hyperlink ref="J353" r:id="rId58"/>
+    <hyperlink ref="I353" display="https://http2.mlstatic.com/D_NQ_NP_2X_654570-MLA114163554383_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_820669-MLA112176540320_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_827402-MLA113697495744_072026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="J350" r:id="rId59"/>
+    <hyperlink ref="I350" display="https://http2.mlstatic.com/D_NQ_NP_2X_622982-MLA91998379772_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_918567-MLA93316673763_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_951409-MLA93316693351_092025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="I351" r:id="rId60"/>
+    <hyperlink ref="J351" r:id="rId61"/>
     <hyperlink ref="J167" r:id="rId62"/>
     <hyperlink ref="I167" display="https://http2.mlstatic.com/D_NQ_NP_2X_630634-MLA83929492736_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_826427-MLA83875691856_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_778506-MLA83875632066_042025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I283" display="https://http2.mlstatic.com/D_NQ_NP_2X_601798-MLA74779553000_032024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_784677-MLA71729912500_092023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_982997-MLA73375012815_122023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="J57" r:id="rId63"/>
     <hyperlink ref="I57" r:id="rId64"/>
-    <hyperlink ref="I349" r:id="rId65"/>
-    <hyperlink ref="I350" r:id="rId66"/>
+    <hyperlink ref="I348" r:id="rId65"/>
+    <hyperlink ref="I349" r:id="rId66"/>
     <hyperlink ref="I131" r:id="rId67"/>
-    <hyperlink ref="I348" r:id="rId68"/>
-    <hyperlink ref="J348" r:id="rId69"/>
-    <hyperlink ref="I361" display="https://http2.mlstatic.com/D_NQ_NP_2X_730160-MLA112550162587_062026-F.webp;http://http2.mlstatic.com/D_NQ_NP_2X_748872-MLA113290799753_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_824232-MLA112954608093_062026-F.webp;https://http2.mlstatic.com/D_NQ"/>
+    <hyperlink ref="I347" r:id="rId68"/>
+    <hyperlink ref="J347" r:id="rId69"/>
+    <hyperlink ref="I360" display="https://http2.mlstatic.com/D_NQ_NP_2X_730160-MLA112550162587_062026-F.webp;http://http2.mlstatic.com/D_NQ_NP_2X_748872-MLA113290799753_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_824232-MLA112954608093_062026-F.webp;https://http2.mlstatic.com/D_NQ"/>
     <hyperlink ref="I107" r:id="rId70"/>
     <hyperlink ref="I3" display="https://http2.mlstatic.com/D_NQ_NP_2X_644970-MLA111138624893_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_618974-MLA113557256809_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_849248-MLA111414716285_052026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I12" r:id="rId71"/>
-    <hyperlink ref="I359" r:id="rId72"/>
-    <hyperlink ref="J359" r:id="rId73"/>
+    <hyperlink ref="I358" r:id="rId72"/>
+    <hyperlink ref="J358" r:id="rId73"/>
     <hyperlink ref="E144" r:id="rId74"/>
     <hyperlink ref="I144" r:id="rId75"/>
     <hyperlink ref="J178" r:id="rId76"/>
@@ -15610,14 +15566,14 @@
     <hyperlink ref="I74" r:id="rId84"/>
     <hyperlink ref="I264" r:id="rId85"/>
     <hyperlink ref="E248" r:id="rId86"/>
-    <hyperlink ref="J319" r:id="rId87"/>
-    <hyperlink ref="I319" r:id="rId88"/>
+    <hyperlink ref="J318" r:id="rId87"/>
+    <hyperlink ref="I318" r:id="rId88"/>
     <hyperlink ref="J55" r:id="rId89"/>
     <hyperlink ref="I55" r:id="rId90"/>
-    <hyperlink ref="I347" r:id="rId91"/>
-    <hyperlink ref="J357" r:id="rId92"/>
-    <hyperlink ref="I357" display="https://http2.mlstatic.com/D_NQ_NP_2X_967252-MLA112857017004_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_802434-MLA114058497103_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_904877-MLA112857136140_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I332" display="https://http2.mlstatic.com/D_NQ_NP_2X_871513-MLA105683275105_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_921467-MLA106225093215_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_768089-MLA111241397693_052026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I346" r:id="rId91"/>
+    <hyperlink ref="J356" r:id="rId92"/>
+    <hyperlink ref="I356" display="https://http2.mlstatic.com/D_NQ_NP_2X_967252-MLA112857017004_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_802434-MLA114058497103_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_904877-MLA112857136140_072026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I331" display="https://http2.mlstatic.com/D_NQ_NP_2X_871513-MLA105683275105_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_921467-MLA106225093215_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_768089-MLA111241397693_052026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I270" r:id="rId93"/>
     <hyperlink ref="J265" r:id="rId94"/>
     <hyperlink ref="I265" display="https://http2.mlstatic.com/D_NQ_NP_2X_723996-MLA101839595031_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_648298-MLA100279286785_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_899562-MLA105452243109_012026-F.webp;https://http2.mlstatic.com/D_N"/>
@@ -15625,11 +15581,11 @@
     <hyperlink ref="I106" display="https://http2.mlstatic.com/D_NQ_NP_2X_986480-MLA92403239851_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_992851-MLA91999385090_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_790783-MLA94732447073_102025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I183" display="https://http2.mlstatic.com/D_NQ_NP_2X_714527-MLA94159366454_102025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_847366-MLA97737335743_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_618907-MLA100261323194_122025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
     <hyperlink ref="I285" r:id="rId96"/>
-    <hyperlink ref="J336" r:id="rId97"/>
-    <hyperlink ref="I336" r:id="rId98"/>
+    <hyperlink ref="J335" r:id="rId97"/>
+    <hyperlink ref="I335" r:id="rId98"/>
     <hyperlink ref="J297" r:id="rId99"/>
     <hyperlink ref="I297" r:id="rId100"/>
-    <hyperlink ref="I325" display="https://http2.mlstatic.com/D_NQ_NP_2X_886751-MLA110760597980_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_722285-MLA111072136212_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_745568-MLA111456288976_052026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I324" display="https://http2.mlstatic.com/D_NQ_NP_2X_886751-MLA110760597980_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_722285-MLA111072136212_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_745568-MLA111456288976_052026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I148" r:id="rId101"/>
     <hyperlink ref="I27" r:id="rId102"/>
     <hyperlink ref="J136" r:id="rId103"/>
@@ -15646,9 +15602,9 @@
     <hyperlink ref="I194" r:id="rId111"/>
     <hyperlink ref="J268" r:id="rId112"/>
     <hyperlink ref="I268" r:id="rId113"/>
-    <hyperlink ref="I321" r:id="rId114"/>
-    <hyperlink ref="J365" r:id="rId115"/>
-    <hyperlink ref="I365" r:id="rId116"/>
+    <hyperlink ref="I320" r:id="rId114"/>
+    <hyperlink ref="J364" r:id="rId115"/>
+    <hyperlink ref="I364" r:id="rId116"/>
     <hyperlink ref="J54" r:id="rId117"/>
     <hyperlink ref="I54" r:id="rId118"/>
     <hyperlink ref="I220" display="https://http2.mlstatic.com/D_NQ_NP_2X_931197-MLA111097282025_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_647752-MLA86304062244_062025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_697099-MLA86808814199_062025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
@@ -15670,11 +15626,11 @@
     <hyperlink ref="I4" display="https://http2.mlstatic.com/D_NQ_NP_2X_652387-MLA81262109420_122024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_964100-MLA74205385415_012024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_663926-MLA71594815900_092023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="J53" r:id="rId127"/>
     <hyperlink ref="I53" display="https://http2.mlstatic.com/D_NQ_NP_2X_787566-MLA112208805453_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_610420-MLA108420590498_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_778316-MLA108420330866_032026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I327" display="https://http2.mlstatic.com/D_NQ_NP_2X_811172-MLA108871819192_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_673692-MLA109653928111_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_807085-MLA109742422391_032026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I326" display="https://http2.mlstatic.com/D_NQ_NP_2X_811172-MLA108871819192_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_673692-MLA109653928111_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_807085-MLA109742422391_032026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I208" display="https://http2.mlstatic.com/D_NQ_NP_2X_787733-MLA73258839528_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_702415-MLA111282425851_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_934591-MLA108763618671_032026-F.webp;https://http2.mlstatic.com/D_NQ"/>
     <hyperlink ref="I203" r:id="rId128"/>
-    <hyperlink ref="J328" r:id="rId129"/>
-    <hyperlink ref="I328" r:id="rId130"/>
+    <hyperlink ref="J327" r:id="rId129"/>
+    <hyperlink ref="I327" r:id="rId130"/>
     <hyperlink ref="I142" display="https://http2.mlstatic.com/D_NQ_NP_2X_951908-MLA106095526036_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_697058-MLA92029170496_092025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_770689-MLA112170606647_052026-F.webp;https://http2.mlstatic.com/D_NQ"/>
     <hyperlink ref="J142" r:id="rId131"/>
     <hyperlink ref="J87" r:id="rId132"/>
@@ -15689,108 +15645,107 @@
     <hyperlink ref="J165" r:id="rId140"/>
     <hyperlink ref="I165" display="https://http2.mlstatic.com/D_NQ_NP_2X_949414-MLA115597206229_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_781530-MLA115596590455_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_794977-MLA113865153424_072026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="I239" r:id="rId141"/>
-    <hyperlink ref="I331" r:id="rId142"/>
-    <hyperlink ref="J360" r:id="rId143"/>
-    <hyperlink ref="I360" r:id="rId144"/>
+    <hyperlink ref="I330" r:id="rId142"/>
+    <hyperlink ref="J359" r:id="rId143"/>
+    <hyperlink ref="I359" r:id="rId144"/>
     <hyperlink ref="I112" display="https://http2.mlstatic.com/D_NQ_NP_2X_602967-MLA106207657120_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_937184-MLA99857184303_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_615655-MLA93805615686_102025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
     <hyperlink ref="J112" r:id="rId145"/>
     <hyperlink ref="I271" display="https://http2.mlstatic.com/D_NQ_NP_2X_811367-MLA96964641173_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_724534-MLA95972455447_102025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_862711-MLA94582890276_102025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I186" r:id="rId146"/>
     <hyperlink ref="I111" display="https://http2.mlstatic.com/D_NQ_NP_2X_832809-MLA100859657141_122025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_651615-MLA104572148023_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_683702-MLA104248384382_012026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I318" r:id="rId147"/>
     <hyperlink ref="I294" display="https://http2.mlstatic.com/D_NQ_NP_2X_672294-MLA110281902509_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_995715-MLA110918042491_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_936537-MLA110364709430_052026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J294" r:id="rId148"/>
-    <hyperlink ref="J322" r:id="rId149"/>
-    <hyperlink ref="I322" display="https://http2.mlstatic.com/D_NQ_NP_2X_623123-MLA111040290746_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_934760-MLA111878498611_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_790070-MLA112661729675_062026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I317" r:id="rId150"/>
-    <hyperlink ref="I121" r:id="rId151"/>
-    <hyperlink ref="J56" r:id="rId152"/>
+    <hyperlink ref="J294" r:id="rId147"/>
+    <hyperlink ref="J321" r:id="rId148"/>
+    <hyperlink ref="I321" display="https://http2.mlstatic.com/D_NQ_NP_2X_623123-MLA111040290746_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_934760-MLA111878498611_052026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_790070-MLA112661729675_062026-F.webp;https://http2.mlstatic.com/D_N"/>
+    <hyperlink ref="I317" r:id="rId149"/>
+    <hyperlink ref="I121" r:id="rId150"/>
+    <hyperlink ref="J56" r:id="rId151"/>
     <hyperlink ref="I56" display="https://http2.mlstatic.com/D_NQ_NP_2X_707272-MLA81406001662_122024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_992452-MLA71699440818_092023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_616985-MLA84032409756_052025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J290" r:id="rId153"/>
+    <hyperlink ref="J290" r:id="rId152"/>
     <hyperlink ref="I290" display="https://http2.mlstatic.com/D_NQ_NP_2X_699847-MLA83204192108_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_847455-MLA79932861627_102024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_823994-MLA70105011582_062023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="J244" r:id="rId154"/>
+    <hyperlink ref="J244" r:id="rId153"/>
     <hyperlink ref="I244" display="https://http2.mlstatic.com/D_NQ_NP_2X_896395-MLA74651133358_022024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_757231-MLA73307952803_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_773664-MLA113844190574_072026-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="I266" r:id="rId155"/>
-    <hyperlink ref="J212" r:id="rId156"/>
+    <hyperlink ref="I266" r:id="rId154"/>
+    <hyperlink ref="J212" r:id="rId155"/>
     <hyperlink ref="I212" display="https://http2.mlstatic.com/D_NQ_NP_2X_857704-MLA105910693631_012026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_785878-MLA115684445439_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_732723-MLA114610870605_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="I123" r:id="rId157"/>
+    <hyperlink ref="I123" r:id="rId156"/>
     <hyperlink ref="I138" display="https://http2.mlstatic.com/D_NQ_NP_2X_731885-MLA81735782871_012025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_877502-MLA81736505623_012025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_739624-MLA81735782869_012025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
     <hyperlink ref="I150" display="https://http2.mlstatic.com/D_NQ_NP_2X_852777-MLA73231184100_122023-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_953229-MLA74068746840_012024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_727505-MLA74823139724_032024-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I162" r:id="rId158"/>
-    <hyperlink ref="J162" r:id="rId159"/>
-    <hyperlink ref="F110" r:id="rId160" location="reviews"/>
-    <hyperlink ref="I110" r:id="rId161"/>
-    <hyperlink ref="I320" r:id="rId162"/>
-    <hyperlink ref="I323" r:id="rId163"/>
+    <hyperlink ref="I162" r:id="rId157"/>
+    <hyperlink ref="J162" r:id="rId158"/>
+    <hyperlink ref="F110" r:id="rId159" location="reviews"/>
+    <hyperlink ref="I110" r:id="rId160"/>
+    <hyperlink ref="I319" r:id="rId161"/>
+    <hyperlink ref="I322" r:id="rId162"/>
     <hyperlink ref="I102" display="https://http2.mlstatic.com/D_NQ_NP_2X_701490-MLA108653774761_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_910611-MLA87584829978_072025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_761367-MLA87718920709_072025-F.webp;https://http2.mlstatic.com/D_NQ_"/>
-    <hyperlink ref="E229" r:id="rId164"/>
-    <hyperlink ref="I229" r:id="rId165"/>
-    <hyperlink ref="I275" r:id="rId166"/>
-    <hyperlink ref="F30" r:id="rId167"/>
-    <hyperlink ref="I329" display="https://http2.mlstatic.com/D_NQ_NP_2X_661292-MLA98293086467_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_907390-MLA106707175024_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_876338-MLA108047534008_032026-F.webp;https://http2.mlstatic.com/D_NQ"/>
-    <hyperlink ref="J329" r:id="rId168"/>
-    <hyperlink ref="J276" r:id="rId169"/>
+    <hyperlink ref="E229" r:id="rId163"/>
+    <hyperlink ref="I229" r:id="rId164"/>
+    <hyperlink ref="I275" r:id="rId165"/>
+    <hyperlink ref="F30" r:id="rId166"/>
+    <hyperlink ref="I328" display="https://http2.mlstatic.com/D_NQ_NP_2X_661292-MLA98293086467_112025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_907390-MLA106707175024_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_876338-MLA108047534008_032026-F.webp;https://http2.mlstatic.com/D_NQ"/>
+    <hyperlink ref="J328" r:id="rId167"/>
+    <hyperlink ref="J276" r:id="rId168"/>
     <hyperlink ref="I276" display="https://http2.mlstatic.com/D_NQ_NP_2X_609731-MLA83282009211_032025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_965155-MLA83841127402_042025-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_758965-MLA85304541601_052025-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
-    <hyperlink ref="I161" r:id="rId170"/>
-    <hyperlink ref="J161" r:id="rId171"/>
-    <hyperlink ref="I140" r:id="rId172"/>
-    <hyperlink ref="J141" r:id="rId173"/>
+    <hyperlink ref="I161" r:id="rId169"/>
+    <hyperlink ref="J161" r:id="rId170"/>
+    <hyperlink ref="I140" r:id="rId171"/>
+    <hyperlink ref="J141" r:id="rId172"/>
     <hyperlink ref="I141" display="https://http2.mlstatic.com/D_NQ_NP_2X_863418-MLA109994960812_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_927650-MLA105811665406_022026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_743624-MLA105810281830_022026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="J86" r:id="rId174"/>
+    <hyperlink ref="J86" r:id="rId173"/>
     <hyperlink ref="I86" display="https://http2.mlstatic.com/D_NQ_NP_2X_929447-MLA114868215933_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_688697-MLA113791320300_072026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_631693-MLA113790881904_072026-F.webp;https://http2.mlstatic.com/D_N"/>
-    <hyperlink ref="F86" r:id="rId175"/>
-    <hyperlink ref="J293" r:id="rId176"/>
-    <hyperlink ref="E2" r:id="rId177"/>
-    <hyperlink ref="F2" r:id="rId178"/>
-    <hyperlink ref="E366"/>
-    <hyperlink ref="F366" r:id="rId179" location="reviews"/>
-    <hyperlink ref="I366" r:id="rId180"/>
-    <hyperlink ref="E367" r:id="rId181"/>
-    <hyperlink ref="F367" r:id="rId182"/>
-    <hyperlink ref="E368" r:id="rId183"/>
-    <hyperlink ref="F368" r:id="rId184"/>
-    <hyperlink ref="I368" r:id="rId185"/>
-    <hyperlink ref="E369" r:id="rId186"/>
-    <hyperlink ref="I369" r:id="rId187"/>
-    <hyperlink ref="F369" r:id="rId188" location="reviews"/>
-    <hyperlink ref="E370" r:id="rId189"/>
+    <hyperlink ref="F86" r:id="rId174"/>
+    <hyperlink ref="J293" r:id="rId175"/>
+    <hyperlink ref="E2" r:id="rId176"/>
+    <hyperlink ref="F2" r:id="rId177"/>
+    <hyperlink ref="E365"/>
+    <hyperlink ref="F365" r:id="rId178" location="reviews"/>
+    <hyperlink ref="I365" r:id="rId179"/>
+    <hyperlink ref="E366" r:id="rId180"/>
+    <hyperlink ref="F366" r:id="rId181"/>
+    <hyperlink ref="E367" r:id="rId182"/>
+    <hyperlink ref="F367" r:id="rId183"/>
+    <hyperlink ref="I367" r:id="rId184"/>
+    <hyperlink ref="E368" r:id="rId185"/>
+    <hyperlink ref="I368" r:id="rId186"/>
+    <hyperlink ref="F368" r:id="rId187" location="reviews"/>
+    <hyperlink ref="E369" r:id="rId188"/>
+    <hyperlink ref="F369" r:id="rId189"/>
     <hyperlink ref="F370" r:id="rId190"/>
-    <hyperlink ref="F371" r:id="rId191"/>
-    <hyperlink ref="E371" r:id="rId192"/>
-    <hyperlink ref="I371" r:id="rId193"/>
-    <hyperlink ref="J371" r:id="rId194"/>
-    <hyperlink ref="F372" r:id="rId195"/>
-    <hyperlink ref="E372" r:id="rId196"/>
-    <hyperlink ref="I372" r:id="rId197"/>
-    <hyperlink ref="F373" r:id="rId198"/>
-    <hyperlink ref="E373" r:id="rId199"/>
-    <hyperlink ref="I373" r:id="rId200"/>
-    <hyperlink ref="J373" r:id="rId201"/>
-    <hyperlink ref="F374" r:id="rId202"/>
-    <hyperlink ref="E374" r:id="rId203"/>
-    <hyperlink ref="I374" r:id="rId204"/>
-    <hyperlink ref="F375" r:id="rId205"/>
-    <hyperlink ref="E375" r:id="rId206"/>
-    <hyperlink ref="F376" r:id="rId207"/>
-    <hyperlink ref="E376" r:id="rId208"/>
-    <hyperlink ref="F377" r:id="rId209"/>
-    <hyperlink ref="E377" r:id="rId210"/>
-    <hyperlink ref="F378" r:id="rId211"/>
-    <hyperlink ref="E378" r:id="rId212"/>
-    <hyperlink ref="F379" r:id="rId213"/>
-    <hyperlink ref="E379" r:id="rId214"/>
-    <hyperlink ref="I379" r:id="rId215"/>
-    <hyperlink ref="F380" r:id="rId216"/>
-    <hyperlink ref="E380" r:id="rId217"/>
-    <hyperlink ref="J380" r:id="rId218"/>
-    <hyperlink ref="I380" r:id="rId219"/>
-    <hyperlink ref="F381" r:id="rId220"/>
-    <hyperlink ref="E381" r:id="rId221"/>
+    <hyperlink ref="E370" r:id="rId191"/>
+    <hyperlink ref="I370" r:id="rId192"/>
+    <hyperlink ref="J370" r:id="rId193"/>
+    <hyperlink ref="F371" r:id="rId194"/>
+    <hyperlink ref="E371" r:id="rId195"/>
+    <hyperlink ref="I371" r:id="rId196"/>
+    <hyperlink ref="F372" r:id="rId197"/>
+    <hyperlink ref="E372" r:id="rId198"/>
+    <hyperlink ref="I372" r:id="rId199"/>
+    <hyperlink ref="J372" r:id="rId200"/>
+    <hyperlink ref="F373" r:id="rId201"/>
+    <hyperlink ref="E373" r:id="rId202"/>
+    <hyperlink ref="I373" r:id="rId203"/>
+    <hyperlink ref="F374" r:id="rId204"/>
+    <hyperlink ref="E374" r:id="rId205"/>
+    <hyperlink ref="F375" r:id="rId206"/>
+    <hyperlink ref="E375" r:id="rId207"/>
+    <hyperlink ref="F376" r:id="rId208"/>
+    <hyperlink ref="E376" r:id="rId209"/>
+    <hyperlink ref="F377" r:id="rId210"/>
+    <hyperlink ref="E377" r:id="rId211"/>
+    <hyperlink ref="F378" r:id="rId212"/>
+    <hyperlink ref="E378" r:id="rId213"/>
+    <hyperlink ref="I378" r:id="rId214"/>
+    <hyperlink ref="F379" r:id="rId215"/>
+    <hyperlink ref="E379" r:id="rId216"/>
+    <hyperlink ref="J379" r:id="rId217"/>
+    <hyperlink ref="I379" r:id="rId218"/>
+    <hyperlink ref="F380" r:id="rId219"/>
+    <hyperlink ref="E380" r:id="rId220"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId222"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId221"/>
   <tableParts count="1">
-    <tablePart r:id="rId223"/>
+    <tablePart r:id="rId222"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -15662,7 +15662,7 @@
     <hyperlink ref="J292" r:id="rId175"/>
     <hyperlink ref="E2" r:id="rId176"/>
     <hyperlink ref="F2" r:id="rId177"/>
-    <hyperlink ref="E364"/>
+    <hyperlink ref="E364" display="https://http2.mlstatic.com/D_NQ_NP_2X_809531-CBT116457079477_082026-F-andadera-para-bebes-5en1-con-altura-ajustable-musica-y-luces.webp;https://http2.mlstatic.com/D_NQ_NP_2X_922369-CBT114838652809_072026-F-andadera-para-bebes-5en1-con-altura-ajustable-mus"/>
     <hyperlink ref="F364" r:id="rId178" location="reviews"/>
     <hyperlink ref="I364" r:id="rId179"/>
     <hyperlink ref="E365" r:id="rId180"/>

--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="1660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="1662">
   <si>
     <t>Nombre</t>
   </si>
@@ -4980,9 +4980,6 @@
     <t>https://articulo.mercadolibre.com.mx/MLM-5261216182-funda-para-volante-fibra-de-carbono-gama-alta-forma-d-negro-_JM?quantity=1&amp;sid=purchases</t>
   </si>
   <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_647314-MLA112718039093_062026-F.webp;;https://http2.mlstatic.com/D_NQ_NP_2X_893993-MLA114600687014_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_679978-MLA113117754927_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_992169-MLA113116577615_062026-F.webp</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pistola para Pintar Inalámbrica </t>
   </si>
   <si>
@@ -4996,9 +4993,6 @@
   </si>
   <si>
     <t>2 PIEZA</t>
-  </si>
-  <si>
-    <t>https://http2.mlstatic.com/D_766480-MLM74144490966_012024-N.jpg;https://http2.mlstatic.com/D_969489-MLM74157311644_012024-N.jpg</t>
   </si>
   <si>
     <t>Tiras Trasera Luces Direccionales Secuencial Drl Auto</t>
@@ -5015,6 +5009,18 @@
   </si>
   <si>
     <t>Par de Faros led, Luces Decorativas Led Blancas Y Amarilla para Auto/Carro</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_647314-MLA112718039093_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_893993-MLA114600687014_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_679978-MLA113117754927_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_992169-MLA113116577615_062026-F.webp</t>
+  </si>
+  <si>
+    <t>http://panchochacharas.netlify.app/Imagenes/WhatsApp Image 2026-09-06 at 5.24.25 PM.jpeg</t>
+  </si>
+  <si>
+    <t>Soporte Celular Impermeable Fácil Uso Para Gorra, Bicicleta, Motocicleta</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_740027-CBT97828404288_112025-F.webp</t>
   </si>
 </sst>
 </file>
@@ -5176,8 +5182,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J377" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J377"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:J378" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J378">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="AUTOMOVIL"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState ref="A2:H342">
     <sortCondition ref="A1:A342"/>
   </sortState>
@@ -5482,7 +5494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J377"/>
+  <dimension ref="A1:J378"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70" style="1" customWidth="1"/>
@@ -5528,7 +5540,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="11.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="11.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1433</v>
       </c>
@@ -5557,7 +5569,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>982</v>
       </c>
@@ -5587,7 +5599,7 @@
       </c>
       <c r="J3" s="12"/>
     </row>
-    <row r="4" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>984</v>
       </c>
@@ -5616,7 +5628,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>533</v>
       </c>
@@ -5639,7 +5651,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>136</v>
       </c>
@@ -5668,7 +5680,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>357</v>
       </c>
@@ -5691,7 +5703,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>795</v>
       </c>
@@ -5717,7 +5729,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>90</v>
       </c>
@@ -5743,7 +5755,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="72.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>637</v>
       </c>
@@ -5769,7 +5781,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>794</v>
       </c>
@@ -5795,7 +5807,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>208</v>
       </c>
@@ -5824,7 +5836,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="72.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>687</v>
       </c>
@@ -5850,7 +5862,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>886</v>
       </c>
@@ -5873,7 +5885,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>576</v>
       </c>
@@ -5899,7 +5911,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>907</v>
       </c>
@@ -5922,7 +5934,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>95</v>
       </c>
@@ -5945,7 +5957,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>789</v>
       </c>
@@ -5968,7 +5980,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>700</v>
       </c>
@@ -5994,7 +6006,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>523</v>
       </c>
@@ -6017,7 +6029,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>726</v>
       </c>
@@ -6040,7 +6052,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>702</v>
       </c>
@@ -6066,7 +6078,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>478</v>
       </c>
@@ -6089,7 +6101,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>478</v>
       </c>
@@ -6112,7 +6124,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>478</v>
       </c>
@@ -6135,7 +6147,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>445</v>
       </c>
@@ -6164,7 +6176,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>97</v>
       </c>
@@ -6196,7 +6208,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>783</v>
       </c>
@@ -6222,7 +6234,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>772</v>
       </c>
@@ -6248,7 +6260,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>100</v>
       </c>
@@ -6271,7 +6283,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>773</v>
       </c>
@@ -6300,7 +6312,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>782</v>
       </c>
@@ -6326,7 +6338,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>774</v>
       </c>
@@ -6358,7 +6370,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>777</v>
       </c>
@@ -6384,7 +6396,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>775</v>
       </c>
@@ -6413,7 +6425,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>776</v>
       </c>
@@ -6436,7 +6448,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>971</v>
       </c>
@@ -6465,7 +6477,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>1187</v>
       </c>
@@ -6491,7 +6503,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>915</v>
       </c>
@@ -6514,7 +6526,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>543</v>
       </c>
@@ -6537,7 +6549,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>841</v>
       </c>
@@ -6566,7 +6578,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>68</v>
       </c>
@@ -6586,7 +6598,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>162</v>
       </c>
@@ -6609,7 +6621,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>140</v>
       </c>
@@ -6635,7 +6647,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>848</v>
       </c>
@@ -6658,7 +6670,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>853</v>
       </c>
@@ -6681,7 +6693,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>849</v>
       </c>
@@ -6704,7 +6716,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>849</v>
       </c>
@@ -6727,7 +6739,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>418</v>
       </c>
@@ -6759,7 +6771,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>173</v>
       </c>
@@ -6785,7 +6797,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>301</v>
       </c>
@@ -6811,7 +6823,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>164</v>
       </c>
@@ -6834,7 +6846,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>745</v>
       </c>
@@ -6866,7 +6878,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>744</v>
       </c>
@@ -6898,7 +6910,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>407</v>
       </c>
@@ -6930,7 +6942,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>191</v>
       </c>
@@ -6962,7 +6974,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>749</v>
       </c>
@@ -6994,7 +7006,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>893</v>
       </c>
@@ -7017,7 +7029,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>733</v>
       </c>
@@ -7040,7 +7052,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>973</v>
       </c>
@@ -7072,7 +7084,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>304</v>
       </c>
@@ -7098,7 +7110,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>889</v>
       </c>
@@ -7121,7 +7133,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>786</v>
       </c>
@@ -7147,7 +7159,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>861</v>
       </c>
@@ -7173,7 +7185,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>978</v>
       </c>
@@ -7205,7 +7217,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>105</v>
       </c>
@@ -7234,7 +7246,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>684</v>
       </c>
@@ -7257,7 +7269,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>620</v>
       </c>
@@ -7283,7 +7295,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>308</v>
       </c>
@@ -7312,7 +7324,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>361</v>
       </c>
@@ -7338,7 +7350,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>821</v>
       </c>
@@ -7370,7 +7382,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>337</v>
       </c>
@@ -7393,7 +7405,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>333</v>
       </c>
@@ -7422,7 +7434,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>364</v>
       </c>
@@ -7451,7 +7463,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>723</v>
       </c>
@@ -7477,7 +7489,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>711</v>
       </c>
@@ -7500,7 +7512,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>722</v>
       </c>
@@ -7523,7 +7535,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>947</v>
       </c>
@@ -7549,7 +7561,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>708</v>
       </c>
@@ -7575,7 +7587,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>520</v>
       </c>
@@ -7598,7 +7610,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>514</v>
       </c>
@@ -7621,7 +7633,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>953</v>
       </c>
@@ -7647,7 +7659,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>961</v>
       </c>
@@ -7673,7 +7685,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>282</v>
       </c>
@@ -7702,7 +7714,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>545</v>
       </c>
@@ -7731,7 +7743,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>1177</v>
       </c>
@@ -7763,7 +7775,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>825</v>
       </c>
@@ -7789,7 +7801,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:10" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>595</v>
       </c>
@@ -7815,7 +7827,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>626</v>
       </c>
@@ -7841,7 +7853,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>669</v>
       </c>
@@ -7864,7 +7876,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>201</v>
       </c>
@@ -7890,7 +7902,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10" ht="72.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>555</v>
       </c>
@@ -7916,7 +7928,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>592</v>
       </c>
@@ -7945,7 +7957,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>590</v>
       </c>
@@ -7977,7 +7989,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>590</v>
       </c>
@@ -8006,7 +8018,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>276</v>
       </c>
@@ -8032,7 +8044,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>178</v>
       </c>
@@ -8058,7 +8070,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>213</v>
       </c>
@@ -8087,7 +8099,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>154</v>
       </c>
@@ -8113,7 +8125,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>414</v>
       </c>
@@ -8142,7 +8154,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>837</v>
       </c>
@@ -8168,7 +8180,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>182</v>
       </c>
@@ -8194,7 +8206,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>918</v>
       </c>
@@ -8220,7 +8232,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>311</v>
       </c>
@@ -8249,7 +8261,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>919</v>
       </c>
@@ -8283,10 +8295,10 @@
     </row>
     <row r="106" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="C106" s="7">
         <v>199</v>
@@ -8295,7 +8307,7 @@
         <v>150</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>1654</v>
+        <v>1659</v>
       </c>
       <c r="G106" s="7" t="s">
         <v>863</v>
@@ -8304,10 +8316,10 @@
         <v>476</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>1658</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>458</v>
       </c>
@@ -8336,7 +8348,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>472</v>
       </c>
@@ -8365,7 +8377,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>368</v>
       </c>
@@ -8397,7 +8409,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>804</v>
       </c>
@@ -8426,7 +8438,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>800</v>
       </c>
@@ -8452,7 +8464,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>372</v>
       </c>
@@ -8484,7 +8496,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>1514</v>
       </c>
@@ -8516,7 +8528,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>644</v>
       </c>
@@ -8542,7 +8554,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>672</v>
       </c>
@@ -8568,7 +8580,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>630</v>
       </c>
@@ -8594,7 +8606,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>652</v>
       </c>
@@ -8617,7 +8629,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>8</v>
       </c>
@@ -8646,7 +8658,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>461</v>
       </c>
@@ -8669,7 +8681,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>639</v>
       </c>
@@ -8695,7 +8707,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>510</v>
       </c>
@@ -8718,7 +8730,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>214</v>
       </c>
@@ -8741,7 +8753,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>217</v>
       </c>
@@ -8767,7 +8779,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>220</v>
       </c>
@@ -8793,7 +8805,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>339</v>
       </c>
@@ -8819,7 +8831,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>343</v>
       </c>
@@ -8845,7 +8857,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>70</v>
       </c>
@@ -8871,12 +8883,12 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>1631</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="C128" s="7">
         <v>1356</v>
@@ -8900,7 +8912,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>904</v>
       </c>
@@ -8923,7 +8935,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>396</v>
       </c>
@@ -8949,7 +8961,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>73</v>
       </c>
@@ -8975,7 +8987,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>256</v>
       </c>
@@ -9004,7 +9016,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>1178</v>
       </c>
@@ -9036,7 +9048,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>76</v>
       </c>
@@ -9059,7 +9071,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>79</v>
       </c>
@@ -9088,7 +9100,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>81</v>
       </c>
@@ -9111,7 +9123,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>422</v>
       </c>
@@ -9137,7 +9149,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>436</v>
       </c>
@@ -9166,7 +9178,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>432</v>
       </c>
@@ -9195,7 +9207,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>223</v>
       </c>
@@ -9221,7 +9233,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>84</v>
       </c>
@@ -9337,7 +9349,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>145</v>
       </c>
@@ -9366,7 +9378,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>148</v>
       </c>
@@ -9392,7 +9404,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>151</v>
       </c>
@@ -9421,7 +9433,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>557</v>
       </c>
@@ -9447,7 +9459,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>1523</v>
       </c>
@@ -9473,7 +9485,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>586</v>
       </c>
@@ -9499,7 +9511,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>428</v>
       </c>
@@ -9551,7 +9563,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>551</v>
       </c>
@@ -9597,7 +9609,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>658</v>
       </c>
@@ -9623,7 +9635,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>656</v>
       </c>
@@ -9646,7 +9658,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>648</v>
       </c>
@@ -9669,7 +9681,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>259</v>
       </c>
@@ -9701,7 +9713,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>448</v>
       </c>
@@ -9730,7 +9742,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:10" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>272</v>
       </c>
@@ -9756,7 +9768,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:10" ht="15.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>109</v>
       </c>
@@ -9782,7 +9794,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>59</v>
       </c>
@@ -9840,12 +9852,12 @@
         <v>476</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>1632</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="C164" s="7">
         <v>1526</v>
@@ -9872,7 +9884,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>697</v>
       </c>
@@ -9898,7 +9910,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>712</v>
       </c>
@@ -9924,7 +9936,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>454</v>
       </c>
@@ -10002,7 +10014,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>583</v>
       </c>
@@ -10033,7 +10045,7 @@
         <v>49</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="C171" s="7">
         <v>250</v>
@@ -10054,7 +10066,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>502</v>
       </c>
@@ -10077,7 +10089,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>502</v>
       </c>
@@ -10100,7 +10112,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>910</v>
       </c>
@@ -10123,7 +10135,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>870</v>
       </c>
@@ -10146,7 +10158,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:10" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>680</v>
       </c>
@@ -10172,7 +10184,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>499</v>
       </c>
@@ -10195,7 +10207,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>376</v>
       </c>
@@ -10221,7 +10233,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>769</v>
       </c>
@@ -10250,7 +10262,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>166</v>
       </c>
@@ -10276,7 +10288,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>318</v>
       </c>
@@ -10302,7 +10314,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>858</v>
       </c>
@@ -10328,7 +10340,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:10" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>197</v>
       </c>
@@ -10357,7 +10369,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>522</v>
       </c>
@@ -10380,7 +10392,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>522</v>
       </c>
@@ -10403,7 +10415,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>874</v>
       </c>
@@ -10426,7 +10438,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>876</v>
       </c>
@@ -10449,7 +10461,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>539</v>
       </c>
@@ -10472,7 +10484,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>237</v>
       </c>
@@ -10501,7 +10513,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>924</v>
       </c>
@@ -10533,7 +10545,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>169</v>
       </c>
@@ -10559,7 +10571,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>17</v>
       </c>
@@ -10585,7 +10597,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>960</v>
       </c>
@@ -10611,7 +10623,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>561</v>
       </c>
@@ -10637,7 +10649,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>675</v>
       </c>
@@ -10663,7 +10675,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>565</v>
       </c>
@@ -10689,7 +10701,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>717</v>
       </c>
@@ -10712,7 +10724,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>21</v>
       </c>
@@ -10741,7 +10753,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>321</v>
       </c>
@@ -10767,7 +10779,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>548</v>
       </c>
@@ -10790,7 +10802,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>263</v>
       </c>
@@ -10819,7 +10831,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>379</v>
       </c>
@@ -10877,7 +10889,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>465</v>
       </c>
@@ -10903,7 +10915,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>13</v>
       </c>
@@ -10932,7 +10944,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>765</v>
       </c>
@@ -10955,7 +10967,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>469</v>
       </c>
@@ -10987,7 +10999,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>604</v>
       </c>
@@ -11013,7 +11025,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>604</v>
       </c>
@@ -11039,7 +11051,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>604</v>
       </c>
@@ -11065,7 +11077,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>614</v>
       </c>
@@ -11091,7 +11103,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>941</v>
       </c>
@@ -11117,7 +11129,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>813</v>
       </c>
@@ -11143,7 +11155,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>796</v>
       </c>
@@ -11198,7 +11210,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>348</v>
       </c>
@@ -11221,7 +11233,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>266</v>
       </c>
@@ -11247,7 +11259,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>279</v>
       </c>
@@ -11276,7 +11288,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>65</v>
       </c>
@@ -11305,7 +11317,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>615</v>
       </c>
@@ -11334,7 +11346,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>730</v>
       </c>
@@ -11360,7 +11372,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>1175</v>
       </c>
@@ -11386,7 +11398,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>942</v>
       </c>
@@ -11415,7 +11427,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>945</v>
       </c>
@@ -11444,7 +11456,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>616</v>
       </c>
@@ -11473,7 +11485,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>289</v>
       </c>
@@ -11499,7 +11511,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>324</v>
       </c>
@@ -11525,7 +11537,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>205</v>
       </c>
@@ -11557,7 +11569,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>240</v>
       </c>
@@ -11583,7 +11595,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="230" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>933</v>
       </c>
@@ -11609,7 +11621,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>400</v>
       </c>
@@ -11632,7 +11644,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="232" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>487</v>
       </c>
@@ -11655,7 +11667,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>600</v>
       </c>
@@ -11681,7 +11693,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="234" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>227</v>
       </c>
@@ -11707,7 +11719,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="235" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>116</v>
       </c>
@@ -11733,7 +11745,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>119</v>
       </c>
@@ -11762,7 +11774,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>122</v>
       </c>
@@ -11794,7 +11806,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>664</v>
       </c>
@@ -11820,7 +11832,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>352</v>
       </c>
@@ -11852,7 +11864,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="240" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>832</v>
       </c>
@@ -11875,7 +11887,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="241" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>962</v>
       </c>
@@ -11907,7 +11919,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>403</v>
       </c>
@@ -11939,7 +11951,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="243" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>244</v>
       </c>
@@ -11965,7 +11977,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="244" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>689</v>
       </c>
@@ -11988,7 +12000,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="245" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>269</v>
       </c>
@@ -12011,7 +12023,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="246" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>572</v>
       </c>
@@ -12034,7 +12046,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="247" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>693</v>
       </c>
@@ -12060,7 +12072,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="248" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>382</v>
       </c>
@@ -12089,7 +12101,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="249" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>934</v>
       </c>
@@ -12115,7 +12127,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="250" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>808</v>
       </c>
@@ -12141,7 +12153,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>247</v>
       </c>
@@ -12170,7 +12182,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>230</v>
       </c>
@@ -12202,7 +12214,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="253" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>327</v>
       </c>
@@ -12228,7 +12240,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>1149</v>
       </c>
@@ -12251,7 +12263,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="255" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>882</v>
       </c>
@@ -12274,7 +12286,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>234</v>
       </c>
@@ -12297,7 +12309,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>929</v>
       </c>
@@ -12329,7 +12341,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>385</v>
       </c>
@@ -12355,7 +12367,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>250</v>
       </c>
@@ -12384,7 +12396,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="260" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>253</v>
       </c>
@@ -12416,7 +12428,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>753</v>
       </c>
@@ -12445,7 +12457,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>411</v>
       </c>
@@ -12471,7 +12483,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>188</v>
       </c>
@@ -12503,7 +12515,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>194</v>
       </c>
@@ -12532,7 +12544,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>389</v>
       </c>
@@ -12558,7 +12570,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="266" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>938</v>
       </c>
@@ -12584,7 +12596,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>937</v>
       </c>
@@ -12613,7 +12625,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="268" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>936</v>
       </c>
@@ -12645,7 +12657,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="269" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>766</v>
       </c>
@@ -12674,7 +12686,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:10" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>935</v>
       </c>
@@ -12697,7 +12709,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="271" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>767</v>
       </c>
@@ -12725,10 +12737,10 @@
     </row>
     <row r="272" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="C272" s="7">
         <v>290</v>
@@ -12737,7 +12749,7 @@
         <v>150</v>
       </c>
       <c r="E272" s="13" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="G272" s="7" t="s">
         <v>863</v>
@@ -12752,7 +12764,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="273" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>330</v>
       </c>
@@ -12776,7 +12788,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="274" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>185</v>
       </c>
@@ -12805,7 +12817,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="275" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>293</v>
       </c>
@@ -12834,7 +12846,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="276" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>159</v>
       </c>
@@ -12860,7 +12872,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="277" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>393</v>
       </c>
@@ -12889,7 +12901,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="278" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>566</v>
       </c>
@@ -12915,7 +12927,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="279" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>899</v>
       </c>
@@ -12938,7 +12950,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="280" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>507</v>
       </c>
@@ -12961,7 +12973,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="281" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>530</v>
       </c>
@@ -12984,7 +12996,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="282" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>737</v>
       </c>
@@ -13016,7 +13028,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="283" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>1150</v>
       </c>
@@ -13042,7 +13054,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="284" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>985</v>
       </c>
@@ -13068,7 +13080,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="285" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>989</v>
       </c>
@@ -13100,7 +13112,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="286" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>993</v>
       </c>
@@ -13132,7 +13144,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="287" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>1070</v>
       </c>
@@ -13164,7 +13176,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="288" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>998</v>
       </c>
@@ -13196,7 +13208,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="289" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="1" t="s">
         <v>1002</v>
       </c>
@@ -13228,7 +13240,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="290" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>1006</v>
       </c>
@@ -13257,7 +13269,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="291" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>1008</v>
       </c>
@@ -13283,7 +13295,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="292" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>1014</v>
       </c>
@@ -13315,7 +13327,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="293" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
         <v>1018</v>
       </c>
@@ -13341,7 +13353,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="294" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
         <v>1026</v>
       </c>
@@ -13361,7 +13373,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="295" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>1028</v>
       </c>
@@ -13381,7 +13393,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="296" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="1" t="s">
         <v>1032</v>
       </c>
@@ -13404,7 +13416,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="297" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
         <v>1036</v>
       </c>
@@ -13424,7 +13436,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="298" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>1040</v>
       </c>
@@ -13444,7 +13456,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="299" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>1147</v>
       </c>
@@ -13470,7 +13482,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="300" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>1047</v>
       </c>
@@ -13496,7 +13508,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="301" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
         <v>1051</v>
       </c>
@@ -13516,7 +13528,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="302" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>1055</v>
       </c>
@@ -13542,7 +13554,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="303" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>1059</v>
       </c>
@@ -13565,7 +13577,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="304" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>1063</v>
       </c>
@@ -13585,7 +13597,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="305" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>1176</v>
       </c>
@@ -13608,7 +13620,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="306" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>1143</v>
       </c>
@@ -13637,7 +13649,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="307" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
         <v>1074</v>
       </c>
@@ -13669,7 +13681,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="308" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>1077</v>
       </c>
@@ -13701,7 +13713,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="309" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
         <v>1080</v>
       </c>
@@ -13730,7 +13742,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="310" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>1083</v>
       </c>
@@ -13762,7 +13774,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="311" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
         <v>1088</v>
       </c>
@@ -13791,7 +13803,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="312" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>1090</v>
       </c>
@@ -13820,7 +13832,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="313" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
         <v>1091</v>
       </c>
@@ -13843,7 +13855,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="314" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
         <v>1630</v>
       </c>
@@ -13872,7 +13884,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="315" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
         <v>1099</v>
       </c>
@@ -13904,7 +13916,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="316" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
         <v>1104</v>
       </c>
@@ -13936,7 +13948,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="317" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
         <v>1107</v>
       </c>
@@ -13965,7 +13977,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="318" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
         <v>1110</v>
       </c>
@@ -13988,7 +14000,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="319" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
         <v>1600</v>
       </c>
@@ -14017,7 +14029,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="320" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
         <v>1117</v>
       </c>
@@ -14043,7 +14055,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="321" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
         <v>1123</v>
       </c>
@@ -14072,7 +14084,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="322" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
         <v>1125</v>
       </c>
@@ -14101,7 +14113,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="323" spans="1:10" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:10" ht="72.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
         <v>1129</v>
       </c>
@@ -14130,7 +14142,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="324" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>1135</v>
       </c>
@@ -14159,7 +14171,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="325" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
         <v>1185</v>
       </c>
@@ -14185,7 +14197,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="326" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>1186</v>
       </c>
@@ -14211,7 +14223,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="327" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>1151</v>
       </c>
@@ -14240,7 +14252,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="328" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
         <v>1154</v>
       </c>
@@ -14266,7 +14278,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="329" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
         <v>1159</v>
       </c>
@@ -14292,7 +14304,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="330" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
         <v>1162</v>
       </c>
@@ -14318,7 +14330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="331" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
         <v>1167</v>
       </c>
@@ -14344,7 +14356,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="332" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
         <v>1172</v>
       </c>
@@ -14364,7 +14376,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="333" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
         <v>1180</v>
       </c>
@@ -14421,7 +14433,7 @@
     </row>
     <row r="335" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>1199</v>
@@ -14445,13 +14457,13 @@
         <v>476</v>
       </c>
       <c r="I335" s="12" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="J335" s="12" t="s">
         <v>1300</v>
       </c>
     </row>
-    <row r="336" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
         <v>1202</v>
       </c>
@@ -14483,7 +14495,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="337" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>1208</v>
       </c>
@@ -14515,7 +14527,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="338" spans="1:10" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:10" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>1629</v>
       </c>
@@ -14547,7 +14559,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="339" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:10" ht="87" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
         <v>1628</v>
       </c>
@@ -14579,7 +14591,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="340" spans="1:10" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:10" ht="72.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
         <v>1221</v>
       </c>
@@ -14611,7 +14623,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="341" spans="1:10" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:10" ht="72.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
         <v>1627</v>
       </c>
@@ -14643,7 +14655,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="342" spans="1:10" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:10" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
         <v>1223</v>
       </c>
@@ -14672,7 +14684,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="343" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
         <v>1227</v>
       </c>
@@ -14736,7 +14748,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="345" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>1235</v>
       </c>
@@ -14768,7 +14780,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="346" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
         <v>1239</v>
       </c>
@@ -14800,7 +14812,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="347" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>1244</v>
       </c>
@@ -14832,7 +14844,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="348" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>1248</v>
       </c>
@@ -14861,7 +14873,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="349" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
         <v>1253</v>
       </c>
@@ -14893,7 +14905,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="350" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
         <v>1254</v>
       </c>
@@ -14925,7 +14937,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="351" spans="1:10" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:10" ht="58" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
         <v>1438</v>
       </c>
@@ -14957,7 +14969,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="352" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
         <v>1443</v>
       </c>
@@ -14989,7 +15001,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="353" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>1447</v>
       </c>
@@ -15018,7 +15030,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="354" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>1452</v>
       </c>
@@ -15047,7 +15059,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="355" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>1458</v>
       </c>
@@ -15073,7 +15085,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="356" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:10" ht="29" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>1462</v>
       </c>
@@ -15105,7 +15117,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="357" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:10" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>1468</v>
       </c>
@@ -15134,7 +15146,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="358" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>1472</v>
       </c>
@@ -15166,7 +15178,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="359" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>1477</v>
       </c>
@@ -15198,7 +15210,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="360" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>1482</v>
       </c>
@@ -15224,7 +15236,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="361" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>1486</v>
       </c>
@@ -15250,7 +15262,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="362" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>1492</v>
       </c>
@@ -15276,7 +15288,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="363" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>1493</v>
       </c>
@@ -15302,7 +15314,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="364" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:10" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>1498</v>
       </c>
@@ -15331,7 +15343,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="365" spans="1:10" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:10" ht="23.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>1503</v>
       </c>
@@ -15363,7 +15375,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="366" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:10" ht="15.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>1508</v>
       </c>
@@ -15389,7 +15401,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>1590</v>
       </c>
@@ -15413,7 +15425,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>1601</v>
       </c>
@@ -15437,7 +15449,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>1601</v>
       </c>
@@ -15463,7 +15475,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>1605</v>
       </c>
@@ -15489,7 +15501,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>1616</v>
       </c>
@@ -15515,7 +15527,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
         <v>1610</v>
       </c>
@@ -15541,7 +15553,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>1617</v>
       </c>
@@ -15567,7 +15579,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>1622</v>
       </c>
@@ -15596,7 +15608,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
         <v>1633</v>
       </c>
@@ -15628,7 +15640,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>1639</v>
       </c>
@@ -15660,7 +15672,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>1645</v>
       </c>
@@ -15686,10 +15698,25 @@
         <v>476</v>
       </c>
       <c r="I377" s="12" t="s">
-        <v>1648</v>
+        <v>1658</v>
       </c>
       <c r="J377" s="12" t="s">
         <v>1644</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A378" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B378" s="1"/>
+      <c r="C378" s="7">
+        <v>190</v>
+      </c>
+      <c r="D378" s="7">
+        <v>150</v>
+      </c>
+      <c r="E378" s="12" t="s">
+        <v>1661</v>
       </c>
     </row>
   </sheetData>
@@ -16051,16 +16078,17 @@
     <hyperlink ref="J376" r:id="rId278"/>
     <hyperlink ref="E377" r:id="rId279"/>
     <hyperlink ref="F377" r:id="rId280"/>
-    <hyperlink ref="I377" display="https://http2.mlstatic.com/D_NQ_NP_2X_647314-MLA112718039093_062026-F.webp;;https://http2.mlstatic.com/D_NQ_NP_2X_893993-MLA114600687014_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_679978-MLA113117754927_062026-F.webp;https://http2.mlstatic.com/D_"/>
+    <hyperlink ref="I377"/>
     <hyperlink ref="J377" r:id="rId281"/>
     <hyperlink ref="E106" r:id="rId282"/>
     <hyperlink ref="E272" r:id="rId283"/>
     <hyperlink ref="I106" r:id="rId284"/>
+    <hyperlink ref="E378" r:id="rId285"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId285"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId286"/>
   <tableParts count="1">
-    <tablePart r:id="rId286"/>
+    <tablePart r:id="rId287"/>
   </tableParts>
 </worksheet>
 </file>
--- a/datos/productos.xlsx
+++ b/datos/productos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="1663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2491" uniqueCount="1664">
   <si>
     <t>Nombre</t>
   </si>
@@ -4798,10 +4798,6 @@
     <t xml:space="preserve"> 120cm</t>
   </si>
   <si>
-    <t xml:space="preserve">http://panchochacharas.netlify.app/Imagenes/WhatsApp Image 2026-09-06 at 5.24.25 PM.jpeg
-</t>
-  </si>
-  <si>
     <t>http://panchochacharas.netlify.app/Imagenes/WhatsApp Image 2026-09-06 at 5.06.22 PM.jpeg</t>
   </si>
   <si>
@@ -5022,6 +5018,12 @@
   </si>
   <si>
     <t>https://http2.mlstatic.com/D_NQ_NP_2X_964858-MLA75473255162_042024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_986703-MLA110352738797_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_817935-MLA75550976175_042024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_684136-MLA97690322107_112025-F.webp</t>
+  </si>
+  <si>
+    <t>https://http2.mlstatic.com/D_NQ_NP_2X_740090-MLM82436162399_022025-F.webp</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/tiras-trasera-luces-direccionales-secuencial-drl-auto-camion/up/MLMU3015676844#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=6&amp;type=product&amp;tracking_id=2f8ed447-5631-4a96-9e8e-134438f6950d&amp;wid=MLM2237121757&amp;sid=search&amp;gid=1&amp;pid=1</t>
   </si>
 </sst>
 </file>
@@ -5666,7 +5668,7 @@
         <v>131</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>378</v>
+        <v>28</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>462</v>
@@ -5879,10 +5881,10 @@
     </row>
     <row r="15" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>1610</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1611</v>
       </c>
       <c r="C15" s="7">
         <v>200</v>
@@ -8157,7 +8159,7 @@
     </row>
     <row r="101" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>1585</v>
@@ -8169,7 +8171,7 @@
         <v>150</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="G101" s="7" t="s">
         <v>842</v>
@@ -8178,7 +8180,7 @@
         <v>463</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -9577,7 +9579,7 @@
     </row>
     <row r="154" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>436</v>
@@ -11011,7 +11013,7 @@
         <v>778</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>841</v>
+        <v>28</v>
       </c>
       <c r="H208" s="7" t="s">
         <v>86</v>
@@ -11569,10 +11571,10 @@
         <v>400</v>
       </c>
       <c r="E229" s="12" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F229" s="12" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="G229" s="7" t="s">
         <v>841</v>
@@ -11581,10 +11583,10 @@
         <v>86</v>
       </c>
       <c r="I229" s="12" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="J229" s="12" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="230" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12414,7 +12416,7 @@
     </row>
     <row r="260" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>118</v>
@@ -12440,7 +12442,7 @@
     </row>
     <row r="261" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>121</v>
@@ -12469,7 +12471,7 @@
     </row>
     <row r="262" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>105</v>
@@ -12501,7 +12503,7 @@
     </row>
     <row r="263" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>121</v>
@@ -12530,7 +12532,7 @@
     </row>
     <row r="264" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>90</v>
@@ -12553,7 +12555,7 @@
     </row>
     <row r="265" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>753</v>
@@ -12591,7 +12593,10 @@
         <v>150</v>
       </c>
       <c r="E266" s="13" t="s">
-        <v>1588</v>
+        <v>1662</v>
+      </c>
+      <c r="F266" s="12" t="s">
+        <v>1663</v>
       </c>
       <c r="G266" s="7" t="s">
         <v>842</v>
@@ -13554,10 +13559,10 @@
     </row>
     <row r="303" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="C303" s="7">
         <v>299</v>
@@ -13800,6 +13805,9 @@
       <c r="F311" s="7" t="s">
         <v>1076</v>
       </c>
+      <c r="G311" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="H311" s="7" t="s">
         <v>58</v>
       </c>
@@ -14433,7 +14441,7 @@
         <v>1181</v>
       </c>
       <c r="G333" s="7" t="s">
-        <v>798</v>
+        <v>846</v>
       </c>
       <c r="H333" s="7" t="s">
         <v>12</v>
@@ -14700,7 +14708,7 @@
     </row>
     <row r="342" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>1386</v>
@@ -14776,7 +14784,7 @@
         <v>1398</v>
       </c>
       <c r="G344" s="7" t="s">
-        <v>545</v>
+        <v>846</v>
       </c>
       <c r="H344" s="7" t="s">
         <v>12</v>
@@ -14953,7 +14961,7 @@
         <v>1424</v>
       </c>
       <c r="G350" s="7" t="s">
-        <v>545</v>
+        <v>846</v>
       </c>
       <c r="H350" s="7" t="s">
         <v>12</v>
@@ -14979,7 +14987,7 @@
         <v>1428</v>
       </c>
       <c r="G351" s="7" t="s">
-        <v>545</v>
+        <v>846</v>
       </c>
       <c r="H351" s="7" t="s">
         <v>12</v>
@@ -15369,7 +15377,7 @@
         <v>463</v>
       </c>
       <c r="I365" s="12" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="J365" s="12" t="s">
         <v>1577</v>
@@ -15377,7 +15385,7 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B366" s="1"/>
       <c r="C366" s="7">
@@ -15387,15 +15395,18 @@
         <v>150</v>
       </c>
       <c r="E366" s="12" t="s">
-        <v>1594</v>
+        <v>1593</v>
+      </c>
+      <c r="G366" s="7" t="s">
+        <v>842</v>
       </c>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="C367" s="7">
         <v>250</v>
@@ -15404,10 +15415,10 @@
         <v>200</v>
       </c>
       <c r="E367" s="12" t="s">
+        <v>1606</v>
+      </c>
+      <c r="F367" s="12" t="s">
         <v>1607</v>
-      </c>
-      <c r="F367" s="12" t="s">
-        <v>1608</v>
       </c>
       <c r="G367" s="7" t="s">
         <v>841</v>
@@ -15416,12 +15427,12 @@
         <v>86</v>
       </c>
       <c r="I367" s="12" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>18</v>
@@ -15433,10 +15444,10 @@
         <v>500</v>
       </c>
       <c r="E368" s="12" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="F368" s="12" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="G368" s="7" t="s">
         <v>841</v>
@@ -15445,18 +15456,18 @@
         <v>86</v>
       </c>
       <c r="I368" s="12" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="J368" s="12" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="369" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B369" s="1" t="s">
         <v>1621</v>
-      </c>
-      <c r="B369" s="1" t="s">
-        <v>1622</v>
       </c>
       <c r="C369" s="7">
         <v>689</v>
@@ -15465,10 +15476,10 @@
         <v>250</v>
       </c>
       <c r="E369" s="12" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F369" s="12" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="G369" s="7" t="s">
         <v>812</v>
@@ -15479,10 +15490,10 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B370" s="1" t="s">
         <v>1625</v>
-      </c>
-      <c r="B370" s="1" t="s">
-        <v>1626</v>
       </c>
       <c r="C370" s="7">
         <v>150</v>
@@ -15491,10 +15502,10 @@
         <v>100</v>
       </c>
       <c r="E370" s="12" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="F370" s="12" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="G370" s="7" t="s">
         <v>812</v>
@@ -15503,18 +15514,18 @@
         <v>462</v>
       </c>
       <c r="I370" s="12" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="J370" s="12" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C371" s="7">
         <v>189</v>
@@ -15523,10 +15534,10 @@
         <v>150</v>
       </c>
       <c r="E371" s="12" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="F371" s="12" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="G371" s="7" t="s">
         <v>812</v>
@@ -15535,15 +15546,15 @@
         <v>462</v>
       </c>
       <c r="I371" s="12" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="J371" s="12" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>18</v>
@@ -15555,10 +15566,10 @@
         <v>200</v>
       </c>
       <c r="E372" s="12" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F372" s="12" t="s">
         <v>1638</v>
-      </c>
-      <c r="F372" s="12" t="s">
-        <v>1639</v>
       </c>
       <c r="G372" s="7" t="s">
         <v>812</v>
@@ -15569,10 +15580,10 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="C373" s="7">
         <v>200</v>
@@ -15581,10 +15592,10 @@
         <v>150</v>
       </c>
       <c r="E373" s="12" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="F373" s="7" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="G373" s="7" t="s">
         <v>841</v>
@@ -15595,10 +15606,10 @@
     </row>
     <row r="374" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="C374" s="7">
         <v>200</v>
@@ -15607,10 +15618,10 @@
         <v>150</v>
       </c>
       <c r="E374" s="12" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="F374" s="7" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="G374" s="7" t="s">
         <v>841</v>
@@ -15621,10 +15632,10 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B375" s="1" t="s">
         <v>1647</v>
-      </c>
-      <c r="B375" s="1" t="s">
-        <v>1648</v>
       </c>
       <c r="C375" s="7">
         <v>480</v>
@@ -15633,10 +15644,10 @@
         <v>350</v>
       </c>
       <c r="E375" s="12" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="F375" s="7" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="G375" s="7" t="s">
         <v>252</v>
@@ -15645,15 +15656,15 @@
         <v>462</v>
       </c>
       <c r="I375" s="12" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B376" s="1" t="s">
         <v>1652</v>
-      </c>
-      <c r="B376" s="1" t="s">
-        <v>1653</v>
       </c>
       <c r="C376" s="7">
         <v>189</v>
@@ -15662,10 +15673,10 @@
         <v>100</v>
       </c>
       <c r="E376" s="12" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F376" s="12" t="s">
         <v>1654</v>
-      </c>
-      <c r="F376" s="12" t="s">
-        <v>1655</v>
       </c>
       <c r="G376" s="7" t="s">
         <v>28</v>
@@ -15674,15 +15685,15 @@
         <v>86</v>
       </c>
       <c r="I376" s="12" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B377" s="1" t="s">
         <v>1657</v>
-      </c>
-      <c r="B377" s="1" t="s">
-        <v>1658</v>
       </c>
       <c r="C377" s="7">
         <v>250</v>
@@ -15691,10 +15702,10 @@
         <v>200</v>
       </c>
       <c r="E377" s="12" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="F377" s="12" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="G377" s="7" t="s">
         <v>28</v>
@@ -15703,10 +15714,10 @@
         <v>462</v>
       </c>
       <c r="I377" s="12" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="J377" s="12" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
   </sheetData>
@@ -16050,7 +16061,7 @@
     <hyperlink ref="J364" r:id="rId264"/>
     <hyperlink ref="E365" r:id="rId265"/>
     <hyperlink ref="F365" r:id="rId266"/>
-    <hyperlink ref="I365"/>
+    <hyperlink ref="I365" display="https://http2.mlstatic.com/D_NQ_NP_2X_647314-MLA112718039093_062026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_893993-MLA114600687014_082026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_679978-MLA113117754927_062026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="J365" r:id="rId267"/>
     <hyperlink ref="E101" r:id="rId268"/>
     <hyperlink ref="E266" r:id="rId269"/>
@@ -16059,8 +16070,8 @@
     <hyperlink ref="E229" r:id="rId272"/>
     <hyperlink ref="F229" r:id="rId273" location="reviews"/>
     <hyperlink ref="J229" r:id="rId274"/>
-    <hyperlink ref="I229"/>
-    <hyperlink ref="I367"/>
+    <hyperlink ref="I229" display="https://http2.mlstatic.com/D_NQ_NP_2X_925581-MLA77513358615_072024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_781129-MLA74361187982_022024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_910700-MLA70226716177_062023-F.webp;https://http2.mlstatic.com/D_NQ_N"/>
+    <hyperlink ref="I367" display="https://http2.mlstatic.com/D_NQ_NP_2X_641393-MLA109194525072_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_961496-MLA108916752550_032026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_942894-MLA109129688546_042026-F.webp;https://http2.mlstatic.com/D_N"/>
     <hyperlink ref="E367" r:id="rId275"/>
     <hyperlink ref="F367" r:id="rId276" location="reviews"/>
     <hyperlink ref="F362" display="https://www.mercadolibre.com.mx/vasos-magicos-cambian-de-color-con-tapa-y-popote-710ml-20pzs/p/MLM49087857#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=29&amp;type=product&amp;tracking_id=7a7a4321-127a-4df5-"/>
@@ -16069,16 +16080,16 @@
     <hyperlink ref="J368" r:id="rId279"/>
     <hyperlink ref="I368" r:id="rId280"/>
     <hyperlink ref="E369" r:id="rId281"/>
-    <hyperlink ref="F370"/>
+    <hyperlink ref="F370" display="https://www.mercadolibre.com.mx/bloques-apilables-de-equilibrio-16-piezas/p/MLM2051152595#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=3&amp;type=product&amp;tracking_id=cb5890b6-f012-4a54-86f5-e2f58af1075f&amp;"/>
     <hyperlink ref="E370" r:id="rId282"/>
     <hyperlink ref="J370" r:id="rId283"/>
     <hyperlink ref="I370" r:id="rId284"/>
-    <hyperlink ref="F371"/>
+    <hyperlink ref="F371" display="https://www.mercadolibre.com.mx/virus-espanol-juego-de-cartas-2-a-6-jugadores-mesa-set/p/MLM2060333676?pdp_filters=shipping%3Afulfillment#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=17&amp;type=product&amp;"/>
     <hyperlink ref="E371" r:id="rId285"/>
     <hyperlink ref="J371" r:id="rId286"/>
     <hyperlink ref="I371" r:id="rId287"/>
     <hyperlink ref="E372" r:id="rId288"/>
-    <hyperlink ref="F372"/>
+    <hyperlink ref="F372" display="https://www.mercadolibre.com.mx/alcancia-de-dibujos-animados-con-moneda-electronica-red/p/MLM2101052066#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=3&amp;type=product&amp;tracking_id=9098a3f3-8c68-462b-8d69"/>
     <hyperlink ref="E373" r:id="rId289"/>
     <hyperlink ref="E374" r:id="rId290"/>
     <hyperlink ref="I375" r:id="rId291"/>
@@ -16086,10 +16097,11 @@
     <hyperlink ref="E376" r:id="rId293"/>
     <hyperlink ref="F376" r:id="rId294"/>
     <hyperlink ref="I376" r:id="rId295"/>
-    <hyperlink ref="F377"/>
+    <hyperlink ref="F377" display="https://www.mercadolibre.com.mx/pack-de-40-bolsas-transparentes-de-pvc-con-asa-para-de-20x20x8-cm/p/MLM75645634#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=6&amp;type=product&amp;tracking_id=9dc26f76-a55a-4"/>
     <hyperlink ref="E377" r:id="rId296"/>
     <hyperlink ref="J377" r:id="rId297"/>
-    <hyperlink ref="I377"/>
+    <hyperlink ref="I377" display="https://http2.mlstatic.com/D_NQ_NP_2X_964858-MLA75473255162_042024-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_986703-MLA110352738797_042026-F.webp;https://http2.mlstatic.com/D_NQ_NP_2X_817935-MLA75550976175_042024-F.webp;https://http2.mlstatic.com/D_NQ_"/>
+    <hyperlink ref="F266"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId298"/>
